--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0205h\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0205h\Desktop\github\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56AD5349-1D14-4901-8A9B-94282FF142AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FB7AF4-1345-4003-9BFB-024FDEE60735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="86">
   <si>
     <t>概要</t>
     <rPh sb="0" eb="2">
@@ -466,6 +466,48 @@
     <t>素材集め</t>
     <rPh sb="0" eb="3">
       <t>ソザイアツ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>大崎</t>
+    <rPh sb="0" eb="2">
+      <t>オオサキ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>上永</t>
+    <rPh sb="0" eb="2">
+      <t>カミナガ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>佐々木</t>
+    <rPh sb="0" eb="3">
+      <t>ササキ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>川浪</t>
+    <rPh sb="0" eb="2">
+      <t>カワナミ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>誰でも</t>
+    <rPh sb="0" eb="1">
+      <t>ダレ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>誰か～</t>
+    <rPh sb="0" eb="1">
+      <t>ダレ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -540,7 +582,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -601,6 +643,42 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="47">
     <border>
@@ -1169,7 +1247,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1189,9 +1267,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1417,6 +1492,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1768,7 +1861,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="I1" s="47"/>
+      <c r="I1" s="46"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
@@ -1792,12 +1885,15 @@
       <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="46"/>
-      <c r="J2" s="15"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="14"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A3" s="95" t="s">
+        <v>80</v>
+      </c>
       <c r="B3" s="10" t="s">
         <v>16</v>
       </c>
@@ -1815,8 +1911,8 @@
       <c r="H3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I3" s="44"/>
-      <c r="J3" s="16" t="s">
+      <c r="I3" s="43"/>
+      <c r="J3" s="15" t="s">
         <v>9</v>
       </c>
       <c r="K3" s="3">
@@ -1841,8 +1937,8 @@
       <c r="H4" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I4" s="44"/>
-      <c r="J4" s="17" t="s">
+      <c r="I4" s="43"/>
+      <c r="J4" s="16" t="s">
         <v>11</v>
       </c>
       <c r="K4" s="5">
@@ -1852,7 +1948,6 @@
       <c r="L4" s="3"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A5" s="12"/>
       <c r="B5" s="9"/>
       <c r="C5" s="8" t="s">
         <v>23</v>
@@ -1868,8 +1963,8 @@
       <c r="H5" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I5" s="44"/>
-      <c r="J5" s="18" t="s">
+      <c r="I5" s="43"/>
+      <c r="J5" s="17" t="s">
         <v>12</v>
       </c>
       <c r="K5" s="5">
@@ -1879,9 +1974,8 @@
       <c r="L5" s="3"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="27" t="s">
+      <c r="B6" s="12"/>
+      <c r="C6" s="26" t="s">
         <v>24</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -1895,8 +1989,8 @@
       <c r="H6" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="44"/>
-      <c r="J6" s="19" t="s">
+      <c r="I6" s="43"/>
+      <c r="J6" s="18" t="s">
         <v>13</v>
       </c>
       <c r="K6" s="5">
@@ -1906,7 +2000,9 @@
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A7" s="12"/>
+      <c r="A7" s="95" t="s">
+        <v>80</v>
+      </c>
       <c r="B7" s="9" t="s">
         <v>32</v>
       </c>
@@ -1924,8 +2020,8 @@
       <c r="H7" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I7" s="44"/>
-      <c r="J7" s="20" t="s">
+      <c r="I7" s="43"/>
+      <c r="J7" s="19" t="s">
         <v>14</v>
       </c>
       <c r="K7" s="5">
@@ -1953,8 +2049,8 @@
       <c r="H8" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="44"/>
-      <c r="J8" s="21" t="s">
+      <c r="I8" s="43"/>
+      <c r="J8" s="20" t="s">
         <v>15</v>
       </c>
       <c r="K8" s="5">
@@ -1979,11 +2075,11 @@
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
-      <c r="H9" s="48" t="s">
-        <v>63</v>
-      </c>
-      <c r="I9" s="49"/>
-      <c r="J9" s="16" t="s">
+      <c r="H9" s="47" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" s="48"/>
+      <c r="J9" s="15" t="s">
         <v>18</v>
       </c>
       <c r="K9" s="3">
@@ -2008,8 +2104,8 @@
       <c r="H10" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I10" s="50"/>
-      <c r="J10" s="15"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="14"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
     </row>
@@ -2029,8 +2125,8 @@
       <c r="H11" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I11" s="44"/>
-      <c r="J11" s="22" t="s">
+      <c r="I11" s="43"/>
+      <c r="J11" s="21" t="s">
         <v>19</v>
       </c>
       <c r="K11" s="3">
@@ -2040,8 +2136,8 @@
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B12" s="13"/>
-      <c r="C12" s="27" t="s">
+      <c r="B12" s="12"/>
+      <c r="C12" s="26" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="4" t="s">
@@ -2055,8 +2151,8 @@
       <c r="H12" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I12" s="45"/>
-      <c r="J12" s="23" t="s">
+      <c r="I12" s="44"/>
+      <c r="J12" s="22" t="s">
         <v>20</v>
       </c>
       <c r="K12" s="3">
@@ -2066,7 +2162,10 @@
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B13" s="24" t="s">
+      <c r="A13" s="95" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="23" t="s">
         <v>33</v>
       </c>
       <c r="C13" s="8" t="s">
@@ -2085,7 +2184,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B14" s="25"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="8" t="s">
         <v>35</v>
       </c>
@@ -2102,8 +2201,8 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B15" s="26"/>
-      <c r="C15" s="27" t="s">
+      <c r="B15" s="25"/>
+      <c r="C15" s="26" t="s">
         <v>36</v>
       </c>
       <c r="D15" s="4" t="s">
@@ -2119,10 +2218,13 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B16" s="28" t="s">
+      <c r="A16" s="95" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" s="33" t="s">
         <v>38</v>
       </c>
       <c r="D16" s="4" t="s">
@@ -2131,15 +2233,15 @@
       <c r="E16" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
       <c r="H16" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B17" s="31"/>
-      <c r="C17" s="35" t="s">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B17" s="30"/>
+      <c r="C17" s="34" t="s">
         <v>39</v>
       </c>
       <c r="D17" s="4" t="s">
@@ -2148,16 +2250,15 @@
       <c r="E17" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="40"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
       <c r="H17" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I17" s="11"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B18" s="31"/>
-      <c r="C18" s="35" t="s">
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B18" s="30"/>
+      <c r="C18" s="34" t="s">
         <v>40</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -2166,15 +2267,15 @@
       <c r="E18" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
       <c r="H18" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B19" s="32"/>
-      <c r="C19" s="27" t="s">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B19" s="31"/>
+      <c r="C19" s="26" t="s">
         <v>32</v>
       </c>
       <c r="D19" s="4" t="s">
@@ -2183,17 +2284,20 @@
       <c r="E19" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
       <c r="H19" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B20" s="28" t="s">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A20" s="95" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" s="33" t="s">
         <v>38</v>
       </c>
       <c r="D20" s="4" t="s">
@@ -2202,15 +2306,15 @@
       <c r="E20" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
       <c r="H20" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B21" s="31"/>
-      <c r="C21" s="35" t="s">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B21" s="30"/>
+      <c r="C21" s="34" t="s">
         <v>39</v>
       </c>
       <c r="D21" s="4" t="s">
@@ -2219,15 +2323,15 @@
       <c r="E21" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
       <c r="H21" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B22" s="32"/>
-      <c r="C22" s="27" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B22" s="31"/>
+      <c r="C22" s="26" t="s">
         <v>40</v>
       </c>
       <c r="D22" s="4" t="s">
@@ -2236,17 +2340,20 @@
       <c r="E22" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
       <c r="H22" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B23" s="28" t="s">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A23" s="96" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" s="33" t="s">
         <v>44</v>
       </c>
       <c r="D23" s="4" t="s">
@@ -2255,15 +2362,15 @@
       <c r="E23" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="36"/>
-      <c r="G23" s="30"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="29"/>
       <c r="H23" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B24" s="31"/>
-      <c r="C24" s="35" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B24" s="30"/>
+      <c r="C24" s="34" t="s">
         <v>45</v>
       </c>
       <c r="D24" s="4" t="s">
@@ -2272,15 +2379,15 @@
       <c r="E24" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="40"/>
-      <c r="G24" s="43"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="42"/>
       <c r="H24" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B25" s="31"/>
-      <c r="C25" s="35" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B25" s="30"/>
+      <c r="C25" s="34" t="s">
         <v>46</v>
       </c>
       <c r="D25" s="4" t="s">
@@ -2289,15 +2396,15 @@
       <c r="E25" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="37"/>
-      <c r="G25" s="12"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="11"/>
       <c r="H25" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B26" s="31"/>
-      <c r="C26" s="35" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B26" s="30"/>
+      <c r="C26" s="34" t="s">
         <v>28</v>
       </c>
       <c r="D26" s="4" t="s">
@@ -2306,15 +2413,15 @@
       <c r="E26" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="40"/>
-      <c r="G26" s="43"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="42"/>
       <c r="H26" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B27" s="31"/>
-      <c r="C27" s="35" t="s">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B27" s="30"/>
+      <c r="C27" s="34" t="s">
         <v>47</v>
       </c>
       <c r="D27" s="4" t="s">
@@ -2323,15 +2430,15 @@
       <c r="E27" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="40"/>
-      <c r="G27" s="43"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="42"/>
       <c r="H27" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B28" s="32"/>
-      <c r="C28" s="27" t="s">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B28" s="31"/>
+      <c r="C28" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D28" s="4" t="s">
@@ -2340,17 +2447,20 @@
       <c r="E28" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F28" s="38"/>
-      <c r="G28" s="33"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="32"/>
       <c r="H28" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B29" s="28" t="s">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A29" s="96" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" s="33" t="s">
         <v>30</v>
       </c>
       <c r="D29" s="4" t="s">
@@ -2359,15 +2469,15 @@
       <c r="E29" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="30"/>
-      <c r="G29" s="36"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B30" s="31"/>
-      <c r="C30" s="35" t="s">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B30" s="30"/>
+      <c r="C30" s="34" t="s">
         <v>50</v>
       </c>
       <c r="D30" s="4" t="s">
@@ -2376,15 +2486,15 @@
       <c r="E30" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
       <c r="H30" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B31" s="31"/>
-      <c r="C31" s="35" t="s">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B31" s="30"/>
+      <c r="C31" s="34" t="s">
         <v>51</v>
       </c>
       <c r="D31" s="4" t="s">
@@ -2393,15 +2503,15 @@
       <c r="E31" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
       <c r="H31" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B32" s="32"/>
-      <c r="C32" s="27" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B32" s="31"/>
+      <c r="C32" s="26" t="s">
         <v>52</v>
       </c>
       <c r="D32" s="4" t="s">
@@ -2410,17 +2520,20 @@
       <c r="E32" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="33"/>
-      <c r="G32" s="38"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="37"/>
       <c r="H32" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B33" s="28" t="s">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A33" s="96" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" s="33" t="s">
         <v>54</v>
       </c>
       <c r="D33" s="4" t="s">
@@ -2429,15 +2542,15 @@
       <c r="E33" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B34" s="31"/>
-      <c r="C34" s="35" t="s">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B34" s="30"/>
+      <c r="C34" s="34" t="s">
         <v>38</v>
       </c>
       <c r="D34" s="4" t="s">
@@ -2446,15 +2559,15 @@
       <c r="E34" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
       <c r="H34" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B35" s="31"/>
-      <c r="C35" s="35" t="s">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B35" s="30"/>
+      <c r="C35" s="34" t="s">
         <v>39</v>
       </c>
       <c r="D35" s="4" t="s">
@@ -2463,15 +2576,15 @@
       <c r="E35" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F35" s="40"/>
-      <c r="G35" s="40"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
       <c r="H35" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B36" s="32"/>
-      <c r="C36" s="27" t="s">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B36" s="31"/>
+      <c r="C36" s="26" t="s">
         <v>40</v>
       </c>
       <c r="D36" s="4" t="s">
@@ -2480,17 +2593,20 @@
       <c r="E36" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
       <c r="H36" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B37" s="28" t="s">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A37" s="96" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C37" s="34" t="s">
+      <c r="C37" s="33" t="s">
         <v>38</v>
       </c>
       <c r="D37" s="4" t="s">
@@ -2499,15 +2615,15 @@
       <c r="E37" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F37" s="29"/>
-      <c r="G37" s="36"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="35"/>
       <c r="H37" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B38" s="31"/>
-      <c r="C38" s="35" t="s">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B38" s="30"/>
+      <c r="C38" s="34" t="s">
         <v>39</v>
       </c>
       <c r="D38" s="4" t="s">
@@ -2516,15 +2632,15 @@
       <c r="E38" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F38" s="39"/>
-      <c r="G38" s="40"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="39"/>
       <c r="H38" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B39" s="31"/>
-      <c r="C39" s="35" t="s">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B39" s="30"/>
+      <c r="C39" s="34" t="s">
         <v>40</v>
       </c>
       <c r="D39" s="4" t="s">
@@ -2533,15 +2649,15 @@
       <c r="E39" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F39" s="39"/>
-      <c r="G39" s="40"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="39"/>
       <c r="H39" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B40" s="32"/>
-      <c r="C40" s="27" t="s">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B40" s="31"/>
+      <c r="C40" s="26" t="s">
         <v>56</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -2550,17 +2666,20 @@
       <c r="E40" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F40" s="14"/>
-      <c r="G40" s="38"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="37"/>
       <c r="H40" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B41" s="28" t="s">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A41" s="96" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="C41" s="34" t="s">
+      <c r="C41" s="33" t="s">
         <v>58</v>
       </c>
       <c r="D41" s="4" t="s">
@@ -2569,15 +2688,15 @@
       <c r="E41" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F41" s="29"/>
-      <c r="G41" s="36"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="35"/>
       <c r="H41" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B42" s="31"/>
-      <c r="C42" s="35" t="s">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B42" s="30"/>
+      <c r="C42" s="34" t="s">
         <v>38</v>
       </c>
       <c r="D42" s="4" t="s">
@@ -2586,15 +2705,15 @@
       <c r="E42" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F42" s="39"/>
-      <c r="G42" s="40"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="39"/>
       <c r="H42" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B43" s="31"/>
-      <c r="C43" s="35" t="s">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B43" s="30"/>
+      <c r="C43" s="34" t="s">
         <v>39</v>
       </c>
       <c r="D43" s="4" t="s">
@@ -2603,15 +2722,14 @@
       <c r="E43" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F43" s="11"/>
-      <c r="G43" s="37"/>
+      <c r="G43" s="36"/>
       <c r="H43" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B44" s="31"/>
-      <c r="C44" s="35" t="s">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B44" s="30"/>
+      <c r="C44" s="34" t="s">
         <v>40</v>
       </c>
       <c r="D44" s="4" t="s">
@@ -2620,15 +2738,15 @@
       <c r="E44" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F44" s="39"/>
-      <c r="G44" s="40"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="39"/>
       <c r="H44" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B45" s="31"/>
-      <c r="C45" s="35" t="s">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B45" s="30"/>
+      <c r="C45" s="34" t="s">
         <v>59</v>
       </c>
       <c r="D45" s="4" t="s">
@@ -2637,15 +2755,14 @@
       <c r="E45" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F45" s="11"/>
-      <c r="G45" s="37"/>
+      <c r="G45" s="36"/>
       <c r="H45" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B46" s="32"/>
-      <c r="C46" s="27" t="s">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B46" s="31"/>
+      <c r="C46" s="26" t="s">
         <v>32</v>
       </c>
       <c r="D46" s="4" t="s">
@@ -2654,17 +2771,20 @@
       <c r="E46" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F46" s="39"/>
-      <c r="G46" s="40"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="39"/>
       <c r="H46" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B47" s="28" t="s">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A47" s="96" t="s">
+        <v>81</v>
+      </c>
+      <c r="B47" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="C47" s="34" t="s">
+      <c r="C47" s="33" t="s">
         <v>34</v>
       </c>
       <c r="D47" s="4" t="s">
@@ -2673,15 +2793,15 @@
       <c r="E47" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F47" s="39"/>
-      <c r="G47" s="40"/>
+      <c r="F47" s="38"/>
+      <c r="G47" s="39"/>
       <c r="H47" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B48" s="32"/>
-      <c r="C48" s="27" t="s">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B48" s="31"/>
+      <c r="C48" s="26" t="s">
         <v>35</v>
       </c>
       <c r="D48" s="4" t="s">
@@ -2690,17 +2810,20 @@
       <c r="E48" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F48" s="14"/>
-      <c r="G48" s="38"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="37"/>
       <c r="H48" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B49" s="28" t="s">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A49" s="99" t="s">
+        <v>85</v>
+      </c>
+      <c r="B49" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C49" s="41" t="s">
+      <c r="C49" s="40" t="s">
         <v>62</v>
       </c>
       <c r="D49" s="4" t="s">
@@ -2709,17 +2832,20 @@
       <c r="E49" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="42"/>
-      <c r="G49" s="40"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="39"/>
       <c r="H49" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B50" s="52" t="s">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A50" s="94" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="C50" s="53" t="s">
+      <c r="C50" s="52" t="s">
         <v>65</v>
       </c>
       <c r="D50" s="4" t="s">
@@ -2728,427 +2854,440 @@
       <c r="E50" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F50" s="54"/>
-      <c r="G50" s="55"/>
+      <c r="F50" s="53"/>
+      <c r="G50" s="54"/>
       <c r="H50" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B51" s="60" t="s">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A51" s="94" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="C51" s="58" t="s">
+      <c r="C51" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="D51" s="56" t="s">
+      <c r="D51" s="55" t="s">
         <v>17</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F51" s="62"/>
-      <c r="G51" s="51"/>
+      <c r="F51" s="61"/>
+      <c r="G51" s="50"/>
       <c r="H51" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B52" s="65"/>
-      <c r="C52" s="59" t="s">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B52" s="64"/>
+      <c r="C52" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="D52" s="56" t="s">
-        <v>17</v>
-      </c>
-      <c r="E52" s="63" t="s">
+      <c r="D52" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="E52" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="F52" s="64"/>
-      <c r="G52" s="51"/>
+      <c r="F52" s="63"/>
+      <c r="G52" s="50"/>
       <c r="H52" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B53" s="60" t="s">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A53" s="97" t="s">
+        <v>83</v>
+      </c>
+      <c r="B53" s="59" t="s">
         <v>70</v>
       </c>
-      <c r="C53" s="58" t="s">
+      <c r="C53" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="D53" s="56" t="s">
-        <v>17</v>
-      </c>
-      <c r="E53" s="63" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" s="64"/>
-      <c r="G53" s="51"/>
+      <c r="D53" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" s="63"/>
+      <c r="G53" s="50"/>
       <c r="H53" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B54" s="66"/>
-      <c r="C54" s="67" t="s">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B54" s="65"/>
+      <c r="C54" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="D54" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="E54" s="69" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" s="11"/>
-      <c r="G54" s="37"/>
-      <c r="H54" s="69" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B55" s="57" t="s">
+      <c r="D54" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E54" s="68" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" s="36"/>
+      <c r="H54" s="68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A55" s="97" t="s">
+        <v>83</v>
+      </c>
+      <c r="B55" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="C55" s="76" t="s">
+      <c r="C55" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="D55" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="E55" s="69" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" s="70"/>
-      <c r="G55" s="71"/>
-      <c r="H55" s="69" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B56" s="72"/>
-      <c r="C56" s="77" t="s">
+      <c r="D55" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E55" s="68" t="s">
+        <v>8</v>
+      </c>
+      <c r="F55" s="69"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B56" s="71"/>
+      <c r="C56" s="76" t="s">
         <v>74</v>
       </c>
-      <c r="D56" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="E56" s="69" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" s="80"/>
-      <c r="G56" s="81"/>
-      <c r="H56" s="69" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B57" s="72"/>
-      <c r="C57" s="77" t="s">
+      <c r="D56" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E56" s="68" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" s="79"/>
+      <c r="G56" s="80"/>
+      <c r="H56" s="68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B57" s="71"/>
+      <c r="C57" s="76" t="s">
         <v>75</v>
       </c>
-      <c r="D57" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="E57" s="69" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" s="80"/>
-      <c r="G57" s="79"/>
-      <c r="H57" s="69" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B58" s="72"/>
-      <c r="C58" s="77" t="s">
+      <c r="D57" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" s="68" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="79"/>
+      <c r="G57" s="78"/>
+      <c r="H57" s="68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B58" s="71"/>
+      <c r="C58" s="76" t="s">
         <v>29</v>
       </c>
-      <c r="D58" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="E58" s="69" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="11"/>
-      <c r="G58" s="37"/>
-      <c r="H58" s="69" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B59" s="57" t="s">
+      <c r="D58" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" s="68" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="36"/>
+      <c r="H58" s="68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A59" s="97" t="s">
+        <v>83</v>
+      </c>
+      <c r="B59" s="56" t="s">
         <v>76</v>
       </c>
-      <c r="C59" s="76" t="s">
+      <c r="C59" s="75" t="s">
         <v>77</v>
       </c>
-      <c r="D59" s="83" t="s">
-        <v>17</v>
-      </c>
-      <c r="E59" s="84" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" s="70"/>
-      <c r="G59" s="93"/>
-      <c r="H59" s="69" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B60" s="72"/>
-      <c r="C60" s="77" t="s">
+      <c r="D59" s="82" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" s="83" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="69"/>
+      <c r="G59" s="92"/>
+      <c r="H59" s="68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B60" s="71"/>
+      <c r="C60" s="76" t="s">
         <v>32</v>
       </c>
-      <c r="D60" s="87" t="s">
-        <v>17</v>
-      </c>
-      <c r="E60" s="90" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" s="81"/>
-      <c r="G60" s="88"/>
-      <c r="H60" s="69" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B61" s="72"/>
-      <c r="C61" s="77" t="s">
+      <c r="D60" s="86" t="s">
+        <v>17</v>
+      </c>
+      <c r="E60" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" s="80"/>
+      <c r="G60" s="87"/>
+      <c r="H60" s="68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B61" s="71"/>
+      <c r="C61" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="D61" s="86" t="s">
-        <v>17</v>
-      </c>
-      <c r="E61" s="91" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" s="81"/>
-      <c r="G61" s="82"/>
-      <c r="H61" s="69" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B62" s="72"/>
-      <c r="C62" s="77" t="s">
+      <c r="D61" s="85" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="90" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="80"/>
+      <c r="G61" s="81"/>
+      <c r="H61" s="68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B62" s="71"/>
+      <c r="C62" s="76" t="s">
         <v>53</v>
       </c>
-      <c r="D62" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="E62" s="89" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" s="81"/>
-      <c r="G62" s="82"/>
-      <c r="H62" s="69" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B63" s="72"/>
-      <c r="C63" s="77" t="s">
+      <c r="D62" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="80"/>
+      <c r="G62" s="81"/>
+      <c r="H62" s="68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B63" s="71"/>
+      <c r="C63" s="76" t="s">
         <v>38</v>
       </c>
-      <c r="D63" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="E63" s="89" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" s="92"/>
-      <c r="G63" s="73"/>
-      <c r="H63" s="69" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B64" s="72"/>
-      <c r="C64" s="77" t="s">
+      <c r="D63" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" s="91"/>
+      <c r="G63" s="72"/>
+      <c r="H63" s="68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B64" s="71"/>
+      <c r="C64" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="D64" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" s="89" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" s="81"/>
-      <c r="G64" s="82"/>
-      <c r="H64" s="69" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B65" s="72"/>
-      <c r="C65" s="77" t="s">
+      <c r="D64" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" s="80"/>
+      <c r="G64" s="81"/>
+      <c r="H64" s="68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B65" s="71"/>
+      <c r="C65" s="76" t="s">
         <v>78</v>
       </c>
-      <c r="D65" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="E65" s="89" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" s="81"/>
-      <c r="G65" s="82"/>
-      <c r="H65" s="69" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B66" s="74"/>
-      <c r="C66" s="78" t="s">
+      <c r="D65" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" s="80"/>
+      <c r="G65" s="81"/>
+      <c r="H65" s="68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B66" s="73"/>
+      <c r="C66" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="D66" s="85" t="s">
-        <v>17</v>
-      </c>
-      <c r="E66" s="90" t="s">
-        <v>8</v>
-      </c>
-      <c r="F66" s="81"/>
-      <c r="G66" s="75"/>
-      <c r="H66" s="87" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B67" s="57" t="s">
+      <c r="D66" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="F66" s="80"/>
+      <c r="G66" s="74"/>
+      <c r="H66" s="86" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A67" s="98" t="s">
+        <v>84</v>
+      </c>
+      <c r="B67" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="C67" s="76" t="s">
+      <c r="C67" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="D67" s="85" t="s">
-        <v>17</v>
-      </c>
-      <c r="E67" s="90" t="s">
-        <v>8</v>
-      </c>
-      <c r="F67" s="94"/>
-      <c r="G67" s="94"/>
-      <c r="H67" s="87" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B68" s="72"/>
-      <c r="C68" s="77" t="s">
+      <c r="D67" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" s="93"/>
+      <c r="G67" s="93"/>
+      <c r="H67" s="86" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B68" s="71"/>
+      <c r="C68" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="D68" s="85" t="s">
-        <v>17</v>
-      </c>
-      <c r="E68" s="90" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" s="81"/>
-      <c r="G68" s="81"/>
-      <c r="H68" s="87" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B69" s="72"/>
-      <c r="C69" s="77" t="s">
+      <c r="D68" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" s="80"/>
+      <c r="G68" s="80"/>
+      <c r="H68" s="86" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B69" s="71"/>
+      <c r="C69" s="76" t="s">
         <v>53</v>
       </c>
-      <c r="D69" s="85" t="s">
-        <v>17</v>
-      </c>
-      <c r="E69" s="90" t="s">
+      <c r="D69" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="E69" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="F69" s="92"/>
-      <c r="G69" s="92"/>
-      <c r="H69" s="87" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B70" s="72"/>
-      <c r="C70" s="77" t="s">
+      <c r="F69" s="91"/>
+      <c r="G69" s="91"/>
+      <c r="H69" s="86" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B70" s="71"/>
+      <c r="C70" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="D70" s="85" t="s">
-        <v>17</v>
-      </c>
-      <c r="E70" s="90" t="s">
+      <c r="D70" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="F70" s="81"/>
-      <c r="G70" s="81"/>
-      <c r="H70" s="87" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B71" s="72"/>
-      <c r="C71" s="77" t="s">
+      <c r="F70" s="80"/>
+      <c r="G70" s="80"/>
+      <c r="H70" s="86" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B71" s="71"/>
+      <c r="C71" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="D71" s="85" t="s">
-        <v>17</v>
-      </c>
-      <c r="E71" s="90" t="s">
+      <c r="D71" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="E71" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="F71" s="92"/>
-      <c r="G71" s="92"/>
-      <c r="H71" s="87" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B72" s="72"/>
-      <c r="C72" s="77" t="s">
+      <c r="F71" s="91"/>
+      <c r="G71" s="91"/>
+      <c r="H71" s="86" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B72" s="71"/>
+      <c r="C72" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="D72" s="85" t="s">
-        <v>17</v>
-      </c>
-      <c r="E72" s="90" t="s">
+      <c r="D72" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="F72" s="81"/>
-      <c r="G72" s="81"/>
-      <c r="H72" s="87" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B73" s="72"/>
-      <c r="C73" s="77" t="s">
+      <c r="F72" s="80"/>
+      <c r="G72" s="80"/>
+      <c r="H72" s="86" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B73" s="71"/>
+      <c r="C73" s="76" t="s">
         <v>58</v>
       </c>
-      <c r="D73" s="85" t="s">
-        <v>17</v>
-      </c>
-      <c r="E73" s="90" t="s">
+      <c r="D73" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="81"/>
-      <c r="G73" s="81"/>
-      <c r="H73" s="87" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B74" s="74"/>
-      <c r="C74" s="78" t="s">
+      <c r="F73" s="80"/>
+      <c r="G73" s="80"/>
+      <c r="H73" s="86" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B74" s="73"/>
+      <c r="C74" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="D74" s="85" t="s">
-        <v>17</v>
-      </c>
-      <c r="E74" s="90" t="s">
+      <c r="D74" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="F74" s="61"/>
-      <c r="G74" s="61"/>
-      <c r="H74" s="87" t="s">
+      <c r="F74" s="60"/>
+      <c r="G74" s="60"/>
+      <c r="H74" s="86" t="s">
         <v>63</v>
       </c>
     </row>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0205h\Desktop\github\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FB7AF4-1345-4003-9BFB-024FDEE60735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC682BD-2740-4E21-A085-6E3B71F7CBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="K3" s="3">
         <f>SUM(K4,K5,K6)</f>
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L3" s="3"/>
     </row>
@@ -1942,7 +1942,7 @@
         <v>11</v>
       </c>
       <c r="K4" s="5">
-        <f>COUNTIF(E3:E72,J4)</f>
+        <f>COUNTIF(E3:E74,J4)</f>
         <v>39</v>
       </c>
       <c r="L4" s="3"/>
@@ -1968,8 +1968,8 @@
         <v>12</v>
       </c>
       <c r="K5" s="5">
-        <f>COUNTIF(E3:E72,J5)</f>
-        <v>11</v>
+        <f>COUNTIF(E3:E74,J5)</f>
+        <v>12</v>
       </c>
       <c r="L5" s="3"/>
     </row>
@@ -1994,8 +1994,8 @@
         <v>13</v>
       </c>
       <c r="K6" s="5">
-        <f>COUNTIF(E3:E72,J6)</f>
-        <v>18</v>
+        <f>COUNTIF(E3:E74,J6)</f>
+        <v>19</v>
       </c>
       <c r="L6" s="3"/>
     </row>
@@ -2025,7 +2025,7 @@
         <v>14</v>
       </c>
       <c r="K7" s="5">
-        <f>COUNTIF(H3:H72,J7)</f>
+        <f>COUNTIF(H3:H74,J7)</f>
         <v>0</v>
       </c>
       <c r="L7" s="6">
@@ -2054,12 +2054,12 @@
         <v>15</v>
       </c>
       <c r="K8" s="5">
-        <f>COUNTIF(H3:H72,J8)</f>
-        <v>70</v>
+        <f>COUNTIF(H3:H74,J8)</f>
+        <v>72</v>
       </c>
       <c r="L8" s="7">
         <f>(K8+K9)/K3</f>
-        <v>1.0294117647058822</v>
+        <v>1.0285714285714285</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
@@ -2083,7 +2083,7 @@
         <v>18</v>
       </c>
       <c r="K9" s="3">
-        <f>COUNTIF(H3:H72,J9)</f>
+        <f>COUNTIF(H3:H74,J9)</f>
         <v>0</v>
       </c>
       <c r="L9" s="3"/>
@@ -2130,7 +2130,7 @@
         <v>19</v>
       </c>
       <c r="K11" s="3">
-        <f>SUM(F3:F72)</f>
+        <f>SUM(F3:F74)</f>
         <v>0</v>
       </c>
       <c r="L11" s="3"/>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0205h\Desktop\github\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC682BD-2740-4E21-A085-6E3B71F7CBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C0DCF5-FEBC-443E-BC90-C6259C0BB790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="3735" yWindow="810" windowWidth="21600" windowHeight="14565" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1247,7 +1247,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1511,6 +1511,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1906,7 +1912,9 @@
       <c r="E3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="4"/>
+      <c r="F3" s="100">
+        <v>0.5</v>
+      </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
         <v>63</v>
@@ -1932,7 +1940,9 @@
       <c r="E4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="4"/>
+      <c r="F4" s="100">
+        <v>0.5</v>
+      </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
         <v>63</v>
@@ -1958,7 +1968,9 @@
       <c r="E5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="4"/>
+      <c r="F5" s="100">
+        <v>0.5</v>
+      </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
         <v>63</v>
@@ -1984,7 +1996,9 @@
       <c r="E6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="4"/>
+      <c r="F6" s="100">
+        <v>1</v>
+      </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
         <v>63</v>
@@ -2015,7 +2029,9 @@
       <c r="E7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="4"/>
+      <c r="F7" s="100">
+        <v>1</v>
+      </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
         <v>63</v>
@@ -2044,7 +2060,9 @@
       <c r="E8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="4"/>
+      <c r="F8" s="100">
+        <v>0.5</v>
+      </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
         <v>63</v>
@@ -2073,7 +2091,9 @@
       <c r="E9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="4"/>
+      <c r="F9" s="100">
+        <v>0.5</v>
+      </c>
       <c r="G9" s="4"/>
       <c r="H9" s="47" t="s">
         <v>63</v>
@@ -2099,7 +2119,9 @@
       <c r="E10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="4"/>
+      <c r="F10" s="100">
+        <v>0.5</v>
+      </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
         <v>63</v>
@@ -2120,7 +2142,9 @@
       <c r="E11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="4"/>
+      <c r="F11" s="100">
+        <v>0.5</v>
+      </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
         <v>63</v>
@@ -2131,7 +2155,7 @@
       </c>
       <c r="K11" s="3">
         <f>SUM(F3:F74)</f>
-        <v>0</v>
+        <v>10.600000000000001</v>
       </c>
       <c r="L11" s="3"/>
     </row>
@@ -2146,7 +2170,9 @@
       <c r="E12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="4"/>
+      <c r="F12" s="100">
+        <v>1</v>
+      </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
         <v>63</v>
@@ -2157,7 +2183,7 @@
       </c>
       <c r="K12" s="3">
         <f>8*K11</f>
-        <v>0</v>
+        <v>84.800000000000011</v>
       </c>
       <c r="L12" s="3"/>
     </row>
@@ -2177,7 +2203,9 @@
       <c r="E13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="4"/>
+      <c r="F13" s="100">
+        <v>0.2</v>
+      </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
         <v>63</v>
@@ -2194,7 +2222,9 @@
       <c r="E14" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="4"/>
+      <c r="F14" s="100">
+        <v>0.2</v>
+      </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
         <v>63</v>
@@ -2211,7 +2241,9 @@
       <c r="E15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="4"/>
+      <c r="F15" s="100">
+        <v>0.2</v>
+      </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
         <v>63</v>
@@ -2233,7 +2265,9 @@
       <c r="E16" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="35"/>
+      <c r="F16" s="101">
+        <v>0.5</v>
+      </c>
       <c r="G16" s="35"/>
       <c r="H16" s="4" t="s">
         <v>63</v>
@@ -2250,7 +2284,9 @@
       <c r="E17" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="39"/>
+      <c r="F17" s="101">
+        <v>0.5</v>
+      </c>
       <c r="G17" s="39"/>
       <c r="H17" s="4" t="s">
         <v>63</v>
@@ -2267,7 +2303,9 @@
       <c r="E18" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="37"/>
+      <c r="F18" s="101">
+        <v>0.5</v>
+      </c>
       <c r="G18" s="37"/>
       <c r="H18" s="4" t="s">
         <v>63</v>
@@ -2284,7 +2322,9 @@
       <c r="E19" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="37"/>
+      <c r="F19" s="101">
+        <v>0.5</v>
+      </c>
       <c r="G19" s="37"/>
       <c r="H19" s="4" t="s">
         <v>63</v>
@@ -2306,7 +2346,9 @@
       <c r="E20" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="35"/>
+      <c r="F20" s="101">
+        <v>0.5</v>
+      </c>
       <c r="G20" s="35"/>
       <c r="H20" s="4" t="s">
         <v>63</v>
@@ -2323,7 +2365,9 @@
       <c r="E21" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="39"/>
+      <c r="F21" s="101">
+        <v>0.5</v>
+      </c>
       <c r="G21" s="39"/>
       <c r="H21" s="4" t="s">
         <v>63</v>
@@ -2340,7 +2384,9 @@
       <c r="E22" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="37"/>
+      <c r="F22" s="101">
+        <v>0.5</v>
+      </c>
       <c r="G22" s="37"/>
       <c r="H22" s="4" t="s">
         <v>63</v>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AyumuKaminaga\Documents\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C0DCF5-FEBC-443E-BC90-C6259C0BB790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBA94F8-69F8-4191-85DE-9C23AE3E5006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3735" yWindow="810" windowWidth="21600" windowHeight="14565" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="K11" s="3">
         <f>SUM(F3:F74)</f>
-        <v>10.600000000000001</v>
+        <v>27.6</v>
       </c>
       <c r="L11" s="3"/>
     </row>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="K12" s="3">
         <f>8*K11</f>
-        <v>84.800000000000011</v>
+        <v>220.8</v>
       </c>
       <c r="L12" s="3"/>
     </row>
@@ -2408,7 +2408,9 @@
       <c r="E23" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="35"/>
+      <c r="F23" s="35">
+        <v>1</v>
+      </c>
       <c r="G23" s="29"/>
       <c r="H23" s="4" t="s">
         <v>63</v>
@@ -2425,7 +2427,9 @@
       <c r="E24" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="39"/>
+      <c r="F24" s="39">
+        <v>1</v>
+      </c>
       <c r="G24" s="42"/>
       <c r="H24" s="4" t="s">
         <v>63</v>
@@ -2442,7 +2446,9 @@
       <c r="E25" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="36"/>
+      <c r="F25" s="36">
+        <v>0.5</v>
+      </c>
       <c r="G25" s="11"/>
       <c r="H25" s="4" t="s">
         <v>63</v>
@@ -2459,7 +2465,9 @@
       <c r="E26" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="39"/>
+      <c r="F26" s="39">
+        <v>1</v>
+      </c>
       <c r="G26" s="42"/>
       <c r="H26" s="4" t="s">
         <v>63</v>
@@ -2476,7 +2484,9 @@
       <c r="E27" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="39"/>
+      <c r="F27" s="36">
+        <v>0.5</v>
+      </c>
       <c r="G27" s="42"/>
       <c r="H27" s="4" t="s">
         <v>63</v>
@@ -2493,7 +2503,9 @@
       <c r="E28" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F28" s="37"/>
+      <c r="F28" s="37">
+        <v>1</v>
+      </c>
       <c r="G28" s="32"/>
       <c r="H28" s="4" t="s">
         <v>63</v>
@@ -2515,7 +2527,9 @@
       <c r="E29" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="29"/>
+      <c r="F29" s="29">
+        <v>1</v>
+      </c>
       <c r="G29" s="35"/>
       <c r="H29" s="4" t="s">
         <v>63</v>
@@ -2532,7 +2546,9 @@
       <c r="E30" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="39"/>
+      <c r="F30" s="39">
+        <v>0.5</v>
+      </c>
       <c r="G30" s="39"/>
       <c r="H30" s="4" t="s">
         <v>63</v>
@@ -2549,7 +2565,9 @@
       <c r="E31" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F31" s="39"/>
+      <c r="F31" s="39">
+        <v>0.5</v>
+      </c>
       <c r="G31" s="39"/>
       <c r="H31" s="4" t="s">
         <v>63</v>
@@ -2566,7 +2584,9 @@
       <c r="E32" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="32"/>
+      <c r="F32" s="32">
+        <v>1</v>
+      </c>
       <c r="G32" s="37"/>
       <c r="H32" s="4" t="s">
         <v>63</v>
@@ -2588,7 +2608,9 @@
       <c r="E33" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F33" s="35"/>
+      <c r="F33" s="35">
+        <v>0.5</v>
+      </c>
       <c r="G33" s="35"/>
       <c r="H33" s="4" t="s">
         <v>63</v>
@@ -2605,7 +2627,9 @@
       <c r="E34" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F34" s="39"/>
+      <c r="F34" s="39">
+        <v>0.5</v>
+      </c>
       <c r="G34" s="39"/>
       <c r="H34" s="4" t="s">
         <v>63</v>
@@ -2622,7 +2646,9 @@
       <c r="E35" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F35" s="39"/>
+      <c r="F35" s="39">
+        <v>0.5</v>
+      </c>
       <c r="G35" s="39"/>
       <c r="H35" s="4" t="s">
         <v>63</v>
@@ -2639,7 +2665,9 @@
       <c r="E36" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F36" s="37"/>
+      <c r="F36" s="37">
+        <v>0.5</v>
+      </c>
       <c r="G36" s="37"/>
       <c r="H36" s="4" t="s">
         <v>63</v>
@@ -2661,7 +2689,9 @@
       <c r="E37" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F37" s="28"/>
+      <c r="F37" s="28">
+        <v>0.5</v>
+      </c>
       <c r="G37" s="35"/>
       <c r="H37" s="4" t="s">
         <v>63</v>
@@ -2678,7 +2708,9 @@
       <c r="E38" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F38" s="38"/>
+      <c r="F38" s="38">
+        <v>0.5</v>
+      </c>
       <c r="G38" s="39"/>
       <c r="H38" s="4" t="s">
         <v>63</v>
@@ -2695,7 +2727,9 @@
       <c r="E39" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F39" s="38"/>
+      <c r="F39" s="38">
+        <v>0.5</v>
+      </c>
       <c r="G39" s="39"/>
       <c r="H39" s="4" t="s">
         <v>63</v>
@@ -2712,7 +2746,9 @@
       <c r="E40" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F40" s="13"/>
+      <c r="F40" s="13">
+        <v>1</v>
+      </c>
       <c r="G40" s="37"/>
       <c r="H40" s="4" t="s">
         <v>63</v>
@@ -2734,7 +2770,9 @@
       <c r="E41" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F41" s="28"/>
+      <c r="F41" s="28">
+        <v>1</v>
+      </c>
       <c r="G41" s="35"/>
       <c r="H41" s="4" t="s">
         <v>63</v>
@@ -2751,7 +2789,9 @@
       <c r="E42" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F42" s="38"/>
+      <c r="F42" s="38">
+        <v>0.5</v>
+      </c>
       <c r="G42" s="39"/>
       <c r="H42" s="4" t="s">
         <v>63</v>
@@ -2768,6 +2808,9 @@
       <c r="E43" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F43" s="38">
+        <v>0.5</v>
+      </c>
       <c r="G43" s="36"/>
       <c r="H43" s="4" t="s">
         <v>63</v>
@@ -2784,7 +2827,9 @@
       <c r="E44" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F44" s="38"/>
+      <c r="F44" s="38">
+        <v>0.5</v>
+      </c>
       <c r="G44" s="39"/>
       <c r="H44" s="4" t="s">
         <v>63</v>
@@ -2801,6 +2846,9 @@
       <c r="E45" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F45" s="38">
+        <v>0.5</v>
+      </c>
       <c r="G45" s="36"/>
       <c r="H45" s="4" t="s">
         <v>63</v>
@@ -2817,7 +2865,9 @@
       <c r="E46" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F46" s="38"/>
+      <c r="F46" s="38">
+        <v>0.5</v>
+      </c>
       <c r="G46" s="39"/>
       <c r="H46" s="4" t="s">
         <v>63</v>
@@ -2839,7 +2889,9 @@
       <c r="E47" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F47" s="38"/>
+      <c r="F47" s="38">
+        <v>0.5</v>
+      </c>
       <c r="G47" s="39"/>
       <c r="H47" s="4" t="s">
         <v>63</v>
@@ -2856,7 +2908,9 @@
       <c r="E48" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F48" s="13"/>
+      <c r="F48" s="38">
+        <v>0.5</v>
+      </c>
       <c r="G48" s="37"/>
       <c r="H48" s="4" t="s">
         <v>63</v>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AyumuKaminaga\Documents\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0205h\Desktop\github\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBA94F8-69F8-4191-85DE-9C23AE3E5006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4841506-492A-4DE2-800A-4A802383924D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1247,7 +1247,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1517,6 +1517,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2155,7 +2158,7 @@
       </c>
       <c r="K11" s="3">
         <f>SUM(F3:F74)</f>
-        <v>27.6</v>
+        <v>37.1</v>
       </c>
       <c r="L11" s="3"/>
     </row>
@@ -2183,7 +2186,7 @@
       </c>
       <c r="K12" s="3">
         <f>8*K11</f>
-        <v>220.8</v>
+        <v>296.8</v>
       </c>
       <c r="L12" s="3"/>
     </row>
@@ -3015,7 +3018,9 @@
       <c r="E53" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="F53" s="63"/>
+      <c r="F53" s="63">
+        <v>1</v>
+      </c>
       <c r="G53" s="50"/>
       <c r="H53" s="4" t="s">
         <v>63</v>
@@ -3032,6 +3037,9 @@
       <c r="E54" s="68" t="s">
         <v>8</v>
       </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
       <c r="G54" s="36"/>
       <c r="H54" s="68" t="s">
         <v>63</v>
@@ -3053,7 +3061,9 @@
       <c r="E55" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="F55" s="69"/>
+      <c r="F55" s="69">
+        <v>0.5</v>
+      </c>
       <c r="G55" s="70"/>
       <c r="H55" s="68" t="s">
         <v>63</v>
@@ -3070,7 +3080,9 @@
       <c r="E56" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="F56" s="79"/>
+      <c r="F56" s="79">
+        <v>1</v>
+      </c>
       <c r="G56" s="80"/>
       <c r="H56" s="68" t="s">
         <v>63</v>
@@ -3087,7 +3099,9 @@
       <c r="E57" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="79"/>
+      <c r="F57" s="79">
+        <v>1</v>
+      </c>
       <c r="G57" s="78"/>
       <c r="H57" s="68" t="s">
         <v>63</v>
@@ -3104,6 +3118,9 @@
       <c r="E58" s="68" t="s">
         <v>8</v>
       </c>
+      <c r="F58" s="102">
+        <v>1</v>
+      </c>
       <c r="G58" s="36"/>
       <c r="H58" s="68" t="s">
         <v>63</v>
@@ -3125,7 +3142,9 @@
       <c r="E59" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="69"/>
+      <c r="F59" s="69">
+        <v>0.5</v>
+      </c>
       <c r="G59" s="92"/>
       <c r="H59" s="68" t="s">
         <v>63</v>
@@ -3142,7 +3161,9 @@
       <c r="E60" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="F60" s="80"/>
+      <c r="F60" s="80">
+        <v>0.5</v>
+      </c>
       <c r="G60" s="87"/>
       <c r="H60" s="68" t="s">
         <v>63</v>
@@ -3159,7 +3180,9 @@
       <c r="E61" s="90" t="s">
         <v>8</v>
       </c>
-      <c r="F61" s="80"/>
+      <c r="F61" s="80">
+        <v>0.5</v>
+      </c>
       <c r="G61" s="81"/>
       <c r="H61" s="68" t="s">
         <v>63</v>
@@ -3176,7 +3199,9 @@
       <c r="E62" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="F62" s="80"/>
+      <c r="F62" s="80">
+        <v>0.5</v>
+      </c>
       <c r="G62" s="81"/>
       <c r="H62" s="68" t="s">
         <v>63</v>
@@ -3193,7 +3218,9 @@
       <c r="E63" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="F63" s="91"/>
+      <c r="F63" s="91">
+        <v>0.5</v>
+      </c>
       <c r="G63" s="72"/>
       <c r="H63" s="68" t="s">
         <v>63</v>
@@ -3210,7 +3237,9 @@
       <c r="E64" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="F64" s="80"/>
+      <c r="F64" s="80">
+        <v>0.5</v>
+      </c>
       <c r="G64" s="81"/>
       <c r="H64" s="68" t="s">
         <v>63</v>
@@ -3227,7 +3256,9 @@
       <c r="E65" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="F65" s="80"/>
+      <c r="F65" s="80">
+        <v>0.5</v>
+      </c>
       <c r="G65" s="81"/>
       <c r="H65" s="68" t="s">
         <v>63</v>
@@ -3244,7 +3275,9 @@
       <c r="E66" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="F66" s="80"/>
+      <c r="F66" s="80">
+        <v>0.5</v>
+      </c>
       <c r="G66" s="74"/>
       <c r="H66" s="86" t="s">
         <v>63</v>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0205h\Desktop\github\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4841506-492A-4DE2-800A-4A802383924D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18DC24CE-382B-43C9-A517-9BBD77EC1A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="87">
   <si>
     <t>概要</t>
     <rPh sb="0" eb="2">
@@ -510,6 +510,9 @@
       <t>ダレ</t>
     </rPh>
     <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>完了</t>
   </si>
 </sst>
 </file>
@@ -1247,7 +1250,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1517,9 +1520,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2045,11 +2045,11 @@
       </c>
       <c r="K7" s="5">
         <f>COUNTIF(H3:H74,J7)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="6">
         <f>K7/K3</f>
-        <v>0</v>
+        <v>1.4285714285714285E-2</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
@@ -2076,11 +2076,11 @@
       </c>
       <c r="K8" s="5">
         <f>COUNTIF(H3:H74,J8)</f>
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L8" s="7">
         <f>(K8+K9)/K3</f>
-        <v>1.0285714285714285</v>
+        <v>1.0142857142857142</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
@@ -2958,9 +2958,11 @@
         <v>8</v>
       </c>
       <c r="F50" s="53"/>
-      <c r="G50" s="54"/>
+      <c r="G50" s="54">
+        <v>3</v>
+      </c>
       <c r="H50" s="4" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.4">
@@ -3118,7 +3120,7 @@
       <c r="E58" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="F58" s="102">
+      <c r="F58">
         <v>1</v>
       </c>
       <c r="G58" s="36"/>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opencampus\Documents\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18DC24CE-382B-43C9-A517-9BBD77EC1A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56AC2D5-E7ED-4340-96DE-79ADB098DCE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,16 +27,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="89">
   <si>
     <t>概要</t>
     <rPh sb="0" eb="2">
@@ -513,6 +514,13 @@
   </si>
   <si>
     <t>完了</t>
+  </si>
+  <si>
+    <t>作業中</t>
+  </si>
+  <si>
+    <t>S</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -683,7 +691,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="47">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -1179,44 +1187,18 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
         <color theme="1"/>
       </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
@@ -1250,7 +1232,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1431,15 +1413,9 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="39" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="29" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1458,27 +1434,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1491,7 +1461,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
@@ -1521,6 +1491,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -1856,7 +1831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039B1606-320D-4390-8B98-CE6030BB2FAA}">
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="3" width="25.375" bestFit="1" customWidth="1"/>
@@ -1900,7 +1875,7 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A3" s="95" t="s">
+      <c r="A3" s="91" t="s">
         <v>80</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -1915,7 +1890,7 @@
       <c r="E3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="100">
+      <c r="F3" s="96">
         <v>0.5</v>
       </c>
       <c r="G3" s="4"/>
@@ -1928,7 +1903,7 @@
       </c>
       <c r="K3" s="3">
         <f>SUM(K4,K5,K6)</f>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L3" s="3"/>
     </row>
@@ -1943,7 +1918,7 @@
       <c r="E4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="100">
+      <c r="F4" s="96">
         <v>0.5</v>
       </c>
       <c r="G4" s="4"/>
@@ -1955,8 +1930,8 @@
         <v>11</v>
       </c>
       <c r="K4" s="5">
-        <f>COUNTIF(E3:E74,J4)</f>
-        <v>39</v>
+        <f>COUNTIF(E3:E75,J4)</f>
+        <v>37</v>
       </c>
       <c r="L4" s="3"/>
     </row>
@@ -1971,7 +1946,7 @@
       <c r="E5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="100">
+      <c r="F5" s="96">
         <v>0.5</v>
       </c>
       <c r="G5" s="4"/>
@@ -1983,8 +1958,8 @@
         <v>12</v>
       </c>
       <c r="K5" s="5">
-        <f>COUNTIF(E3:E74,J5)</f>
-        <v>12</v>
+        <f>COUNTIF(E3:E75,J5)</f>
+        <v>15</v>
       </c>
       <c r="L5" s="3"/>
     </row>
@@ -1999,7 +1974,7 @@
       <c r="E6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="100">
+      <c r="F6" s="96">
         <v>1</v>
       </c>
       <c r="G6" s="4"/>
@@ -2011,13 +1986,13 @@
         <v>13</v>
       </c>
       <c r="K6" s="5">
-        <f>COUNTIF(E3:E74,J6)</f>
+        <f>COUNTIF(E3:E75,J6)</f>
         <v>19</v>
       </c>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A7" s="95" t="s">
+      <c r="A7" s="91" t="s">
         <v>80</v>
       </c>
       <c r="B7" s="9" t="s">
@@ -2032,24 +2007,24 @@
       <c r="E7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="100">
+      <c r="F7" s="96">
         <v>1</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="I7" s="43"/>
       <c r="J7" s="19" t="s">
         <v>14</v>
       </c>
       <c r="K7" s="5">
-        <f>COUNTIF(H3:H74,J7)</f>
-        <v>1</v>
+        <f>COUNTIF(H3:H75,J7)</f>
+        <v>11</v>
       </c>
       <c r="L7" s="6">
         <f>K7/K3</f>
-        <v>1.4285714285714285E-2</v>
+        <v>0.15492957746478872</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
@@ -2063,7 +2038,7 @@
       <c r="E8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="100">
+      <c r="F8" s="96">
         <v>0.5</v>
       </c>
       <c r="G8" s="4"/>
@@ -2075,12 +2050,12 @@
         <v>15</v>
       </c>
       <c r="K8" s="5">
-        <f>COUNTIF(H3:H74,J8)</f>
-        <v>71</v>
+        <f>COUNTIF(H3:H75,J8)</f>
+        <v>56</v>
       </c>
       <c r="L8" s="7">
         <f>(K8+K9)/K3</f>
-        <v>1.0142857142857142</v>
+        <v>0.87323943661971826</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
@@ -2094,20 +2069,20 @@
       <c r="E9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="100">
+      <c r="F9" s="96">
         <v>0.5</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="47" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="I9" s="48"/>
       <c r="J9" s="15" t="s">
         <v>18</v>
       </c>
       <c r="K9" s="3">
-        <f>COUNTIF(H3:H74,J9)</f>
-        <v>0</v>
+        <f>COUNTIF(H3:H75,J9)</f>
+        <v>6</v>
       </c>
       <c r="L9" s="3"/>
     </row>
@@ -2122,12 +2097,14 @@
       <c r="E10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="100">
-        <v>0.5</v>
-      </c>
-      <c r="G10" s="4"/>
+      <c r="F10" s="96">
+        <v>0.5</v>
+      </c>
+      <c r="G10" s="96">
+        <v>0.5</v>
+      </c>
       <c r="H10" s="4" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="I10" s="49"/>
       <c r="J10" s="14"/>
@@ -2135,6 +2112,7 @@
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A11" s="11"/>
       <c r="B11" s="9"/>
       <c r="C11" s="8" t="s">
         <v>29</v>
@@ -2145,7 +2123,7 @@
       <c r="E11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="100">
+      <c r="F11" s="96">
         <v>0.5</v>
       </c>
       <c r="G11" s="4"/>
@@ -2157,14 +2135,15 @@
         <v>19</v>
       </c>
       <c r="K11" s="3">
-        <f>SUM(F3:F74)</f>
-        <v>37.1</v>
+        <f>SUM(F3:F75)</f>
+        <v>37.6</v>
       </c>
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B12" s="12"/>
-      <c r="C12" s="26" t="s">
+      <c r="A12" s="11"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="34" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="4" t="s">
@@ -2173,7 +2152,7 @@
       <c r="E12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="100">
+      <c r="F12" s="96">
         <v>1</v>
       </c>
       <c r="G12" s="4"/>
@@ -2186,46 +2165,51 @@
       </c>
       <c r="K12" s="3">
         <f>8*K11</f>
-        <v>296.8</v>
+        <v>300.8</v>
       </c>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A13" s="95" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>34</v>
+      <c r="A13" s="11"/>
+      <c r="B13" s="100"/>
+      <c r="C13" s="26" t="s">
+        <v>77</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="100">
-        <v>0.2</v>
+      <c r="F13" s="96">
+        <v>0.5</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
         <v>63</v>
       </c>
+      <c r="I13" s="98"/>
+      <c r="J13" s="99"/>
+      <c r="K13" s="98"/>
+      <c r="L13" s="98"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B14" s="24"/>
+      <c r="A14" s="91" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>33</v>
+      </c>
       <c r="C14" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="100">
+        <v>10</v>
+      </c>
+      <c r="F14" s="96">
         <v>0.2</v>
       </c>
       <c r="G14" s="4"/>
@@ -2234,17 +2218,17 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B15" s="25"/>
-      <c r="C15" s="26" t="s">
-        <v>36</v>
+      <c r="B15" s="24"/>
+      <c r="C15" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="100">
+        <v>10</v>
+      </c>
+      <c r="F15" s="96">
         <v>0.2</v>
       </c>
       <c r="G15" s="4"/>
@@ -2253,33 +2237,33 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A16" s="95" t="s">
+      <c r="B16" s="25"/>
+      <c r="C16" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="96">
+        <v>0.2</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="B17" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C17" s="33" t="s">
         <v>38</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="101">
-        <v>0.5</v>
-      </c>
-      <c r="G16" s="35"/>
-      <c r="H16" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B17" s="30"/>
-      <c r="C17" s="34" t="s">
-        <v>39</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>17</v>
@@ -2287,10 +2271,10 @@
       <c r="E17" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="101">
-        <v>0.5</v>
-      </c>
-      <c r="G17" s="39"/>
+      <c r="F17" s="97">
+        <v>0.5</v>
+      </c>
+      <c r="G17" s="35"/>
       <c r="H17" s="4" t="s">
         <v>63</v>
       </c>
@@ -2298,7 +2282,7 @@
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B18" s="30"/>
       <c r="C18" s="34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>17</v>
@@ -2306,18 +2290,18 @@
       <c r="E18" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="101">
-        <v>0.5</v>
-      </c>
-      <c r="G18" s="37"/>
+      <c r="F18" s="97">
+        <v>0.5</v>
+      </c>
+      <c r="G18" s="39"/>
       <c r="H18" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B19" s="31"/>
-      <c r="C19" s="26" t="s">
-        <v>32</v>
+      <c r="B19" s="30"/>
+      <c r="C19" s="34" t="s">
+        <v>40</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>17</v>
@@ -2325,7 +2309,7 @@
       <c r="E19" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="101">
+      <c r="F19" s="97">
         <v>0.5</v>
       </c>
       <c r="G19" s="37"/>
@@ -2334,14 +2318,9 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A20" s="95" t="s">
-        <v>80</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="33" t="s">
-        <v>38</v>
+      <c r="B20" s="31"/>
+      <c r="C20" s="26" t="s">
+        <v>32</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>17</v>
@@ -2349,18 +2328,23 @@
       <c r="E20" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="101">
-        <v>0.5</v>
-      </c>
-      <c r="G20" s="35"/>
+      <c r="F20" s="97">
+        <v>0.5</v>
+      </c>
+      <c r="G20" s="37"/>
       <c r="H20" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B21" s="30"/>
-      <c r="C21" s="34" t="s">
-        <v>39</v>
+      <c r="A21" s="91" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>38</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>17</v>
@@ -2368,18 +2352,18 @@
       <c r="E21" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="101">
-        <v>0.5</v>
-      </c>
-      <c r="G21" s="39"/>
+      <c r="F21" s="97">
+        <v>0.5</v>
+      </c>
+      <c r="G21" s="35"/>
       <c r="H21" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B22" s="31"/>
-      <c r="C22" s="26" t="s">
-        <v>40</v>
+      <c r="B22" s="30"/>
+      <c r="C22" s="34" t="s">
+        <v>39</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>17</v>
@@ -2387,53 +2371,53 @@
       <c r="E22" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="101">
-        <v>0.5</v>
-      </c>
-      <c r="G22" s="37"/>
+      <c r="F22" s="97">
+        <v>0.5</v>
+      </c>
+      <c r="G22" s="39"/>
       <c r="H22" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A23" s="96" t="s">
+      <c r="B23" s="31"/>
+      <c r="C23" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="97">
+        <v>0.5</v>
+      </c>
+      <c r="G23" s="37"/>
+      <c r="H23" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A24" s="92" t="s">
         <v>81</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B24" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C24" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="35">
+      <c r="D24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="35">
         <v>1</v>
       </c>
-      <c r="G23" s="29"/>
-      <c r="H23" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B24" s="30"/>
-      <c r="C24" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="39">
-        <v>1</v>
-      </c>
-      <c r="G24" s="42"/>
+      <c r="G24" s="29"/>
       <c r="H24" s="4" t="s">
         <v>63</v>
       </c>
@@ -2441,7 +2425,7 @@
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B25" s="30"/>
       <c r="C25" s="34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>17</v>
@@ -2449,10 +2433,10 @@
       <c r="E25" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="36">
-        <v>0.5</v>
-      </c>
-      <c r="G25" s="11"/>
+      <c r="F25" s="39">
+        <v>1</v>
+      </c>
+      <c r="G25" s="42"/>
       <c r="H25" s="4" t="s">
         <v>63</v>
       </c>
@@ -2460,7 +2444,7 @@
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B26" s="30"/>
       <c r="C26" s="34" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>17</v>
@@ -2468,10 +2452,10 @@
       <c r="E26" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="39">
-        <v>1</v>
-      </c>
-      <c r="G26" s="42"/>
+      <c r="F26" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="G26" s="11"/>
       <c r="H26" s="4" t="s">
         <v>63</v>
       </c>
@@ -2479,7 +2463,7 @@
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B27" s="30"/>
       <c r="C27" s="34" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>17</v>
@@ -2487,8 +2471,8 @@
       <c r="E27" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="36">
-        <v>0.5</v>
+      <c r="F27" s="39">
+        <v>1</v>
       </c>
       <c r="G27" s="42"/>
       <c r="H27" s="4" t="s">
@@ -2496,63 +2480,63 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B28" s="31"/>
-      <c r="C28" s="26" t="s">
+      <c r="B28" s="30"/>
+      <c r="C28" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="G28" s="42"/>
+      <c r="H28" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B29" s="31"/>
+      <c r="C29" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E29" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F28" s="37">
+      <c r="F29" s="37">
         <v>1</v>
       </c>
-      <c r="G28" s="32"/>
-      <c r="H28" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A29" s="96" t="s">
+      <c r="G29" s="32"/>
+      <c r="H29" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A30" s="92" t="s">
         <v>81</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B30" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C30" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="29">
+      <c r="D30" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="29">
         <v>1</v>
       </c>
-      <c r="G29" s="35"/>
-      <c r="H29" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B30" s="30"/>
-      <c r="C30" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" s="39">
-        <v>0.5</v>
-      </c>
-      <c r="G30" s="39"/>
+      <c r="G30" s="35"/>
       <c r="H30" s="4" t="s">
         <v>63</v>
       </c>
@@ -2560,69 +2544,71 @@
     <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B31" s="30"/>
       <c r="C31" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="39">
+        <v>0.5</v>
+      </c>
+      <c r="G31" s="39">
+        <v>0.5</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B32" s="30"/>
+      <c r="C32" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" s="39">
-        <v>0.5</v>
-      </c>
-      <c r="G31" s="39"/>
-      <c r="H31" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B32" s="31"/>
-      <c r="C32" s="26" t="s">
+      <c r="D32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="39">
+        <v>0.5</v>
+      </c>
+      <c r="G32" s="39"/>
+      <c r="H32" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B33" s="31"/>
+      <c r="C33" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="32">
+      <c r="D33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="32">
         <v>1</v>
       </c>
-      <c r="G32" s="37"/>
-      <c r="H32" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A33" s="96" t="s">
+      <c r="G33" s="37"/>
+      <c r="H33" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A34" s="92" t="s">
         <v>81</v>
       </c>
-      <c r="B33" s="27" t="s">
+      <c r="B34" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="C34" s="33" t="s">
         <v>54</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F33" s="35">
-        <v>0.5</v>
-      </c>
-      <c r="G33" s="35"/>
-      <c r="H33" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B34" s="30"/>
-      <c r="C34" s="34" t="s">
-        <v>38</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>17</v>
@@ -2630,10 +2616,10 @@
       <c r="E34" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F34" s="39">
-        <v>0.5</v>
-      </c>
-      <c r="G34" s="39"/>
+      <c r="F34" s="35">
+        <v>0.5</v>
+      </c>
+      <c r="G34" s="35"/>
       <c r="H34" s="4" t="s">
         <v>63</v>
       </c>
@@ -2641,7 +2627,7 @@
     <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B35" s="30"/>
       <c r="C35" s="34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>17</v>
@@ -2658,9 +2644,9 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B36" s="31"/>
-      <c r="C36" s="26" t="s">
-        <v>40</v>
+      <c r="B36" s="30"/>
+      <c r="C36" s="34" t="s">
+        <v>39</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>17</v>
@@ -2668,42 +2654,42 @@
       <c r="E36" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F36" s="37">
-        <v>0.5</v>
-      </c>
-      <c r="G36" s="37"/>
+      <c r="F36" s="39">
+        <v>0.5</v>
+      </c>
+      <c r="G36" s="39"/>
       <c r="H36" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A37" s="96" t="s">
+      <c r="B37" s="31"/>
+      <c r="C37" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="G37" s="37"/>
+      <c r="H37" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A38" s="92" t="s">
         <v>81</v>
       </c>
-      <c r="B37" s="27" t="s">
+      <c r="B38" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C37" s="33" t="s">
+      <c r="C38" s="33" t="s">
         <v>38</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="G37" s="35"/>
-      <c r="H37" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B38" s="30"/>
-      <c r="C38" s="34" t="s">
-        <v>39</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>17</v>
@@ -2711,10 +2697,10 @@
       <c r="E38" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F38" s="38">
-        <v>0.5</v>
-      </c>
-      <c r="G38" s="39"/>
+      <c r="F38" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="G38" s="35"/>
       <c r="H38" s="4" t="s">
         <v>63</v>
       </c>
@@ -2722,7 +2708,7 @@
     <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B39" s="30"/>
       <c r="C39" s="34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>17</v>
@@ -2739,52 +2725,52 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B40" s="31"/>
-      <c r="C40" s="26" t="s">
+      <c r="B40" s="30"/>
+      <c r="C40" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="G40" s="39"/>
+      <c r="H40" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B41" s="31"/>
+      <c r="C41" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="13">
+      <c r="D41" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="13">
         <v>1</v>
       </c>
-      <c r="G40" s="37"/>
-      <c r="H40" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A41" s="96" t="s">
+      <c r="G41" s="37"/>
+      <c r="H41" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A42" s="92" t="s">
         <v>81</v>
       </c>
-      <c r="B41" s="27" t="s">
+      <c r="B42" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="C41" s="33" t="s">
+      <c r="C42" s="33" t="s">
         <v>58</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F41" s="28">
-        <v>1</v>
-      </c>
-      <c r="G41" s="35"/>
-      <c r="H41" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B42" s="30"/>
-      <c r="C42" s="34" t="s">
-        <v>38</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>7</v>
@@ -2792,10 +2778,10 @@
       <c r="E42" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F42" s="38">
-        <v>0.5</v>
-      </c>
-      <c r="G42" s="39"/>
+      <c r="F42" s="28">
+        <v>1</v>
+      </c>
+      <c r="G42" s="35"/>
       <c r="H42" s="4" t="s">
         <v>63</v>
       </c>
@@ -2803,18 +2789,18 @@
     <row r="43" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B43" s="30"/>
       <c r="C43" s="34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="F43" s="38">
         <v>0.5</v>
       </c>
-      <c r="G43" s="36"/>
+      <c r="G43" s="39"/>
       <c r="H43" s="4" t="s">
         <v>63</v>
       </c>
@@ -2822,18 +2808,18 @@
     <row r="44" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B44" s="30"/>
       <c r="C44" s="34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="F44" s="38">
         <v>0.5</v>
       </c>
-      <c r="G44" s="39"/>
+      <c r="G44" s="36"/>
       <c r="H44" s="4" t="s">
         <v>63</v>
       </c>
@@ -2841,26 +2827,26 @@
     <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B45" s="30"/>
       <c r="C45" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F45" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="G45" s="39"/>
+      <c r="H45" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B46" s="30"/>
+      <c r="C46" s="34" t="s">
         <v>59</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="38">
-        <v>0.5</v>
-      </c>
-      <c r="G45" s="36"/>
-      <c r="H45" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B46" s="31"/>
-      <c r="C46" s="26" t="s">
-        <v>32</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>17</v>
@@ -2871,23 +2857,18 @@
       <c r="F46" s="38">
         <v>0.5</v>
       </c>
-      <c r="G46" s="39"/>
+      <c r="G46" s="36"/>
       <c r="H46" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A47" s="96" t="s">
-        <v>81</v>
-      </c>
-      <c r="B47" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="C47" s="33" t="s">
-        <v>34</v>
+      <c r="B47" s="31"/>
+      <c r="C47" s="26" t="s">
+        <v>32</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>10</v>
@@ -2901,9 +2882,14 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B48" s="31"/>
-      <c r="C48" s="26" t="s">
-        <v>35</v>
+      <c r="A48" s="92" t="s">
+        <v>81</v>
+      </c>
+      <c r="B48" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48" s="33" t="s">
+        <v>34</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>7</v>
@@ -2914,186 +2900,186 @@
       <c r="F48" s="38">
         <v>0.5</v>
       </c>
-      <c r="G48" s="37"/>
+      <c r="G48" s="39"/>
       <c r="H48" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A49" s="99" t="s">
+      <c r="B49" s="31"/>
+      <c r="C49" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="G49" s="37"/>
+      <c r="H49" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A50" s="95" t="s">
         <v>85</v>
       </c>
-      <c r="B49" s="27" t="s">
+      <c r="B50" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C49" s="40" t="s">
+      <c r="C50" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="D49" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" s="41"/>
-      <c r="G49" s="39"/>
-      <c r="H49" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A50" s="94" t="s">
+      <c r="D50" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" s="41"/>
+      <c r="G50" s="39"/>
+      <c r="H50" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A51" s="90" t="s">
         <v>82</v>
       </c>
-      <c r="B50" s="51" t="s">
+      <c r="B51" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="C50" s="52" t="s">
+      <c r="C51" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="D50" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" s="53"/>
-      <c r="G50" s="54">
+      <c r="D51" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" s="53"/>
+      <c r="G51" s="54">
         <v>3</v>
       </c>
-      <c r="H50" s="4" t="s">
+      <c r="H51" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A51" s="94" t="s">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A52" s="90" t="s">
         <v>82</v>
       </c>
-      <c r="B51" s="59" t="s">
+      <c r="B52" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="C51" s="57" t="s">
+      <c r="C52" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="D51" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" s="4" t="s">
+      <c r="D52" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="E52" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F51" s="61"/>
-      <c r="G51" s="50"/>
-      <c r="H51" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B52" s="64"/>
-      <c r="C52" s="58" t="s">
-        <v>68</v>
-      </c>
-      <c r="D52" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="E52" s="62" t="s">
-        <v>69</v>
-      </c>
-      <c r="F52" s="63"/>
+      <c r="F52" s="61"/>
       <c r="G52" s="50"/>
       <c r="H52" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A53" s="97" t="s">
-        <v>83</v>
-      </c>
-      <c r="B53" s="59" t="s">
-        <v>70</v>
-      </c>
-      <c r="C53" s="57" t="s">
-        <v>71</v>
+      <c r="B53" s="64"/>
+      <c r="C53" s="58" t="s">
+        <v>68</v>
       </c>
       <c r="D53" s="55" t="s">
         <v>17</v>
       </c>
       <c r="E53" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" s="63">
-        <v>1</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="F53" s="63"/>
       <c r="G53" s="50"/>
       <c r="H53" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B54" s="65"/>
-      <c r="C54" s="66" t="s">
+      <c r="A54" s="93" t="s">
+        <v>83</v>
+      </c>
+      <c r="B54" s="59" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="D54" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="E54" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" s="63">
+        <v>1</v>
+      </c>
+      <c r="G54" s="50"/>
+      <c r="H54" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B55" s="65"/>
+      <c r="C55" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="D54" s="67" t="s">
-        <v>17</v>
-      </c>
-      <c r="E54" s="68" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54">
+      <c r="D55" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E55" s="68" t="s">
+        <v>8</v>
+      </c>
+      <c r="F55">
         <v>1</v>
       </c>
-      <c r="G54" s="36"/>
-      <c r="H54" s="68" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A55" s="97" t="s">
+      <c r="G55" s="36"/>
+      <c r="H55" s="68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A56" s="93" t="s">
         <v>83</v>
       </c>
-      <c r="B55" s="56" t="s">
+      <c r="B56" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="C55" s="75" t="s">
+      <c r="C56" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="D55" s="67" t="s">
-        <v>17</v>
-      </c>
-      <c r="E55" s="68" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" s="69">
-        <v>0.5</v>
-      </c>
-      <c r="G55" s="70"/>
-      <c r="H55" s="68" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B56" s="71"/>
-      <c r="C56" s="76" t="s">
-        <v>74</v>
-      </c>
       <c r="D56" s="67" t="s">
         <v>17</v>
       </c>
       <c r="E56" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="F56" s="79">
-        <v>1</v>
-      </c>
-      <c r="G56" s="80"/>
+      <c r="F56" s="69">
+        <v>0.5</v>
+      </c>
+      <c r="G56" s="70"/>
       <c r="H56" s="68" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B57" s="71"/>
-      <c r="C57" s="76" t="s">
-        <v>75</v>
+      <c r="C57" s="74" t="s">
+        <v>74</v>
       </c>
       <c r="D57" s="67" t="s">
         <v>17</v>
@@ -3101,344 +3087,380 @@
       <c r="E57" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="79">
+      <c r="F57" s="77">
         <v>1</v>
       </c>
-      <c r="G57" s="78"/>
+      <c r="G57" s="78">
+        <v>1</v>
+      </c>
       <c r="H57" s="68" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B58" s="71"/>
-      <c r="C58" s="76" t="s">
+      <c r="C58" s="74" t="s">
+        <v>75</v>
+      </c>
+      <c r="D58" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" s="68" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="77">
+        <v>1</v>
+      </c>
+      <c r="G58" s="76"/>
+      <c r="H58" s="68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B59" s="71"/>
+      <c r="C59" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="D58" s="67" t="s">
-        <v>17</v>
-      </c>
-      <c r="E58" s="68" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58">
+      <c r="D59" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" s="68" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59">
         <v>1</v>
       </c>
-      <c r="G58" s="36"/>
-      <c r="H58" s="68" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A59" s="97" t="s">
+      <c r="G59" s="36"/>
+      <c r="H59" s="68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A60" s="93" t="s">
         <v>83</v>
       </c>
-      <c r="B59" s="56" t="s">
+      <c r="B60" s="56" t="s">
         <v>76</v>
       </c>
-      <c r="C59" s="75" t="s">
+      <c r="C60" s="73" t="s">
         <v>77</v>
       </c>
-      <c r="D59" s="82" t="s">
-        <v>17</v>
-      </c>
-      <c r="E59" s="83" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" s="69">
-        <v>0.5</v>
-      </c>
-      <c r="G59" s="92"/>
-      <c r="H59" s="68" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B60" s="71"/>
-      <c r="C60" s="76" t="s">
-        <v>32</v>
-      </c>
-      <c r="D60" s="86" t="s">
-        <v>17</v>
-      </c>
-      <c r="E60" s="89" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" s="80">
-        <v>0.5</v>
-      </c>
-      <c r="G60" s="87"/>
+      <c r="D60" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="E60" s="80" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" s="69">
+        <v>0.5</v>
+      </c>
+      <c r="G60" s="88">
+        <v>0.5</v>
+      </c>
       <c r="H60" s="68" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B61" s="71"/>
-      <c r="C61" s="76" t="s">
-        <v>59</v>
-      </c>
-      <c r="D61" s="85" t="s">
-        <v>17</v>
-      </c>
-      <c r="E61" s="90" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" s="80">
-        <v>0.5</v>
-      </c>
-      <c r="G61" s="81"/>
+      <c r="C61" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="85" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="78">
+        <v>0.5</v>
+      </c>
+      <c r="G61" s="88">
+        <v>0.5</v>
+      </c>
       <c r="H61" s="68" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B62" s="71"/>
-      <c r="C62" s="76" t="s">
-        <v>53</v>
-      </c>
-      <c r="D62" s="67" t="s">
-        <v>17</v>
-      </c>
-      <c r="E62" s="88" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" s="80">
-        <v>0.5</v>
-      </c>
-      <c r="G62" s="81"/>
+      <c r="C62" s="74" t="s">
+        <v>59</v>
+      </c>
+      <c r="D62" s="82" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="86" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="78">
+        <v>0.5</v>
+      </c>
+      <c r="G62" s="88">
+        <v>0.5</v>
+      </c>
       <c r="H62" s="68" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B63" s="71"/>
-      <c r="C63" s="76" t="s">
-        <v>38</v>
+      <c r="C63" s="74" t="s">
+        <v>53</v>
       </c>
       <c r="D63" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="E63" s="88" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" s="91">
-        <v>0.5</v>
-      </c>
-      <c r="G63" s="72"/>
+      <c r="E63" s="84" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" s="78">
+        <v>0.5</v>
+      </c>
+      <c r="G63" s="88"/>
       <c r="H63" s="68" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B64" s="71"/>
-      <c r="C64" s="76" t="s">
-        <v>40</v>
+      <c r="C64" s="74" t="s">
+        <v>38</v>
       </c>
       <c r="D64" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="E64" s="88" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" s="80">
-        <v>0.5</v>
-      </c>
-      <c r="G64" s="81"/>
+      <c r="E64" s="84" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" s="87">
+        <v>0.5</v>
+      </c>
+      <c r="G64" s="88">
+        <v>0.5</v>
+      </c>
       <c r="H64" s="68" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B65" s="71"/>
-      <c r="C65" s="76" t="s">
+      <c r="C65" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="D65" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" s="84" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" s="78">
+        <v>0.5</v>
+      </c>
+      <c r="G65" s="88">
+        <v>0.5</v>
+      </c>
+      <c r="H65" s="68" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B66" s="71"/>
+      <c r="C66" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="D65" s="67" t="s">
-        <v>17</v>
-      </c>
-      <c r="E65" s="88" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" s="80">
-        <v>0.5</v>
-      </c>
-      <c r="G65" s="81"/>
-      <c r="H65" s="68" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B66" s="73"/>
-      <c r="C66" s="77" t="s">
+      <c r="D66" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="84" t="s">
+        <v>8</v>
+      </c>
+      <c r="F66" s="78">
+        <v>0.5</v>
+      </c>
+      <c r="G66" s="88">
+        <v>0.5</v>
+      </c>
+      <c r="H66" s="68" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B67" s="72"/>
+      <c r="C67" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="D66" s="84" t="s">
-        <v>17</v>
-      </c>
-      <c r="E66" s="89" t="s">
-        <v>8</v>
-      </c>
-      <c r="F66" s="80">
-        <v>0.5</v>
-      </c>
-      <c r="G66" s="74"/>
-      <c r="H66" s="86" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A67" s="98" t="s">
+      <c r="D67" s="81" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" s="85" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" s="78">
+        <v>0.5</v>
+      </c>
+      <c r="G67" s="88">
+        <v>0.5</v>
+      </c>
+      <c r="H67" s="83" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A68" s="94" t="s">
         <v>84</v>
       </c>
-      <c r="B67" s="56" t="s">
+      <c r="B68" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="C67" s="75" t="s">
+      <c r="C68" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="D67" s="84" t="s">
-        <v>17</v>
-      </c>
-      <c r="E67" s="89" t="s">
-        <v>8</v>
-      </c>
-      <c r="F67" s="93"/>
-      <c r="G67" s="93"/>
-      <c r="H67" s="86" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B68" s="71"/>
-      <c r="C68" s="76" t="s">
-        <v>59</v>
-      </c>
-      <c r="D68" s="84" t="s">
-        <v>17</v>
-      </c>
-      <c r="E68" s="89" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" s="80"/>
-      <c r="G68" s="80"/>
-      <c r="H68" s="86" t="s">
-        <v>63</v>
+      <c r="D68" s="81" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" s="85" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" s="89"/>
+      <c r="G68" s="89"/>
+      <c r="H68" s="83" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B69" s="71"/>
-      <c r="C69" s="76" t="s">
-        <v>53</v>
-      </c>
-      <c r="D69" s="84" t="s">
-        <v>17</v>
-      </c>
-      <c r="E69" s="89" t="s">
-        <v>42</v>
-      </c>
-      <c r="F69" s="91"/>
-      <c r="G69" s="91"/>
-      <c r="H69" s="86" t="s">
-        <v>63</v>
+      <c r="C69" s="74" t="s">
+        <v>59</v>
+      </c>
+      <c r="D69" s="81" t="s">
+        <v>17</v>
+      </c>
+      <c r="E69" s="85" t="s">
+        <v>8</v>
+      </c>
+      <c r="F69" s="78"/>
+      <c r="G69" s="78"/>
+      <c r="H69" s="83" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B70" s="71"/>
-      <c r="C70" s="76" t="s">
-        <v>41</v>
-      </c>
-      <c r="D70" s="84" t="s">
-        <v>17</v>
-      </c>
-      <c r="E70" s="89" t="s">
+      <c r="C70" s="74" t="s">
+        <v>53</v>
+      </c>
+      <c r="D70" s="81" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" s="85" t="s">
         <v>42</v>
       </c>
-      <c r="F70" s="80"/>
-      <c r="G70" s="80"/>
-      <c r="H70" s="86" t="s">
+      <c r="F70" s="87"/>
+      <c r="G70" s="87"/>
+      <c r="H70" s="83" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B71" s="71"/>
-      <c r="C71" s="76" t="s">
-        <v>37</v>
-      </c>
-      <c r="D71" s="84" t="s">
-        <v>17</v>
-      </c>
-      <c r="E71" s="89" t="s">
+      <c r="C71" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="D71" s="81" t="s">
+        <v>17</v>
+      </c>
+      <c r="E71" s="85" t="s">
         <v>42</v>
       </c>
-      <c r="F71" s="91"/>
-      <c r="G71" s="91"/>
-      <c r="H71" s="86" t="s">
+      <c r="F71" s="78"/>
+      <c r="G71" s="78"/>
+      <c r="H71" s="83" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B72" s="71"/>
-      <c r="C72" s="76" t="s">
-        <v>25</v>
-      </c>
-      <c r="D72" s="84" t="s">
-        <v>17</v>
-      </c>
-      <c r="E72" s="89" t="s">
-        <v>10</v>
-      </c>
-      <c r="F72" s="80"/>
-      <c r="G72" s="80"/>
-      <c r="H72" s="86" t="s">
+      <c r="C72" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="D72" s="81" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="85" t="s">
+        <v>42</v>
+      </c>
+      <c r="F72" s="87"/>
+      <c r="G72" s="87"/>
+      <c r="H72" s="83" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B73" s="71"/>
-      <c r="C73" s="76" t="s">
+      <c r="C73" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="D73" s="81" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" s="85" t="s">
+        <v>10</v>
+      </c>
+      <c r="F73" s="78"/>
+      <c r="G73" s="78"/>
+      <c r="H73" s="83" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B74" s="71"/>
+      <c r="C74" s="74" t="s">
         <v>58</v>
       </c>
-      <c r="D73" s="84" t="s">
-        <v>17</v>
-      </c>
-      <c r="E73" s="89" t="s">
+      <c r="D74" s="81" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74" s="85" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="80"/>
-      <c r="G73" s="80"/>
-      <c r="H73" s="86" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B74" s="73"/>
-      <c r="C74" s="77" t="s">
+      <c r="F74" s="78"/>
+      <c r="G74" s="78"/>
+      <c r="H74" s="83" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B75" s="72"/>
+      <c r="C75" s="75" t="s">
         <v>77</v>
       </c>
-      <c r="D74" s="84" t="s">
-        <v>17</v>
-      </c>
-      <c r="E74" s="89" t="s">
+      <c r="D75" s="81" t="s">
+        <v>17</v>
+      </c>
+      <c r="E75" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="F74" s="60"/>
-      <c r="G74" s="60"/>
-      <c r="H74" s="86" t="s">
+      <c r="F75" s="60"/>
+      <c r="G75" s="60"/>
+      <c r="H75" s="83" t="s">
         <v>63</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H74" xr:uid="{6668A6B0-AE49-40A9-BDCA-1EF7E08764AB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H75" xr:uid="{6668A6B0-AE49-40A9-BDCA-1EF7E08764AB}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E74" xr:uid="{3F25CF45-EEFF-4838-8184-2DB508A95967}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E75" xr:uid="{3F25CF45-EEFF-4838-8184-2DB508A95967}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D74" xr:uid="{D99FF9D9-52C2-47CC-BC93-4ACF23B2DA2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D75" xr:uid="{D99FF9D9-52C2-47CC-BC93-4ACF23B2DA2A}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opencampus\Documents\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56AC2D5-E7ED-4340-96DE-79ADB098DCE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6E71B4-2EF0-4A51-8193-B56D697900F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="104">
   <si>
     <t>概要</t>
     <rPh sb="0" eb="2">
@@ -506,20 +506,149 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>誰か～</t>
+    <t>完了</t>
+  </si>
+  <si>
+    <t>作業中</t>
+  </si>
+  <si>
+    <t>S</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>工数表</t>
+    <rPh sb="0" eb="3">
+      <t>コウスウヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>全体の工数</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウスウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>項目表</t>
+    <rPh sb="0" eb="2">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>人間表</t>
+    <rPh sb="0" eb="3">
+      <t>ニンゲンヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>全体の人間ごとの工数</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ニンゲン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウスウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>プロト</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アルファ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ベータ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>今日の日付</t>
+    <rPh sb="0" eb="2">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>プロト締め切り</t>
+    <rPh sb="3" eb="4">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アルファ締め切り</t>
+    <rPh sb="4" eb="5">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ベータ締め切り</t>
+    <rPh sb="3" eb="4">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>完全提出</t>
+    <rPh sb="0" eb="4">
+      <t>カンゼンテイシュツ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>残り日数</t>
     <rPh sb="0" eb="1">
-      <t>ダレ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>完了</t>
-  </si>
-  <si>
-    <t>作業中</t>
-  </si>
-  <si>
-    <t>S</t>
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニッスウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>一日の平均コスト</t>
+    <rPh sb="0" eb="2">
+      <t>イチニチ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヘイキン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>のこり一日の平均コスト</t>
+    <rPh sb="3" eb="5">
+      <t>イチニチ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヘイキン</t>
+    </rPh>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -593,7 +722,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -684,14 +813,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="45">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -876,21 +999,6 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color theme="2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="2"/>
-      </top>
       <bottom style="thin">
         <color theme="2"/>
       </bottom>
@@ -1223,6 +1331,67 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2"/>
+      </right>
+      <top style="thin">
+        <color theme="2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2"/>
+      </left>
+      <right style="thin">
+        <color theme="2"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2"/>
+      </left>
+      <right style="thin">
+        <color theme="2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1232,7 +1401,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1273,9 +1442,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1337,134 +1503,130 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="23" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="28" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="27" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="31" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="34" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="38" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="28" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="30" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="31" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="34" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="32" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="35" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="39" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="29" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="32" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
@@ -1480,9 +1642,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1491,11 +1650,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -1831,7 +2043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039B1606-320D-4390-8B98-CE6030BB2FAA}">
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:S75"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="3" width="25.375" bestFit="1" customWidth="1"/>
@@ -1840,14 +2052,18 @@
     <col min="6" max="7" width="9.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.875" customWidth="1"/>
+    <col min="18" max="18" width="21.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="I1" s="46"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="I1" s="44"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1869,13 +2085,23 @@
       <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="45"/>
-      <c r="J2" s="14"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="14" t="s">
+        <v>90</v>
+      </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A3" s="91" t="s">
+      <c r="N2" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="O2" s="38"/>
+      <c r="R2" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="S2" s="38"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A3" s="88" t="s">
         <v>80</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -1890,14 +2116,14 @@
       <c r="E3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="96">
+      <c r="F3" s="92">
         <v>0.5</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I3" s="43"/>
+      <c r="I3" s="42"/>
       <c r="J3" s="15" t="s">
         <v>9</v>
       </c>
@@ -1906,8 +2132,22 @@
         <v>71</v>
       </c>
       <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="N3" s="107" t="s">
+        <v>89</v>
+      </c>
+      <c r="O3" s="38">
+        <f>SUM(F3:F75)</f>
+        <v>51.6</v>
+      </c>
+      <c r="R3" s="107" t="s">
+        <v>92</v>
+      </c>
+      <c r="S3" s="38"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A4" s="88" t="s">
+        <v>80</v>
+      </c>
       <c r="B4" s="9"/>
       <c r="C4" s="8" t="s">
         <v>22</v>
@@ -1918,14 +2158,14 @@
       <c r="E4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="96">
+      <c r="F4" s="92">
         <v>0.5</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I4" s="43"/>
+      <c r="I4" s="42"/>
       <c r="J4" s="16" t="s">
         <v>11</v>
       </c>
@@ -1934,8 +2174,25 @@
         <v>37</v>
       </c>
       <c r="L4" s="3"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="N4" s="101" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="38">
+        <f>SUMIF(E3:E75,"プロト",F3:F75)</f>
+        <v>29</v>
+      </c>
+      <c r="R4" s="108" t="s">
+        <v>80</v>
+      </c>
+      <c r="S4" s="38">
+        <f>SUMIF(A3:A75,"大崎",F3:F75)</f>
+        <v>11.100000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A5" s="88" t="s">
+        <v>80</v>
+      </c>
       <c r="B5" s="9"/>
       <c r="C5" s="8" t="s">
         <v>23</v>
@@ -1946,14 +2203,14 @@
       <c r="E5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="96">
+      <c r="F5" s="92">
         <v>0.5</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I5" s="43"/>
+      <c r="I5" s="42"/>
       <c r="J5" s="17" t="s">
         <v>12</v>
       </c>
@@ -1962,10 +2219,27 @@
         <v>15</v>
       </c>
       <c r="L5" s="3"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="N5" s="102" t="s">
+        <v>12</v>
+      </c>
+      <c r="O5" s="38">
+        <f>SUMIF(E3:E75,"アルファ",F3:F75)</f>
+        <v>8.1</v>
+      </c>
+      <c r="R5" s="109" t="s">
+        <v>81</v>
+      </c>
+      <c r="S5" s="38">
+        <f>SUMIF(A3:A75,"上永",F3:F75)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A6" s="88" t="s">
+        <v>80</v>
+      </c>
       <c r="B6" s="12"/>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>24</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -1974,14 +2248,14 @@
       <c r="E6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="96">
+      <c r="F6" s="92">
         <v>1</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="43"/>
+      <c r="I6" s="42"/>
       <c r="J6" s="18" t="s">
         <v>13</v>
       </c>
@@ -1990,9 +2264,23 @@
         <v>19</v>
       </c>
       <c r="L6" s="3"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A7" s="91" t="s">
+      <c r="N6" s="103" t="s">
+        <v>13</v>
+      </c>
+      <c r="O6" s="38">
+        <f>SUMIF(E3:E75,"ベータ",F3:F75)</f>
+        <v>12.5</v>
+      </c>
+      <c r="R6" s="110" t="s">
+        <v>83</v>
+      </c>
+      <c r="S6" s="38">
+        <f>SUMIF(A3:A75,"川浪",F3:F75)</f>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A7" s="88" t="s">
         <v>80</v>
       </c>
       <c r="B7" s="9" t="s">
@@ -2007,14 +2295,14 @@
       <c r="E7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="96">
+      <c r="F7" s="92">
         <v>1</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I7" s="43"/>
+        <v>86</v>
+      </c>
+      <c r="I7" s="42"/>
       <c r="J7" s="19" t="s">
         <v>14</v>
       </c>
@@ -2026,8 +2314,25 @@
         <f>K7/K3</f>
         <v>0.15492957746478872</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="N7" s="104" t="s">
+        <v>14</v>
+      </c>
+      <c r="O7" s="38">
+        <f>SUMIF(H3:H75,"完了",F3:F75)</f>
+        <v>8.5</v>
+      </c>
+      <c r="R7" s="111" t="s">
+        <v>82</v>
+      </c>
+      <c r="S7" s="38">
+        <f>SUMIF(A3:A75,"佐々木",F3:F75)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A8" s="88" t="s">
+        <v>80</v>
+      </c>
       <c r="B8" s="9"/>
       <c r="C8" s="8" t="s">
         <v>26</v>
@@ -2038,27 +2343,44 @@
       <c r="E8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="96">
+      <c r="F8" s="92">
         <v>0.5</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="43"/>
+      <c r="I8" s="42"/>
       <c r="J8" s="20" t="s">
         <v>15</v>
       </c>
       <c r="K8" s="5">
         <f>COUNTIF(H3:H75,J8)</f>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L8" s="7">
         <f>(K8+K9)/K3</f>
         <v>0.87323943661971826</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="N8" s="105" t="s">
+        <v>15</v>
+      </c>
+      <c r="O8" s="38">
+        <f>SUMIF(H3:H75,"未着手",F3:F75)</f>
+        <v>37.6</v>
+      </c>
+      <c r="R8" s="112" t="s">
+        <v>84</v>
+      </c>
+      <c r="S8" s="38">
+        <f>SUMIF(A3:A75,"誰でも",F3:F75)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A9" s="88" t="s">
+        <v>80</v>
+      </c>
       <c r="B9" s="9"/>
       <c r="C9" s="8" t="s">
         <v>27</v>
@@ -2069,24 +2391,34 @@
       <c r="E9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="96">
+      <c r="F9" s="92">
         <v>0.5</v>
       </c>
       <c r="G9" s="4"/>
-      <c r="H9" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="I9" s="48"/>
+      <c r="H9" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="I9" s="46"/>
       <c r="J9" s="15" t="s">
         <v>18</v>
       </c>
       <c r="K9" s="3">
         <f>COUNTIF(H3:H75,J9)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="N9" s="106" t="s">
+        <v>18</v>
+      </c>
+      <c r="O9" s="38">
+        <f>SUMIF(H3:H75,"作業中",F3:F75)</f>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A10" s="88" t="s">
+        <v>80</v>
+      </c>
       <c r="B10" s="9"/>
       <c r="C10" s="8" t="s">
         <v>28</v>
@@ -2097,22 +2429,26 @@
       <c r="E10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="96">
-        <v>0.5</v>
-      </c>
-      <c r="G10" s="96">
+      <c r="F10" s="92">
+        <v>0.5</v>
+      </c>
+      <c r="G10" s="92">
         <v>0.5</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="I10" s="49"/>
+        <v>85</v>
+      </c>
+      <c r="I10" s="47"/>
       <c r="J10" s="14"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A11" s="11"/>
+      <c r="N10" s="38"/>
+      <c r="O10" s="38"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A11" s="88" t="s">
+        <v>80</v>
+      </c>
       <c r="B11" s="9"/>
       <c r="C11" s="8" t="s">
         <v>29</v>
@@ -2123,27 +2459,31 @@
       <c r="E11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="96">
+      <c r="F11" s="92">
         <v>0.5</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I11" s="43"/>
+      <c r="I11" s="42"/>
       <c r="J11" s="21" t="s">
         <v>19</v>
       </c>
       <c r="K11" s="3">
         <f>SUM(F3:F75)</f>
-        <v>37.6</v>
+        <v>51.6</v>
       </c>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A12" s="11"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A12" s="88" t="s">
+        <v>80</v>
+      </c>
       <c r="B12" s="9"/>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="33" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="4" t="s">
@@ -2152,52 +2492,58 @@
       <c r="E12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="96">
+      <c r="F12" s="92">
         <v>1</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I12" s="44"/>
-      <c r="J12" s="22" t="s">
+      <c r="I12" s="95"/>
+      <c r="J12" s="98" t="s">
         <v>20</v>
       </c>
       <c r="K12" s="3">
         <f>8*K11</f>
-        <v>300.8</v>
+        <v>412.8</v>
       </c>
       <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A13" s="11"/>
-      <c r="B13" s="100"/>
-      <c r="C13" s="26" t="s">
+      <c r="N12" s="38"/>
+      <c r="O12" s="38"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A13" s="88" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="94"/>
+      <c r="C13" s="25" t="s">
         <v>77</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="96">
+      <c r="F13" s="92">
         <v>0.5</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="98"/>
-      <c r="J13" s="99"/>
-      <c r="K13" s="98"/>
-      <c r="L13" s="98"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A14" s="91" t="s">
+      <c r="I13" s="96"/>
+      <c r="J13" s="114"/>
+      <c r="K13" s="115"/>
+      <c r="L13" s="115"/>
+      <c r="M13" s="116"/>
+      <c r="N13" s="100"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A14" s="88" t="s">
         <v>80</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="22" t="s">
         <v>33</v>
       </c>
       <c r="C14" s="8" t="s">
@@ -2209,16 +2555,31 @@
       <c r="E14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="96">
+      <c r="F14" s="92">
         <v>0.2</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B15" s="24"/>
+      <c r="I14" s="113"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="L14" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="M14" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="N14" s="97"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A15" s="88" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="23"/>
       <c r="C15" s="8" t="s">
         <v>35</v>
       </c>
@@ -2228,17 +2589,35 @@
       <c r="E15" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="96">
+      <c r="F15" s="92">
         <v>0.2</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B16" s="25"/>
-      <c r="C16" s="26" t="s">
+      <c r="J15" s="108" t="s">
+        <v>80</v>
+      </c>
+      <c r="K15" s="38">
+        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"プロト")</f>
+        <v>5.5</v>
+      </c>
+      <c r="L15" s="38">
+        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"アルファ")</f>
+        <v>2.1</v>
+      </c>
+      <c r="M15" s="38">
+        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"ベータ")</f>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A16" s="88" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="24"/>
+      <c r="C16" s="25" t="s">
         <v>36</v>
       </c>
       <c r="D16" s="4" t="s">
@@ -2247,22 +2626,37 @@
       <c r="E16" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="96">
+      <c r="F16" s="92">
         <v>0.2</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A17" s="91" t="s">
+      <c r="J16" s="109" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16" s="38">
+        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"プロト")</f>
+        <v>8</v>
+      </c>
+      <c r="L16" s="38">
+        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"アルファ")</f>
+        <v>4</v>
+      </c>
+      <c r="M16" s="38">
+        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"ベータ")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A17" s="88" t="s">
         <v>80</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="32" t="s">
         <v>38</v>
       </c>
       <c r="D17" s="4" t="s">
@@ -2271,17 +2665,35 @@
       <c r="E17" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="97">
-        <v>0.5</v>
-      </c>
-      <c r="G17" s="35"/>
+      <c r="F17" s="93">
+        <v>0.5</v>
+      </c>
+      <c r="G17" s="34"/>
       <c r="H17" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B18" s="30"/>
-      <c r="C18" s="34" t="s">
+      <c r="J17" s="110" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="38">
+        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"プロト")</f>
+        <v>9.5</v>
+      </c>
+      <c r="L17" s="38">
+        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"アルファ")</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="38">
+        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"ベータ")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A18" s="88" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="29"/>
+      <c r="C18" s="33" t="s">
         <v>39</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -2290,17 +2702,35 @@
       <c r="E18" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="97">
-        <v>0.5</v>
-      </c>
-      <c r="G18" s="39"/>
+      <c r="F18" s="93">
+        <v>0.5</v>
+      </c>
+      <c r="G18" s="38"/>
       <c r="H18" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B19" s="30"/>
-      <c r="C19" s="34" t="s">
+      <c r="J18" s="111" t="s">
+        <v>82</v>
+      </c>
+      <c r="K18" s="38">
+        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"プロト")</f>
+        <v>4</v>
+      </c>
+      <c r="L18" s="38">
+        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"アルファ")</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="38">
+        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"ベータ")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A19" s="88" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="29"/>
+      <c r="C19" s="33" t="s">
         <v>40</v>
       </c>
       <c r="D19" s="4" t="s">
@@ -2309,17 +2739,35 @@
       <c r="E19" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="97">
-        <v>0.5</v>
-      </c>
-      <c r="G19" s="37"/>
+      <c r="F19" s="93">
+        <v>0.5</v>
+      </c>
+      <c r="G19" s="36"/>
       <c r="H19" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B20" s="31"/>
-      <c r="C20" s="26" t="s">
+      <c r="J19" s="112" t="s">
+        <v>84</v>
+      </c>
+      <c r="K19" s="38">
+        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"プロト")</f>
+        <v>2</v>
+      </c>
+      <c r="L19" s="38">
+        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"アルファ")</f>
+        <v>2</v>
+      </c>
+      <c r="M19" s="38">
+        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"ベータ")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A20" s="88" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="25" t="s">
         <v>32</v>
       </c>
       <c r="D20" s="4" t="s">
@@ -2328,22 +2776,22 @@
       <c r="E20" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="97">
-        <v>0.5</v>
-      </c>
-      <c r="G20" s="37"/>
+      <c r="F20" s="93">
+        <v>0.5</v>
+      </c>
+      <c r="G20" s="36"/>
       <c r="H20" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A21" s="91" t="s">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A21" s="88" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="32" t="s">
         <v>38</v>
       </c>
       <c r="D21" s="4" t="s">
@@ -2352,17 +2800,29 @@
       <c r="E21" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="97">
-        <v>0.5</v>
-      </c>
-      <c r="G21" s="35"/>
+      <c r="F21" s="93">
+        <v>0.5</v>
+      </c>
+      <c r="G21" s="34"/>
       <c r="H21" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B22" s="30"/>
-      <c r="C22" s="34" t="s">
+      <c r="L21" t="s">
+        <v>101</v>
+      </c>
+      <c r="M21" t="s">
+        <v>102</v>
+      </c>
+      <c r="N21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A22" s="88" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="29"/>
+      <c r="C22" s="33" t="s">
         <v>39</v>
       </c>
       <c r="D22" s="4" t="s">
@@ -2371,17 +2831,27 @@
       <c r="E22" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="97">
-        <v>0.5</v>
-      </c>
-      <c r="G22" s="39"/>
+      <c r="F22" s="93">
+        <v>0.5</v>
+      </c>
+      <c r="G22" s="38"/>
       <c r="H22" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B23" s="31"/>
-      <c r="C23" s="26" t="s">
+      <c r="J22" t="s">
+        <v>96</v>
+      </c>
+      <c r="K22" s="117">
+        <f ca="1">TODAY()</f>
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A23" s="88" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="25" t="s">
         <v>40</v>
       </c>
       <c r="D23" s="4" t="s">
@@ -2390,22 +2860,44 @@
       <c r="E23" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="97">
-        <v>0.5</v>
-      </c>
-      <c r="G23" s="37"/>
+      <c r="F23" s="93">
+        <v>0.5</v>
+      </c>
+      <c r="G23" s="36"/>
       <c r="H23" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A24" s="92" t="s">
+      <c r="J23" t="s">
+        <v>97</v>
+      </c>
+      <c r="K23" s="117">
+        <v>46072</v>
+      </c>
+      <c r="L23">
+        <f ca="1">DATE(2026,2,19) - TODAY()</f>
+        <v>7</v>
+      </c>
+      <c r="M23">
+        <f ca="1">SUMIF(E3:E75,"プロト",F3:F75) / L23</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="N23">
+        <f ca="1">(SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"未着手") + SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"作業中"))/ L23</f>
+        <v>2.9285714285714284</v>
+      </c>
+      <c r="O23">
+        <f xml:space="preserve"> 29 / 15</f>
+        <v>1.9333333333333333</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A24" s="89" t="s">
         <v>81</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="33" t="s">
+      <c r="C24" s="32" t="s">
         <v>44</v>
       </c>
       <c r="D24" s="4" t="s">
@@ -2414,17 +2906,42 @@
       <c r="E24" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="35">
+      <c r="F24" s="34">
         <v>1</v>
       </c>
-      <c r="G24" s="29"/>
+      <c r="G24" s="28"/>
       <c r="H24" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B25" s="30"/>
-      <c r="C25" s="34" t="s">
+      <c r="J24" t="s">
+        <v>98</v>
+      </c>
+      <c r="K24" s="117">
+        <v>46082</v>
+      </c>
+      <c r="L24">
+        <f ca="1">DATE(2026,3,1) - TODAY()</f>
+        <v>17</v>
+      </c>
+      <c r="M24">
+        <f ca="1">SUMIF(E3:E75,"アルファ",F3:F75) / L24</f>
+        <v>0.47647058823529409</v>
+      </c>
+      <c r="N24">
+        <f ca="1">(SUMIFS(F3:F75,E3:E75,"アルファ",H3:H75,"未着手") + SUMIFS(F3:F75,E3:E75,"アルファ",H3:H75,"作業中"))/ L24</f>
+        <v>0.47647058823529409</v>
+      </c>
+      <c r="O24">
+        <f xml:space="preserve"> 8.1 / 10</f>
+        <v>0.80999999999999994</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A25" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="29"/>
+      <c r="C25" s="33" t="s">
         <v>45</v>
       </c>
       <c r="D25" s="4" t="s">
@@ -2433,17 +2950,42 @@
       <c r="E25" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="39">
+      <c r="F25" s="38">
         <v>1</v>
       </c>
-      <c r="G25" s="42"/>
+      <c r="G25" s="41"/>
       <c r="H25" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B26" s="30"/>
-      <c r="C26" s="34" t="s">
+      <c r="J25" t="s">
+        <v>99</v>
+      </c>
+      <c r="K25" s="117">
+        <v>46091</v>
+      </c>
+      <c r="L25">
+        <f ca="1">DATE(2026,3,10) - TODAY()</f>
+        <v>26</v>
+      </c>
+      <c r="M25">
+        <f ca="1">SUMIF(E3:E75,"ベータ",F3:F75) / L25</f>
+        <v>0.48076923076923078</v>
+      </c>
+      <c r="N25">
+        <f ca="1">(SUMIFS(F3:F75,E3:E75,"ベータ",H3:H75,"未着手") + SUMIFS(F3:F75,E3:E75,"ベータ",H3:H75,"作業中"))/ L25</f>
+        <v>0.48076923076923078</v>
+      </c>
+      <c r="O25">
+        <f xml:space="preserve"> 12.5 / 9</f>
+        <v>1.3888888888888888</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A26" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="29"/>
+      <c r="C26" s="33" t="s">
         <v>46</v>
       </c>
       <c r="D26" s="4" t="s">
@@ -2452,17 +2994,38 @@
       <c r="E26" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="36">
+      <c r="F26" s="35">
         <v>0.5</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B27" s="30"/>
-      <c r="C27" s="34" t="s">
+      <c r="J26" t="s">
+        <v>100</v>
+      </c>
+      <c r="K26" s="117">
+        <v>46096</v>
+      </c>
+      <c r="L26">
+        <f ca="1">DATE(2026,3,15) - TODAY()</f>
+        <v>31</v>
+      </c>
+      <c r="M26">
+        <f ca="1">SUM(F3:F75) / L26</f>
+        <v>1.6645161290322581</v>
+      </c>
+      <c r="N26">
+        <f ca="1" xml:space="preserve"> (O3 - O7) / L26</f>
+        <v>1.3903225806451613</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A27" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="29"/>
+      <c r="C27" s="33" t="s">
         <v>28</v>
       </c>
       <c r="D27" s="4" t="s">
@@ -2471,17 +3034,20 @@
       <c r="E27" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="39">
+      <c r="F27" s="38">
         <v>1</v>
       </c>
-      <c r="G27" s="42"/>
+      <c r="G27" s="41"/>
       <c r="H27" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B28" s="30"/>
-      <c r="C28" s="34" t="s">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A28" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="29"/>
+      <c r="C28" s="33" t="s">
         <v>47</v>
       </c>
       <c r="D28" s="4" t="s">
@@ -2490,17 +3056,20 @@
       <c r="E28" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="36">
-        <v>0.5</v>
-      </c>
-      <c r="G28" s="42"/>
+      <c r="F28" s="35">
+        <v>0.5</v>
+      </c>
+      <c r="G28" s="41"/>
       <c r="H28" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B29" s="31"/>
-      <c r="C29" s="26" t="s">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A29" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="30"/>
+      <c r="C29" s="25" t="s">
         <v>48</v>
       </c>
       <c r="D29" s="4" t="s">
@@ -2509,22 +3078,22 @@
       <c r="E29" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F29" s="37">
+      <c r="F29" s="36">
         <v>1</v>
       </c>
-      <c r="G29" s="32"/>
+      <c r="G29" s="31"/>
       <c r="H29" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A30" s="92" t="s">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A30" s="89" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="33" t="s">
+      <c r="C30" s="32" t="s">
         <v>30</v>
       </c>
       <c r="D30" s="4" t="s">
@@ -2533,17 +3102,20 @@
       <c r="E30" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="29">
+      <c r="F30" s="28">
         <v>1</v>
       </c>
-      <c r="G30" s="35"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B31" s="30"/>
-      <c r="C31" s="34" t="s">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A31" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" s="29"/>
+      <c r="C31" s="33" t="s">
         <v>50</v>
       </c>
       <c r="D31" s="4" t="s">
@@ -2552,19 +3124,22 @@
       <c r="E31" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F31" s="39">
-        <v>0.5</v>
-      </c>
-      <c r="G31" s="39">
+      <c r="F31" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="G31" s="38">
         <v>0.5</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B32" s="30"/>
-      <c r="C32" s="34" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A32" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" s="29"/>
+      <c r="C32" s="33" t="s">
         <v>51</v>
       </c>
       <c r="D32" s="4" t="s">
@@ -2573,17 +3148,20 @@
       <c r="E32" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="39">
-        <v>0.5</v>
-      </c>
-      <c r="G32" s="39"/>
+      <c r="F32" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="G32" s="38"/>
       <c r="H32" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B33" s="31"/>
-      <c r="C33" s="26" t="s">
+      <c r="A33" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="30"/>
+      <c r="C33" s="25" t="s">
         <v>52</v>
       </c>
       <c r="D33" s="4" t="s">
@@ -2592,22 +3170,22 @@
       <c r="E33" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F33" s="32">
+      <c r="F33" s="31">
         <v>1</v>
       </c>
-      <c r="G33" s="37"/>
+      <c r="G33" s="36"/>
       <c r="H33" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A34" s="92" t="s">
+      <c r="A34" s="89" t="s">
         <v>81</v>
       </c>
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="33" t="s">
+      <c r="C34" s="32" t="s">
         <v>54</v>
       </c>
       <c r="D34" s="4" t="s">
@@ -2616,17 +3194,20 @@
       <c r="E34" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F34" s="35">
-        <v>0.5</v>
-      </c>
-      <c r="G34" s="35"/>
+      <c r="F34" s="34">
+        <v>0.5</v>
+      </c>
+      <c r="G34" s="34"/>
       <c r="H34" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B35" s="30"/>
-      <c r="C35" s="34" t="s">
+      <c r="A35" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="29"/>
+      <c r="C35" s="33" t="s">
         <v>38</v>
       </c>
       <c r="D35" s="4" t="s">
@@ -2635,17 +3216,20 @@
       <c r="E35" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F35" s="39">
-        <v>0.5</v>
-      </c>
-      <c r="G35" s="39"/>
+      <c r="F35" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="G35" s="38"/>
       <c r="H35" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B36" s="30"/>
-      <c r="C36" s="34" t="s">
+      <c r="A36" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="29"/>
+      <c r="C36" s="33" t="s">
         <v>39</v>
       </c>
       <c r="D36" s="4" t="s">
@@ -2654,17 +3238,20 @@
       <c r="E36" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F36" s="39">
-        <v>0.5</v>
-      </c>
-      <c r="G36" s="39"/>
+      <c r="F36" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="G36" s="38"/>
       <c r="H36" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B37" s="31"/>
-      <c r="C37" s="26" t="s">
+      <c r="A37" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" s="30"/>
+      <c r="C37" s="25" t="s">
         <v>40</v>
       </c>
       <c r="D37" s="4" t="s">
@@ -2673,22 +3260,22 @@
       <c r="E37" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F37" s="37">
-        <v>0.5</v>
-      </c>
-      <c r="G37" s="37"/>
+      <c r="F37" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="G37" s="36"/>
       <c r="H37" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A38" s="92" t="s">
+      <c r="A38" s="89" t="s">
         <v>81</v>
       </c>
-      <c r="B38" s="27" t="s">
+      <c r="B38" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C38" s="33" t="s">
+      <c r="C38" s="32" t="s">
         <v>38</v>
       </c>
       <c r="D38" s="4" t="s">
@@ -2697,17 +3284,20 @@
       <c r="E38" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F38" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="G38" s="35"/>
+      <c r="F38" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="G38" s="34"/>
       <c r="H38" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B39" s="30"/>
-      <c r="C39" s="34" t="s">
+      <c r="A39" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B39" s="29"/>
+      <c r="C39" s="33" t="s">
         <v>39</v>
       </c>
       <c r="D39" s="4" t="s">
@@ -2716,17 +3306,20 @@
       <c r="E39" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F39" s="38">
-        <v>0.5</v>
-      </c>
-      <c r="G39" s="39"/>
+      <c r="F39" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="G39" s="38"/>
       <c r="H39" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B40" s="30"/>
-      <c r="C40" s="34" t="s">
+      <c r="A40" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" s="29"/>
+      <c r="C40" s="33" t="s">
         <v>40</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -2735,17 +3328,20 @@
       <c r="E40" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F40" s="38">
-        <v>0.5</v>
-      </c>
-      <c r="G40" s="39"/>
+      <c r="F40" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="G40" s="38"/>
       <c r="H40" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B41" s="31"/>
-      <c r="C41" s="26" t="s">
+      <c r="A41" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="30"/>
+      <c r="C41" s="25" t="s">
         <v>56</v>
       </c>
       <c r="D41" s="4" t="s">
@@ -2757,19 +3353,19 @@
       <c r="F41" s="13">
         <v>1</v>
       </c>
-      <c r="G41" s="37"/>
+      <c r="G41" s="36"/>
       <c r="H41" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A42" s="92" t="s">
+      <c r="A42" s="89" t="s">
         <v>81</v>
       </c>
-      <c r="B42" s="27" t="s">
+      <c r="B42" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C42" s="33" t="s">
+      <c r="C42" s="32" t="s">
         <v>58</v>
       </c>
       <c r="D42" s="4" t="s">
@@ -2778,17 +3374,20 @@
       <c r="E42" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F42" s="28">
+      <c r="F42" s="27">
         <v>1</v>
       </c>
-      <c r="G42" s="35"/>
+      <c r="G42" s="34"/>
       <c r="H42" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B43" s="30"/>
-      <c r="C43" s="34" t="s">
+      <c r="A43" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B43" s="29"/>
+      <c r="C43" s="33" t="s">
         <v>38</v>
       </c>
       <c r="D43" s="4" t="s">
@@ -2797,17 +3396,20 @@
       <c r="E43" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F43" s="38">
-        <v>0.5</v>
-      </c>
-      <c r="G43" s="39"/>
+      <c r="F43" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="G43" s="38"/>
       <c r="H43" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B44" s="30"/>
-      <c r="C44" s="34" t="s">
+      <c r="A44" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" s="29"/>
+      <c r="C44" s="33" t="s">
         <v>39</v>
       </c>
       <c r="D44" s="4" t="s">
@@ -2816,17 +3418,20 @@
       <c r="E44" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F44" s="38">
-        <v>0.5</v>
-      </c>
-      <c r="G44" s="36"/>
+      <c r="F44" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="G44" s="35"/>
       <c r="H44" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B45" s="30"/>
-      <c r="C45" s="34" t="s">
+      <c r="A45" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B45" s="29"/>
+      <c r="C45" s="33" t="s">
         <v>40</v>
       </c>
       <c r="D45" s="4" t="s">
@@ -2835,17 +3440,20 @@
       <c r="E45" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F45" s="38">
-        <v>0.5</v>
-      </c>
-      <c r="G45" s="39"/>
+      <c r="F45" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="G45" s="38"/>
       <c r="H45" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B46" s="30"/>
-      <c r="C46" s="34" t="s">
+      <c r="A46" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B46" s="29"/>
+      <c r="C46" s="33" t="s">
         <v>59</v>
       </c>
       <c r="D46" s="4" t="s">
@@ -2854,17 +3462,20 @@
       <c r="E46" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F46" s="38">
-        <v>0.5</v>
-      </c>
-      <c r="G46" s="36"/>
+      <c r="F46" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="G46" s="35"/>
       <c r="H46" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B47" s="31"/>
-      <c r="C47" s="26" t="s">
+      <c r="A47" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B47" s="30"/>
+      <c r="C47" s="25" t="s">
         <v>32</v>
       </c>
       <c r="D47" s="4" t="s">
@@ -2873,22 +3484,22 @@
       <c r="E47" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F47" s="38">
-        <v>0.5</v>
-      </c>
-      <c r="G47" s="39"/>
+      <c r="F47" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="G47" s="38"/>
       <c r="H47" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A48" s="92" t="s">
+      <c r="A48" s="89" t="s">
         <v>81</v>
       </c>
-      <c r="B48" s="27" t="s">
+      <c r="B48" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="33" t="s">
+      <c r="C48" s="32" t="s">
         <v>34</v>
       </c>
       <c r="D48" s="4" t="s">
@@ -2897,17 +3508,20 @@
       <c r="E48" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F48" s="38">
-        <v>0.5</v>
-      </c>
-      <c r="G48" s="39"/>
+      <c r="F48" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="G48" s="38"/>
       <c r="H48" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B49" s="31"/>
-      <c r="C49" s="26" t="s">
+      <c r="A49" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="30"/>
+      <c r="C49" s="25" t="s">
         <v>35</v>
       </c>
       <c r="D49" s="4" t="s">
@@ -2916,22 +3530,22 @@
       <c r="E49" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F49" s="38">
-        <v>0.5</v>
-      </c>
-      <c r="G49" s="37"/>
+      <c r="F49" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="G49" s="36"/>
       <c r="H49" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A50" s="95" t="s">
-        <v>85</v>
-      </c>
-      <c r="B50" s="27" t="s">
+      <c r="A50" s="87" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="C50" s="40" t="s">
+      <c r="C50" s="39" t="s">
         <v>62</v>
       </c>
       <c r="D50" s="4" t="s">
@@ -2940,20 +3554,22 @@
       <c r="E50" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F50" s="41"/>
-      <c r="G50" s="39"/>
+      <c r="F50" s="40">
+        <v>1</v>
+      </c>
+      <c r="G50" s="38"/>
       <c r="H50" s="4" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A51" s="90" t="s">
+      <c r="A51" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="B51" s="51" t="s">
+      <c r="B51" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="52" t="s">
+      <c r="C51" s="50" t="s">
         <v>65</v>
       </c>
       <c r="D51" s="4" t="s">
@@ -2962,488 +3578,567 @@
       <c r="E51" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F51" s="53"/>
-      <c r="G51" s="54">
+      <c r="F51" s="51">
         <v>3</v>
       </c>
+      <c r="G51" s="52">
+        <v>3</v>
+      </c>
       <c r="H51" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A52" s="90" t="s">
+      <c r="A52" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="B52" s="59" t="s">
+      <c r="B52" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="C52" s="57" t="s">
+      <c r="C52" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="D52" s="55" t="s">
+      <c r="D52" s="53" t="s">
         <v>17</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F52" s="61"/>
-      <c r="G52" s="50"/>
+      <c r="F52" s="58">
+        <v>1</v>
+      </c>
+      <c r="G52" s="48"/>
       <c r="H52" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B53" s="64"/>
-      <c r="C53" s="58" t="s">
+      <c r="A53" s="87" t="s">
+        <v>82</v>
+      </c>
+      <c r="B53" s="61"/>
+      <c r="C53" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="D53" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="E53" s="62" t="s">
+      <c r="D53" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" s="59" t="s">
         <v>69</v>
       </c>
-      <c r="F53" s="63"/>
-      <c r="G53" s="50"/>
+      <c r="F53" s="58">
+        <v>1</v>
+      </c>
+      <c r="G53" s="48"/>
       <c r="H53" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A54" s="93" t="s">
+      <c r="A54" s="90" t="s">
         <v>83</v>
       </c>
-      <c r="B54" s="59" t="s">
+      <c r="B54" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="C54" s="57" t="s">
+      <c r="C54" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="D54" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="E54" s="62" t="s">
+      <c r="D54" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="E54" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="63">
+      <c r="F54" s="60">
         <v>1</v>
       </c>
-      <c r="G54" s="50"/>
+      <c r="G54" s="48"/>
       <c r="H54" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B55" s="65"/>
-      <c r="C55" s="66" t="s">
+      <c r="A55" s="90" t="s">
+        <v>83</v>
+      </c>
+      <c r="B55" s="62"/>
+      <c r="C55" s="63" t="s">
         <v>72</v>
       </c>
-      <c r="D55" s="67" t="s">
-        <v>17</v>
-      </c>
-      <c r="E55" s="68" t="s">
+      <c r="D55" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E55" s="65" t="s">
         <v>8</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
-      <c r="G55" s="36"/>
-      <c r="H55" s="68" t="s">
+      <c r="G55" s="35"/>
+      <c r="H55" s="65" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A56" s="93" t="s">
+      <c r="A56" s="90" t="s">
         <v>83</v>
       </c>
-      <c r="B56" s="56" t="s">
+      <c r="B56" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="C56" s="73" t="s">
+      <c r="C56" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="D56" s="67" t="s">
-        <v>17</v>
-      </c>
-      <c r="E56" s="68" t="s">
+      <c r="D56" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E56" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F56" s="69">
-        <v>0.5</v>
-      </c>
-      <c r="G56" s="70"/>
-      <c r="H56" s="68" t="s">
-        <v>87</v>
+      <c r="F56" s="66">
+        <v>0.5</v>
+      </c>
+      <c r="G56" s="67"/>
+      <c r="H56" s="65" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B57" s="71"/>
-      <c r="C57" s="74" t="s">
+      <c r="A57" s="90" t="s">
+        <v>83</v>
+      </c>
+      <c r="B57" s="68"/>
+      <c r="C57" s="71" t="s">
         <v>74</v>
       </c>
-      <c r="D57" s="67" t="s">
-        <v>17</v>
-      </c>
-      <c r="E57" s="68" t="s">
+      <c r="D57" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="77">
+      <c r="F57" s="74">
         <v>1</v>
       </c>
-      <c r="G57" s="78">
+      <c r="G57" s="75">
         <v>1</v>
       </c>
-      <c r="H57" s="68" t="s">
-        <v>86</v>
+      <c r="H57" s="65" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B58" s="71"/>
-      <c r="C58" s="74" t="s">
+      <c r="A58" s="90" t="s">
+        <v>83</v>
+      </c>
+      <c r="B58" s="68"/>
+      <c r="C58" s="71" t="s">
         <v>75</v>
       </c>
-      <c r="D58" s="67" t="s">
-        <v>17</v>
-      </c>
-      <c r="E58" s="68" t="s">
+      <c r="D58" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F58" s="77">
+      <c r="F58" s="74">
         <v>1</v>
       </c>
-      <c r="G58" s="76"/>
-      <c r="H58" s="68" t="s">
+      <c r="G58" s="73"/>
+      <c r="H58" s="65" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B59" s="71"/>
-      <c r="C59" s="74" t="s">
+      <c r="A59" s="90" t="s">
+        <v>83</v>
+      </c>
+      <c r="B59" s="68"/>
+      <c r="C59" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="D59" s="67" t="s">
-        <v>17</v>
-      </c>
-      <c r="E59" s="68" t="s">
+      <c r="D59" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" s="65" t="s">
         <v>8</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
-      <c r="G59" s="36"/>
-      <c r="H59" s="68" t="s">
+      <c r="G59" s="35"/>
+      <c r="H59" s="65" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A60" s="93" t="s">
+      <c r="A60" s="90" t="s">
         <v>83</v>
       </c>
-      <c r="B60" s="56" t="s">
+      <c r="B60" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="C60" s="73" t="s">
+      <c r="C60" s="70" t="s">
         <v>77</v>
       </c>
-      <c r="D60" s="79" t="s">
-        <v>17</v>
-      </c>
-      <c r="E60" s="80" t="s">
+      <c r="D60" s="76" t="s">
+        <v>17</v>
+      </c>
+      <c r="E60" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="F60" s="69">
-        <v>0.5</v>
-      </c>
-      <c r="G60" s="88">
-        <v>0.5</v>
-      </c>
-      <c r="H60" s="68" t="s">
+      <c r="F60" s="66">
+        <v>0.5</v>
+      </c>
+      <c r="G60" s="85">
+        <v>0.5</v>
+      </c>
+      <c r="H60" s="65" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A61" s="90" t="s">
+        <v>83</v>
+      </c>
+      <c r="B61" s="68"/>
+      <c r="C61" s="71" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" s="80" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="82" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="75">
+        <v>0.5</v>
+      </c>
+      <c r="G61" s="85">
+        <v>0.5</v>
+      </c>
+      <c r="H61" s="65" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A62" s="90" t="s">
+        <v>83</v>
+      </c>
+      <c r="B62" s="68"/>
+      <c r="C62" s="71" t="s">
+        <v>59</v>
+      </c>
+      <c r="D62" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="83" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="75">
+        <v>0.5</v>
+      </c>
+      <c r="G62" s="85">
+        <v>0.5</v>
+      </c>
+      <c r="H62" s="65" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A63" s="90" t="s">
+        <v>83</v>
+      </c>
+      <c r="B63" s="68"/>
+      <c r="C63" s="71" t="s">
+        <v>53</v>
+      </c>
+      <c r="D63" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63" s="81" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" s="75">
+        <v>0.5</v>
+      </c>
+      <c r="G63" s="85"/>
+      <c r="H63" s="65" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A64" s="90" t="s">
+        <v>83</v>
+      </c>
+      <c r="B64" s="68"/>
+      <c r="C64" s="71" t="s">
+        <v>38</v>
+      </c>
+      <c r="D64" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="81" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" s="84">
+        <v>0.5</v>
+      </c>
+      <c r="G64" s="85">
+        <v>0.5</v>
+      </c>
+      <c r="H64" s="65" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A65" s="90" t="s">
+        <v>83</v>
+      </c>
+      <c r="B65" s="68"/>
+      <c r="C65" s="71" t="s">
+        <v>40</v>
+      </c>
+      <c r="D65" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" s="81" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" s="75">
+        <v>0.5</v>
+      </c>
+      <c r="G65" s="85">
+        <v>0.5</v>
+      </c>
+      <c r="H65" s="65" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A66" s="90" t="s">
+        <v>83</v>
+      </c>
+      <c r="B66" s="68"/>
+      <c r="C66" s="71" t="s">
+        <v>78</v>
+      </c>
+      <c r="D66" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="81" t="s">
+        <v>8</v>
+      </c>
+      <c r="F66" s="75">
+        <v>0.5</v>
+      </c>
+      <c r="G66" s="85">
+        <v>0.5</v>
+      </c>
+      <c r="H66" s="65" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A67" s="90" t="s">
+        <v>83</v>
+      </c>
+      <c r="B67" s="69"/>
+      <c r="C67" s="72" t="s">
+        <v>43</v>
+      </c>
+      <c r="D67" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" s="82" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" s="75">
+        <v>0.5</v>
+      </c>
+      <c r="G67" s="85">
+        <v>0.5</v>
+      </c>
+      <c r="H67" s="80" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A68" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="B68" s="54" t="s">
+        <v>79</v>
+      </c>
+      <c r="C68" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="D68" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" s="82" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" s="86">
+        <v>1</v>
+      </c>
+      <c r="G68" s="86"/>
+      <c r="H68" s="80" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B61" s="71"/>
-      <c r="C61" s="74" t="s">
-        <v>32</v>
-      </c>
-      <c r="D61" s="83" t="s">
-        <v>17</v>
-      </c>
-      <c r="E61" s="85" t="s">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A69" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="B69" s="68"/>
+      <c r="C69" s="71" t="s">
+        <v>59</v>
+      </c>
+      <c r="D69" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="E69" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="F61" s="78">
-        <v>0.5</v>
-      </c>
-      <c r="G61" s="88">
-        <v>0.5</v>
-      </c>
-      <c r="H61" s="68" t="s">
+      <c r="F69" s="86">
+        <v>1</v>
+      </c>
+      <c r="G69" s="75"/>
+      <c r="H69" s="80" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B62" s="71"/>
-      <c r="C62" s="74" t="s">
-        <v>59</v>
-      </c>
-      <c r="D62" s="82" t="s">
-        <v>17</v>
-      </c>
-      <c r="E62" s="86" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" s="78">
-        <v>0.5</v>
-      </c>
-      <c r="G62" s="88">
-        <v>0.5</v>
-      </c>
-      <c r="H62" s="68" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B63" s="71"/>
-      <c r="C63" s="74" t="s">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A70" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="B70" s="68"/>
+      <c r="C70" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="D63" s="67" t="s">
-        <v>17</v>
-      </c>
-      <c r="E63" s="84" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" s="78">
-        <v>0.5</v>
-      </c>
-      <c r="G63" s="88"/>
-      <c r="H63" s="68" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B64" s="71"/>
-      <c r="C64" s="74" t="s">
-        <v>38</v>
-      </c>
-      <c r="D64" s="67" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" s="84" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" s="87">
-        <v>0.5</v>
-      </c>
-      <c r="G64" s="88">
-        <v>0.5</v>
-      </c>
-      <c r="H64" s="68" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B65" s="71"/>
-      <c r="C65" s="74" t="s">
-        <v>40</v>
-      </c>
-      <c r="D65" s="67" t="s">
-        <v>17</v>
-      </c>
-      <c r="E65" s="84" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" s="78">
-        <v>0.5</v>
-      </c>
-      <c r="G65" s="88">
-        <v>0.5</v>
-      </c>
-      <c r="H65" s="68" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B66" s="71"/>
-      <c r="C66" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="D66" s="67" t="s">
-        <v>17</v>
-      </c>
-      <c r="E66" s="84" t="s">
-        <v>8</v>
-      </c>
-      <c r="F66" s="78">
-        <v>0.5</v>
-      </c>
-      <c r="G66" s="88">
-        <v>0.5</v>
-      </c>
-      <c r="H66" s="68" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B67" s="72"/>
-      <c r="C67" s="75" t="s">
-        <v>43</v>
-      </c>
-      <c r="D67" s="81" t="s">
-        <v>17</v>
-      </c>
-      <c r="E67" s="85" t="s">
-        <v>8</v>
-      </c>
-      <c r="F67" s="78">
-        <v>0.5</v>
-      </c>
-      <c r="G67" s="88">
-        <v>0.5</v>
-      </c>
-      <c r="H67" s="83" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A68" s="94" t="s">
+      <c r="D70" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" s="82" t="s">
+        <v>42</v>
+      </c>
+      <c r="F70" s="86">
+        <v>1</v>
+      </c>
+      <c r="G70" s="84"/>
+      <c r="H70" s="80" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A71" s="91" t="s">
         <v>84</v>
       </c>
-      <c r="B68" s="56" t="s">
-        <v>79</v>
-      </c>
-      <c r="C68" s="73" t="s">
-        <v>32</v>
-      </c>
-      <c r="D68" s="81" t="s">
-        <v>17</v>
-      </c>
-      <c r="E68" s="85" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" s="89"/>
-      <c r="G68" s="89"/>
-      <c r="H68" s="83" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B69" s="71"/>
-      <c r="C69" s="74" t="s">
-        <v>59</v>
-      </c>
-      <c r="D69" s="81" t="s">
-        <v>17</v>
-      </c>
-      <c r="E69" s="85" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" s="78"/>
-      <c r="G69" s="78"/>
-      <c r="H69" s="83" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B70" s="71"/>
-      <c r="C70" s="74" t="s">
-        <v>53</v>
-      </c>
-      <c r="D70" s="81" t="s">
-        <v>17</v>
-      </c>
-      <c r="E70" s="85" t="s">
+      <c r="B71" s="68"/>
+      <c r="C71" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="D71" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="E71" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="F70" s="87"/>
-      <c r="G70" s="87"/>
-      <c r="H70" s="83" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B71" s="71"/>
-      <c r="C71" s="74" t="s">
-        <v>41</v>
-      </c>
-      <c r="D71" s="81" t="s">
-        <v>17</v>
-      </c>
-      <c r="E71" s="85" t="s">
+      <c r="F71" s="86">
+        <v>1</v>
+      </c>
+      <c r="G71" s="75"/>
+      <c r="H71" s="80" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A72" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="B72" s="68"/>
+      <c r="C72" s="71" t="s">
+        <v>37</v>
+      </c>
+      <c r="D72" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="F71" s="78"/>
-      <c r="G71" s="78"/>
-      <c r="H71" s="83" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B72" s="71"/>
-      <c r="C72" s="74" t="s">
-        <v>37</v>
-      </c>
-      <c r="D72" s="81" t="s">
-        <v>17</v>
-      </c>
-      <c r="E72" s="85" t="s">
+      <c r="F72" s="86">
+        <v>1</v>
+      </c>
+      <c r="G72" s="84"/>
+      <c r="H72" s="80" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A73" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="B73" s="68"/>
+      <c r="C73" s="71" t="s">
+        <v>25</v>
+      </c>
+      <c r="D73" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" s="82" t="s">
+        <v>10</v>
+      </c>
+      <c r="F73" s="86">
+        <v>1</v>
+      </c>
+      <c r="G73" s="75"/>
+      <c r="H73" s="80" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A74" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="B74" s="68"/>
+      <c r="C74" s="71" t="s">
+        <v>58</v>
+      </c>
+      <c r="D74" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="F72" s="87"/>
-      <c r="G72" s="87"/>
-      <c r="H72" s="83" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B73" s="71"/>
-      <c r="C73" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="D73" s="81" t="s">
-        <v>17</v>
-      </c>
-      <c r="E73" s="85" t="s">
+      <c r="F74" s="86">
+        <v>1</v>
+      </c>
+      <c r="G74" s="75"/>
+      <c r="H74" s="80" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A75" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="B75" s="69"/>
+      <c r="C75" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D75" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="E75" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="F73" s="78"/>
-      <c r="G73" s="78"/>
-      <c r="H73" s="83" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B74" s="71"/>
-      <c r="C74" s="74" t="s">
-        <v>58</v>
-      </c>
-      <c r="D74" s="81" t="s">
-        <v>17</v>
-      </c>
-      <c r="E74" s="85" t="s">
-        <v>42</v>
-      </c>
-      <c r="F74" s="78"/>
-      <c r="G74" s="78"/>
-      <c r="H74" s="83" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B75" s="72"/>
-      <c r="C75" s="75" t="s">
-        <v>77</v>
-      </c>
-      <c r="D75" s="81" t="s">
-        <v>17</v>
-      </c>
-      <c r="E75" s="85" t="s">
-        <v>10</v>
-      </c>
-      <c r="F75" s="60"/>
-      <c r="G75" s="60"/>
-      <c r="H75" s="83" t="s">
+      <c r="F75" s="38">
+        <v>1</v>
+      </c>
+      <c r="G75" s="99"/>
+      <c r="H75" s="80" t="s">
         <v>63</v>
       </c>
     </row>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opencampus\Documents\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yongy\git\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6E71B4-2EF0-4A51-8193-B56D697900F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B965D4E3-469C-4E52-BEA8-F57D0EC8E5AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="0" yWindow="1110" windowWidth="28485" windowHeight="14370" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -2119,9 +2116,11 @@
       <c r="F3" s="92">
         <v>0.5</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="92">
+        <v>0.5</v>
+      </c>
       <c r="H3" s="4" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="I3" s="42"/>
       <c r="J3" s="15" t="s">
@@ -2253,7 +2252,7 @@
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="I6" s="42"/>
       <c r="J6" s="18" t="s">
@@ -2308,18 +2307,18 @@
       </c>
       <c r="K7" s="5">
         <f>COUNTIF(H3:H75,J7)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L7" s="6">
         <f>K7/K3</f>
-        <v>0.15492957746478872</v>
+        <v>0.19718309859154928</v>
       </c>
       <c r="N7" s="104" t="s">
         <v>14</v>
       </c>
       <c r="O7" s="38">
         <f>SUMIF(H3:H75,"完了",F3:F75)</f>
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="R7" s="111" t="s">
         <v>82</v>
@@ -2356,18 +2355,18 @@
       </c>
       <c r="K8" s="5">
         <f>COUNTIF(H3:H75,J8)</f>
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="L8" s="7">
         <f>(K8+K9)/K3</f>
-        <v>0.87323943661971826</v>
+        <v>0.83098591549295775</v>
       </c>
       <c r="N8" s="105" t="s">
         <v>15</v>
       </c>
       <c r="O8" s="38">
         <f>SUMIF(H3:H75,"未着手",F3:F75)</f>
-        <v>37.6</v>
+        <v>35.1</v>
       </c>
       <c r="R8" s="112" t="s">
         <v>84</v>
@@ -2404,7 +2403,7 @@
       </c>
       <c r="K9" s="3">
         <f>COUNTIF(H3:H75,J9)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L9" s="3"/>
       <c r="N9" s="106" t="s">
@@ -2412,7 +2411,7 @@
       </c>
       <c r="O9" s="38">
         <f>SUMIF(H3:H75,"作業中",F3:F75)</f>
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.4">
@@ -2462,9 +2461,11 @@
       <c r="F11" s="92">
         <v>0.5</v>
       </c>
-      <c r="G11" s="4"/>
+      <c r="G11" s="92">
+        <v>0.25</v>
+      </c>
       <c r="H11" s="4" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="I11" s="42"/>
       <c r="J11" s="21" t="s">
@@ -2528,9 +2529,11 @@
       <c r="F13" s="92">
         <v>0.5</v>
       </c>
-      <c r="G13" s="4"/>
+      <c r="G13" s="92">
+        <v>0.25</v>
+      </c>
       <c r="H13" s="4" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="I13" s="96"/>
       <c r="J13" s="114"/>
@@ -2843,7 +2846,7 @@
       </c>
       <c r="K22" s="117">
         <f ca="1">TODAY()</f>
-        <v>46065</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.4">
@@ -2875,15 +2878,15 @@
       </c>
       <c r="L23">
         <f ca="1">DATE(2026,2,19) - TODAY()</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M23">
         <f ca="1">SUMIF(E3:E75,"プロト",F3:F75) / L23</f>
-        <v>4.1428571428571432</v>
+        <v>7.25</v>
       </c>
       <c r="N23">
         <f ca="1">(SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"未着手") + SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"作業中"))/ L23</f>
-        <v>2.9285714285714284</v>
+        <v>4.75</v>
       </c>
       <c r="O23">
         <f xml:space="preserve"> 29 / 15</f>
@@ -2921,15 +2924,15 @@
       </c>
       <c r="L24">
         <f ca="1">DATE(2026,3,1) - TODAY()</f>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M24">
         <f ca="1">SUMIF(E3:E75,"アルファ",F3:F75) / L24</f>
-        <v>0.47647058823529409</v>
+        <v>0.57857142857142851</v>
       </c>
       <c r="N24">
         <f ca="1">(SUMIFS(F3:F75,E3:E75,"アルファ",H3:H75,"未着手") + SUMIFS(F3:F75,E3:E75,"アルファ",H3:H75,"作業中"))/ L24</f>
-        <v>0.47647058823529409</v>
+        <v>0.57857142857142851</v>
       </c>
       <c r="O24">
         <f xml:space="preserve"> 8.1 / 10</f>
@@ -2965,15 +2968,15 @@
       </c>
       <c r="L25">
         <f ca="1">DATE(2026,3,10) - TODAY()</f>
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M25">
         <f ca="1">SUMIF(E3:E75,"ベータ",F3:F75) / L25</f>
-        <v>0.48076923076923078</v>
+        <v>0.54347826086956519</v>
       </c>
       <c r="N25">
         <f ca="1">(SUMIFS(F3:F75,E3:E75,"ベータ",H3:H75,"未着手") + SUMIFS(F3:F75,E3:E75,"ベータ",H3:H75,"作業中"))/ L25</f>
-        <v>0.48076923076923078</v>
+        <v>0.54347826086956519</v>
       </c>
       <c r="O25">
         <f xml:space="preserve"> 12.5 / 9</f>
@@ -3009,15 +3012,15 @@
       </c>
       <c r="L26">
         <f ca="1">DATE(2026,3,15) - TODAY()</f>
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M26">
         <f ca="1">SUM(F3:F75) / L26</f>
-        <v>1.6645161290322581</v>
+        <v>1.842857142857143</v>
       </c>
       <c r="N26">
         <f ca="1" xml:space="preserve"> (O3 - O7) / L26</f>
-        <v>1.3903225806451613</v>
+        <v>1.4857142857142858</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.4">

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yongy\git\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B965D4E3-469C-4E52-BEA8-F57D0EC8E5AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{361D8617-9CCD-4B22-A5F3-E105A1B7FB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1110" windowWidth="28485" windowHeight="14370" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="I4" s="42"/>
       <c r="J4" s="16" t="s">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="I5" s="42"/>
       <c r="J5" s="17" t="s">
@@ -2307,18 +2307,18 @@
       </c>
       <c r="K7" s="5">
         <f>COUNTIF(H3:H75,J7)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L7" s="6">
         <f>K7/K3</f>
-        <v>0.19718309859154928</v>
+        <v>0.21126760563380281</v>
       </c>
       <c r="N7" s="104" t="s">
         <v>14</v>
       </c>
       <c r="O7" s="38">
         <f>SUMIF(H3:H75,"完了",F3:F75)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R7" s="111" t="s">
         <v>82</v>
@@ -2355,18 +2355,18 @@
       </c>
       <c r="K8" s="5">
         <f>COUNTIF(H3:H75,J8)</f>
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L8" s="7">
         <f>(K8+K9)/K3</f>
-        <v>0.83098591549295775</v>
+        <v>0.81690140845070425</v>
       </c>
       <c r="N8" s="105" t="s">
         <v>15</v>
       </c>
       <c r="O8" s="38">
         <f>SUMIF(H3:H75,"未着手",F3:F75)</f>
-        <v>35.1</v>
+        <v>34.6</v>
       </c>
       <c r="R8" s="112" t="s">
         <v>84</v>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="45" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="I9" s="46"/>
       <c r="J9" s="15" t="s">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="O9" s="38">
         <f>SUMIF(H3:H75,"作業中",F3:F75)</f>
-        <v>6.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.4">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="N23">
         <f ca="1">(SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"未着手") + SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"作業中"))/ L23</f>
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="O23">
         <f xml:space="preserve"> 29 / 15</f>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="N26">
         <f ca="1" xml:space="preserve"> (O3 - O7) / L26</f>
-        <v>1.4857142857142858</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.4">
@@ -3986,9 +3986,11 @@
       <c r="F68" s="86">
         <v>1</v>
       </c>
-      <c r="G68" s="86"/>
+      <c r="G68" s="86">
+        <v>1</v>
+      </c>
       <c r="H68" s="80" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.4">

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yongy\git\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{361D8617-9CCD-4B22-A5F3-E105A1B7FB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E554C8-C732-45A9-9E17-D17F04CB65A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1110" windowWidth="28485" windowHeight="14370" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -2116,11 +2116,9 @@
       <c r="F3" s="92">
         <v>0.5</v>
       </c>
-      <c r="G3" s="92">
-        <v>0.5</v>
-      </c>
+      <c r="G3" s="92"/>
       <c r="H3" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I3" s="42"/>
       <c r="J3" s="15" t="s">
@@ -2355,7 +2353,7 @@
       </c>
       <c r="K8" s="5">
         <f>COUNTIF(H3:H75,J8)</f>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L8" s="7">
         <f>(K8+K9)/K3</f>
@@ -2366,7 +2364,7 @@
       </c>
       <c r="O8" s="38">
         <f>SUMIF(H3:H75,"未着手",F3:F75)</f>
-        <v>34.6</v>
+        <v>34.1</v>
       </c>
       <c r="R8" s="112" t="s">
         <v>84</v>
@@ -2393,9 +2391,11 @@
       <c r="F9" s="92">
         <v>0.5</v>
       </c>
-      <c r="G9" s="4"/>
+      <c r="G9" s="92">
+        <v>0.25</v>
+      </c>
       <c r="H9" s="45" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="I9" s="46"/>
       <c r="J9" s="15" t="s">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="K9" s="3">
         <f>COUNTIF(H3:H75,J9)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L9" s="3"/>
       <c r="N9" s="106" t="s">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="O9" s="38">
         <f>SUMIF(H3:H75,"作業中",F3:F75)</f>
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.4">

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yongy\git\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0205h\Desktop\github\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E554C8-C732-45A9-9E17-D17F04CB65A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715C941B-742C-4D34-ABB4-A580AFFA6B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1110" windowWidth="28485" windowHeight="14370" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2305,18 +2305,18 @@
       </c>
       <c r="K7" s="5">
         <f>COUNTIF(H3:H75,J7)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L7" s="6">
         <f>K7/K3</f>
-        <v>0.21126760563380281</v>
+        <v>0.22535211267605634</v>
       </c>
       <c r="N7" s="104" t="s">
         <v>14</v>
       </c>
       <c r="O7" s="38">
         <f>SUMIF(H3:H75,"完了",F3:F75)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R7" s="111" t="s">
         <v>82</v>
@@ -2353,18 +2353,18 @@
       </c>
       <c r="K8" s="5">
         <f>COUNTIF(H3:H75,J8)</f>
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L8" s="7">
         <f>(K8+K9)/K3</f>
-        <v>0.81690140845070425</v>
+        <v>0.80281690140845074</v>
       </c>
       <c r="N8" s="105" t="s">
         <v>15</v>
       </c>
       <c r="O8" s="38">
         <f>SUMIF(H3:H75,"未着手",F3:F75)</f>
-        <v>34.1</v>
+        <v>32.6</v>
       </c>
       <c r="R8" s="112" t="s">
         <v>84</v>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="O9" s="38">
         <f>SUMIF(H3:H75,"作業中",F3:F75)</f>
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.4">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="K22" s="117">
         <f ca="1">TODAY()</f>
-        <v>46068</v>
+        <v>46069</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.4">
@@ -2878,15 +2878,15 @@
       </c>
       <c r="L23">
         <f ca="1">DATE(2026,2,19) - TODAY()</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M23">
         <f ca="1">SUMIF(E3:E75,"プロト",F3:F75) / L23</f>
-        <v>7.25</v>
+        <v>9.6666666666666661</v>
       </c>
       <c r="N23">
         <f ca="1">(SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"未着手") + SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"作業中"))/ L23</f>
-        <v>4.5</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="O23">
         <f xml:space="preserve"> 29 / 15</f>
@@ -2924,15 +2924,15 @@
       </c>
       <c r="L24">
         <f ca="1">DATE(2026,3,1) - TODAY()</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M24">
         <f ca="1">SUMIF(E3:E75,"アルファ",F3:F75) / L24</f>
-        <v>0.57857142857142851</v>
+        <v>0.62307692307692308</v>
       </c>
       <c r="N24">
         <f ca="1">(SUMIFS(F3:F75,E3:E75,"アルファ",H3:H75,"未着手") + SUMIFS(F3:F75,E3:E75,"アルファ",H3:H75,"作業中"))/ L24</f>
-        <v>0.57857142857142851</v>
+        <v>0.62307692307692308</v>
       </c>
       <c r="O24">
         <f xml:space="preserve"> 8.1 / 10</f>
@@ -2968,15 +2968,15 @@
       </c>
       <c r="L25">
         <f ca="1">DATE(2026,3,10) - TODAY()</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M25">
         <f ca="1">SUMIF(E3:E75,"ベータ",F3:F75) / L25</f>
-        <v>0.54347826086956519</v>
+        <v>0.56818181818181823</v>
       </c>
       <c r="N25">
         <f ca="1">(SUMIFS(F3:F75,E3:E75,"ベータ",H3:H75,"未着手") + SUMIFS(F3:F75,E3:E75,"ベータ",H3:H75,"作業中"))/ L25</f>
-        <v>0.54347826086956519</v>
+        <v>0.56818181818181823</v>
       </c>
       <c r="O25">
         <f xml:space="preserve"> 12.5 / 9</f>
@@ -3012,15 +3012,15 @@
       </c>
       <c r="L26">
         <f ca="1">DATE(2026,3,15) - TODAY()</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M26">
         <f ca="1">SUM(F3:F75) / L26</f>
-        <v>1.842857142857143</v>
+        <v>1.9111111111111112</v>
       </c>
       <c r="N26">
         <f ca="1" xml:space="preserve"> (O3 - O7) / L26</f>
-        <v>1.45</v>
+        <v>1.4666666666666668</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.4">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="G56" s="67"/>
       <c r="H56" s="65" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.4">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="G58" s="73"/>
       <c r="H58" s="65" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.4">
@@ -3770,9 +3770,11 @@
       <c r="F59">
         <v>1</v>
       </c>
-      <c r="G59" s="35"/>
+      <c r="G59" s="35">
+        <v>1</v>
+      </c>
       <c r="H59" s="65" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.4">

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0205h\Desktop\github\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715C941B-742C-4D34-ABB4-A580AFFA6B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF77C910-623F-4695-89AF-8DBA822DA9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2041,26 +2041,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039B1606-320D-4390-8B98-CE6030BB2FAA}">
   <dimension ref="A1:S75"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="3" width="25.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="25.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.19921875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.8984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.19921875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.875" customWidth="1"/>
+    <col min="17" max="17" width="8.8984375" customWidth="1"/>
     <col min="18" max="18" width="21.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
       <c r="I1" s="44"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="S2" s="38"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A3" s="88" t="s">
         <v>80</v>
       </c>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="S3" s="38"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A4" s="88" t="s">
         <v>80</v>
       </c>
@@ -2186,7 +2186,7 @@
         <v>11.100000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A5" s="88" t="s">
         <v>80</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A6" s="88" t="s">
         <v>80</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A7" s="88" t="s">
         <v>80</v>
       </c>
@@ -2305,18 +2305,18 @@
       </c>
       <c r="K7" s="5">
         <f>COUNTIF(H3:H75,J7)</f>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L7" s="6">
         <f>K7/K3</f>
-        <v>0.22535211267605634</v>
+        <v>0.29577464788732394</v>
       </c>
       <c r="N7" s="104" t="s">
         <v>14</v>
       </c>
       <c r="O7" s="38">
         <f>SUMIF(H3:H75,"完了",F3:F75)</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R7" s="111" t="s">
         <v>82</v>
@@ -2326,7 +2326,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A8" s="88" t="s">
         <v>80</v>
       </c>
@@ -2353,18 +2353,18 @@
       </c>
       <c r="K8" s="5">
         <f>COUNTIF(H3:H75,J8)</f>
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L8" s="7">
         <f>(K8+K9)/K3</f>
-        <v>0.80281690140845074</v>
+        <v>0.73239436619718312</v>
       </c>
       <c r="N8" s="105" t="s">
         <v>15</v>
       </c>
       <c r="O8" s="38">
         <f>SUMIF(H3:H75,"未着手",F3:F75)</f>
-        <v>32.6</v>
+        <v>27.6</v>
       </c>
       <c r="R8" s="112" t="s">
         <v>84</v>
@@ -2374,7 +2374,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A9" s="88" t="s">
         <v>80</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A10" s="88" t="s">
         <v>80</v>
       </c>
@@ -2444,7 +2444,7 @@
       <c r="N10" s="38"/>
       <c r="O10" s="38"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A11" s="88" t="s">
         <v>80</v>
       </c>
@@ -2479,7 +2479,7 @@
       <c r="N11" s="38"/>
       <c r="O11" s="38"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A12" s="88" t="s">
         <v>80</v>
       </c>
@@ -2512,7 +2512,7 @@
       <c r="N12" s="38"/>
       <c r="O12" s="38"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A13" s="88" t="s">
         <v>80</v>
       </c>
@@ -2542,7 +2542,7 @@
       <c r="M13" s="116"/>
       <c r="N13" s="100"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A14" s="88" t="s">
         <v>80</v>
       </c>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="N14" s="97"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A15" s="88" t="s">
         <v>80</v>
       </c>
@@ -2615,7 +2615,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A16" s="88" t="s">
         <v>80</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A17" s="88" t="s">
         <v>80</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A18" s="88" t="s">
         <v>80</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A19" s="88" t="s">
         <v>80</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A20" s="88" t="s">
         <v>80</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A21" s="88" t="s">
         <v>80</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A22" s="88" t="s">
         <v>80</v>
       </c>
@@ -2846,10 +2846,10 @@
       </c>
       <c r="K22" s="117">
         <f ca="1">TODAY()</f>
-        <v>46069</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A23" s="88" t="s">
         <v>80</v>
       </c>
@@ -2878,22 +2878,22 @@
       </c>
       <c r="L23">
         <f ca="1">DATE(2026,2,19) - TODAY()</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M23">
         <f ca="1">SUMIF(E3:E75,"プロト",F3:F75) / L23</f>
-        <v>9.6666666666666661</v>
+        <v>14.5</v>
       </c>
       <c r="N23">
         <f ca="1">(SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"未着手") + SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"作業中"))/ L23</f>
-        <v>5.666666666666667</v>
+        <v>6</v>
       </c>
       <c r="O23">
         <f xml:space="preserve"> 29 / 15</f>
         <v>1.9333333333333333</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A24" s="89" t="s">
         <v>81</v>
       </c>
@@ -2912,9 +2912,11 @@
       <c r="F24" s="34">
         <v>1</v>
       </c>
-      <c r="G24" s="28"/>
+      <c r="G24" s="28">
+        <v>1</v>
+      </c>
       <c r="H24" s="4" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="J24" t="s">
         <v>98</v>
@@ -2924,22 +2926,22 @@
       </c>
       <c r="L24">
         <f ca="1">DATE(2026,3,1) - TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M24">
         <f ca="1">SUMIF(E3:E75,"アルファ",F3:F75) / L24</f>
-        <v>0.62307692307692308</v>
+        <v>0.67499999999999993</v>
       </c>
       <c r="N24">
         <f ca="1">(SUMIFS(F3:F75,E3:E75,"アルファ",H3:H75,"未着手") + SUMIFS(F3:F75,E3:E75,"アルファ",H3:H75,"作業中"))/ L24</f>
-        <v>0.62307692307692308</v>
+        <v>0.67499999999999993</v>
       </c>
       <c r="O24">
         <f xml:space="preserve"> 8.1 / 10</f>
         <v>0.80999999999999994</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A25" s="89" t="s">
         <v>81</v>
       </c>
@@ -2956,9 +2958,11 @@
       <c r="F25" s="38">
         <v>1</v>
       </c>
-      <c r="G25" s="41"/>
+      <c r="G25" s="41">
+        <v>1</v>
+      </c>
       <c r="H25" s="4" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="J25" t="s">
         <v>99</v>
@@ -2968,22 +2972,22 @@
       </c>
       <c r="L25">
         <f ca="1">DATE(2026,3,10) - TODAY()</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M25">
         <f ca="1">SUMIF(E3:E75,"ベータ",F3:F75) / L25</f>
-        <v>0.56818181818181823</v>
+        <v>0.59523809523809523</v>
       </c>
       <c r="N25">
         <f ca="1">(SUMIFS(F3:F75,E3:E75,"ベータ",H3:H75,"未着手") + SUMIFS(F3:F75,E3:E75,"ベータ",H3:H75,"作業中"))/ L25</f>
-        <v>0.56818181818181823</v>
+        <v>0.59523809523809523</v>
       </c>
       <c r="O25">
         <f xml:space="preserve"> 12.5 / 9</f>
         <v>1.3888888888888888</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A26" s="89" t="s">
         <v>81</v>
       </c>
@@ -3012,18 +3016,18 @@
       </c>
       <c r="L26">
         <f ca="1">DATE(2026,3,15) - TODAY()</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M26">
         <f ca="1">SUM(F3:F75) / L26</f>
-        <v>1.9111111111111112</v>
+        <v>1.9846153846153847</v>
       </c>
       <c r="N26">
         <f ca="1" xml:space="preserve"> (O3 - O7) / L26</f>
-        <v>1.4666666666666668</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.4">
+        <v>1.3307692307692309</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A27" s="89" t="s">
         <v>81</v>
       </c>
@@ -3040,12 +3044,14 @@
       <c r="F27" s="38">
         <v>1</v>
       </c>
-      <c r="G27" s="41"/>
+      <c r="G27" s="41">
+        <v>1</v>
+      </c>
       <c r="H27" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A28" s="89" t="s">
         <v>81</v>
       </c>
@@ -3059,7 +3065,7 @@
       <c r="E28" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="35">
+      <c r="F28" s="38">
         <v>0.5</v>
       </c>
       <c r="G28" s="41"/>
@@ -3067,7 +3073,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A29" s="89" t="s">
         <v>81</v>
       </c>
@@ -3081,15 +3087,15 @@
       <c r="E29" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F29" s="36">
+      <c r="F29" s="35">
         <v>1</v>
       </c>
-      <c r="G29" s="31"/>
+      <c r="G29" s="41"/>
       <c r="H29" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A30" s="89" t="s">
         <v>81</v>
       </c>
@@ -3108,12 +3114,14 @@
       <c r="F30" s="28">
         <v>1</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="34">
+        <v>2</v>
+      </c>
       <c r="H30" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A31" s="89" t="s">
         <v>81</v>
       </c>
@@ -3137,7 +3145,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A32" s="89" t="s">
         <v>81</v>
       </c>
@@ -3159,7 +3167,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" s="89" t="s">
         <v>81</v>
       </c>
@@ -3176,12 +3184,14 @@
       <c r="F33" s="31">
         <v>1</v>
       </c>
-      <c r="G33" s="36"/>
+      <c r="G33" s="36">
+        <v>1</v>
+      </c>
       <c r="H33" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" s="89" t="s">
         <v>81</v>
       </c>
@@ -3205,7 +3215,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" s="89" t="s">
         <v>81</v>
       </c>
@@ -3227,7 +3237,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" s="89" t="s">
         <v>81</v>
       </c>
@@ -3249,7 +3259,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" s="89" t="s">
         <v>81</v>
       </c>
@@ -3271,7 +3281,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" s="89" t="s">
         <v>81</v>
       </c>
@@ -3295,7 +3305,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" s="89" t="s">
         <v>81</v>
       </c>
@@ -3317,7 +3327,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" s="89" t="s">
         <v>81</v>
       </c>
@@ -3339,7 +3349,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" s="89" t="s">
         <v>81</v>
       </c>
@@ -3361,7 +3371,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" s="89" t="s">
         <v>81</v>
       </c>
@@ -3385,7 +3395,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" s="89" t="s">
         <v>81</v>
       </c>
@@ -3407,7 +3417,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" s="89" t="s">
         <v>81</v>
       </c>
@@ -3429,7 +3439,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" s="89" t="s">
         <v>81</v>
       </c>
@@ -3451,7 +3461,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" s="89" t="s">
         <v>81</v>
       </c>
@@ -3473,7 +3483,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A47" s="89" t="s">
         <v>81</v>
       </c>
@@ -3495,7 +3505,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48" s="89" t="s">
         <v>81</v>
       </c>
@@ -3519,7 +3529,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49" s="89" t="s">
         <v>81</v>
       </c>
@@ -3541,7 +3551,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A50" s="87" t="s">
         <v>82</v>
       </c>
@@ -3565,7 +3575,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="87" t="s">
         <v>82</v>
       </c>
@@ -3591,7 +3601,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="87" t="s">
         <v>82</v>
       </c>
@@ -3615,7 +3625,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="87" t="s">
         <v>82</v>
       </c>
@@ -3637,7 +3647,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" s="90" t="s">
         <v>83</v>
       </c>
@@ -3661,7 +3671,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" s="90" t="s">
         <v>83</v>
       </c>
@@ -3683,7 +3693,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" s="90" t="s">
         <v>83</v>
       </c>
@@ -3707,7 +3717,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" s="90" t="s">
         <v>83</v>
       </c>
@@ -3731,7 +3741,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" s="90" t="s">
         <v>83</v>
       </c>
@@ -3753,7 +3763,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" s="90" t="s">
         <v>83</v>
       </c>
@@ -3777,7 +3787,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" s="90" t="s">
         <v>83</v>
       </c>
@@ -3803,7 +3813,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" s="90" t="s">
         <v>83</v>
       </c>
@@ -3827,7 +3837,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A62" s="90" t="s">
         <v>83</v>
       </c>
@@ -3851,7 +3861,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63" s="90" t="s">
         <v>83</v>
       </c>
@@ -3873,7 +3883,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A64" s="90" t="s">
         <v>83</v>
       </c>
@@ -3897,7 +3907,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" s="90" t="s">
         <v>83</v>
       </c>
@@ -3921,7 +3931,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" s="90" t="s">
         <v>83</v>
       </c>
@@ -3945,7 +3955,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" s="90" t="s">
         <v>83</v>
       </c>
@@ -3969,7 +3979,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" s="91" t="s">
         <v>84</v>
       </c>
@@ -3995,7 +4005,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A69" s="91" t="s">
         <v>84</v>
       </c>
@@ -4017,7 +4027,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A70" s="91" t="s">
         <v>84</v>
       </c>
@@ -4039,7 +4049,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A71" s="91" t="s">
         <v>84</v>
       </c>
@@ -4061,7 +4071,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A72" s="91" t="s">
         <v>84</v>
       </c>
@@ -4083,7 +4093,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" s="91" t="s">
         <v>84</v>
       </c>
@@ -4105,7 +4115,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74" s="91" t="s">
         <v>84</v>
       </c>
@@ -4127,7 +4137,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75" s="91" t="s">
         <v>84</v>
       </c>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yongy\git\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF77C910-623F-4695-89AF-8DBA822DA9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED8AA5C-6673-4E48-A79B-CD7164C5143A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="0" yWindow="1110" windowWidth="28485" windowHeight="14370" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2041,26 +2041,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039B1606-320D-4390-8B98-CE6030BB2FAA}">
   <dimension ref="A1:S75"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="3" width="25.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="25.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.8984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.25" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.8984375" customWidth="1"/>
+    <col min="17" max="17" width="8.875" customWidth="1"/>
     <col min="18" max="18" width="21.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.4">
       <c r="I1" s="44"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="S2" s="38"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A3" s="88" t="s">
         <v>80</v>
       </c>
@@ -2116,9 +2116,11 @@
       <c r="F3" s="92">
         <v>0.5</v>
       </c>
-      <c r="G3" s="92"/>
+      <c r="G3" s="92">
+        <v>0.5</v>
+      </c>
       <c r="H3" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I3" s="42"/>
       <c r="J3" s="15" t="s">
@@ -2141,7 +2143,7 @@
       </c>
       <c r="S3" s="38"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A4" s="88" t="s">
         <v>80</v>
       </c>
@@ -2158,9 +2160,11 @@
       <c r="F4" s="92">
         <v>0.5</v>
       </c>
-      <c r="G4" s="4"/>
+      <c r="G4" s="92">
+        <v>0.5</v>
+      </c>
       <c r="H4" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I4" s="42"/>
       <c r="J4" s="16" t="s">
@@ -2186,7 +2190,7 @@
         <v>11.100000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A5" s="88" t="s">
         <v>80</v>
       </c>
@@ -2203,9 +2207,11 @@
       <c r="F5" s="92">
         <v>0.5</v>
       </c>
-      <c r="G5" s="4"/>
+      <c r="G5" s="92">
+        <v>0.5</v>
+      </c>
       <c r="H5" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I5" s="42"/>
       <c r="J5" s="17" t="s">
@@ -2231,7 +2237,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A6" s="88" t="s">
         <v>80</v>
       </c>
@@ -2248,9 +2254,11 @@
       <c r="F6" s="92">
         <v>1</v>
       </c>
-      <c r="G6" s="4"/>
+      <c r="G6" s="92">
+        <v>1</v>
+      </c>
       <c r="H6" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I6" s="42"/>
       <c r="J6" s="18" t="s">
@@ -2276,7 +2284,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A7" s="88" t="s">
         <v>80</v>
       </c>
@@ -2305,18 +2313,18 @@
       </c>
       <c r="K7" s="5">
         <f>COUNTIF(H3:H75,J7)</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L7" s="6">
         <f>K7/K3</f>
-        <v>0.29577464788732394</v>
+        <v>0.352112676056338</v>
       </c>
       <c r="N7" s="104" t="s">
         <v>14</v>
       </c>
       <c r="O7" s="38">
         <f>SUMIF(H3:H75,"完了",F3:F75)</f>
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="R7" s="111" t="s">
         <v>82</v>
@@ -2326,7 +2334,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A8" s="88" t="s">
         <v>80</v>
       </c>
@@ -2353,18 +2361,18 @@
       </c>
       <c r="K8" s="5">
         <f>COUNTIF(H3:H75,J8)</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L8" s="7">
         <f>(K8+K9)/K3</f>
-        <v>0.73239436619718312</v>
+        <v>0.676056338028169</v>
       </c>
       <c r="N8" s="105" t="s">
         <v>15</v>
       </c>
       <c r="O8" s="38">
         <f>SUMIF(H3:H75,"未着手",F3:F75)</f>
-        <v>27.6</v>
+        <v>26.6</v>
       </c>
       <c r="R8" s="112" t="s">
         <v>84</v>
@@ -2374,7 +2382,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A9" s="88" t="s">
         <v>80</v>
       </c>
@@ -2403,7 +2411,7 @@
       </c>
       <c r="K9" s="3">
         <f>COUNTIF(H3:H75,J9)</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L9" s="3"/>
       <c r="N9" s="106" t="s">
@@ -2411,10 +2419,10 @@
       </c>
       <c r="O9" s="38">
         <f>SUMIF(H3:H75,"作業中",F3:F75)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A10" s="88" t="s">
         <v>80</v>
       </c>
@@ -2444,7 +2452,7 @@
       <c r="N10" s="38"/>
       <c r="O10" s="38"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A11" s="88" t="s">
         <v>80</v>
       </c>
@@ -2479,7 +2487,7 @@
       <c r="N11" s="38"/>
       <c r="O11" s="38"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A12" s="88" t="s">
         <v>80</v>
       </c>
@@ -2498,7 +2506,7 @@
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="I12" s="95"/>
       <c r="J12" s="98" t="s">
@@ -2512,7 +2520,7 @@
       <c r="N12" s="38"/>
       <c r="O12" s="38"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A13" s="88" t="s">
         <v>80</v>
       </c>
@@ -2542,7 +2550,7 @@
       <c r="M13" s="116"/>
       <c r="N13" s="100"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A14" s="88" t="s">
         <v>80</v>
       </c>
@@ -2578,7 +2586,7 @@
       </c>
       <c r="N14" s="97"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A15" s="88" t="s">
         <v>80</v>
       </c>
@@ -2615,7 +2623,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A16" s="88" t="s">
         <v>80</v>
       </c>
@@ -2652,7 +2660,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A17" s="88" t="s">
         <v>80</v>
       </c>
@@ -2691,7 +2699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A18" s="88" t="s">
         <v>80</v>
       </c>
@@ -2728,7 +2736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A19" s="88" t="s">
         <v>80</v>
       </c>
@@ -2765,7 +2773,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A20" s="88" t="s">
         <v>80</v>
       </c>
@@ -2787,7 +2795,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A21" s="88" t="s">
         <v>80</v>
       </c>
@@ -2820,7 +2828,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A22" s="88" t="s">
         <v>80</v>
       </c>
@@ -2849,7 +2857,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A23" s="88" t="s">
         <v>80</v>
       </c>
@@ -2886,14 +2894,14 @@
       </c>
       <c r="N23">
         <f ca="1">(SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"未着手") + SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"作業中"))/ L23</f>
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="O23">
         <f xml:space="preserve"> 29 / 15</f>
         <v>1.9333333333333333</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A24" s="89" t="s">
         <v>81</v>
       </c>
@@ -2941,7 +2949,7 @@
         <v>0.80999999999999994</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A25" s="89" t="s">
         <v>81</v>
       </c>
@@ -2987,7 +2995,7 @@
         <v>1.3888888888888888</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A26" s="89" t="s">
         <v>81</v>
       </c>
@@ -3024,10 +3032,10 @@
       </c>
       <c r="N26">
         <f ca="1" xml:space="preserve"> (O3 - O7) / L26</f>
-        <v>1.3307692307692309</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
+        <v>1.2346153846153847</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A27" s="89" t="s">
         <v>81</v>
       </c>
@@ -3051,7 +3059,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A28" s="89" t="s">
         <v>81</v>
       </c>
@@ -3073,7 +3081,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A29" s="89" t="s">
         <v>81</v>
       </c>
@@ -3095,7 +3103,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A30" s="89" t="s">
         <v>81</v>
       </c>
@@ -3121,7 +3129,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A31" s="89" t="s">
         <v>81</v>
       </c>
@@ -3145,7 +3153,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A32" s="89" t="s">
         <v>81</v>
       </c>
@@ -3167,7 +3175,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" s="89" t="s">
         <v>81</v>
       </c>
@@ -3191,7 +3199,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34" s="89" t="s">
         <v>81</v>
       </c>
@@ -3215,7 +3223,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A35" s="89" t="s">
         <v>81</v>
       </c>
@@ -3237,7 +3245,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A36" s="89" t="s">
         <v>81</v>
       </c>
@@ -3259,7 +3267,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A37" s="89" t="s">
         <v>81</v>
       </c>
@@ -3281,7 +3289,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A38" s="89" t="s">
         <v>81</v>
       </c>
@@ -3305,7 +3313,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39" s="89" t="s">
         <v>81</v>
       </c>
@@ -3327,7 +3335,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A40" s="89" t="s">
         <v>81</v>
       </c>
@@ -3349,7 +3357,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A41" s="89" t="s">
         <v>81</v>
       </c>
@@ -3371,7 +3379,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A42" s="89" t="s">
         <v>81</v>
       </c>
@@ -3395,7 +3403,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A43" s="89" t="s">
         <v>81</v>
       </c>
@@ -3417,7 +3425,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A44" s="89" t="s">
         <v>81</v>
       </c>
@@ -3439,7 +3447,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A45" s="89" t="s">
         <v>81</v>
       </c>
@@ -3461,7 +3469,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A46" s="89" t="s">
         <v>81</v>
       </c>
@@ -3483,7 +3491,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47" s="89" t="s">
         <v>81</v>
       </c>
@@ -3505,7 +3513,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A48" s="89" t="s">
         <v>81</v>
       </c>
@@ -3529,7 +3537,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A49" s="89" t="s">
         <v>81</v>
       </c>
@@ -3551,7 +3559,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A50" s="87" t="s">
         <v>82</v>
       </c>
@@ -3575,7 +3583,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A51" s="87" t="s">
         <v>82</v>
       </c>
@@ -3601,7 +3609,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A52" s="87" t="s">
         <v>82</v>
       </c>
@@ -3625,7 +3633,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A53" s="87" t="s">
         <v>82</v>
       </c>
@@ -3647,7 +3655,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A54" s="90" t="s">
         <v>83</v>
       </c>
@@ -3671,7 +3679,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A55" s="90" t="s">
         <v>83</v>
       </c>
@@ -3693,7 +3701,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A56" s="90" t="s">
         <v>83</v>
       </c>
@@ -3717,7 +3725,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A57" s="90" t="s">
         <v>83</v>
       </c>
@@ -3741,7 +3749,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A58" s="90" t="s">
         <v>83</v>
       </c>
@@ -3763,7 +3771,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A59" s="90" t="s">
         <v>83</v>
       </c>
@@ -3787,7 +3795,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A60" s="90" t="s">
         <v>83</v>
       </c>
@@ -3813,7 +3821,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A61" s="90" t="s">
         <v>83</v>
       </c>
@@ -3837,7 +3845,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A62" s="90" t="s">
         <v>83</v>
       </c>
@@ -3861,7 +3869,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A63" s="90" t="s">
         <v>83</v>
       </c>
@@ -3883,7 +3891,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A64" s="90" t="s">
         <v>83</v>
       </c>
@@ -3907,7 +3915,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A65" s="90" t="s">
         <v>83</v>
       </c>
@@ -3931,7 +3939,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A66" s="90" t="s">
         <v>83</v>
       </c>
@@ -3955,7 +3963,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A67" s="90" t="s">
         <v>83</v>
       </c>
@@ -3979,7 +3987,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A68" s="91" t="s">
         <v>84</v>
       </c>
@@ -4005,7 +4013,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A69" s="91" t="s">
         <v>84</v>
       </c>
@@ -4027,7 +4035,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A70" s="91" t="s">
         <v>84</v>
       </c>
@@ -4049,7 +4057,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A71" s="91" t="s">
         <v>84</v>
       </c>
@@ -4071,7 +4079,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A72" s="91" t="s">
         <v>84</v>
       </c>
@@ -4093,7 +4101,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A73" s="91" t="s">
         <v>84</v>
       </c>
@@ -4115,7 +4123,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A74" s="91" t="s">
         <v>84</v>
       </c>
@@ -4137,7 +4145,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A75" s="91" t="s">
         <v>84</v>
       </c>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yongy\git\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED8AA5C-6673-4E48-A79B-CD7164C5143A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E16608D-413F-4125-AE50-404B41A63066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1110" windowWidth="28485" windowHeight="14370" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2041,26 +2041,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039B1606-320D-4390-8B98-CE6030BB2FAA}">
   <dimension ref="A1:S75"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="3" width="25.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="25.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.19921875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.8984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.19921875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.875" customWidth="1"/>
+    <col min="17" max="17" width="8.8984375" customWidth="1"/>
     <col min="18" max="18" width="21.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
       <c r="I1" s="44"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="S2" s="38"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A3" s="88" t="s">
         <v>80</v>
       </c>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="S3" s="38"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A4" s="88" t="s">
         <v>80</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>11.100000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A5" s="88" t="s">
         <v>80</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A6" s="88" t="s">
         <v>80</v>
       </c>
@@ -2284,7 +2284,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A7" s="88" t="s">
         <v>80</v>
       </c>
@@ -2313,18 +2313,18 @@
       </c>
       <c r="K7" s="5">
         <f>COUNTIF(H3:H75,J7)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L7" s="6">
         <f>K7/K3</f>
-        <v>0.352112676056338</v>
+        <v>0.38028169014084506</v>
       </c>
       <c r="N7" s="104" t="s">
         <v>14</v>
       </c>
       <c r="O7" s="38">
         <f>SUMIF(H3:H75,"完了",F3:F75)</f>
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
       <c r="R7" s="111" t="s">
         <v>82</v>
@@ -2334,7 +2334,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A8" s="88" t="s">
         <v>80</v>
       </c>
@@ -2361,18 +2361,18 @@
       </c>
       <c r="K8" s="5">
         <f>COUNTIF(H3:H75,J8)</f>
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="L8" s="7">
         <f>(K8+K9)/K3</f>
-        <v>0.676056338028169</v>
+        <v>0.647887323943662</v>
       </c>
       <c r="N8" s="105" t="s">
         <v>15</v>
       </c>
       <c r="O8" s="38">
         <f>SUMIF(H3:H75,"未着手",F3:F75)</f>
-        <v>26.6</v>
+        <v>24.6</v>
       </c>
       <c r="R8" s="112" t="s">
         <v>84</v>
@@ -2382,7 +2382,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A9" s="88" t="s">
         <v>80</v>
       </c>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="K9" s="3">
         <f>COUNTIF(H3:H75,J9)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L9" s="3"/>
       <c r="N9" s="106" t="s">
@@ -2419,10 +2419,10 @@
       </c>
       <c r="O9" s="38">
         <f>SUMIF(H3:H75,"作業中",F3:F75)</f>
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A10" s="88" t="s">
         <v>80</v>
       </c>
@@ -2452,7 +2452,7 @@
       <c r="N10" s="38"/>
       <c r="O10" s="38"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A11" s="88" t="s">
         <v>80</v>
       </c>
@@ -2487,7 +2487,7 @@
       <c r="N11" s="38"/>
       <c r="O11" s="38"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A12" s="88" t="s">
         <v>80</v>
       </c>
@@ -2520,7 +2520,7 @@
       <c r="N12" s="38"/>
       <c r="O12" s="38"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A13" s="88" t="s">
         <v>80</v>
       </c>
@@ -2550,7 +2550,7 @@
       <c r="M13" s="116"/>
       <c r="N13" s="100"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A14" s="88" t="s">
         <v>80</v>
       </c>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="N14" s="97"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A15" s="88" t="s">
         <v>80</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A16" s="88" t="s">
         <v>80</v>
       </c>
@@ -2660,7 +2660,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A17" s="88" t="s">
         <v>80</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A18" s="88" t="s">
         <v>80</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A19" s="88" t="s">
         <v>80</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A20" s="88" t="s">
         <v>80</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A21" s="88" t="s">
         <v>80</v>
       </c>
@@ -2828,7 +2828,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A22" s="88" t="s">
         <v>80</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A23" s="88" t="s">
         <v>80</v>
       </c>
@@ -2894,14 +2894,14 @@
       </c>
       <c r="N23">
         <f ca="1">(SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"未着手") + SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"作業中"))/ L23</f>
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="O23">
         <f xml:space="preserve"> 29 / 15</f>
         <v>1.9333333333333333</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A24" s="89" t="s">
         <v>81</v>
       </c>
@@ -2949,7 +2949,7 @@
         <v>0.80999999999999994</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A25" s="89" t="s">
         <v>81</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>1.3888888888888888</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A26" s="89" t="s">
         <v>81</v>
       </c>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="4" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="J26" t="s">
         <v>100</v>
@@ -3032,10 +3032,10 @@
       </c>
       <c r="N26">
         <f ca="1" xml:space="preserve"> (O3 - O7) / L26</f>
-        <v>1.2346153846153847</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.4">
+        <v>1.1961538461538461</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A27" s="89" t="s">
         <v>81</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A28" s="89" t="s">
         <v>81</v>
       </c>
@@ -3076,12 +3076,14 @@
       <c r="F28" s="38">
         <v>0.5</v>
       </c>
-      <c r="G28" s="41"/>
+      <c r="G28" s="41">
+        <v>0.5</v>
+      </c>
       <c r="H28" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A29" s="89" t="s">
         <v>81</v>
       </c>
@@ -3103,7 +3105,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A30" s="89" t="s">
         <v>81</v>
       </c>
@@ -3129,7 +3131,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A31" s="89" t="s">
         <v>81</v>
       </c>
@@ -3153,7 +3155,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A32" s="89" t="s">
         <v>81</v>
       </c>
@@ -3170,12 +3172,14 @@
       <c r="F32" s="38">
         <v>0.5</v>
       </c>
-      <c r="G32" s="38"/>
+      <c r="G32" s="38">
+        <v>1</v>
+      </c>
       <c r="H32" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" s="89" t="s">
         <v>81</v>
       </c>
@@ -3199,7 +3203,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" s="89" t="s">
         <v>81</v>
       </c>
@@ -3223,7 +3227,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" s="89" t="s">
         <v>81</v>
       </c>
@@ -3245,7 +3249,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" s="89" t="s">
         <v>81</v>
       </c>
@@ -3267,7 +3271,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" s="89" t="s">
         <v>81</v>
       </c>
@@ -3289,7 +3293,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" s="89" t="s">
         <v>81</v>
       </c>
@@ -3313,7 +3317,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" s="89" t="s">
         <v>81</v>
       </c>
@@ -3335,7 +3339,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" s="89" t="s">
         <v>81</v>
       </c>
@@ -3357,7 +3361,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" s="89" t="s">
         <v>81</v>
       </c>
@@ -3376,10 +3380,10 @@
       </c>
       <c r="G41" s="36"/>
       <c r="H41" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" s="89" t="s">
         <v>81</v>
       </c>
@@ -3403,7 +3407,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" s="89" t="s">
         <v>81</v>
       </c>
@@ -3425,7 +3429,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" s="89" t="s">
         <v>81</v>
       </c>
@@ -3447,7 +3451,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" s="89" t="s">
         <v>81</v>
       </c>
@@ -3469,7 +3473,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" s="89" t="s">
         <v>81</v>
       </c>
@@ -3491,7 +3495,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A47" s="89" t="s">
         <v>81</v>
       </c>
@@ -3513,7 +3517,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48" s="89" t="s">
         <v>81</v>
       </c>
@@ -3537,7 +3541,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49" s="89" t="s">
         <v>81</v>
       </c>
@@ -3559,7 +3563,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A50" s="87" t="s">
         <v>82</v>
       </c>
@@ -3583,7 +3587,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="87" t="s">
         <v>82</v>
       </c>
@@ -3609,7 +3613,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="87" t="s">
         <v>82</v>
       </c>
@@ -3633,7 +3637,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="87" t="s">
         <v>82</v>
       </c>
@@ -3655,7 +3659,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" s="90" t="s">
         <v>83</v>
       </c>
@@ -3679,7 +3683,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" s="90" t="s">
         <v>83</v>
       </c>
@@ -3701,7 +3705,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" s="90" t="s">
         <v>83</v>
       </c>
@@ -3725,7 +3729,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" s="90" t="s">
         <v>83</v>
       </c>
@@ -3749,7 +3753,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" s="90" t="s">
         <v>83</v>
       </c>
@@ -3771,7 +3775,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" s="90" t="s">
         <v>83</v>
       </c>
@@ -3795,7 +3799,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" s="90" t="s">
         <v>83</v>
       </c>
@@ -3821,7 +3825,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" s="90" t="s">
         <v>83</v>
       </c>
@@ -3845,7 +3849,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A62" s="90" t="s">
         <v>83</v>
       </c>
@@ -3869,7 +3873,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63" s="90" t="s">
         <v>83</v>
       </c>
@@ -3891,7 +3895,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A64" s="90" t="s">
         <v>83</v>
       </c>
@@ -3915,7 +3919,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" s="90" t="s">
         <v>83</v>
       </c>
@@ -3939,7 +3943,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" s="90" t="s">
         <v>83</v>
       </c>
@@ -3963,7 +3967,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" s="90" t="s">
         <v>83</v>
       </c>
@@ -3987,7 +3991,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" s="91" t="s">
         <v>84</v>
       </c>
@@ -4013,7 +4017,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A69" s="91" t="s">
         <v>84</v>
       </c>
@@ -4035,7 +4039,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A70" s="91" t="s">
         <v>84</v>
       </c>
@@ -4057,7 +4061,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A71" s="91" t="s">
         <v>84</v>
       </c>
@@ -4079,7 +4083,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A72" s="91" t="s">
         <v>84</v>
       </c>
@@ -4101,7 +4105,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" s="91" t="s">
         <v>84</v>
       </c>
@@ -4123,7 +4127,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74" s="91" t="s">
         <v>84</v>
       </c>
@@ -4145,7 +4149,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75" s="91" t="s">
         <v>84</v>
       </c>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E16608D-413F-4125-AE50-404B41A63066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7B2935-1E2E-43B5-A791-54C2E6345057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2041,26 +2041,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039B1606-320D-4390-8B98-CE6030BB2FAA}">
   <dimension ref="A1:S75"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="3" width="25.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="25.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.8984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.25" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.8984375" customWidth="1"/>
+    <col min="17" max="17" width="8.875" customWidth="1"/>
     <col min="18" max="18" width="21.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.4">
       <c r="I1" s="44"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="S2" s="38"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A3" s="88" t="s">
         <v>80</v>
       </c>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="S3" s="38"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A4" s="88" t="s">
         <v>80</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>11.100000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A5" s="88" t="s">
         <v>80</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A6" s="88" t="s">
         <v>80</v>
       </c>
@@ -2284,7 +2284,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A7" s="88" t="s">
         <v>80</v>
       </c>
@@ -2313,18 +2313,18 @@
       </c>
       <c r="K7" s="5">
         <f>COUNTIF(H3:H75,J7)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L7" s="6">
         <f>K7/K3</f>
-        <v>0.38028169014084506</v>
+        <v>0.39436619718309857</v>
       </c>
       <c r="N7" s="104" t="s">
         <v>14</v>
       </c>
       <c r="O7" s="38">
         <f>SUMIF(H3:H75,"完了",F3:F75)</f>
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="R7" s="111" t="s">
         <v>82</v>
@@ -2334,7 +2334,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A8" s="88" t="s">
         <v>80</v>
       </c>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L8" s="7">
         <f>(K8+K9)/K3</f>
-        <v>0.647887323943662</v>
+        <v>0.63380281690140849</v>
       </c>
       <c r="N8" s="105" t="s">
         <v>15</v>
@@ -2382,7 +2382,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A9" s="88" t="s">
         <v>80</v>
       </c>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="K9" s="3">
         <f>COUNTIF(H3:H75,J9)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L9" s="3"/>
       <c r="N9" s="106" t="s">
@@ -2419,10 +2419,10 @@
       </c>
       <c r="O9" s="38">
         <f>SUMIF(H3:H75,"作業中",F3:F75)</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A10" s="88" t="s">
         <v>80</v>
       </c>
@@ -2452,7 +2452,7 @@
       <c r="N10" s="38"/>
       <c r="O10" s="38"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A11" s="88" t="s">
         <v>80</v>
       </c>
@@ -2487,7 +2487,7 @@
       <c r="N11" s="38"/>
       <c r="O11" s="38"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A12" s="88" t="s">
         <v>80</v>
       </c>
@@ -2504,9 +2504,11 @@
       <c r="F12" s="92">
         <v>1</v>
       </c>
-      <c r="G12" s="4"/>
+      <c r="G12" s="92">
+        <v>0.5</v>
+      </c>
       <c r="H12" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I12" s="95"/>
       <c r="J12" s="98" t="s">
@@ -2520,7 +2522,7 @@
       <c r="N12" s="38"/>
       <c r="O12" s="38"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A13" s="88" t="s">
         <v>80</v>
       </c>
@@ -2550,7 +2552,7 @@
       <c r="M13" s="116"/>
       <c r="N13" s="100"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A14" s="88" t="s">
         <v>80</v>
       </c>
@@ -2586,7 +2588,7 @@
       </c>
       <c r="N14" s="97"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A15" s="88" t="s">
         <v>80</v>
       </c>
@@ -2623,7 +2625,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A16" s="88" t="s">
         <v>80</v>
       </c>
@@ -2660,7 +2662,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A17" s="88" t="s">
         <v>80</v>
       </c>
@@ -2699,7 +2701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A18" s="88" t="s">
         <v>80</v>
       </c>
@@ -2736,7 +2738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A19" s="88" t="s">
         <v>80</v>
       </c>
@@ -2773,7 +2775,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A20" s="88" t="s">
         <v>80</v>
       </c>
@@ -2795,7 +2797,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A21" s="88" t="s">
         <v>80</v>
       </c>
@@ -2828,7 +2830,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A22" s="88" t="s">
         <v>80</v>
       </c>
@@ -2854,10 +2856,10 @@
       </c>
       <c r="K22" s="117">
         <f ca="1">TODAY()</f>
-        <v>46070</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A23" s="88" t="s">
         <v>80</v>
       </c>
@@ -2886,22 +2888,22 @@
       </c>
       <c r="L23">
         <f ca="1">DATE(2026,2,19) - TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M23">
         <f ca="1">SUMIF(E3:E75,"プロト",F3:F75) / L23</f>
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="N23">
         <f ca="1">(SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"未着手") + SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"作業中"))/ L23</f>
-        <v>4.25</v>
+        <v>7.5</v>
       </c>
       <c r="O23">
         <f xml:space="preserve"> 29 / 15</f>
         <v>1.9333333333333333</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A24" s="89" t="s">
         <v>81</v>
       </c>
@@ -2934,22 +2936,22 @@
       </c>
       <c r="L24">
         <f ca="1">DATE(2026,3,1) - TODAY()</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M24">
         <f ca="1">SUMIF(E3:E75,"アルファ",F3:F75) / L24</f>
-        <v>0.67499999999999993</v>
+        <v>0.73636363636363633</v>
       </c>
       <c r="N24">
         <f ca="1">(SUMIFS(F3:F75,E3:E75,"アルファ",H3:H75,"未着手") + SUMIFS(F3:F75,E3:E75,"アルファ",H3:H75,"作業中"))/ L24</f>
-        <v>0.67499999999999993</v>
+        <v>0.73636363636363633</v>
       </c>
       <c r="O24">
         <f xml:space="preserve"> 8.1 / 10</f>
         <v>0.80999999999999994</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A25" s="89" t="s">
         <v>81</v>
       </c>
@@ -2980,22 +2982,22 @@
       </c>
       <c r="L25">
         <f ca="1">DATE(2026,3,10) - TODAY()</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M25">
         <f ca="1">SUMIF(E3:E75,"ベータ",F3:F75) / L25</f>
-        <v>0.59523809523809523</v>
+        <v>0.625</v>
       </c>
       <c r="N25">
         <f ca="1">(SUMIFS(F3:F75,E3:E75,"ベータ",H3:H75,"未着手") + SUMIFS(F3:F75,E3:E75,"ベータ",H3:H75,"作業中"))/ L25</f>
-        <v>0.59523809523809523</v>
+        <v>0.625</v>
       </c>
       <c r="O25">
         <f xml:space="preserve"> 12.5 / 9</f>
         <v>1.3888888888888888</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A26" s="89" t="s">
         <v>81</v>
       </c>
@@ -3024,18 +3026,18 @@
       </c>
       <c r="L26">
         <f ca="1">DATE(2026,3,15) - TODAY()</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M26">
         <f ca="1">SUM(F3:F75) / L26</f>
-        <v>1.9846153846153847</v>
+        <v>2.0640000000000001</v>
       </c>
       <c r="N26">
         <f ca="1" xml:space="preserve"> (O3 - O7) / L26</f>
-        <v>1.1961538461538461</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
+        <v>1.204</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A27" s="89" t="s">
         <v>81</v>
       </c>
@@ -3059,7 +3061,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A28" s="89" t="s">
         <v>81</v>
       </c>
@@ -3083,7 +3085,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A29" s="89" t="s">
         <v>81</v>
       </c>
@@ -3105,7 +3107,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A30" s="89" t="s">
         <v>81</v>
       </c>
@@ -3131,7 +3133,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A31" s="89" t="s">
         <v>81</v>
       </c>
@@ -3155,7 +3157,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A32" s="89" t="s">
         <v>81</v>
       </c>
@@ -3179,7 +3181,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" s="89" t="s">
         <v>81</v>
       </c>
@@ -3203,7 +3205,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34" s="89" t="s">
         <v>81</v>
       </c>
@@ -3227,7 +3229,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A35" s="89" t="s">
         <v>81</v>
       </c>
@@ -3249,7 +3251,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A36" s="89" t="s">
         <v>81</v>
       </c>
@@ -3271,7 +3273,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A37" s="89" t="s">
         <v>81</v>
       </c>
@@ -3293,7 +3295,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A38" s="89" t="s">
         <v>81</v>
       </c>
@@ -3317,7 +3319,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39" s="89" t="s">
         <v>81</v>
       </c>
@@ -3339,7 +3341,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A40" s="89" t="s">
         <v>81</v>
       </c>
@@ -3361,7 +3363,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A41" s="89" t="s">
         <v>81</v>
       </c>
@@ -3383,7 +3385,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A42" s="89" t="s">
         <v>81</v>
       </c>
@@ -3407,7 +3409,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A43" s="89" t="s">
         <v>81</v>
       </c>
@@ -3429,7 +3431,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A44" s="89" t="s">
         <v>81</v>
       </c>
@@ -3451,7 +3453,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A45" s="89" t="s">
         <v>81</v>
       </c>
@@ -3473,7 +3475,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A46" s="89" t="s">
         <v>81</v>
       </c>
@@ -3495,7 +3497,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47" s="89" t="s">
         <v>81</v>
       </c>
@@ -3517,7 +3519,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A48" s="89" t="s">
         <v>81</v>
       </c>
@@ -3541,7 +3543,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A49" s="89" t="s">
         <v>81</v>
       </c>
@@ -3563,7 +3565,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A50" s="87" t="s">
         <v>82</v>
       </c>
@@ -3587,7 +3589,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A51" s="87" t="s">
         <v>82</v>
       </c>
@@ -3613,7 +3615,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A52" s="87" t="s">
         <v>82</v>
       </c>
@@ -3637,7 +3639,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A53" s="87" t="s">
         <v>82</v>
       </c>
@@ -3659,7 +3661,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A54" s="90" t="s">
         <v>83</v>
       </c>
@@ -3683,7 +3685,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A55" s="90" t="s">
         <v>83</v>
       </c>
@@ -3705,7 +3707,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A56" s="90" t="s">
         <v>83</v>
       </c>
@@ -3729,7 +3731,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A57" s="90" t="s">
         <v>83</v>
       </c>
@@ -3753,7 +3755,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A58" s="90" t="s">
         <v>83</v>
       </c>
@@ -3775,7 +3777,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A59" s="90" t="s">
         <v>83</v>
       </c>
@@ -3799,7 +3801,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A60" s="90" t="s">
         <v>83</v>
       </c>
@@ -3825,7 +3827,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A61" s="90" t="s">
         <v>83</v>
       </c>
@@ -3849,7 +3851,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A62" s="90" t="s">
         <v>83</v>
       </c>
@@ -3873,7 +3875,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A63" s="90" t="s">
         <v>83</v>
       </c>
@@ -3895,7 +3897,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A64" s="90" t="s">
         <v>83</v>
       </c>
@@ -3919,7 +3921,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A65" s="90" t="s">
         <v>83</v>
       </c>
@@ -3943,7 +3945,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A66" s="90" t="s">
         <v>83</v>
       </c>
@@ -3967,7 +3969,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A67" s="90" t="s">
         <v>83</v>
       </c>
@@ -3991,7 +3993,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A68" s="91" t="s">
         <v>84</v>
       </c>
@@ -4017,7 +4019,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A69" s="91" t="s">
         <v>84</v>
       </c>
@@ -4039,7 +4041,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A70" s="91" t="s">
         <v>84</v>
       </c>
@@ -4061,7 +4063,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A71" s="91" t="s">
         <v>84</v>
       </c>
@@ -4083,7 +4085,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A72" s="91" t="s">
         <v>84</v>
       </c>
@@ -4105,7 +4107,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A73" s="91" t="s">
         <v>84</v>
       </c>
@@ -4127,7 +4129,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A74" s="91" t="s">
         <v>84</v>
       </c>
@@ -4149,7 +4151,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A75" s="91" t="s">
         <v>84</v>
       </c>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492C8641-C364-4E91-B7C1-7D7980DAE54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09964F7D-4BEB-4CB0-ADED-658F537CC88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1194,7 +1194,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1425,24 +1425,18 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1458,12 +1452,6 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1482,9 +1470,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1881,16 +1866,16 @@
       <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="98" t="s">
+      <c r="J2" s="94" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="98" t="s">
+      <c r="K2" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="L2" s="98" t="s">
+      <c r="L2" s="94" t="s">
         <v>86</v>
       </c>
-      <c r="M2" s="98" t="s">
+      <c r="M2" s="94" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1919,7 +1904,7 @@
       <c r="H3" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J3" s="81" t="s">
+      <c r="J3" s="80" t="s">
         <v>89</v>
       </c>
       <c r="K3" s="58">
@@ -1928,11 +1913,11 @@
       </c>
       <c r="L3" s="58">
         <f>SUMIF(H3:H75,"完了",F3:F75)</f>
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="M3" s="58">
         <f>K3-L3</f>
-        <v>31.099999999999994</v>
+        <v>29.599999999999994</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
@@ -1958,7 +1943,7 @@
       <c r="H4" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J4" s="82" t="s">
+      <c r="J4" s="81" t="s">
         <v>10</v>
       </c>
       <c r="K4" s="58">
@@ -1967,11 +1952,11 @@
       </c>
       <c r="L4" s="58">
         <f>SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"完了")</f>
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="M4" s="58">
         <f t="shared" ref="M4:M7" si="0">K4-L4</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
@@ -1997,7 +1982,7 @@
       <c r="H5" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J5" s="91" t="s">
+      <c r="J5" s="89" t="s">
         <v>11</v>
       </c>
       <c r="K5" s="58">
@@ -2006,11 +1991,11 @@
       </c>
       <c r="L5" s="58">
         <f>SUMIFS(F3:F75,E3:E75,"アルファ",H3:H75,"完了")</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M5" s="58">
         <f t="shared" si="0"/>
-        <v>10.600000000000001</v>
+        <v>10.100000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.4">
@@ -2036,7 +2021,7 @@
       <c r="H6" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J6" s="83" t="s">
+      <c r="J6" s="82" t="s">
         <v>12</v>
       </c>
       <c r="K6" s="58">
@@ -2075,14 +2060,14 @@
       <c r="H7" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="J7" s="92" t="s">
+      <c r="J7" s="90" t="s">
         <v>90</v>
       </c>
-      <c r="K7" s="87">
+      <c r="K7" s="85">
         <f>SUMIF(E3:E75,"マスタ",F3:F75)</f>
         <v>2</v>
       </c>
-      <c r="L7" s="87">
+      <c r="L7" s="85">
         <f>SUMIFS(F3:F75,E3:E75,"ベータ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
@@ -2108,17 +2093,19 @@
       <c r="F8" s="75">
         <v>0.5</v>
       </c>
-      <c r="G8" s="3"/>
+      <c r="G8" s="75">
+        <v>0.25</v>
+      </c>
       <c r="H8" s="48" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8" s="93"/>
-      <c r="J8" s="84"/>
-      <c r="K8" s="85"/>
-      <c r="L8" s="86"/>
-      <c r="M8" s="93"/>
-      <c r="N8" s="93"/>
-      <c r="O8" s="93"/>
+        <v>79</v>
+      </c>
+      <c r="I8" s="84"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="84"/>
+      <c r="L8" s="84"/>
+      <c r="M8" s="84"/>
+      <c r="N8" s="84"/>
+      <c r="O8" s="84"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A9" s="71" t="s">
@@ -2137,20 +2124,20 @@
       <c r="F9" s="75">
         <v>0.5</v>
       </c>
-      <c r="G9" s="88">
+      <c r="G9" s="86">
         <v>0.25</v>
       </c>
-      <c r="H9" s="90" t="s">
+      <c r="H9" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="I9" s="99"/>
-      <c r="J9" s="101" t="s">
+      <c r="I9" s="95"/>
+      <c r="J9" s="97" t="s">
         <v>91</v>
       </c>
-      <c r="K9" s="102"/>
-      <c r="L9" s="102"/>
-      <c r="M9" s="102"/>
-      <c r="N9" s="93"/>
+      <c r="K9" s="98"/>
+      <c r="L9" s="98"/>
+      <c r="M9" s="98"/>
+      <c r="N9" s="84"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A10" s="71" t="s">
@@ -2169,36 +2156,36 @@
       <c r="F10" s="75">
         <v>0.5</v>
       </c>
-      <c r="G10" s="88">
-        <v>0.5</v>
-      </c>
-      <c r="H10" s="90" t="s">
+      <c r="G10" s="86">
+        <v>0.5</v>
+      </c>
+      <c r="H10" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="I10" s="100"/>
-      <c r="J10" s="81" t="s">
+      <c r="I10" s="96"/>
+      <c r="J10" s="80" t="s">
         <v>89</v>
       </c>
-      <c r="K10" s="81" t="s">
+      <c r="K10" s="80" t="s">
         <v>88</v>
       </c>
-      <c r="L10" s="81" t="s">
+      <c r="L10" s="80" t="s">
         <v>86</v>
       </c>
-      <c r="M10" s="81" t="s">
+      <c r="M10" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="N10" s="93"/>
-      <c r="O10" s="109" t="s">
+      <c r="N10" s="84"/>
+      <c r="O10" s="104" t="s">
         <v>83</v>
       </c>
-      <c r="P10" s="109" t="s">
+      <c r="P10" s="104" t="s">
         <v>88</v>
       </c>
-      <c r="Q10" s="109" t="s">
+      <c r="Q10" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="R10" s="109" t="s">
+      <c r="R10" s="104" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2219,43 +2206,43 @@
       <c r="F11" s="75">
         <v>0.5</v>
       </c>
-      <c r="G11" s="88">
+      <c r="G11" s="86">
         <v>0.25</v>
       </c>
-      <c r="H11" s="90" t="s">
+      <c r="H11" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="I11" s="100"/>
-      <c r="J11" s="104" t="s">
+      <c r="I11" s="96"/>
+      <c r="J11" s="99" t="s">
         <v>74</v>
       </c>
-      <c r="K11" s="103">
+      <c r="K11" s="85">
         <f>SUMIF(A3:A75,"大崎",F3:F75)</f>
         <v>12.099999999999998</v>
       </c>
-      <c r="L11" s="103">
+      <c r="L11" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"大崎",H3:H75,"完了")</f>
-        <v>4</v>
-      </c>
-      <c r="M11" s="103">
+        <v>5.5</v>
+      </c>
+      <c r="M11" s="85">
         <f>K11 - L11</f>
-        <v>8.0999999999999979</v>
-      </c>
-      <c r="N11" s="93"/>
-      <c r="O11" s="104" t="s">
+        <v>6.5999999999999979</v>
+      </c>
+      <c r="N11" s="84"/>
+      <c r="O11" s="99" t="s">
         <v>74</v>
       </c>
-      <c r="P11" s="103">
+      <c r="P11" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"プロト")</f>
         <v>5</v>
       </c>
-      <c r="Q11" s="103">
+      <c r="Q11" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"プロト",H3:H75,"完了")</f>
-        <v>4</v>
-      </c>
-      <c r="R11" s="103">
+        <v>5</v>
+      </c>
+      <c r="R11" s="85">
         <f>P11 - Q11</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.4">
@@ -2275,39 +2262,41 @@
       <c r="F12" s="75">
         <v>1</v>
       </c>
-      <c r="G12" s="80"/>
-      <c r="H12" s="90" t="s">
-        <v>80</v>
-      </c>
-      <c r="I12" s="100"/>
-      <c r="J12" s="105" t="s">
+      <c r="G12" s="86">
+        <v>0.5</v>
+      </c>
+      <c r="H12" s="88" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12" s="96"/>
+      <c r="J12" s="100" t="s">
         <v>75</v>
       </c>
-      <c r="K12" s="103">
+      <c r="K12" s="85">
         <f>SUMIF(A3:A75,"上永",F3:F75)</f>
         <v>17</v>
       </c>
-      <c r="L12" s="103">
+      <c r="L12" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"上永",H3:H75,"完了")</f>
         <v>6.5</v>
       </c>
-      <c r="M12" s="103">
+      <c r="M12" s="85">
         <f t="shared" ref="M12:M15" si="1">K12 - L12</f>
         <v>10.5</v>
       </c>
-      <c r="N12" s="93"/>
-      <c r="O12" s="105" t="s">
+      <c r="N12" s="84"/>
+      <c r="O12" s="100" t="s">
         <v>75</v>
       </c>
-      <c r="P12" s="103">
+      <c r="P12" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"プロト")</f>
         <v>8</v>
       </c>
-      <c r="Q12" s="103">
+      <c r="Q12" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"プロト",H3:H75,"完了")</f>
         <v>6.5</v>
       </c>
-      <c r="R12" s="103">
+      <c r="R12" s="85">
         <f t="shared" ref="R12:R15" si="2">P12 - Q12</f>
         <v>1.5</v>
       </c>
@@ -2330,38 +2319,38 @@
         <v>1.5</v>
       </c>
       <c r="G13" s="75"/>
-      <c r="H13" s="89" t="s">
+      <c r="H13" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="I13" s="95"/>
-      <c r="J13" s="106" t="s">
+      <c r="I13" s="91"/>
+      <c r="J13" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="K13" s="103">
+      <c r="K13" s="85">
         <f>SUMIF(A3:A75,"川浪",F3:F75)</f>
         <v>9.5</v>
       </c>
-      <c r="L13" s="103">
+      <c r="L13" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"川浪",H3:H75,"完了")</f>
         <v>6</v>
       </c>
-      <c r="M13" s="103">
+      <c r="M13" s="85">
         <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
-      <c r="N13" s="93"/>
-      <c r="O13" s="106" t="s">
+      <c r="N13" s="84"/>
+      <c r="O13" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="P13" s="103">
+      <c r="P13" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"プロト")</f>
         <v>8.5</v>
       </c>
-      <c r="Q13" s="103">
+      <c r="Q13" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"プロト",H3:H75,"完了")</f>
         <v>6</v>
       </c>
-      <c r="R13" s="103">
+      <c r="R13" s="85">
         <f t="shared" si="2"/>
         <v>2.5</v>
       </c>
@@ -2389,35 +2378,35 @@
       <c r="H14" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I14" s="96"/>
-      <c r="J14" s="107" t="s">
+      <c r="I14" s="92"/>
+      <c r="J14" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="K14" s="103">
+      <c r="K14" s="85">
         <f>SUMIF(A3:A75,"佐々木",F3:F75)</f>
         <v>6</v>
       </c>
-      <c r="L14" s="103">
+      <c r="L14" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"佐々木",H3:H75,"完了")</f>
         <v>4</v>
       </c>
-      <c r="M14" s="103">
+      <c r="M14" s="85">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="N14" s="94"/>
-      <c r="O14" s="107" t="s">
+      <c r="N14" s="84"/>
+      <c r="O14" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="P14" s="103">
+      <c r="P14" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"プロト")</f>
         <v>4</v>
       </c>
-      <c r="Q14" s="103">
+      <c r="Q14" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"プロト",H3:H75,"完了")</f>
         <v>4</v>
       </c>
-      <c r="R14" s="103">
+      <c r="R14" s="85">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2443,35 +2432,35 @@
       <c r="H15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I15" s="93"/>
-      <c r="J15" s="108" t="s">
+      <c r="I15" s="84"/>
+      <c r="J15" s="103" t="s">
         <v>78</v>
       </c>
-      <c r="K15" s="103">
+      <c r="K15" s="85">
         <f>SUMIF(A3:A75,"誰でも",F3:F75)</f>
         <v>8</v>
       </c>
-      <c r="L15" s="103">
+      <c r="L15" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"誰でも",H3:H75,"完了")</f>
         <v>1</v>
       </c>
-      <c r="M15" s="103">
+      <c r="M15" s="85">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="N15" s="93"/>
-      <c r="O15" s="108" t="s">
+      <c r="N15" s="84"/>
+      <c r="O15" s="103" t="s">
         <v>78</v>
       </c>
-      <c r="P15" s="103">
+      <c r="P15" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"プロト")</f>
         <v>2</v>
       </c>
-      <c r="Q15" s="103">
+      <c r="Q15" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"プロト",H3:H75,"完了")</f>
         <v>1</v>
       </c>
-      <c r="R15" s="103">
+      <c r="R15" s="85">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -2497,9 +2486,9 @@
       <c r="H16" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I16" s="93"/>
-      <c r="N16" s="93"/>
-      <c r="O16" s="93"/>
+      <c r="I16" s="84"/>
+      <c r="N16" s="84"/>
+      <c r="O16" s="84"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A17" s="71" t="s">
@@ -2524,30 +2513,30 @@
       <c r="H17" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I17" s="93"/>
-      <c r="J17" s="110" t="s">
+      <c r="I17" s="84"/>
+      <c r="J17" s="105" t="s">
         <v>84</v>
       </c>
-      <c r="K17" s="110" t="s">
+      <c r="K17" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="L17" s="110" t="s">
+      <c r="L17" s="105" t="s">
         <v>86</v>
       </c>
-      <c r="M17" s="110" t="s">
+      <c r="M17" s="105" t="s">
         <v>92</v>
       </c>
-      <c r="N17" s="97"/>
-      <c r="O17" s="111" t="s">
+      <c r="N17" s="93"/>
+      <c r="O17" s="106" t="s">
         <v>85</v>
       </c>
-      <c r="P17" s="111" t="s">
+      <c r="P17" s="106" t="s">
         <v>88</v>
       </c>
-      <c r="Q17" s="111" t="s">
+      <c r="Q17" s="106" t="s">
         <v>86</v>
       </c>
-      <c r="R17" s="111" t="s">
+      <c r="R17" s="106" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2572,35 +2561,35 @@
       <c r="H18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I18" s="93"/>
-      <c r="J18" s="104" t="s">
+      <c r="I18" s="84"/>
+      <c r="J18" s="99" t="s">
         <v>74</v>
       </c>
-      <c r="K18" s="103">
+      <c r="K18" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"アルファ")</f>
         <v>3.6000000000000005</v>
       </c>
-      <c r="L18" s="103">
+      <c r="L18" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"アルファ",H3:H75,"完了")</f>
-        <v>0</v>
-      </c>
-      <c r="M18" s="103">
+        <v>0.5</v>
+      </c>
+      <c r="M18" s="85">
         <f>K18 - L18</f>
-        <v>3.6000000000000005</v>
-      </c>
-      <c r="N18" s="93"/>
-      <c r="O18" s="104" t="s">
+        <v>3.1000000000000005</v>
+      </c>
+      <c r="N18" s="84"/>
+      <c r="O18" s="99" t="s">
         <v>74</v>
       </c>
-      <c r="P18" s="103">
+      <c r="P18" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"ベータ")</f>
         <v>3.5</v>
       </c>
-      <c r="Q18" s="103">
+      <c r="Q18" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"ベータ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
-      <c r="R18" s="103">
+      <c r="R18" s="85">
         <f>P18 - Q18</f>
         <v>3.5</v>
       </c>
@@ -2626,35 +2615,35 @@
       <c r="H19" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I19" s="93"/>
-      <c r="J19" s="105" t="s">
+      <c r="I19" s="84"/>
+      <c r="J19" s="100" t="s">
         <v>75</v>
       </c>
-      <c r="K19" s="103">
+      <c r="K19" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"アルファ")</f>
         <v>4</v>
       </c>
-      <c r="L19" s="103">
+      <c r="L19" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"アルファ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
-      <c r="M19" s="103">
+      <c r="M19" s="85">
         <f t="shared" ref="M19:M22" si="3">K19 - L19</f>
         <v>4</v>
       </c>
-      <c r="N19" s="93"/>
-      <c r="O19" s="105" t="s">
+      <c r="N19" s="84"/>
+      <c r="O19" s="100" t="s">
         <v>75</v>
       </c>
-      <c r="P19" s="103">
+      <c r="P19" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"ベータ")</f>
         <v>5</v>
       </c>
-      <c r="Q19" s="103">
+      <c r="Q19" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"ベータ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
-      <c r="R19" s="103">
+      <c r="R19" s="85">
         <f t="shared" ref="R19:R22" si="4">P19 - Q19</f>
         <v>5</v>
       </c>
@@ -2680,33 +2669,33 @@
       <c r="H20" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J20" s="106" t="s">
+      <c r="J20" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="K20" s="103">
+      <c r="K20" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"アルファ")</f>
         <v>1</v>
       </c>
-      <c r="L20" s="103">
+      <c r="L20" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"アルファ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
-      <c r="M20" s="103">
+      <c r="M20" s="85">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="O20" s="106" t="s">
+      <c r="O20" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="P20" s="103">
+      <c r="P20" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"ベータ")</f>
         <v>0</v>
       </c>
-      <c r="Q20" s="103">
+      <c r="Q20" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"ベータ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
-      <c r="R20" s="103">
+      <c r="R20" s="85">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -2734,33 +2723,33 @@
       <c r="H21" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J21" s="107" t="s">
+      <c r="J21" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="K21" s="103">
+      <c r="K21" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"アルファ")</f>
         <v>0</v>
       </c>
-      <c r="L21" s="103">
+      <c r="L21" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"アルファ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
-      <c r="M21" s="103">
+      <c r="M21" s="85">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O21" s="107" t="s">
+      <c r="O21" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="P21" s="103">
+      <c r="P21" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"ベータ")</f>
         <v>0</v>
       </c>
-      <c r="Q21" s="103">
+      <c r="Q21" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"ベータ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
-      <c r="R21" s="103">
+      <c r="R21" s="85">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -2786,33 +2775,33 @@
       <c r="H22" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J22" s="108" t="s">
+      <c r="J22" s="103" t="s">
         <v>78</v>
       </c>
-      <c r="K22" s="103">
+      <c r="K22" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"アルファ")</f>
         <v>2</v>
       </c>
-      <c r="L22" s="103">
+      <c r="L22" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"アルファ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
-      <c r="M22" s="103">
+      <c r="M22" s="85">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="O22" s="108" t="s">
+      <c r="O22" s="103" t="s">
         <v>78</v>
       </c>
-      <c r="P22" s="103">
+      <c r="P22" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"ベータ")</f>
         <v>4</v>
       </c>
-      <c r="Q22" s="103">
+      <c r="Q22" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"ベータ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
-      <c r="R22" s="103">
+      <c r="R22" s="85">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09964F7D-4BEB-4CB0-ADED-658F537CC88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF70DCB-98C7-45E7-BF31-A84D30FE7ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1823,28 +1823,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039B1606-320D-4390-8B98-CE6030BB2FAA}">
   <dimension ref="A1:R75"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="3" width="25.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.75" customWidth="1"/>
-    <col min="11" max="11" width="7.125" customWidth="1"/>
+    <col min="2" max="3" width="25.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.69921875" customWidth="1"/>
+    <col min="11" max="11" width="7.09765625" customWidth="1"/>
     <col min="12" max="12" width="6.5" customWidth="1"/>
-    <col min="13" max="13" width="11.75" customWidth="1"/>
+    <col min="13" max="13" width="11.69921875" customWidth="1"/>
     <col min="14" max="14" width="7.5" customWidth="1"/>
-    <col min="15" max="15" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.75" customWidth="1"/>
+    <col min="15" max="15" width="13.09765625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.69921875" customWidth="1"/>
     <col min="17" max="17" width="7.5" customWidth="1"/>
-    <col min="18" max="18" width="7.625" customWidth="1"/>
+    <col min="18" max="18" width="7.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.45">
       <c r="I1" s="30"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A3" s="71" t="s">
         <v>74</v>
       </c>
@@ -1913,14 +1913,14 @@
       </c>
       <c r="L3" s="58">
         <f>SUMIF(H3:H75,"完了",F3:F75)</f>
-        <v>23</v>
+        <v>24.5</v>
       </c>
       <c r="M3" s="58">
         <f>K3-L3</f>
-        <v>29.599999999999994</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+        <v>28.099999999999994</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A4" s="71" t="s">
         <v>74</v>
       </c>
@@ -1952,14 +1952,14 @@
       </c>
       <c r="L4" s="58">
         <f>SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"完了")</f>
-        <v>22.5</v>
+        <v>24</v>
       </c>
       <c r="M4" s="58">
         <f t="shared" ref="M4:M7" si="0">K4-L4</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A5" s="71" t="s">
         <v>74</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>10.100000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A6" s="71" t="s">
         <v>74</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A7" s="71" t="s">
         <v>74</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A8" s="71" t="s">
         <v>74</v>
       </c>
@@ -2107,7 +2107,7 @@
       <c r="N8" s="84"/>
       <c r="O8" s="84"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A9" s="71" t="s">
         <v>74</v>
       </c>
@@ -2139,7 +2139,7 @@
       <c r="M9" s="98"/>
       <c r="N9" s="84"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A10" s="71" t="s">
         <v>74</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A11" s="71" t="s">
         <v>74</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A12" s="71" t="s">
         <v>74</v>
       </c>
@@ -2278,11 +2278,11 @@
       </c>
       <c r="L12" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"上永",H3:H75,"完了")</f>
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="M12" s="85">
         <f t="shared" ref="M12:M15" si="1">K12 - L12</f>
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="N12" s="84"/>
       <c r="O12" s="100" t="s">
@@ -2294,14 +2294,14 @@
       </c>
       <c r="Q12" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"プロト",H3:H75,"完了")</f>
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="R12" s="85">
         <f t="shared" ref="R12:R15" si="2">P12 - Q12</f>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A13" s="71" t="s">
         <v>74</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A14" s="71" t="s">
         <v>74</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A15" s="71" t="s">
         <v>74</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A16" s="71" t="s">
         <v>74</v>
       </c>
@@ -2490,7 +2490,7 @@
       <c r="N16" s="84"/>
       <c r="O16" s="84"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A17" s="71" t="s">
         <v>74</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A18" s="71" t="s">
         <v>74</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A19" s="71" t="s">
         <v>74</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A20" s="71" t="s">
         <v>74</v>
       </c>
@@ -2700,7 +2700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A21" s="71" t="s">
         <v>74</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A22" s="71" t="s">
         <v>74</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A23" s="71" t="s">
         <v>74</v>
       </c>
@@ -2828,7 +2828,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A24" s="72" t="s">
         <v>75</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A25" s="72" t="s">
         <v>75</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A26" s="72" t="s">
         <v>75</v>
       </c>
@@ -2895,12 +2895,14 @@
       <c r="F26" s="23">
         <v>0.5</v>
       </c>
-      <c r="G26" s="7"/>
+      <c r="G26" s="7">
+        <v>0.5</v>
+      </c>
       <c r="H26" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.4">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A27" s="72" t="s">
         <v>75</v>
       </c>
@@ -2924,7 +2926,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A28" s="72" t="s">
         <v>75</v>
       </c>
@@ -2948,7 +2950,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A29" s="72" t="s">
         <v>75</v>
       </c>
@@ -2970,7 +2972,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A30" s="72" t="s">
         <v>75</v>
       </c>
@@ -2996,7 +2998,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A31" s="72" t="s">
         <v>75</v>
       </c>
@@ -3020,7 +3022,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A32" s="72" t="s">
         <v>75</v>
       </c>
@@ -3044,7 +3046,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" s="72" t="s">
         <v>75</v>
       </c>
@@ -3068,7 +3070,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" s="72" t="s">
         <v>75</v>
       </c>
@@ -3092,7 +3094,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" s="72" t="s">
         <v>75</v>
       </c>
@@ -3114,7 +3116,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36" s="72" t="s">
         <v>75</v>
       </c>
@@ -3136,7 +3138,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37" s="72" t="s">
         <v>75</v>
       </c>
@@ -3158,7 +3160,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38" s="72" t="s">
         <v>75</v>
       </c>
@@ -3182,7 +3184,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39" s="72" t="s">
         <v>75</v>
       </c>
@@ -3205,7 +3207,7 @@
       </c>
       <c r="K39" s="79"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40" s="72" t="s">
         <v>75</v>
       </c>
@@ -3228,7 +3230,7 @@
       </c>
       <c r="K40" s="79"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" s="72" t="s">
         <v>75</v>
       </c>
@@ -3245,13 +3247,15 @@
       <c r="F41" s="9">
         <v>1</v>
       </c>
-      <c r="G41" s="24"/>
+      <c r="G41" s="24">
+        <v>0.5</v>
+      </c>
       <c r="H41" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K41" s="79"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" s="72" t="s">
         <v>75</v>
       </c>
@@ -3276,7 +3280,7 @@
       </c>
       <c r="K42" s="79"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" s="72" t="s">
         <v>75</v>
       </c>
@@ -3299,7 +3303,7 @@
       </c>
       <c r="K43" s="79"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" s="72" t="s">
         <v>75</v>
       </c>
@@ -3321,7 +3325,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45" s="72" t="s">
         <v>75</v>
       </c>
@@ -3343,7 +3347,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46" s="72" t="s">
         <v>75</v>
       </c>
@@ -3365,7 +3369,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A47" s="72" t="s">
         <v>75</v>
       </c>
@@ -3387,7 +3391,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48" s="72" t="s">
         <v>75</v>
       </c>
@@ -3411,7 +3415,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49" s="72" t="s">
         <v>75</v>
       </c>
@@ -3433,7 +3437,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A50" s="70" t="s">
         <v>76</v>
       </c>
@@ -3459,7 +3463,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="70" t="s">
         <v>76</v>
       </c>
@@ -3485,7 +3489,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="70" t="s">
         <v>76</v>
       </c>
@@ -3509,7 +3513,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="70" t="s">
         <v>76</v>
       </c>
@@ -3531,7 +3535,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" s="73" t="s">
         <v>77</v>
       </c>
@@ -3555,7 +3559,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" s="73" t="s">
         <v>77</v>
       </c>
@@ -3577,7 +3581,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" s="73" t="s">
         <v>77</v>
       </c>
@@ -3603,7 +3607,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" s="73" t="s">
         <v>77</v>
       </c>
@@ -3627,7 +3631,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" s="73" t="s">
         <v>77</v>
       </c>
@@ -3649,7 +3653,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" s="73" t="s">
         <v>77</v>
       </c>
@@ -3673,7 +3677,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" s="73" t="s">
         <v>77</v>
       </c>
@@ -3699,7 +3703,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" s="73" t="s">
         <v>77</v>
       </c>
@@ -3723,7 +3727,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A62" s="73" t="s">
         <v>77</v>
       </c>
@@ -3747,7 +3751,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63" s="73" t="s">
         <v>77</v>
       </c>
@@ -3769,7 +3773,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A64" s="73" t="s">
         <v>77</v>
       </c>
@@ -3793,7 +3797,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" s="73" t="s">
         <v>77</v>
       </c>
@@ -3817,7 +3821,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" s="73" t="s">
         <v>77</v>
       </c>
@@ -3841,7 +3845,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" s="73" t="s">
         <v>77</v>
       </c>
@@ -3865,7 +3869,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" s="74" t="s">
         <v>78</v>
       </c>
@@ -3891,7 +3895,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A69" s="74" t="s">
         <v>78</v>
       </c>
@@ -3913,7 +3917,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A70" s="74" t="s">
         <v>78</v>
       </c>
@@ -3935,7 +3939,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A71" s="74" t="s">
         <v>78</v>
       </c>
@@ -3957,7 +3961,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A72" s="74" t="s">
         <v>78</v>
       </c>
@@ -3979,7 +3983,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" s="74" t="s">
         <v>78</v>
       </c>
@@ -4001,7 +4005,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74" s="74" t="s">
         <v>78</v>
       </c>
@@ -4023,7 +4027,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75" s="74" t="s">
         <v>78</v>
       </c>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF70DCB-98C7-45E7-BF31-A84D30FE7ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6BF63C4-6B7C-4028-9B45-0E04092AC936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1823,28 +1823,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039B1606-320D-4390-8B98-CE6030BB2FAA}">
   <dimension ref="A1:R75"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="3" width="25.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.69921875" customWidth="1"/>
-    <col min="11" max="11" width="7.09765625" customWidth="1"/>
+    <col min="2" max="3" width="25.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.75" customWidth="1"/>
+    <col min="11" max="11" width="7.125" customWidth="1"/>
     <col min="12" max="12" width="6.5" customWidth="1"/>
-    <col min="13" max="13" width="11.69921875" customWidth="1"/>
+    <col min="13" max="13" width="11.75" customWidth="1"/>
     <col min="14" max="14" width="7.5" customWidth="1"/>
-    <col min="15" max="15" width="13.09765625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.69921875" customWidth="1"/>
+    <col min="15" max="15" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.75" customWidth="1"/>
     <col min="17" max="17" width="7.5" customWidth="1"/>
-    <col min="18" max="18" width="7.59765625" customWidth="1"/>
+    <col min="18" max="18" width="7.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
       <c r="I1" s="30"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A3" s="71" t="s">
         <v>74</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>28.099999999999994</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A4" s="71" t="s">
         <v>74</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5" s="71" t="s">
         <v>74</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>10.100000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A6" s="71" t="s">
         <v>74</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A7" s="71" t="s">
         <v>74</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A8" s="71" t="s">
         <v>74</v>
       </c>
@@ -2107,7 +2107,7 @@
       <c r="N8" s="84"/>
       <c r="O8" s="84"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A9" s="71" t="s">
         <v>74</v>
       </c>
@@ -2139,7 +2139,7 @@
       <c r="M9" s="98"/>
       <c r="N9" s="84"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A10" s="71" t="s">
         <v>74</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A11" s="71" t="s">
         <v>74</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A12" s="71" t="s">
         <v>74</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A13" s="71" t="s">
         <v>74</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" s="71" t="s">
         <v>74</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A15" s="71" t="s">
         <v>74</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A16" s="71" t="s">
         <v>74</v>
       </c>
@@ -2490,7 +2490,7 @@
       <c r="N16" s="84"/>
       <c r="O16" s="84"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A17" s="71" t="s">
         <v>74</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18" s="71" t="s">
         <v>74</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A19" s="71" t="s">
         <v>74</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A20" s="71" t="s">
         <v>74</v>
       </c>
@@ -2700,7 +2700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21" s="71" t="s">
         <v>74</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A22" s="71" t="s">
         <v>74</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A23" s="71" t="s">
         <v>74</v>
       </c>
@@ -2828,7 +2828,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A24" s="72" t="s">
         <v>75</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A25" s="72" t="s">
         <v>75</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A26" s="72" t="s">
         <v>75</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A27" s="72" t="s">
         <v>75</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A28" s="72" t="s">
         <v>75</v>
       </c>
@@ -2950,7 +2950,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A29" s="72" t="s">
         <v>75</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A30" s="72" t="s">
         <v>75</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A31" s="72" t="s">
         <v>75</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A32" s="72" t="s">
         <v>75</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A33" s="72" t="s">
         <v>75</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A34" s="72" t="s">
         <v>75</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A35" s="72" t="s">
         <v>75</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A36" s="72" t="s">
         <v>75</v>
       </c>
@@ -3138,7 +3138,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A37" s="72" t="s">
         <v>75</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A38" s="72" t="s">
         <v>75</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A39" s="72" t="s">
         <v>75</v>
       </c>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="K39" s="79"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A40" s="72" t="s">
         <v>75</v>
       </c>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="K40" s="79"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A41" s="72" t="s">
         <v>75</v>
       </c>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="K41" s="79"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A42" s="72" t="s">
         <v>75</v>
       </c>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="K42" s="79"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A43" s="72" t="s">
         <v>75</v>
       </c>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="K43" s="79"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A44" s="72" t="s">
         <v>75</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A45" s="72" t="s">
         <v>75</v>
       </c>
@@ -3347,7 +3347,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A46" s="72" t="s">
         <v>75</v>
       </c>
@@ -3369,7 +3369,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A47" s="72" t="s">
         <v>75</v>
       </c>
@@ -3391,7 +3391,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A48" s="72" t="s">
         <v>75</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A49" s="72" t="s">
         <v>75</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A50" s="70" t="s">
         <v>76</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A51" s="70" t="s">
         <v>76</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A52" s="70" t="s">
         <v>76</v>
       </c>
@@ -3513,7 +3513,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A53" s="70" t="s">
         <v>76</v>
       </c>
@@ -3535,7 +3535,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A54" s="73" t="s">
         <v>77</v>
       </c>
@@ -3559,7 +3559,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A55" s="73" t="s">
         <v>77</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A56" s="73" t="s">
         <v>77</v>
       </c>
@@ -3607,7 +3607,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A57" s="73" t="s">
         <v>77</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A58" s="73" t="s">
         <v>77</v>
       </c>
@@ -3650,10 +3650,10 @@
       </c>
       <c r="G58" s="56"/>
       <c r="H58" s="48" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A59" s="73" t="s">
         <v>77</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A60" s="73" t="s">
         <v>77</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A61" s="73" t="s">
         <v>77</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A62" s="73" t="s">
         <v>77</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A63" s="73" t="s">
         <v>77</v>
       </c>
@@ -3773,7 +3773,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A64" s="73" t="s">
         <v>77</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A65" s="73" t="s">
         <v>77</v>
       </c>
@@ -3821,7 +3821,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A66" s="73" t="s">
         <v>77</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A67" s="73" t="s">
         <v>77</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A68" s="74" t="s">
         <v>78</v>
       </c>
@@ -3895,7 +3895,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A69" s="74" t="s">
         <v>78</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A70" s="74" t="s">
         <v>78</v>
       </c>
@@ -3939,7 +3939,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A71" s="74" t="s">
         <v>78</v>
       </c>
@@ -3961,7 +3961,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A72" s="74" t="s">
         <v>78</v>
       </c>
@@ -3983,7 +3983,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A73" s="74" t="s">
         <v>78</v>
       </c>
@@ -4005,7 +4005,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A74" s="74" t="s">
         <v>78</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A75" s="74" t="s">
         <v>78</v>
       </c>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AyumuKaminaga\Documents\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6BF63C4-6B7C-4028-9B45-0E04092AC936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D687D1-CE81-4475-9379-4D60B0A3E02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1913,11 +1913,11 @@
       </c>
       <c r="L3" s="58">
         <f>SUMIF(H3:H75,"完了",F3:F75)</f>
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="M3" s="58">
         <f>K3-L3</f>
-        <v>28.099999999999994</v>
+        <v>27.599999999999994</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
@@ -1991,11 +1991,11 @@
       </c>
       <c r="L5" s="58">
         <f>SUMIFS(F3:F75,E3:E75,"アルファ",H3:H75,"完了")</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M5" s="58">
         <f t="shared" si="0"/>
-        <v>10.100000000000001</v>
+        <v>9.6000000000000014</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.4">
@@ -2278,11 +2278,11 @@
       </c>
       <c r="L12" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"上永",H3:H75,"完了")</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="M12" s="85">
         <f t="shared" ref="M12:M15" si="1">K12 - L12</f>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="N12" s="84"/>
       <c r="O12" s="100" t="s">
@@ -2625,11 +2625,11 @@
       </c>
       <c r="L19" s="85">
         <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"アルファ",H3:H75,"完了")</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M19" s="85">
         <f t="shared" ref="M19:M22" si="3">K19 - L19</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N19" s="84"/>
       <c r="O19" s="100" t="s">
@@ -3179,9 +3179,11 @@
       <c r="F38" s="15">
         <v>0.5</v>
       </c>
-      <c r="G38" s="22"/>
+      <c r="G38" s="22">
+        <v>0.5</v>
+      </c>
       <c r="H38" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.4">

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AyumuKaminaga\Documents\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D687D1-CE81-4475-9379-4D60B0A3E02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFC9B82-1003-419A-96BC-772F59C629CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="89">
   <si>
     <t>概要</t>
     <rPh sb="0" eb="2">
@@ -374,24 +374,6 @@
     <t>マスタ</t>
   </si>
   <si>
-    <t>ゲームコントローラ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>環境変数</t>
-    <rPh sb="0" eb="4">
-      <t>カンキョウヘンスウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>フラグ管理</t>
-    <rPh sb="3" eb="5">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>設計</t>
     <rPh sb="0" eb="2">
       <t>セッケイ</t>
@@ -402,13 +384,6 @@
     <t>床</t>
     <rPh sb="0" eb="1">
       <t>ユカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>破壊</t>
-    <rPh sb="0" eb="2">
-      <t>ハカイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -694,7 +669,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -1033,27 +1008,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="1"/>
       </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color theme="1"/>
       </right>
@@ -1090,21 +1047,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1194,7 +1136,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1316,16 +1258,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1334,43 +1267,40 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="32" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1388,10 +1318,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
@@ -1453,19 +1383,19 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1822,7 +1752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039B1606-320D-4390-8B98-CE6030BB2FAA}">
-  <dimension ref="A1:R75"/>
+  <dimension ref="A1:R72"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="3" width="25.375" bestFit="1" customWidth="1"/>
@@ -1866,22 +1796,22 @@
       <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="94" t="s">
+      <c r="J2" s="90" t="s">
+        <v>78</v>
+      </c>
+      <c r="K2" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="L2" s="90" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="94" t="s">
-        <v>88</v>
-      </c>
-      <c r="L2" s="94" t="s">
-        <v>86</v>
-      </c>
-      <c r="M2" s="94" t="s">
-        <v>87</v>
+      <c r="M2" s="90" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A3" s="71" t="s">
-        <v>74</v>
+      <c r="A3" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>13</v>
@@ -1895,34 +1825,34 @@
       <c r="E3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="75">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="75">
+      <c r="F3" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="71">
         <v>0.5</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J3" s="80" t="s">
-        <v>89</v>
-      </c>
-      <c r="K3" s="58">
-        <f>SUM(F3:F75)</f>
-        <v>52.599999999999994</v>
-      </c>
-      <c r="L3" s="58">
-        <f>SUMIF(H3:H75,"完了",F3:F75)</f>
+        <v>75</v>
+      </c>
+      <c r="J3" s="76" t="s">
+        <v>85</v>
+      </c>
+      <c r="K3" s="54">
+        <f>SUM(F3:F72)</f>
+        <v>49.599999999999994</v>
+      </c>
+      <c r="L3" s="54">
+        <f>SUMIF(H3:H72,"完了",F3:F72)</f>
         <v>25</v>
       </c>
-      <c r="M3" s="58">
+      <c r="M3" s="54">
         <f>K3-L3</f>
-        <v>27.599999999999994</v>
+        <v>24.599999999999994</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A4" s="71" t="s">
-        <v>74</v>
+      <c r="A4" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="4" t="s">
@@ -1934,34 +1864,34 @@
       <c r="E4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="75">
-        <v>0.5</v>
-      </c>
-      <c r="G4" s="75">
+      <c r="F4" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="71">
         <v>0.5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J4" s="81" t="s">
+        <v>75</v>
+      </c>
+      <c r="J4" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="58">
-        <f>SUMIF(E3:E75,"プロト",F3:F75)</f>
-        <v>27.5</v>
-      </c>
-      <c r="L4" s="58">
-        <f>SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"完了")</f>
+      <c r="K4" s="54">
+        <f>SUMIF(E3:E72,"プロト",F3:F72)</f>
         <v>24</v>
       </c>
-      <c r="M4" s="58">
+      <c r="L4" s="54">
+        <f>SUMIFS(F3:F72,E3:E72,"プロト",H3:H72,"完了")</f>
+        <v>24</v>
+      </c>
+      <c r="M4" s="54">
         <f t="shared" ref="M4:M7" si="0">K4-L4</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A5" s="71" t="s">
-        <v>74</v>
+      <c r="A5" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="4" t="s">
@@ -1973,34 +1903,34 @@
       <c r="E5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="75">
-        <v>0.5</v>
-      </c>
-      <c r="G5" s="75">
+      <c r="F5" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="71">
         <v>0.5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J5" s="89" t="s">
+        <v>75</v>
+      </c>
+      <c r="J5" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="58">
-        <f>SUMIF(E3:E75,"アルファ",F3:F75)</f>
-        <v>10.600000000000001</v>
-      </c>
-      <c r="L5" s="58">
-        <f>SUMIFS(F3:F75,E3:E75,"アルファ",H3:H75,"完了")</f>
+      <c r="K5" s="54">
+        <f>SUMIF(E3:E72,"アルファ",F3:F72)</f>
+        <v>11.100000000000001</v>
+      </c>
+      <c r="L5" s="54">
+        <f>SUMIFS(F3:F72,E3:E72,"アルファ",H3:H72,"完了")</f>
         <v>1</v>
       </c>
-      <c r="M5" s="58">
+      <c r="M5" s="54">
         <f t="shared" si="0"/>
-        <v>9.6000000000000014</v>
+        <v>10.100000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A6" s="71" t="s">
-        <v>74</v>
+      <c r="A6" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="13" t="s">
@@ -2012,34 +1942,34 @@
       <c r="E6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="75">
+      <c r="F6" s="71">
         <v>1</v>
       </c>
-      <c r="G6" s="75">
+      <c r="G6" s="71">
         <v>1</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J6" s="82" t="s">
+        <v>75</v>
+      </c>
+      <c r="J6" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="58">
-        <f>SUMIF(E3:E75,"ベータ",F3:F75)</f>
+      <c r="K6" s="54">
+        <f>SUMIF(E3:E72,"ベータ",F3:F72)</f>
         <v>12.5</v>
       </c>
-      <c r="L6" s="58">
-        <f>SUMIFS(F3:F75,E3:E75,"ベータ",H3:H75,"完了")</f>
+      <c r="L6" s="54">
+        <f>SUMIFS(F3:F72,E3:E72,"ベータ",H3:H72,"完了")</f>
         <v>0</v>
       </c>
-      <c r="M6" s="58">
+      <c r="M6" s="54">
         <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A7" s="71" t="s">
-        <v>74</v>
+      <c r="A7" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>26</v>
@@ -2053,32 +1983,32 @@
       <c r="E7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="75">
+      <c r="F7" s="71">
         <v>1</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J7" s="90" t="s">
-        <v>90</v>
-      </c>
-      <c r="K7" s="85">
-        <f>SUMIF(E3:E75,"マスタ",F3:F75)</f>
+        <v>76</v>
+      </c>
+      <c r="J7" s="86" t="s">
+        <v>86</v>
+      </c>
+      <c r="K7" s="81">
+        <f>SUMIF(E3:E72,"マスタ",F3:F72)</f>
         <v>2</v>
       </c>
-      <c r="L7" s="85">
-        <f>SUMIFS(F3:F75,E3:E75,"ベータ",H3:H75,"完了")</f>
+      <c r="L7" s="81">
+        <f>SUMIFS(F3:F72,E3:E72,"ベータ",H3:H72,"完了")</f>
         <v>0</v>
       </c>
-      <c r="M7" s="58">
+      <c r="M7" s="54">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A8" s="71" t="s">
-        <v>74</v>
+      <c r="A8" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="4" t="s">
@@ -2090,26 +2020,26 @@
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="75">
-        <v>0.5</v>
-      </c>
-      <c r="G8" s="75">
+      <c r="F8" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="71">
         <v>0.25</v>
       </c>
-      <c r="H8" s="48" t="s">
-        <v>79</v>
-      </c>
-      <c r="I8" s="84"/>
-      <c r="J8" s="83"/>
-      <c r="K8" s="84"/>
-      <c r="L8" s="84"/>
-      <c r="M8" s="84"/>
-      <c r="N8" s="84"/>
-      <c r="O8" s="84"/>
+      <c r="H8" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="I8" s="80"/>
+      <c r="J8" s="79"/>
+      <c r="K8" s="80"/>
+      <c r="L8" s="80"/>
+      <c r="M8" s="80"/>
+      <c r="N8" s="80"/>
+      <c r="O8" s="80"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A9" s="71" t="s">
-        <v>74</v>
+      <c r="A9" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="4" t="s">
@@ -2121,27 +2051,27 @@
       <c r="E9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="75">
-        <v>0.5</v>
-      </c>
-      <c r="G9" s="86">
+      <c r="F9" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="G9" s="82">
         <v>0.25</v>
       </c>
-      <c r="H9" s="88" t="s">
-        <v>79</v>
-      </c>
-      <c r="I9" s="95"/>
-      <c r="J9" s="97" t="s">
-        <v>91</v>
-      </c>
-      <c r="K9" s="98"/>
-      <c r="L9" s="98"/>
-      <c r="M9" s="98"/>
-      <c r="N9" s="84"/>
+      <c r="H9" s="84" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="91"/>
+      <c r="J9" s="93" t="s">
+        <v>87</v>
+      </c>
+      <c r="K9" s="94"/>
+      <c r="L9" s="94"/>
+      <c r="M9" s="94"/>
+      <c r="N9" s="80"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A10" s="71" t="s">
-        <v>74</v>
+      <c r="A10" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="4" t="s">
@@ -2153,45 +2083,45 @@
       <c r="E10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="75">
-        <v>0.5</v>
-      </c>
-      <c r="G10" s="86">
-        <v>0.5</v>
-      </c>
-      <c r="H10" s="88" t="s">
+      <c r="F10" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="G10" s="82">
+        <v>0.5</v>
+      </c>
+      <c r="H10" s="84" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="92"/>
+      <c r="J10" s="76" t="s">
+        <v>85</v>
+      </c>
+      <c r="K10" s="76" t="s">
+        <v>84</v>
+      </c>
+      <c r="L10" s="76" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="76" t="s">
+        <v>88</v>
+      </c>
+      <c r="N10" s="80"/>
+      <c r="O10" s="100" t="s">
         <v>79</v>
       </c>
-      <c r="I10" s="96"/>
-      <c r="J10" s="80" t="s">
-        <v>89</v>
-      </c>
-      <c r="K10" s="80" t="s">
+      <c r="P10" s="100" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q10" s="100" t="s">
+        <v>82</v>
+      </c>
+      <c r="R10" s="100" t="s">
         <v>88</v>
       </c>
-      <c r="L10" s="80" t="s">
-        <v>86</v>
-      </c>
-      <c r="M10" s="80" t="s">
-        <v>92</v>
-      </c>
-      <c r="N10" s="84"/>
-      <c r="O10" s="104" t="s">
-        <v>83</v>
-      </c>
-      <c r="P10" s="104" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q10" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="R10" s="104" t="s">
-        <v>92</v>
-      </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A11" s="71" t="s">
-        <v>74</v>
+      <c r="A11" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="4" t="s">
@@ -2203,51 +2133,51 @@
       <c r="E11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="75">
-        <v>0.5</v>
-      </c>
-      <c r="G11" s="86">
+      <c r="F11" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="82">
         <v>0.25</v>
       </c>
-      <c r="H11" s="88" t="s">
-        <v>79</v>
-      </c>
-      <c r="I11" s="96"/>
-      <c r="J11" s="99" t="s">
-        <v>74</v>
-      </c>
-      <c r="K11" s="85">
-        <f>SUMIF(A3:A75,"大崎",F3:F75)</f>
+      <c r="H11" s="84" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" s="92"/>
+      <c r="J11" s="95" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11" s="81">
+        <f>SUMIF(A3:A72,"大崎",F3:F72)</f>
         <v>12.099999999999998</v>
       </c>
-      <c r="L11" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"大崎",H3:H75,"完了")</f>
+      <c r="L11" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"大崎",H3:H72,"完了")</f>
         <v>5.5</v>
       </c>
-      <c r="M11" s="85">
+      <c r="M11" s="81">
         <f>K11 - L11</f>
         <v>6.5999999999999979</v>
       </c>
-      <c r="N11" s="84"/>
-      <c r="O11" s="99" t="s">
-        <v>74</v>
-      </c>
-      <c r="P11" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"プロト")</f>
+      <c r="N11" s="80"/>
+      <c r="O11" s="95" t="s">
+        <v>70</v>
+      </c>
+      <c r="P11" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"大崎",E3:E72,"プロト")</f>
         <v>5</v>
       </c>
-      <c r="Q11" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"プロト",H3:H75,"完了")</f>
+      <c r="Q11" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"大崎",E3:E72,"プロト",H3:H72,"完了")</f>
         <v>5</v>
       </c>
-      <c r="R11" s="85">
+      <c r="R11" s="81">
         <f>P11 - Q11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A12" s="71" t="s">
-        <v>74</v>
+      <c r="A12" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="21" t="s">
@@ -2259,105 +2189,105 @@
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="75">
+      <c r="F12" s="71">
         <v>1</v>
       </c>
-      <c r="G12" s="86">
-        <v>0.5</v>
-      </c>
-      <c r="H12" s="88" t="s">
-        <v>79</v>
-      </c>
-      <c r="I12" s="96"/>
-      <c r="J12" s="100" t="s">
+      <c r="G12" s="82">
+        <v>0.5</v>
+      </c>
+      <c r="H12" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="K12" s="85">
-        <f>SUMIF(A3:A75,"上永",F3:F75)</f>
+      <c r="I12" s="92"/>
+      <c r="J12" s="96" t="s">
+        <v>71</v>
+      </c>
+      <c r="K12" s="81">
+        <f>SUMIF(A3:A72,"上永",F3:F72)</f>
         <v>17</v>
       </c>
-      <c r="L12" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"上永",H3:H75,"完了")</f>
+      <c r="L12" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"上永",H3:H72,"完了")</f>
         <v>8.5</v>
       </c>
-      <c r="M12" s="85">
+      <c r="M12" s="81">
         <f t="shared" ref="M12:M15" si="1">K12 - L12</f>
         <v>8.5</v>
       </c>
-      <c r="N12" s="84"/>
-      <c r="O12" s="100" t="s">
-        <v>75</v>
-      </c>
-      <c r="P12" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"プロト")</f>
+      <c r="N12" s="80"/>
+      <c r="O12" s="96" t="s">
+        <v>71</v>
+      </c>
+      <c r="P12" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"上永",E3:E72,"プロト")</f>
         <v>8</v>
       </c>
-      <c r="Q12" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"プロト",H3:H75,"完了")</f>
+      <c r="Q12" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"上永",E3:E72,"プロト",H3:H72,"完了")</f>
         <v>8</v>
       </c>
-      <c r="R12" s="85">
+      <c r="R12" s="81">
         <f t="shared" ref="R12:R15" si="2">P12 - Q12</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A13" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" s="77"/>
+      <c r="A13" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="73"/>
       <c r="C13" s="13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="75">
+      <c r="F13" s="71">
         <v>1.5</v>
       </c>
-      <c r="G13" s="75"/>
-      <c r="H13" s="87" t="s">
-        <v>80</v>
-      </c>
-      <c r="I13" s="91"/>
-      <c r="J13" s="101" t="s">
-        <v>77</v>
-      </c>
-      <c r="K13" s="85">
-        <f>SUMIF(A3:A75,"川浪",F3:F75)</f>
-        <v>9.5</v>
-      </c>
-      <c r="L13" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"川浪",H3:H75,"完了")</f>
+      <c r="G13" s="71"/>
+      <c r="H13" s="83" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" s="87"/>
+      <c r="J13" s="97" t="s">
+        <v>73</v>
+      </c>
+      <c r="K13" s="81">
+        <f>SUMIF(A3:A72,"川浪",F3:F72)</f>
+        <v>6.5</v>
+      </c>
+      <c r="L13" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"川浪",H3:H72,"完了")</f>
         <v>6</v>
       </c>
-      <c r="M13" s="85">
+      <c r="M13" s="81">
         <f t="shared" si="1"/>
-        <v>3.5</v>
-      </c>
-      <c r="N13" s="84"/>
-      <c r="O13" s="101" t="s">
-        <v>77</v>
-      </c>
-      <c r="P13" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"プロト")</f>
-        <v>8.5</v>
-      </c>
-      <c r="Q13" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"プロト",H3:H75,"完了")</f>
+        <v>0.5</v>
+      </c>
+      <c r="N13" s="80"/>
+      <c r="O13" s="97" t="s">
+        <v>73</v>
+      </c>
+      <c r="P13" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"川浪",E3:E72,"プロト")</f>
         <v>6</v>
       </c>
-      <c r="R13" s="85">
+      <c r="Q13" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"川浪",E3:E72,"プロト",H3:H72,"完了")</f>
+        <v>6</v>
+      </c>
+      <c r="R13" s="81">
         <f t="shared" si="2"/>
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A14" s="71" t="s">
-        <v>74</v>
+      <c r="A14" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>27</v>
@@ -2371,49 +2301,49 @@
       <c r="E14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="75">
+      <c r="F14" s="71">
         <v>0.2</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I14" s="92"/>
-      <c r="J14" s="102" t="s">
-        <v>76</v>
-      </c>
-      <c r="K14" s="85">
-        <f>SUMIF(A3:A75,"佐々木",F3:F75)</f>
+      <c r="I14" s="88"/>
+      <c r="J14" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="K14" s="81">
+        <f>SUMIF(A3:A72,"佐々木",F3:F72)</f>
         <v>6</v>
       </c>
-      <c r="L14" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"佐々木",H3:H75,"完了")</f>
+      <c r="L14" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"佐々木",H3:H72,"完了")</f>
         <v>4</v>
       </c>
-      <c r="M14" s="85">
+      <c r="M14" s="81">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="N14" s="84"/>
-      <c r="O14" s="102" t="s">
-        <v>76</v>
-      </c>
-      <c r="P14" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"プロト")</f>
+      <c r="N14" s="80"/>
+      <c r="O14" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P14" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"佐々木",E3:E72,"プロト")</f>
         <v>4</v>
       </c>
-      <c r="Q14" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"プロト",H3:H75,"完了")</f>
+      <c r="Q14" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"佐々木",E3:E72,"プロト",H3:H72,"完了")</f>
         <v>4</v>
       </c>
-      <c r="R14" s="85">
+      <c r="R14" s="81">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A15" s="71" t="s">
-        <v>74</v>
+      <c r="A15" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="4" t="s">
@@ -2425,49 +2355,49 @@
       <c r="E15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="75">
+      <c r="F15" s="71">
         <v>0.2</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I15" s="84"/>
-      <c r="J15" s="103" t="s">
-        <v>78</v>
-      </c>
-      <c r="K15" s="85">
-        <f>SUMIF(A3:A75,"誰でも",F3:F75)</f>
+      <c r="I15" s="80"/>
+      <c r="J15" s="99" t="s">
+        <v>74</v>
+      </c>
+      <c r="K15" s="81">
+        <f>SUMIF(A3:A72,"誰でも",F3:F72)</f>
         <v>8</v>
       </c>
-      <c r="L15" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"誰でも",H3:H75,"完了")</f>
+      <c r="L15" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"誰でも",H3:H72,"完了")</f>
         <v>1</v>
       </c>
-      <c r="M15" s="85">
+      <c r="M15" s="81">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="N15" s="84"/>
-      <c r="O15" s="103" t="s">
-        <v>78</v>
-      </c>
-      <c r="P15" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"プロト")</f>
-        <v>2</v>
-      </c>
-      <c r="Q15" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"プロト",H3:H75,"完了")</f>
+      <c r="N15" s="80"/>
+      <c r="O15" s="99" t="s">
+        <v>74</v>
+      </c>
+      <c r="P15" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"誰でも",E3:E72,"プロト")</f>
         <v>1</v>
       </c>
-      <c r="R15" s="85">
+      <c r="Q15" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"誰でも",E3:E72,"プロト",H3:H72,"完了")</f>
+        <v>1</v>
+      </c>
+      <c r="R15" s="81">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A16" s="71" t="s">
-        <v>74</v>
+      <c r="A16" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B16" s="12"/>
       <c r="C16" s="13" t="s">
@@ -2479,20 +2409,20 @@
       <c r="E16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="75">
+      <c r="F16" s="71">
         <v>0.2</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I16" s="84"/>
-      <c r="N16" s="84"/>
-      <c r="O16" s="84"/>
+      <c r="I16" s="80"/>
+      <c r="N16" s="80"/>
+      <c r="O16" s="80"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A17" s="71" t="s">
-        <v>74</v>
+      <c r="A17" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>31</v>
@@ -2506,43 +2436,43 @@
       <c r="E17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="76">
+      <c r="F17" s="72">
         <v>0.5</v>
       </c>
       <c r="G17" s="22"/>
       <c r="H17" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I17" s="84"/>
-      <c r="J17" s="105" t="s">
+      <c r="I17" s="80"/>
+      <c r="J17" s="101" t="s">
+        <v>80</v>
+      </c>
+      <c r="K17" s="101" t="s">
         <v>84</v>
       </c>
-      <c r="K17" s="105" t="s">
+      <c r="L17" s="101" t="s">
+        <v>82</v>
+      </c>
+      <c r="M17" s="101" t="s">
         <v>88</v>
       </c>
-      <c r="L17" s="105" t="s">
-        <v>86</v>
-      </c>
-      <c r="M17" s="105" t="s">
-        <v>92</v>
-      </c>
-      <c r="N17" s="93"/>
-      <c r="O17" s="106" t="s">
-        <v>85</v>
-      </c>
-      <c r="P17" s="106" t="s">
+      <c r="N17" s="89"/>
+      <c r="O17" s="102" t="s">
+        <v>81</v>
+      </c>
+      <c r="P17" s="102" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q17" s="102" t="s">
+        <v>82</v>
+      </c>
+      <c r="R17" s="102" t="s">
         <v>88</v>
       </c>
-      <c r="Q17" s="106" t="s">
-        <v>86</v>
-      </c>
-      <c r="R17" s="106" t="s">
-        <v>92</v>
-      </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A18" s="71" t="s">
-        <v>74</v>
+      <c r="A18" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B18" s="17"/>
       <c r="C18" s="21" t="s">
@@ -2554,49 +2484,49 @@
       <c r="E18" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="76">
+      <c r="F18" s="72">
         <v>0.5</v>
       </c>
       <c r="G18" s="26"/>
       <c r="H18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I18" s="84"/>
-      <c r="J18" s="99" t="s">
-        <v>74</v>
-      </c>
-      <c r="K18" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"アルファ")</f>
+      <c r="I18" s="80"/>
+      <c r="J18" s="95" t="s">
+        <v>70</v>
+      </c>
+      <c r="K18" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"大崎",E3:E72,"アルファ")</f>
         <v>3.6000000000000005</v>
       </c>
-      <c r="L18" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"アルファ",H3:H75,"完了")</f>
-        <v>0.5</v>
-      </c>
-      <c r="M18" s="85">
+      <c r="L18" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"大崎",E3:E72,"アルファ",H3:H72,"完了")</f>
+        <v>0.5</v>
+      </c>
+      <c r="M18" s="81">
         <f>K18 - L18</f>
         <v>3.1000000000000005</v>
       </c>
-      <c r="N18" s="84"/>
-      <c r="O18" s="99" t="s">
-        <v>74</v>
-      </c>
-      <c r="P18" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"ベータ")</f>
+      <c r="N18" s="80"/>
+      <c r="O18" s="95" t="s">
+        <v>70</v>
+      </c>
+      <c r="P18" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"大崎",E3:E72,"ベータ")</f>
         <v>3.5</v>
       </c>
-      <c r="Q18" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"ベータ",H3:H75,"完了")</f>
+      <c r="Q18" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"大崎",E3:E72,"ベータ",H3:H72,"完了")</f>
         <v>0</v>
       </c>
-      <c r="R18" s="85">
+      <c r="R18" s="81">
         <f>P18 - Q18</f>
         <v>3.5</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A19" s="71" t="s">
-        <v>74</v>
+      <c r="A19" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="21" t="s">
@@ -2608,49 +2538,49 @@
       <c r="E19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="76">
+      <c r="F19" s="72">
         <v>0.5</v>
       </c>
       <c r="G19" s="24"/>
       <c r="H19" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I19" s="84"/>
-      <c r="J19" s="100" t="s">
-        <v>75</v>
-      </c>
-      <c r="K19" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"アルファ")</f>
+      <c r="I19" s="80"/>
+      <c r="J19" s="96" t="s">
+        <v>71</v>
+      </c>
+      <c r="K19" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"上永",E3:E72,"アルファ")</f>
         <v>4</v>
       </c>
-      <c r="L19" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"アルファ",H3:H75,"完了")</f>
-        <v>0.5</v>
-      </c>
-      <c r="M19" s="85">
+      <c r="L19" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"上永",E3:E72,"アルファ",H3:H72,"完了")</f>
+        <v>0.5</v>
+      </c>
+      <c r="M19" s="81">
         <f t="shared" ref="M19:M22" si="3">K19 - L19</f>
         <v>3.5</v>
       </c>
-      <c r="N19" s="84"/>
-      <c r="O19" s="100" t="s">
-        <v>75</v>
-      </c>
-      <c r="P19" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"ベータ")</f>
+      <c r="N19" s="80"/>
+      <c r="O19" s="96" t="s">
+        <v>71</v>
+      </c>
+      <c r="P19" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"上永",E3:E72,"ベータ")</f>
         <v>5</v>
       </c>
-      <c r="Q19" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"ベータ",H3:H75,"完了")</f>
+      <c r="Q19" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"上永",E3:E72,"ベータ",H3:H72,"完了")</f>
         <v>0</v>
       </c>
-      <c r="R19" s="85">
+      <c r="R19" s="81">
         <f t="shared" ref="R19:R22" si="4">P19 - Q19</f>
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A20" s="71" t="s">
-        <v>74</v>
+      <c r="A20" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="13" t="s">
@@ -2662,47 +2592,47 @@
       <c r="E20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="76">
+      <c r="F20" s="72">
         <v>0.5</v>
       </c>
       <c r="G20" s="24"/>
       <c r="H20" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J20" s="101" t="s">
-        <v>77</v>
-      </c>
-      <c r="K20" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"アルファ")</f>
-        <v>1</v>
-      </c>
-      <c r="L20" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"アルファ",H3:H75,"完了")</f>
+      <c r="J20" s="97" t="s">
+        <v>73</v>
+      </c>
+      <c r="K20" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"川浪",E3:E72,"アルファ")</f>
+        <v>0.5</v>
+      </c>
+      <c r="L20" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"川浪",E3:E72,"アルファ",H3:H72,"完了")</f>
         <v>0</v>
       </c>
-      <c r="M20" s="85">
+      <c r="M20" s="81">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O20" s="101" t="s">
-        <v>77</v>
-      </c>
-      <c r="P20" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"ベータ")</f>
+        <v>0.5</v>
+      </c>
+      <c r="O20" s="97" t="s">
+        <v>73</v>
+      </c>
+      <c r="P20" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"川浪",E3:E72,"ベータ")</f>
         <v>0</v>
       </c>
-      <c r="Q20" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"ベータ",H3:H75,"完了")</f>
+      <c r="Q20" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"川浪",E3:E72,"ベータ",H3:H72,"完了")</f>
         <v>0</v>
       </c>
-      <c r="R20" s="85">
+      <c r="R20" s="81">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A21" s="71" t="s">
-        <v>74</v>
+      <c r="A21" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>35</v>
@@ -2716,47 +2646,47 @@
       <c r="E21" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="76">
+      <c r="F21" s="72">
         <v>0.5</v>
       </c>
       <c r="G21" s="22"/>
       <c r="H21" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J21" s="102" t="s">
-        <v>76</v>
-      </c>
-      <c r="K21" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"アルファ")</f>
+      <c r="J21" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="K21" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"佐々木",E3:E72,"アルファ")</f>
         <v>0</v>
       </c>
-      <c r="L21" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"アルファ",H3:H75,"完了")</f>
+      <c r="L21" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"佐々木",E3:E72,"アルファ",H3:H72,"完了")</f>
         <v>0</v>
       </c>
-      <c r="M21" s="85">
+      <c r="M21" s="81">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O21" s="102" t="s">
-        <v>76</v>
-      </c>
-      <c r="P21" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"ベータ")</f>
+      <c r="O21" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P21" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"佐々木",E3:E72,"ベータ")</f>
         <v>0</v>
       </c>
-      <c r="Q21" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"ベータ",H3:H75,"完了")</f>
+      <c r="Q21" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"佐々木",E3:E72,"ベータ",H3:H72,"完了")</f>
         <v>0</v>
       </c>
-      <c r="R21" s="85">
+      <c r="R21" s="81">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A22" s="71" t="s">
-        <v>74</v>
+      <c r="A22" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B22" s="17"/>
       <c r="C22" s="21" t="s">
@@ -2768,47 +2698,47 @@
       <c r="E22" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="76">
+      <c r="F22" s="72">
         <v>0.5</v>
       </c>
       <c r="G22" s="26"/>
       <c r="H22" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J22" s="103" t="s">
-        <v>78</v>
-      </c>
-      <c r="K22" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"アルファ")</f>
-        <v>2</v>
-      </c>
-      <c r="L22" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"アルファ",H3:H75,"完了")</f>
+      <c r="J22" s="99" t="s">
+        <v>74</v>
+      </c>
+      <c r="K22" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"誰でも",E3:E72,"アルファ")</f>
+        <v>3</v>
+      </c>
+      <c r="L22" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"誰でも",E3:E72,"アルファ",H3:H72,"完了")</f>
         <v>0</v>
       </c>
-      <c r="M22" s="85">
+      <c r="M22" s="81">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="O22" s="103" t="s">
-        <v>78</v>
-      </c>
-      <c r="P22" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"ベータ")</f>
+        <v>3</v>
+      </c>
+      <c r="O22" s="99" t="s">
+        <v>74</v>
+      </c>
+      <c r="P22" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"誰でも",E3:E72,"ベータ")</f>
         <v>4</v>
       </c>
-      <c r="Q22" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"ベータ",H3:H75,"完了")</f>
+      <c r="Q22" s="81">
+        <f>SUMIFS(F3:F72,A3:A72,"誰でも",E3:E72,"ベータ",H3:H72,"完了")</f>
         <v>0</v>
       </c>
-      <c r="R22" s="85">
+      <c r="R22" s="81">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A23" s="71" t="s">
-        <v>74</v>
+      <c r="A23" s="67" t="s">
+        <v>70</v>
       </c>
       <c r="B23" s="18"/>
       <c r="C23" s="13" t="s">
@@ -2820,7 +2750,7 @@
       <c r="E23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F23" s="76">
+      <c r="F23" s="72">
         <v>0.5</v>
       </c>
       <c r="G23" s="24"/>
@@ -2829,8 +2759,8 @@
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A24" s="72" t="s">
-        <v>75</v>
+      <c r="A24" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>37</v>
@@ -2851,12 +2781,12 @@
         <v>1</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A25" s="72" t="s">
-        <v>75</v>
+      <c r="A25" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B25" s="17"/>
       <c r="C25" s="21" t="s">
@@ -2875,12 +2805,12 @@
         <v>1</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A26" s="72" t="s">
-        <v>75</v>
+      <c r="A26" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B26" s="17"/>
       <c r="C26" s="21" t="s">
@@ -2899,12 +2829,12 @@
         <v>0.5</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A27" s="72" t="s">
-        <v>75</v>
+      <c r="A27" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B27" s="17"/>
       <c r="C27" s="21" t="s">
@@ -2923,12 +2853,12 @@
         <v>1</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A28" s="72" t="s">
-        <v>75</v>
+      <c r="A28" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B28" s="17"/>
       <c r="C28" s="21" t="s">
@@ -2947,12 +2877,12 @@
         <v>0.5</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A29" s="72" t="s">
-        <v>75</v>
+      <c r="A29" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B29" s="18"/>
       <c r="C29" s="13" t="s">
@@ -2973,8 +2903,8 @@
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A30" s="72" t="s">
-        <v>75</v>
+      <c r="A30" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>43</v>
@@ -2995,12 +2925,12 @@
         <v>2</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A31" s="72" t="s">
-        <v>75</v>
+      <c r="A31" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B31" s="17"/>
       <c r="C31" s="21" t="s">
@@ -3019,12 +2949,12 @@
         <v>0.5</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A32" s="72" t="s">
-        <v>75</v>
+      <c r="A32" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B32" s="17"/>
       <c r="C32" s="21" t="s">
@@ -3043,12 +2973,12 @@
         <v>1</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A33" s="72" t="s">
-        <v>75</v>
+      <c r="A33" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B33" s="18"/>
       <c r="C33" s="13" t="s">
@@ -3067,12 +2997,12 @@
         <v>1</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A34" s="72" t="s">
-        <v>75</v>
+      <c r="A34" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>47</v>
@@ -3095,8 +3025,8 @@
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A35" s="72" t="s">
-        <v>75</v>
+      <c r="A35" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B35" s="17"/>
       <c r="C35" s="21" t="s">
@@ -3117,8 +3047,8 @@
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A36" s="72" t="s">
-        <v>75</v>
+      <c r="A36" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B36" s="17"/>
       <c r="C36" s="21" t="s">
@@ -3139,8 +3069,8 @@
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A37" s="72" t="s">
-        <v>75</v>
+      <c r="A37" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B37" s="18"/>
       <c r="C37" s="13" t="s">
@@ -3161,8 +3091,8 @@
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A38" s="72" t="s">
-        <v>75</v>
+      <c r="A38" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B38" s="14" t="s">
         <v>49</v>
@@ -3183,12 +3113,12 @@
         <v>0.5</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A39" s="72" t="s">
-        <v>75</v>
+      <c r="A39" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="21" t="s">
@@ -3207,11 +3137,11 @@
       <c r="H39" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K39" s="79"/>
+      <c r="K39" s="75"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A40" s="72" t="s">
-        <v>75</v>
+      <c r="A40" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B40" s="17"/>
       <c r="C40" s="21" t="s">
@@ -3230,11 +3160,11 @@
       <c r="H40" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K40" s="79"/>
+      <c r="K40" s="75"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A41" s="72" t="s">
-        <v>75</v>
+      <c r="A41" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="13" t="s">
@@ -3253,13 +3183,13 @@
         <v>0.5</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="K41" s="79"/>
+        <v>75</v>
+      </c>
+      <c r="K41" s="75"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A42" s="72" t="s">
-        <v>75</v>
+      <c r="A42" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>51</v>
@@ -3280,11 +3210,11 @@
       <c r="H42" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K42" s="79"/>
+      <c r="K42" s="75"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A43" s="72" t="s">
-        <v>75</v>
+      <c r="A43" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B43" s="17"/>
       <c r="C43" s="21" t="s">
@@ -3303,11 +3233,11 @@
       <c r="H43" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K43" s="79"/>
+      <c r="K43" s="75"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A44" s="72" t="s">
-        <v>75</v>
+      <c r="A44" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B44" s="17"/>
       <c r="C44" s="21" t="s">
@@ -3328,8 +3258,8 @@
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A45" s="72" t="s">
-        <v>75</v>
+      <c r="A45" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B45" s="17"/>
       <c r="C45" s="21" t="s">
@@ -3350,8 +3280,8 @@
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A46" s="72" t="s">
-        <v>75</v>
+      <c r="A46" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B46" s="17"/>
       <c r="C46" s="21" t="s">
@@ -3372,8 +3302,8 @@
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A47" s="72" t="s">
-        <v>75</v>
+      <c r="A47" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B47" s="18"/>
       <c r="C47" s="13" t="s">
@@ -3394,8 +3324,8 @@
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A48" s="72" t="s">
-        <v>75</v>
+      <c r="A48" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B48" s="14" t="s">
         <v>54</v>
@@ -3418,8 +3348,8 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A49" s="72" t="s">
-        <v>75</v>
+      <c r="A49" s="68" t="s">
+        <v>71</v>
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="13" t="s">
@@ -3440,8 +3370,8 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A50" s="70" t="s">
-        <v>76</v>
+      <c r="A50" s="66" t="s">
+        <v>72</v>
       </c>
       <c r="B50" s="14" t="s">
         <v>55</v>
@@ -3462,12 +3392,12 @@
         <v>0.5</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A51" s="70" t="s">
-        <v>76</v>
+      <c r="A51" s="66" t="s">
+        <v>72</v>
       </c>
       <c r="B51" s="32" t="s">
         <v>58</v>
@@ -3488,12 +3418,12 @@
         <v>3</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A52" s="70" t="s">
-        <v>76</v>
+      <c r="A52" s="66" t="s">
+        <v>72</v>
       </c>
       <c r="B52" s="40" t="s">
         <v>60</v>
@@ -3516,10 +3446,10 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A53" s="70" t="s">
-        <v>76</v>
-      </c>
-      <c r="B53" s="44"/>
+      <c r="A53" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="B53" s="43"/>
       <c r="C53" s="39" t="s">
         <v>62</v>
       </c>
@@ -3538,529 +3468,461 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A54" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B54" s="40" t="s">
+      <c r="A54" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C54" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="C54" s="38" t="s">
+      <c r="D54" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="E54" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" s="46">
+        <v>0.5</v>
+      </c>
+      <c r="G54" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="H54" s="45" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A55" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="B55" s="48"/>
+      <c r="C55" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="D54" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="E54" s="42" t="s">
+      <c r="D55" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="43">
+      <c r="F55" s="53">
         <v>1</v>
       </c>
-      <c r="G54" s="31"/>
-      <c r="H54" s="3" t="s">
+      <c r="G55" s="54">
+        <v>1</v>
+      </c>
+      <c r="H55" s="45" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A56" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56" s="48"/>
+      <c r="C56" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="D56" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56" s="23">
+        <v>1</v>
+      </c>
+      <c r="H56" s="45" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A57" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="B57" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="C57" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="D57" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="46">
+        <v>0.5</v>
+      </c>
+      <c r="G57" s="64">
+        <v>0.5</v>
+      </c>
+      <c r="H57" s="45" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A58" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="B58" s="48"/>
+      <c r="C58" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="D58" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="G58" s="64">
+        <v>0.5</v>
+      </c>
+      <c r="H58" s="45" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A59" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="48"/>
+      <c r="C59" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="D59" s="58" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="G59" s="64">
+        <v>0.5</v>
+      </c>
+      <c r="H59" s="45" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A60" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="B60" s="48"/>
+      <c r="C60" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="D60" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="G60" s="64"/>
+      <c r="H60" s="45" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A55" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B55" s="45"/>
-      <c r="C55" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="D55" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E55" s="48" t="s">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A61" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" s="48"/>
+      <c r="C61" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="60" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="63">
+        <v>0.5</v>
+      </c>
+      <c r="G61" s="64">
+        <v>0.5</v>
+      </c>
+      <c r="H61" s="45" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A62" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="B62" s="48"/>
+      <c r="C62" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="D62" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" s="60" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="G62" s="64">
+        <v>0.5</v>
+      </c>
+      <c r="H62" s="45" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A63" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="B63" s="48"/>
+      <c r="C63" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D63" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="60" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="G63" s="64">
+        <v>0.5</v>
+      </c>
+      <c r="H63" s="45" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A64" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="B64" s="49"/>
+      <c r="C64" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="D64" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="G64" s="64">
+        <v>0.5</v>
+      </c>
+      <c r="H64" s="59" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A65" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="B65" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="D65" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" s="65">
+        <v>1</v>
+      </c>
+      <c r="G65" s="65">
+        <v>1</v>
+      </c>
+      <c r="H65" s="59" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A66" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="B66" s="48"/>
+      <c r="C66" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="D66" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="F55">
+      <c r="F66" s="65">
         <v>1</v>
       </c>
-      <c r="G55" s="23"/>
-      <c r="H55" s="48" t="s">
+      <c r="G66" s="54"/>
+      <c r="H66" s="59" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A67" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" s="48"/>
+      <c r="C67" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="D67" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="F67" s="65">
+        <v>1</v>
+      </c>
+      <c r="G67" s="63"/>
+      <c r="H67" s="59" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A56" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B56" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="C56" s="53" t="s">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A68" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="48"/>
+      <c r="C68" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D68" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="F68" s="65">
+        <v>1</v>
+      </c>
+      <c r="G68" s="54"/>
+      <c r="H68" s="59" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A69" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="B69" s="48"/>
+      <c r="C69" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="D69" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="F69" s="65">
+        <v>1</v>
+      </c>
+      <c r="G69" s="63"/>
+      <c r="H69" s="59" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A70" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" s="48"/>
+      <c r="C70" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="D70" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" s="65">
+        <v>1</v>
+      </c>
+      <c r="G70" s="54"/>
+      <c r="H70" s="59" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A71" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="B71" s="48"/>
+      <c r="C71" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D71" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="F71" s="65">
+        <v>1</v>
+      </c>
+      <c r="G71" s="54"/>
+      <c r="H71" s="59" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A72" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="B72" s="49"/>
+      <c r="C72" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="D56" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E56" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" s="49">
-        <v>0.5</v>
-      </c>
-      <c r="G56" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="H56" s="48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A57" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B57" s="51"/>
-      <c r="C57" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="D57" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E57" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" s="57">
+      <c r="D72" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" s="26">
         <v>1</v>
       </c>
-      <c r="G57" s="58">
-        <v>1</v>
-      </c>
-      <c r="H57" s="48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A58" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B58" s="51"/>
-      <c r="C58" s="54" t="s">
-        <v>69</v>
-      </c>
-      <c r="D58" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E58" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="57">
-        <v>1</v>
-      </c>
-      <c r="G58" s="56"/>
-      <c r="H58" s="48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A59" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B59" s="51"/>
-      <c r="C59" s="54" t="s">
-        <v>23</v>
-      </c>
-      <c r="D59" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E59" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59">
-        <v>1</v>
-      </c>
-      <c r="G59" s="23">
-        <v>1</v>
-      </c>
-      <c r="H59" s="48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A60" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B60" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="C60" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="D60" s="59" t="s">
-        <v>14</v>
-      </c>
-      <c r="E60" s="60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" s="49">
-        <v>0.5</v>
-      </c>
-      <c r="G60" s="68">
-        <v>0.5</v>
-      </c>
-      <c r="H60" s="48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A61" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B61" s="51"/>
-      <c r="C61" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="D61" s="63" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" s="58">
-        <v>0.5</v>
-      </c>
-      <c r="G61" s="68">
-        <v>0.5</v>
-      </c>
-      <c r="H61" s="48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A62" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B62" s="51"/>
-      <c r="C62" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="D62" s="62" t="s">
-        <v>14</v>
-      </c>
-      <c r="E62" s="66" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" s="58">
-        <v>0.5</v>
-      </c>
-      <c r="G62" s="68">
-        <v>0.5</v>
-      </c>
-      <c r="H62" s="48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A63" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B63" s="51"/>
-      <c r="C63" s="54" t="s">
-        <v>47</v>
-      </c>
-      <c r="D63" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E63" s="64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" s="58">
-        <v>0.5</v>
-      </c>
-      <c r="G63" s="68"/>
-      <c r="H63" s="48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A64" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B64" s="51"/>
-      <c r="C64" s="54" t="s">
-        <v>32</v>
-      </c>
-      <c r="D64" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E64" s="64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" s="67">
-        <v>0.5</v>
-      </c>
-      <c r="G64" s="68">
-        <v>0.5</v>
-      </c>
-      <c r="H64" s="48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A65" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B65" s="51"/>
-      <c r="C65" s="54" t="s">
-        <v>34</v>
-      </c>
-      <c r="D65" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E65" s="64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" s="58">
-        <v>0.5</v>
-      </c>
-      <c r="G65" s="68">
-        <v>0.5</v>
-      </c>
-      <c r="H65" s="48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A66" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B66" s="51"/>
-      <c r="C66" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="D66" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F66" s="58">
-        <v>0.5</v>
-      </c>
-      <c r="G66" s="68">
-        <v>0.5</v>
-      </c>
-      <c r="H66" s="48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A67" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B67" s="52"/>
-      <c r="C67" s="55" t="s">
-        <v>37</v>
-      </c>
-      <c r="D67" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F67" s="58">
-        <v>0.5</v>
-      </c>
-      <c r="G67" s="68">
-        <v>0.5</v>
-      </c>
-      <c r="H67" s="63" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A68" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B68" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="C68" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="D68" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E68" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" s="69">
-        <v>1</v>
-      </c>
-      <c r="G68" s="69">
-        <v>1</v>
-      </c>
-      <c r="H68" s="63" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A69" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B69" s="51"/>
-      <c r="C69" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="D69" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E69" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" s="69">
-        <v>1</v>
-      </c>
-      <c r="G69" s="58"/>
-      <c r="H69" s="63" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A70" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B70" s="51"/>
-      <c r="C70" s="54" t="s">
-        <v>47</v>
-      </c>
-      <c r="D70" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="F70" s="69">
-        <v>1</v>
-      </c>
-      <c r="G70" s="67"/>
-      <c r="H70" s="63" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A71" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B71" s="51"/>
-      <c r="C71" s="54" t="s">
-        <v>35</v>
-      </c>
-      <c r="D71" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E71" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="F71" s="69">
-        <v>1</v>
-      </c>
-      <c r="G71" s="58"/>
-      <c r="H71" s="63" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A72" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B72" s="51"/>
-      <c r="C72" s="54" t="s">
-        <v>31</v>
-      </c>
-      <c r="D72" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E72" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="F72" s="69">
-        <v>1</v>
-      </c>
-      <c r="G72" s="67"/>
-      <c r="H72" s="63" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A73" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B73" s="51"/>
-      <c r="C73" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="D73" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E73" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="F73" s="69">
-        <v>1</v>
-      </c>
-      <c r="G73" s="58"/>
-      <c r="H73" s="63" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A74" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B74" s="51"/>
-      <c r="C74" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="D74" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E74" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="F74" s="69">
-        <v>1</v>
-      </c>
-      <c r="G74" s="58"/>
-      <c r="H74" s="63" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A75" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B75" s="52"/>
-      <c r="C75" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="D75" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E75" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="F75" s="26">
-        <v>1</v>
-      </c>
-      <c r="G75" s="78"/>
-      <c r="H75" s="63" t="s">
+      <c r="G72" s="74"/>
+      <c r="H72" s="59" t="s">
         <v>57</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H75" xr:uid="{6668A6B0-AE49-40A9-BDCA-1EF7E08764AB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H72" xr:uid="{6668A6B0-AE49-40A9-BDCA-1EF7E08764AB}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E75" xr:uid="{3F25CF45-EEFF-4838-8184-2DB508A95967}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E72" xr:uid="{3F25CF45-EEFF-4838-8184-2DB508A95967}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D75" xr:uid="{D99FF9D9-52C2-47CC-BC93-4ACF23B2DA2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D72" xr:uid="{D99FF9D9-52C2-47CC-BC93-4ACF23B2DA2A}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
   </dataValidations>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AyumuKaminaga\Documents\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFC9B82-1003-419A-96BC-772F59C629CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D687D1-CE81-4475-9379-4D60B0A3E02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="93">
   <si>
     <t>概要</t>
     <rPh sb="0" eb="2">
@@ -374,6 +374,24 @@
     <t>マスタ</t>
   </si>
   <si>
+    <t>ゲームコントローラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>環境変数</t>
+    <rPh sb="0" eb="4">
+      <t>カンキョウヘンスウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フラグ管理</t>
+    <rPh sb="3" eb="5">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>設計</t>
     <rPh sb="0" eb="2">
       <t>セッケイ</t>
@@ -384,6 +402,13 @@
     <t>床</t>
     <rPh sb="0" eb="1">
       <t>ユカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>破壊</t>
+    <rPh sb="0" eb="2">
+      <t>ハカイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -669,7 +694,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="40">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -1008,6 +1033,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color theme="1"/>
       </left>
@@ -1020,6 +1054,15 @@
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="thin">
         <color theme="1"/>
@@ -1047,6 +1090,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1136,7 +1194,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1258,7 +1316,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1267,13 +1334,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="32" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1">
@@ -1282,25 +1349,28 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1318,10 +1388,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
@@ -1383,19 +1453,19 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1752,7 +1822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039B1606-320D-4390-8B98-CE6030BB2FAA}">
-  <dimension ref="A1:R72"/>
+  <dimension ref="A1:R75"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="3" width="25.375" bestFit="1" customWidth="1"/>
@@ -1796,22 +1866,22 @@
       <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="90" t="s">
-        <v>78</v>
-      </c>
-      <c r="K2" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="L2" s="90" t="s">
+      <c r="J2" s="94" t="s">
         <v>82</v>
       </c>
-      <c r="M2" s="90" t="s">
-        <v>83</v>
+      <c r="K2" s="94" t="s">
+        <v>88</v>
+      </c>
+      <c r="L2" s="94" t="s">
+        <v>86</v>
+      </c>
+      <c r="M2" s="94" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A3" s="67" t="s">
-        <v>70</v>
+      <c r="A3" s="71" t="s">
+        <v>74</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>13</v>
@@ -1825,34 +1895,34 @@
       <c r="E3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="71">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="71">
+      <c r="F3" s="75">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="75">
         <v>0.5</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J3" s="76" t="s">
-        <v>85</v>
-      </c>
-      <c r="K3" s="54">
-        <f>SUM(F3:F72)</f>
-        <v>49.599999999999994</v>
-      </c>
-      <c r="L3" s="54">
-        <f>SUMIF(H3:H72,"完了",F3:F72)</f>
+        <v>79</v>
+      </c>
+      <c r="J3" s="80" t="s">
+        <v>89</v>
+      </c>
+      <c r="K3" s="58">
+        <f>SUM(F3:F75)</f>
+        <v>52.599999999999994</v>
+      </c>
+      <c r="L3" s="58">
+        <f>SUMIF(H3:H75,"完了",F3:F75)</f>
         <v>25</v>
       </c>
-      <c r="M3" s="54">
+      <c r="M3" s="58">
         <f>K3-L3</f>
-        <v>24.599999999999994</v>
+        <v>27.599999999999994</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A4" s="67" t="s">
-        <v>70</v>
+      <c r="A4" s="71" t="s">
+        <v>74</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="4" t="s">
@@ -1864,34 +1934,34 @@
       <c r="E4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="71">
-        <v>0.5</v>
-      </c>
-      <c r="G4" s="71">
+      <c r="F4" s="75">
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="75">
         <v>0.5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J4" s="77" t="s">
+        <v>79</v>
+      </c>
+      <c r="J4" s="81" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="54">
-        <f>SUMIF(E3:E72,"プロト",F3:F72)</f>
+      <c r="K4" s="58">
+        <f>SUMIF(E3:E75,"プロト",F3:F75)</f>
+        <v>27.5</v>
+      </c>
+      <c r="L4" s="58">
+        <f>SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"完了")</f>
         <v>24</v>
       </c>
-      <c r="L4" s="54">
-        <f>SUMIFS(F3:F72,E3:E72,"プロト",H3:H72,"完了")</f>
-        <v>24</v>
-      </c>
-      <c r="M4" s="54">
+      <c r="M4" s="58">
         <f t="shared" ref="M4:M7" si="0">K4-L4</f>
-        <v>0</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A5" s="67" t="s">
-        <v>70</v>
+      <c r="A5" s="71" t="s">
+        <v>74</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="4" t="s">
@@ -1903,34 +1973,34 @@
       <c r="E5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="71">
-        <v>0.5</v>
-      </c>
-      <c r="G5" s="71">
+      <c r="F5" s="75">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="75">
         <v>0.5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J5" s="85" t="s">
+        <v>79</v>
+      </c>
+      <c r="J5" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="54">
-        <f>SUMIF(E3:E72,"アルファ",F3:F72)</f>
-        <v>11.100000000000001</v>
-      </c>
-      <c r="L5" s="54">
-        <f>SUMIFS(F3:F72,E3:E72,"アルファ",H3:H72,"完了")</f>
-        <v>1</v>
-      </c>
-      <c r="M5" s="54">
+      <c r="K5" s="58">
+        <f>SUMIF(E3:E75,"アルファ",F3:F75)</f>
+        <v>10.600000000000001</v>
+      </c>
+      <c r="L5" s="58">
+        <f>SUMIFS(F3:F75,E3:E75,"アルファ",H3:H75,"完了")</f>
+        <v>1</v>
+      </c>
+      <c r="M5" s="58">
         <f t="shared" si="0"/>
-        <v>10.100000000000001</v>
+        <v>9.6000000000000014</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A6" s="67" t="s">
-        <v>70</v>
+      <c r="A6" s="71" t="s">
+        <v>74</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="13" t="s">
@@ -1942,34 +2012,34 @@
       <c r="E6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="71">
-        <v>1</v>
-      </c>
-      <c r="G6" s="71">
+      <c r="F6" s="75">
+        <v>1</v>
+      </c>
+      <c r="G6" s="75">
         <v>1</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J6" s="78" t="s">
+        <v>79</v>
+      </c>
+      <c r="J6" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="54">
-        <f>SUMIF(E3:E72,"ベータ",F3:F72)</f>
+      <c r="K6" s="58">
+        <f>SUMIF(E3:E75,"ベータ",F3:F75)</f>
         <v>12.5</v>
       </c>
-      <c r="L6" s="54">
-        <f>SUMIFS(F3:F72,E3:E72,"ベータ",H3:H72,"完了")</f>
+      <c r="L6" s="58">
+        <f>SUMIFS(F3:F75,E3:E75,"ベータ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
-      <c r="M6" s="54">
+      <c r="M6" s="58">
         <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A7" s="67" t="s">
-        <v>70</v>
+      <c r="A7" s="71" t="s">
+        <v>74</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>26</v>
@@ -1983,32 +2053,32 @@
       <c r="E7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="71">
+      <c r="F7" s="75">
         <v>1</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J7" s="86" t="s">
-        <v>86</v>
-      </c>
-      <c r="K7" s="81">
-        <f>SUMIF(E3:E72,"マスタ",F3:F72)</f>
+        <v>80</v>
+      </c>
+      <c r="J7" s="90" t="s">
+        <v>90</v>
+      </c>
+      <c r="K7" s="85">
+        <f>SUMIF(E3:E75,"マスタ",F3:F75)</f>
         <v>2</v>
       </c>
-      <c r="L7" s="81">
-        <f>SUMIFS(F3:F72,E3:E72,"ベータ",H3:H72,"完了")</f>
+      <c r="L7" s="85">
+        <f>SUMIFS(F3:F75,E3:E75,"ベータ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
-      <c r="M7" s="54">
+      <c r="M7" s="58">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A8" s="67" t="s">
-        <v>70</v>
+      <c r="A8" s="71" t="s">
+        <v>74</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="4" t="s">
@@ -2020,26 +2090,26 @@
       <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="71">
-        <v>0.5</v>
-      </c>
-      <c r="G8" s="71">
+      <c r="F8" s="75">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="75">
         <v>0.25</v>
       </c>
-      <c r="H8" s="45" t="s">
-        <v>75</v>
-      </c>
-      <c r="I8" s="80"/>
-      <c r="J8" s="79"/>
-      <c r="K8" s="80"/>
-      <c r="L8" s="80"/>
-      <c r="M8" s="80"/>
-      <c r="N8" s="80"/>
-      <c r="O8" s="80"/>
+      <c r="H8" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="I8" s="84"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="84"/>
+      <c r="L8" s="84"/>
+      <c r="M8" s="84"/>
+      <c r="N8" s="84"/>
+      <c r="O8" s="84"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A9" s="67" t="s">
-        <v>70</v>
+      <c r="A9" s="71" t="s">
+        <v>74</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="4" t="s">
@@ -2051,27 +2121,27 @@
       <c r="E9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="71">
-        <v>0.5</v>
-      </c>
-      <c r="G9" s="82">
+      <c r="F9" s="75">
+        <v>0.5</v>
+      </c>
+      <c r="G9" s="86">
         <v>0.25</v>
       </c>
-      <c r="H9" s="84" t="s">
-        <v>75</v>
-      </c>
-      <c r="I9" s="91"/>
-      <c r="J9" s="93" t="s">
-        <v>87</v>
-      </c>
-      <c r="K9" s="94"/>
-      <c r="L9" s="94"/>
-      <c r="M9" s="94"/>
-      <c r="N9" s="80"/>
+      <c r="H9" s="88" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" s="95"/>
+      <c r="J9" s="97" t="s">
+        <v>91</v>
+      </c>
+      <c r="K9" s="98"/>
+      <c r="L9" s="98"/>
+      <c r="M9" s="98"/>
+      <c r="N9" s="84"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A10" s="67" t="s">
-        <v>70</v>
+      <c r="A10" s="71" t="s">
+        <v>74</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="4" t="s">
@@ -2083,45 +2153,45 @@
       <c r="E10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="71">
-        <v>0.5</v>
-      </c>
-      <c r="G10" s="82">
-        <v>0.5</v>
-      </c>
-      <c r="H10" s="84" t="s">
-        <v>75</v>
-      </c>
-      <c r="I10" s="92"/>
-      <c r="J10" s="76" t="s">
-        <v>85</v>
-      </c>
-      <c r="K10" s="76" t="s">
-        <v>84</v>
-      </c>
-      <c r="L10" s="76" t="s">
-        <v>82</v>
-      </c>
-      <c r="M10" s="76" t="s">
+      <c r="F10" s="75">
+        <v>0.5</v>
+      </c>
+      <c r="G10" s="86">
+        <v>0.5</v>
+      </c>
+      <c r="H10" s="88" t="s">
+        <v>79</v>
+      </c>
+      <c r="I10" s="96"/>
+      <c r="J10" s="80" t="s">
+        <v>89</v>
+      </c>
+      <c r="K10" s="80" t="s">
         <v>88</v>
       </c>
-      <c r="N10" s="80"/>
-      <c r="O10" s="100" t="s">
-        <v>79</v>
-      </c>
-      <c r="P10" s="100" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q10" s="100" t="s">
-        <v>82</v>
-      </c>
-      <c r="R10" s="100" t="s">
+      <c r="L10" s="80" t="s">
+        <v>86</v>
+      </c>
+      <c r="M10" s="80" t="s">
+        <v>92</v>
+      </c>
+      <c r="N10" s="84"/>
+      <c r="O10" s="104" t="s">
+        <v>83</v>
+      </c>
+      <c r="P10" s="104" t="s">
         <v>88</v>
       </c>
+      <c r="Q10" s="104" t="s">
+        <v>86</v>
+      </c>
+      <c r="R10" s="104" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A11" s="67" t="s">
-        <v>70</v>
+      <c r="A11" s="71" t="s">
+        <v>74</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="4" t="s">
@@ -2133,51 +2203,51 @@
       <c r="E11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="71">
-        <v>0.5</v>
-      </c>
-      <c r="G11" s="82">
+      <c r="F11" s="75">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="86">
         <v>0.25</v>
       </c>
-      <c r="H11" s="84" t="s">
-        <v>75</v>
-      </c>
-      <c r="I11" s="92"/>
-      <c r="J11" s="95" t="s">
-        <v>70</v>
-      </c>
-      <c r="K11" s="81">
-        <f>SUMIF(A3:A72,"大崎",F3:F72)</f>
+      <c r="H11" s="88" t="s">
+        <v>79</v>
+      </c>
+      <c r="I11" s="96"/>
+      <c r="J11" s="99" t="s">
+        <v>74</v>
+      </c>
+      <c r="K11" s="85">
+        <f>SUMIF(A3:A75,"大崎",F3:F75)</f>
         <v>12.099999999999998</v>
       </c>
-      <c r="L11" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"大崎",H3:H72,"完了")</f>
+      <c r="L11" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"大崎",H3:H75,"完了")</f>
         <v>5.5</v>
       </c>
-      <c r="M11" s="81">
+      <c r="M11" s="85">
         <f>K11 - L11</f>
         <v>6.5999999999999979</v>
       </c>
-      <c r="N11" s="80"/>
-      <c r="O11" s="95" t="s">
-        <v>70</v>
-      </c>
-      <c r="P11" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"大崎",E3:E72,"プロト")</f>
+      <c r="N11" s="84"/>
+      <c r="O11" s="99" t="s">
+        <v>74</v>
+      </c>
+      <c r="P11" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"プロト")</f>
         <v>5</v>
       </c>
-      <c r="Q11" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"大崎",E3:E72,"プロト",H3:H72,"完了")</f>
+      <c r="Q11" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"プロト",H3:H75,"完了")</f>
         <v>5</v>
       </c>
-      <c r="R11" s="81">
+      <c r="R11" s="85">
         <f>P11 - Q11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A12" s="67" t="s">
-        <v>70</v>
+      <c r="A12" s="71" t="s">
+        <v>74</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="21" t="s">
@@ -2189,105 +2259,105 @@
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="71">
-        <v>1</v>
-      </c>
-      <c r="G12" s="82">
-        <v>0.5</v>
-      </c>
-      <c r="H12" s="84" t="s">
+      <c r="F12" s="75">
+        <v>1</v>
+      </c>
+      <c r="G12" s="86">
+        <v>0.5</v>
+      </c>
+      <c r="H12" s="88" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12" s="96"/>
+      <c r="J12" s="100" t="s">
         <v>75</v>
       </c>
-      <c r="I12" s="92"/>
-      <c r="J12" s="96" t="s">
-        <v>71</v>
-      </c>
-      <c r="K12" s="81">
-        <f>SUMIF(A3:A72,"上永",F3:F72)</f>
+      <c r="K12" s="85">
+        <f>SUMIF(A3:A75,"上永",F3:F75)</f>
         <v>17</v>
       </c>
-      <c r="L12" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"上永",H3:H72,"完了")</f>
+      <c r="L12" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"上永",H3:H75,"完了")</f>
         <v>8.5</v>
       </c>
-      <c r="M12" s="81">
+      <c r="M12" s="85">
         <f t="shared" ref="M12:M15" si="1">K12 - L12</f>
         <v>8.5</v>
       </c>
-      <c r="N12" s="80"/>
-      <c r="O12" s="96" t="s">
-        <v>71</v>
-      </c>
-      <c r="P12" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"上永",E3:E72,"プロト")</f>
+      <c r="N12" s="84"/>
+      <c r="O12" s="100" t="s">
+        <v>75</v>
+      </c>
+      <c r="P12" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"プロト")</f>
         <v>8</v>
       </c>
-      <c r="Q12" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"上永",E3:E72,"プロト",H3:H72,"完了")</f>
+      <c r="Q12" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"プロト",H3:H75,"完了")</f>
         <v>8</v>
       </c>
-      <c r="R12" s="81">
+      <c r="R12" s="85">
         <f t="shared" ref="R12:R15" si="2">P12 - Q12</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A13" s="67" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="73"/>
+      <c r="A13" s="71" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="77"/>
       <c r="C13" s="13" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="71">
+      <c r="F13" s="75">
         <v>1.5</v>
       </c>
-      <c r="G13" s="71"/>
-      <c r="H13" s="83" t="s">
-        <v>76</v>
-      </c>
-      <c r="I13" s="87"/>
-      <c r="J13" s="97" t="s">
-        <v>73</v>
-      </c>
-      <c r="K13" s="81">
-        <f>SUMIF(A3:A72,"川浪",F3:F72)</f>
-        <v>6.5</v>
-      </c>
-      <c r="L13" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"川浪",H3:H72,"完了")</f>
+      <c r="G13" s="75"/>
+      <c r="H13" s="87" t="s">
+        <v>80</v>
+      </c>
+      <c r="I13" s="91"/>
+      <c r="J13" s="101" t="s">
+        <v>77</v>
+      </c>
+      <c r="K13" s="85">
+        <f>SUMIF(A3:A75,"川浪",F3:F75)</f>
+        <v>9.5</v>
+      </c>
+      <c r="L13" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"川浪",H3:H75,"完了")</f>
         <v>6</v>
       </c>
-      <c r="M13" s="81">
+      <c r="M13" s="85">
         <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="N13" s="80"/>
-      <c r="O13" s="97" t="s">
-        <v>73</v>
-      </c>
-      <c r="P13" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"川浪",E3:E72,"プロト")</f>
+        <v>3.5</v>
+      </c>
+      <c r="N13" s="84"/>
+      <c r="O13" s="101" t="s">
+        <v>77</v>
+      </c>
+      <c r="P13" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"プロト")</f>
+        <v>8.5</v>
+      </c>
+      <c r="Q13" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"プロト",H3:H75,"完了")</f>
         <v>6</v>
       </c>
-      <c r="Q13" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"川浪",E3:E72,"プロト",H3:H72,"完了")</f>
-        <v>6</v>
-      </c>
-      <c r="R13" s="81">
+      <c r="R13" s="85">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A14" s="67" t="s">
-        <v>70</v>
+      <c r="A14" s="71" t="s">
+        <v>74</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>27</v>
@@ -2301,49 +2371,49 @@
       <c r="E14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="71">
+      <c r="F14" s="75">
         <v>0.2</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I14" s="88"/>
-      <c r="J14" s="98" t="s">
-        <v>72</v>
-      </c>
-      <c r="K14" s="81">
-        <f>SUMIF(A3:A72,"佐々木",F3:F72)</f>
+      <c r="I14" s="92"/>
+      <c r="J14" s="102" t="s">
+        <v>76</v>
+      </c>
+      <c r="K14" s="85">
+        <f>SUMIF(A3:A75,"佐々木",F3:F75)</f>
         <v>6</v>
       </c>
-      <c r="L14" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"佐々木",H3:H72,"完了")</f>
+      <c r="L14" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"佐々木",H3:H75,"完了")</f>
         <v>4</v>
       </c>
-      <c r="M14" s="81">
+      <c r="M14" s="85">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="N14" s="80"/>
-      <c r="O14" s="98" t="s">
-        <v>72</v>
-      </c>
-      <c r="P14" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"佐々木",E3:E72,"プロト")</f>
+      <c r="N14" s="84"/>
+      <c r="O14" s="102" t="s">
+        <v>76</v>
+      </c>
+      <c r="P14" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"プロト")</f>
         <v>4</v>
       </c>
-      <c r="Q14" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"佐々木",E3:E72,"プロト",H3:H72,"完了")</f>
+      <c r="Q14" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"プロト",H3:H75,"完了")</f>
         <v>4</v>
       </c>
-      <c r="R14" s="81">
+      <c r="R14" s="85">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A15" s="67" t="s">
-        <v>70</v>
+      <c r="A15" s="71" t="s">
+        <v>74</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="4" t="s">
@@ -2355,49 +2425,49 @@
       <c r="E15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="71">
+      <c r="F15" s="75">
         <v>0.2</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I15" s="80"/>
-      <c r="J15" s="99" t="s">
-        <v>74</v>
-      </c>
-      <c r="K15" s="81">
-        <f>SUMIF(A3:A72,"誰でも",F3:F72)</f>
+      <c r="I15" s="84"/>
+      <c r="J15" s="103" t="s">
+        <v>78</v>
+      </c>
+      <c r="K15" s="85">
+        <f>SUMIF(A3:A75,"誰でも",F3:F75)</f>
         <v>8</v>
       </c>
-      <c r="L15" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"誰でも",H3:H72,"完了")</f>
-        <v>1</v>
-      </c>
-      <c r="M15" s="81">
+      <c r="L15" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"誰でも",H3:H75,"完了")</f>
+        <v>1</v>
+      </c>
+      <c r="M15" s="85">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="N15" s="80"/>
-      <c r="O15" s="99" t="s">
+      <c r="N15" s="84"/>
+      <c r="O15" s="103" t="s">
+        <v>78</v>
+      </c>
+      <c r="P15" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"プロト")</f>
+        <v>2</v>
+      </c>
+      <c r="Q15" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"プロト",H3:H75,"完了")</f>
+        <v>1</v>
+      </c>
+      <c r="R15" s="85">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A16" s="71" t="s">
         <v>74</v>
-      </c>
-      <c r="P15" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"誰でも",E3:E72,"プロト")</f>
-        <v>1</v>
-      </c>
-      <c r="Q15" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"誰でも",E3:E72,"プロト",H3:H72,"完了")</f>
-        <v>1</v>
-      </c>
-      <c r="R15" s="81">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A16" s="67" t="s">
-        <v>70</v>
       </c>
       <c r="B16" s="12"/>
       <c r="C16" s="13" t="s">
@@ -2409,20 +2479,20 @@
       <c r="E16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="71">
+      <c r="F16" s="75">
         <v>0.2</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I16" s="80"/>
-      <c r="N16" s="80"/>
-      <c r="O16" s="80"/>
+      <c r="I16" s="84"/>
+      <c r="N16" s="84"/>
+      <c r="O16" s="84"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A17" s="67" t="s">
-        <v>70</v>
+      <c r="A17" s="71" t="s">
+        <v>74</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>31</v>
@@ -2436,43 +2506,43 @@
       <c r="E17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="72">
+      <c r="F17" s="76">
         <v>0.5</v>
       </c>
       <c r="G17" s="22"/>
       <c r="H17" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I17" s="80"/>
-      <c r="J17" s="101" t="s">
-        <v>80</v>
-      </c>
-      <c r="K17" s="101" t="s">
+      <c r="I17" s="84"/>
+      <c r="J17" s="105" t="s">
         <v>84</v>
       </c>
-      <c r="L17" s="101" t="s">
-        <v>82</v>
-      </c>
-      <c r="M17" s="101" t="s">
+      <c r="K17" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="N17" s="89"/>
-      <c r="O17" s="102" t="s">
-        <v>81</v>
-      </c>
-      <c r="P17" s="102" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q17" s="102" t="s">
-        <v>82</v>
-      </c>
-      <c r="R17" s="102" t="s">
+      <c r="L17" s="105" t="s">
+        <v>86</v>
+      </c>
+      <c r="M17" s="105" t="s">
+        <v>92</v>
+      </c>
+      <c r="N17" s="93"/>
+      <c r="O17" s="106" t="s">
+        <v>85</v>
+      </c>
+      <c r="P17" s="106" t="s">
         <v>88</v>
       </c>
+      <c r="Q17" s="106" t="s">
+        <v>86</v>
+      </c>
+      <c r="R17" s="106" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A18" s="67" t="s">
-        <v>70</v>
+      <c r="A18" s="71" t="s">
+        <v>74</v>
       </c>
       <c r="B18" s="17"/>
       <c r="C18" s="21" t="s">
@@ -2484,49 +2554,49 @@
       <c r="E18" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="72">
+      <c r="F18" s="76">
         <v>0.5</v>
       </c>
       <c r="G18" s="26"/>
       <c r="H18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I18" s="80"/>
-      <c r="J18" s="95" t="s">
-        <v>70</v>
-      </c>
-      <c r="K18" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"大崎",E3:E72,"アルファ")</f>
+      <c r="I18" s="84"/>
+      <c r="J18" s="99" t="s">
+        <v>74</v>
+      </c>
+      <c r="K18" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"アルファ")</f>
         <v>3.6000000000000005</v>
       </c>
-      <c r="L18" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"大崎",E3:E72,"アルファ",H3:H72,"完了")</f>
-        <v>0.5</v>
-      </c>
-      <c r="M18" s="81">
+      <c r="L18" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"アルファ",H3:H75,"完了")</f>
+        <v>0.5</v>
+      </c>
+      <c r="M18" s="85">
         <f>K18 - L18</f>
         <v>3.1000000000000005</v>
       </c>
-      <c r="N18" s="80"/>
-      <c r="O18" s="95" t="s">
-        <v>70</v>
-      </c>
-      <c r="P18" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"大崎",E3:E72,"ベータ")</f>
+      <c r="N18" s="84"/>
+      <c r="O18" s="99" t="s">
+        <v>74</v>
+      </c>
+      <c r="P18" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"ベータ")</f>
         <v>3.5</v>
       </c>
-      <c r="Q18" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"大崎",E3:E72,"ベータ",H3:H72,"完了")</f>
+      <c r="Q18" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"ベータ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
-      <c r="R18" s="81">
+      <c r="R18" s="85">
         <f>P18 - Q18</f>
         <v>3.5</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A19" s="67" t="s">
-        <v>70</v>
+      <c r="A19" s="71" t="s">
+        <v>74</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="21" t="s">
@@ -2538,49 +2608,49 @@
       <c r="E19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="72">
+      <c r="F19" s="76">
         <v>0.5</v>
       </c>
       <c r="G19" s="24"/>
       <c r="H19" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I19" s="80"/>
-      <c r="J19" s="96" t="s">
-        <v>71</v>
-      </c>
-      <c r="K19" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"上永",E3:E72,"アルファ")</f>
+      <c r="I19" s="84"/>
+      <c r="J19" s="100" t="s">
+        <v>75</v>
+      </c>
+      <c r="K19" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"アルファ")</f>
         <v>4</v>
       </c>
-      <c r="L19" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"上永",E3:E72,"アルファ",H3:H72,"完了")</f>
-        <v>0.5</v>
-      </c>
-      <c r="M19" s="81">
+      <c r="L19" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"アルファ",H3:H75,"完了")</f>
+        <v>0.5</v>
+      </c>
+      <c r="M19" s="85">
         <f t="shared" ref="M19:M22" si="3">K19 - L19</f>
         <v>3.5</v>
       </c>
-      <c r="N19" s="80"/>
-      <c r="O19" s="96" t="s">
-        <v>71</v>
-      </c>
-      <c r="P19" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"上永",E3:E72,"ベータ")</f>
+      <c r="N19" s="84"/>
+      <c r="O19" s="100" t="s">
+        <v>75</v>
+      </c>
+      <c r="P19" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"ベータ")</f>
         <v>5</v>
       </c>
-      <c r="Q19" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"上永",E3:E72,"ベータ",H3:H72,"完了")</f>
+      <c r="Q19" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"ベータ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
-      <c r="R19" s="81">
+      <c r="R19" s="85">
         <f t="shared" ref="R19:R22" si="4">P19 - Q19</f>
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A20" s="67" t="s">
-        <v>70</v>
+      <c r="A20" s="71" t="s">
+        <v>74</v>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="13" t="s">
@@ -2592,47 +2662,47 @@
       <c r="E20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="72">
+      <c r="F20" s="76">
         <v>0.5</v>
       </c>
       <c r="G20" s="24"/>
       <c r="H20" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J20" s="97" t="s">
-        <v>73</v>
-      </c>
-      <c r="K20" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"川浪",E3:E72,"アルファ")</f>
-        <v>0.5</v>
-      </c>
-      <c r="L20" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"川浪",E3:E72,"アルファ",H3:H72,"完了")</f>
+      <c r="J20" s="101" t="s">
+        <v>77</v>
+      </c>
+      <c r="K20" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"アルファ")</f>
+        <v>1</v>
+      </c>
+      <c r="L20" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"アルファ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
-      <c r="M20" s="81">
+      <c r="M20" s="85">
         <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="O20" s="97" t="s">
-        <v>73</v>
-      </c>
-      <c r="P20" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"川浪",E3:E72,"ベータ")</f>
+        <v>1</v>
+      </c>
+      <c r="O20" s="101" t="s">
+        <v>77</v>
+      </c>
+      <c r="P20" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"ベータ")</f>
         <v>0</v>
       </c>
-      <c r="Q20" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"川浪",E3:E72,"ベータ",H3:H72,"完了")</f>
+      <c r="Q20" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"ベータ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
-      <c r="R20" s="81">
+      <c r="R20" s="85">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A21" s="67" t="s">
-        <v>70</v>
+      <c r="A21" s="71" t="s">
+        <v>74</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>35</v>
@@ -2646,47 +2716,47 @@
       <c r="E21" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="72">
+      <c r="F21" s="76">
         <v>0.5</v>
       </c>
       <c r="G21" s="22"/>
       <c r="H21" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J21" s="98" t="s">
-        <v>72</v>
-      </c>
-      <c r="K21" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"佐々木",E3:E72,"アルファ")</f>
+      <c r="J21" s="102" t="s">
+        <v>76</v>
+      </c>
+      <c r="K21" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"アルファ")</f>
         <v>0</v>
       </c>
-      <c r="L21" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"佐々木",E3:E72,"アルファ",H3:H72,"完了")</f>
+      <c r="L21" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"アルファ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
-      <c r="M21" s="81">
+      <c r="M21" s="85">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O21" s="98" t="s">
-        <v>72</v>
-      </c>
-      <c r="P21" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"佐々木",E3:E72,"ベータ")</f>
+      <c r="O21" s="102" t="s">
+        <v>76</v>
+      </c>
+      <c r="P21" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"ベータ")</f>
         <v>0</v>
       </c>
-      <c r="Q21" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"佐々木",E3:E72,"ベータ",H3:H72,"完了")</f>
+      <c r="Q21" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"ベータ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
-      <c r="R21" s="81">
+      <c r="R21" s="85">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A22" s="67" t="s">
-        <v>70</v>
+      <c r="A22" s="71" t="s">
+        <v>74</v>
       </c>
       <c r="B22" s="17"/>
       <c r="C22" s="21" t="s">
@@ -2698,47 +2768,47 @@
       <c r="E22" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="72">
+      <c r="F22" s="76">
         <v>0.5</v>
       </c>
       <c r="G22" s="26"/>
       <c r="H22" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J22" s="99" t="s">
-        <v>74</v>
-      </c>
-      <c r="K22" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"誰でも",E3:E72,"アルファ")</f>
-        <v>3</v>
-      </c>
-      <c r="L22" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"誰でも",E3:E72,"アルファ",H3:H72,"完了")</f>
+      <c r="J22" s="103" t="s">
+        <v>78</v>
+      </c>
+      <c r="K22" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"アルファ")</f>
+        <v>2</v>
+      </c>
+      <c r="L22" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"アルファ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
-      <c r="M22" s="81">
+      <c r="M22" s="85">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="O22" s="99" t="s">
-        <v>74</v>
-      </c>
-      <c r="P22" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"誰でも",E3:E72,"ベータ")</f>
+        <v>2</v>
+      </c>
+      <c r="O22" s="103" t="s">
+        <v>78</v>
+      </c>
+      <c r="P22" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"ベータ")</f>
         <v>4</v>
       </c>
-      <c r="Q22" s="81">
-        <f>SUMIFS(F3:F72,A3:A72,"誰でも",E3:E72,"ベータ",H3:H72,"完了")</f>
+      <c r="Q22" s="85">
+        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"ベータ",H3:H75,"完了")</f>
         <v>0</v>
       </c>
-      <c r="R22" s="81">
+      <c r="R22" s="85">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A23" s="67" t="s">
-        <v>70</v>
+      <c r="A23" s="71" t="s">
+        <v>74</v>
       </c>
       <c r="B23" s="18"/>
       <c r="C23" s="13" t="s">
@@ -2750,7 +2820,7 @@
       <c r="E23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F23" s="72">
+      <c r="F23" s="76">
         <v>0.5</v>
       </c>
       <c r="G23" s="24"/>
@@ -2759,8 +2829,8 @@
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A24" s="68" t="s">
-        <v>71</v>
+      <c r="A24" s="72" t="s">
+        <v>75</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>37</v>
@@ -2781,12 +2851,12 @@
         <v>1</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A25" s="72" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A25" s="68" t="s">
-        <v>71</v>
       </c>
       <c r="B25" s="17"/>
       <c r="C25" s="21" t="s">
@@ -2805,12 +2875,12 @@
         <v>1</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A26" s="72" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A26" s="68" t="s">
-        <v>71</v>
       </c>
       <c r="B26" s="17"/>
       <c r="C26" s="21" t="s">
@@ -2829,12 +2899,12 @@
         <v>0.5</v>
       </c>
       <c r="H26" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A27" s="72" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A27" s="68" t="s">
-        <v>71</v>
       </c>
       <c r="B27" s="17"/>
       <c r="C27" s="21" t="s">
@@ -2853,12 +2923,12 @@
         <v>1</v>
       </c>
       <c r="H27" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A28" s="72" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A28" s="68" t="s">
-        <v>71</v>
       </c>
       <c r="B28" s="17"/>
       <c r="C28" s="21" t="s">
@@ -2877,12 +2947,12 @@
         <v>0.5</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A29" s="72" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A29" s="68" t="s">
-        <v>71</v>
       </c>
       <c r="B29" s="18"/>
       <c r="C29" s="13" t="s">
@@ -2903,8 +2973,8 @@
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A30" s="68" t="s">
-        <v>71</v>
+      <c r="A30" s="72" t="s">
+        <v>75</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>43</v>
@@ -2925,12 +2995,12 @@
         <v>2</v>
       </c>
       <c r="H30" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A31" s="72" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A31" s="68" t="s">
-        <v>71</v>
       </c>
       <c r="B31" s="17"/>
       <c r="C31" s="21" t="s">
@@ -2949,12 +3019,12 @@
         <v>0.5</v>
       </c>
       <c r="H31" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A32" s="72" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A32" s="68" t="s">
-        <v>71</v>
       </c>
       <c r="B32" s="17"/>
       <c r="C32" s="21" t="s">
@@ -2973,12 +3043,12 @@
         <v>1</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A33" s="72" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A33" s="68" t="s">
-        <v>71</v>
       </c>
       <c r="B33" s="18"/>
       <c r="C33" s="13" t="s">
@@ -2997,12 +3067,12 @@
         <v>1</v>
       </c>
       <c r="H33" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A34" s="72" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A34" s="68" t="s">
-        <v>71</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>47</v>
@@ -3025,8 +3095,8 @@
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A35" s="68" t="s">
-        <v>71</v>
+      <c r="A35" s="72" t="s">
+        <v>75</v>
       </c>
       <c r="B35" s="17"/>
       <c r="C35" s="21" t="s">
@@ -3047,8 +3117,8 @@
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A36" s="68" t="s">
-        <v>71</v>
+      <c r="A36" s="72" t="s">
+        <v>75</v>
       </c>
       <c r="B36" s="17"/>
       <c r="C36" s="21" t="s">
@@ -3069,8 +3139,8 @@
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A37" s="68" t="s">
-        <v>71</v>
+      <c r="A37" s="72" t="s">
+        <v>75</v>
       </c>
       <c r="B37" s="18"/>
       <c r="C37" s="13" t="s">
@@ -3091,8 +3161,8 @@
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A38" s="68" t="s">
-        <v>71</v>
+      <c r="A38" s="72" t="s">
+        <v>75</v>
       </c>
       <c r="B38" s="14" t="s">
         <v>49</v>
@@ -3113,12 +3183,12 @@
         <v>0.5</v>
       </c>
       <c r="H38" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A39" s="72" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A39" s="68" t="s">
-        <v>71</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="21" t="s">
@@ -3137,11 +3207,11 @@
       <c r="H39" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K39" s="75"/>
+      <c r="K39" s="79"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A40" s="68" t="s">
-        <v>71</v>
+      <c r="A40" s="72" t="s">
+        <v>75</v>
       </c>
       <c r="B40" s="17"/>
       <c r="C40" s="21" t="s">
@@ -3160,11 +3230,11 @@
       <c r="H40" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K40" s="75"/>
+      <c r="K40" s="79"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A41" s="68" t="s">
-        <v>71</v>
+      <c r="A41" s="72" t="s">
+        <v>75</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="13" t="s">
@@ -3183,13 +3253,13 @@
         <v>0.5</v>
       </c>
       <c r="H41" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K41" s="79"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A42" s="72" t="s">
         <v>75</v>
-      </c>
-      <c r="K41" s="75"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A42" s="68" t="s">
-        <v>71</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>51</v>
@@ -3210,11 +3280,11 @@
       <c r="H42" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K42" s="75"/>
+      <c r="K42" s="79"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A43" s="68" t="s">
-        <v>71</v>
+      <c r="A43" s="72" t="s">
+        <v>75</v>
       </c>
       <c r="B43" s="17"/>
       <c r="C43" s="21" t="s">
@@ -3233,11 +3303,11 @@
       <c r="H43" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K43" s="75"/>
+      <c r="K43" s="79"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A44" s="68" t="s">
-        <v>71</v>
+      <c r="A44" s="72" t="s">
+        <v>75</v>
       </c>
       <c r="B44" s="17"/>
       <c r="C44" s="21" t="s">
@@ -3258,8 +3328,8 @@
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A45" s="68" t="s">
-        <v>71</v>
+      <c r="A45" s="72" t="s">
+        <v>75</v>
       </c>
       <c r="B45" s="17"/>
       <c r="C45" s="21" t="s">
@@ -3280,8 +3350,8 @@
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A46" s="68" t="s">
-        <v>71</v>
+      <c r="A46" s="72" t="s">
+        <v>75</v>
       </c>
       <c r="B46" s="17"/>
       <c r="C46" s="21" t="s">
@@ -3302,8 +3372,8 @@
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A47" s="68" t="s">
-        <v>71</v>
+      <c r="A47" s="72" t="s">
+        <v>75</v>
       </c>
       <c r="B47" s="18"/>
       <c r="C47" s="13" t="s">
@@ -3324,8 +3394,8 @@
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A48" s="68" t="s">
-        <v>71</v>
+      <c r="A48" s="72" t="s">
+        <v>75</v>
       </c>
       <c r="B48" s="14" t="s">
         <v>54</v>
@@ -3348,8 +3418,8 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A49" s="68" t="s">
-        <v>71</v>
+      <c r="A49" s="72" t="s">
+        <v>75</v>
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="13" t="s">
@@ -3370,8 +3440,8 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A50" s="66" t="s">
-        <v>72</v>
+      <c r="A50" s="70" t="s">
+        <v>76</v>
       </c>
       <c r="B50" s="14" t="s">
         <v>55</v>
@@ -3392,12 +3462,12 @@
         <v>0.5</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A51" s="66" t="s">
-        <v>72</v>
+      <c r="A51" s="70" t="s">
+        <v>76</v>
       </c>
       <c r="B51" s="32" t="s">
         <v>58</v>
@@ -3418,12 +3488,12 @@
         <v>3</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A52" s="66" t="s">
-        <v>72</v>
+      <c r="A52" s="70" t="s">
+        <v>76</v>
       </c>
       <c r="B52" s="40" t="s">
         <v>60</v>
@@ -3446,10 +3516,10 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A53" s="66" t="s">
-        <v>72</v>
-      </c>
-      <c r="B53" s="43"/>
+      <c r="A53" s="70" t="s">
+        <v>76</v>
+      </c>
+      <c r="B53" s="44"/>
       <c r="C53" s="39" t="s">
         <v>62</v>
       </c>
@@ -3468,461 +3538,529 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A54" s="69" t="s">
+      <c r="A54" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B54" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="C54" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="D54" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="E54" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" s="43">
+        <v>1</v>
+      </c>
+      <c r="G54" s="31"/>
+      <c r="H54" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A55" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B55" s="45"/>
+      <c r="C55" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="D55" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55" s="23"/>
+      <c r="H55" s="48" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A56" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B56" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C56" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" s="49">
+        <v>0.5</v>
+      </c>
+      <c r="G56" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="H56" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A57" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B57" s="51"/>
+      <c r="C57" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="D57" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="57">
+        <v>1</v>
+      </c>
+      <c r="G57" s="58">
+        <v>1</v>
+      </c>
+      <c r="H57" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A58" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B58" s="51"/>
+      <c r="C58" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="D58" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="57">
+        <v>1</v>
+      </c>
+      <c r="G58" s="56"/>
+      <c r="H58" s="48" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A59" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B59" s="51"/>
+      <c r="C59" s="54" t="s">
+        <v>23</v>
+      </c>
+      <c r="D59" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59" s="23">
+        <v>1</v>
+      </c>
+      <c r="H59" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A60" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B60" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="C60" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="D60" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60" s="60" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" s="49">
+        <v>0.5</v>
+      </c>
+      <c r="G60" s="68">
+        <v>0.5</v>
+      </c>
+      <c r="H60" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A61" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B61" s="51"/>
+      <c r="C61" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="D61" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="58">
+        <v>0.5</v>
+      </c>
+      <c r="G61" s="68">
+        <v>0.5</v>
+      </c>
+      <c r="H61" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A62" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B62" s="51"/>
+      <c r="C62" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="D62" s="62" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" s="66" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="58">
+        <v>0.5</v>
+      </c>
+      <c r="G62" s="68">
+        <v>0.5</v>
+      </c>
+      <c r="H62" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A63" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B63" s="51"/>
+      <c r="C63" s="54" t="s">
+        <v>47</v>
+      </c>
+      <c r="D63" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" s="58">
+        <v>0.5</v>
+      </c>
+      <c r="G63" s="68"/>
+      <c r="H63" s="48" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A64" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B64" s="51"/>
+      <c r="C64" s="54" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" s="67">
+        <v>0.5</v>
+      </c>
+      <c r="G64" s="68">
+        <v>0.5</v>
+      </c>
+      <c r="H64" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A65" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B65" s="51"/>
+      <c r="C65" s="54" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" s="58">
+        <v>0.5</v>
+      </c>
+      <c r="G65" s="68">
+        <v>0.5</v>
+      </c>
+      <c r="H65" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A66" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B66" s="51"/>
+      <c r="C66" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="D66" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="F66" s="58">
+        <v>0.5</v>
+      </c>
+      <c r="G66" s="68">
+        <v>0.5</v>
+      </c>
+      <c r="H66" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A67" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B67" s="52"/>
+      <c r="C67" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="D67" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" s="58">
+        <v>0.5</v>
+      </c>
+      <c r="G67" s="68">
+        <v>0.5</v>
+      </c>
+      <c r="H67" s="63" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A68" s="74" t="s">
+        <v>78</v>
+      </c>
+      <c r="B68" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="B54" s="37" t="s">
+      <c r="C68" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="D68" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" s="69">
+        <v>1</v>
+      </c>
+      <c r="G68" s="69">
+        <v>1</v>
+      </c>
+      <c r="H68" s="63" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A69" s="74" t="s">
+        <v>78</v>
+      </c>
+      <c r="B69" s="51"/>
+      <c r="C69" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="50" t="s">
-        <v>64</v>
-      </c>
-      <c r="D54" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="E54" s="45" t="s">
+      <c r="D69" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="46">
-        <v>0.5</v>
-      </c>
-      <c r="G54" s="47">
-        <v>0.5</v>
-      </c>
-      <c r="H54" s="45" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A55" s="69" t="s">
-        <v>73</v>
-      </c>
-      <c r="B55" s="48"/>
-      <c r="C55" s="51" t="s">
-        <v>65</v>
-      </c>
-      <c r="D55" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="E55" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" s="53">
-        <v>1</v>
-      </c>
-      <c r="G55" s="54">
-        <v>1</v>
-      </c>
-      <c r="H55" s="45" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A56" s="69" t="s">
-        <v>73</v>
-      </c>
-      <c r="B56" s="48"/>
-      <c r="C56" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="D56" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="E56" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56">
-        <v>1</v>
-      </c>
-      <c r="G56" s="23">
-        <v>1</v>
-      </c>
-      <c r="H56" s="45" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A57" s="69" t="s">
-        <v>73</v>
-      </c>
-      <c r="B57" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="C57" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="D57" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="E57" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" s="46">
-        <v>0.5</v>
-      </c>
-      <c r="G57" s="64">
-        <v>0.5</v>
-      </c>
-      <c r="H57" s="45" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A58" s="69" t="s">
-        <v>73</v>
-      </c>
-      <c r="B58" s="48"/>
-      <c r="C58" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="D58" s="59" t="s">
-        <v>14</v>
-      </c>
-      <c r="E58" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="54">
-        <v>0.5</v>
-      </c>
-      <c r="G58" s="64">
-        <v>0.5</v>
-      </c>
-      <c r="H58" s="45" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A59" s="69" t="s">
-        <v>73</v>
-      </c>
-      <c r="B59" s="48"/>
-      <c r="C59" s="51" t="s">
-        <v>53</v>
-      </c>
-      <c r="D59" s="58" t="s">
-        <v>14</v>
-      </c>
-      <c r="E59" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" s="54">
-        <v>0.5</v>
-      </c>
-      <c r="G59" s="64">
-        <v>0.5</v>
-      </c>
-      <c r="H59" s="45" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A60" s="69" t="s">
-        <v>73</v>
-      </c>
-      <c r="B60" s="48"/>
-      <c r="C60" s="51" t="s">
+      <c r="F69" s="69">
+        <v>1</v>
+      </c>
+      <c r="G69" s="58"/>
+      <c r="H69" s="63" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A70" s="74" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="51"/>
+      <c r="C70" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="D60" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="E60" s="60" t="s">
+      <c r="D70" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="F70" s="69">
+        <v>1</v>
+      </c>
+      <c r="G70" s="67"/>
+      <c r="H70" s="63" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A71" s="74" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71" s="51"/>
+      <c r="C71" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="D71" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="F71" s="69">
+        <v>1</v>
+      </c>
+      <c r="G71" s="58"/>
+      <c r="H71" s="63" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A72" s="74" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="51"/>
+      <c r="C72" s="54" t="s">
+        <v>31</v>
+      </c>
+      <c r="D72" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="F72" s="69">
+        <v>1</v>
+      </c>
+      <c r="G72" s="67"/>
+      <c r="H72" s="63" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A73" s="74" t="s">
+        <v>78</v>
+      </c>
+      <c r="B73" s="51"/>
+      <c r="C73" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F60" s="54">
-        <v>0.5</v>
-      </c>
-      <c r="G60" s="64"/>
-      <c r="H60" s="45" t="s">
+      <c r="F73" s="69">
+        <v>1</v>
+      </c>
+      <c r="G73" s="58"/>
+      <c r="H73" s="63" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A61" s="69" t="s">
-        <v>73</v>
-      </c>
-      <c r="B61" s="48"/>
-      <c r="C61" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="D61" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61" s="60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" s="63">
-        <v>0.5</v>
-      </c>
-      <c r="G61" s="64">
-        <v>0.5</v>
-      </c>
-      <c r="H61" s="45" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A62" s="69" t="s">
-        <v>73</v>
-      </c>
-      <c r="B62" s="48"/>
-      <c r="C62" s="51" t="s">
-        <v>34</v>
-      </c>
-      <c r="D62" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="E62" s="60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" s="54">
-        <v>0.5</v>
-      </c>
-      <c r="G62" s="64">
-        <v>0.5</v>
-      </c>
-      <c r="H62" s="45" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A63" s="69" t="s">
-        <v>73</v>
-      </c>
-      <c r="B63" s="48"/>
-      <c r="C63" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="D63" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="E63" s="60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" s="54">
-        <v>0.5</v>
-      </c>
-      <c r="G63" s="64">
-        <v>0.5</v>
-      </c>
-      <c r="H63" s="45" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A64" s="69" t="s">
-        <v>73</v>
-      </c>
-      <c r="B64" s="49"/>
-      <c r="C64" s="52" t="s">
-        <v>37</v>
-      </c>
-      <c r="D64" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="E64" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" s="54">
-        <v>0.5</v>
-      </c>
-      <c r="G64" s="64">
-        <v>0.5</v>
-      </c>
-      <c r="H64" s="59" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A65" s="70" t="s">
-        <v>74</v>
-      </c>
-      <c r="B65" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="C65" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="D65" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="E65" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" s="65">
-        <v>1</v>
-      </c>
-      <c r="G65" s="65">
-        <v>1</v>
-      </c>
-      <c r="H65" s="59" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A66" s="70" t="s">
-        <v>74</v>
-      </c>
-      <c r="B66" s="48"/>
-      <c r="C66" s="51" t="s">
-        <v>53</v>
-      </c>
-      <c r="D66" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="61" t="s">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A74" s="74" t="s">
+        <v>78</v>
+      </c>
+      <c r="B74" s="51"/>
+      <c r="C74" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="D74" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="F74" s="69">
+        <v>1</v>
+      </c>
+      <c r="G74" s="58"/>
+      <c r="H74" s="63" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A75" s="74" t="s">
+        <v>78</v>
+      </c>
+      <c r="B75" s="52"/>
+      <c r="C75" s="55" t="s">
+        <v>71</v>
+      </c>
+      <c r="D75" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F66" s="65">
-        <v>1</v>
-      </c>
-      <c r="G66" s="54"/>
-      <c r="H66" s="59" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A67" s="70" t="s">
-        <v>74</v>
-      </c>
-      <c r="B67" s="48"/>
-      <c r="C67" s="51" t="s">
-        <v>47</v>
-      </c>
-      <c r="D67" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="F67" s="65">
-        <v>1</v>
-      </c>
-      <c r="G67" s="63"/>
-      <c r="H67" s="59" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A68" s="70" t="s">
-        <v>74</v>
-      </c>
-      <c r="B68" s="48"/>
-      <c r="C68" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="D68" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="E68" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="F68" s="65">
-        <v>1</v>
-      </c>
-      <c r="G68" s="54"/>
-      <c r="H68" s="59" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A69" s="70" t="s">
-        <v>74</v>
-      </c>
-      <c r="B69" s="48"/>
-      <c r="C69" s="51" t="s">
-        <v>31</v>
-      </c>
-      <c r="D69" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="E69" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="F69" s="65">
-        <v>1</v>
-      </c>
-      <c r="G69" s="63"/>
-      <c r="H69" s="59" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A70" s="70" t="s">
-        <v>74</v>
-      </c>
-      <c r="B70" s="48"/>
-      <c r="C70" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="D70" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" s="65">
-        <v>1</v>
-      </c>
-      <c r="G70" s="54"/>
-      <c r="H70" s="59" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A71" s="70" t="s">
-        <v>74</v>
-      </c>
-      <c r="B71" s="48"/>
-      <c r="C71" s="51" t="s">
-        <v>52</v>
-      </c>
-      <c r="D71" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="E71" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="F71" s="65">
-        <v>1</v>
-      </c>
-      <c r="G71" s="54"/>
-      <c r="H71" s="59" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A72" s="70" t="s">
-        <v>74</v>
-      </c>
-      <c r="B72" s="49"/>
-      <c r="C72" s="52" t="s">
-        <v>67</v>
-      </c>
-      <c r="D72" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="E72" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" s="26">
-        <v>1</v>
-      </c>
-      <c r="G72" s="74"/>
-      <c r="H72" s="59" t="s">
+      <c r="F75" s="26">
+        <v>1</v>
+      </c>
+      <c r="G75" s="78"/>
+      <c r="H75" s="63" t="s">
         <v>57</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H72" xr:uid="{6668A6B0-AE49-40A9-BDCA-1EF7E08764AB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H75" xr:uid="{6668A6B0-AE49-40A9-BDCA-1EF7E08764AB}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E72" xr:uid="{3F25CF45-EEFF-4838-8184-2DB508A95967}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E75" xr:uid="{3F25CF45-EEFF-4838-8184-2DB508A95967}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D72" xr:uid="{D99FF9D9-52C2-47CC-BC93-4ACF23B2DA2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D75" xr:uid="{D99FF9D9-52C2-47CC-BC93-4ACF23B2DA2A}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
   </dataValidations>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AyumuKaminaga\Documents\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hakutokawanami\Desktop\github\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D687D1-CE81-4475-9379-4D60B0A3E02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD0CE35-9F3E-4220-8A57-D84D7A3D6477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="106">
   <si>
     <t>概要</t>
     <rPh sb="0" eb="2">
@@ -374,24 +374,6 @@
     <t>マスタ</t>
   </si>
   <si>
-    <t>ゲームコントローラ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>環境変数</t>
-    <rPh sb="0" eb="4">
-      <t>カンキョウヘンスウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>フラグ管理</t>
-    <rPh sb="3" eb="5">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>設計</t>
     <rPh sb="0" eb="2">
       <t>セッケイ</t>
@@ -406,13 +388,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>破壊</t>
-    <rPh sb="0" eb="2">
-      <t>ハカイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>仕様作成</t>
     <rPh sb="0" eb="4">
       <t>シヨウサクセイ</t>
@@ -544,6 +519,140 @@
     <t>残り</t>
     <rPh sb="0" eb="1">
       <t>ノコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2月</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>日</t>
+    <rPh sb="0" eb="1">
+      <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>月</t>
+    <rPh sb="0" eb="1">
+      <t>ゲツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>火</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>水</t>
+    <rPh sb="0" eb="1">
+      <t>スイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>木</t>
+    <rPh sb="0" eb="1">
+      <t>モク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>金</t>
+    <rPh sb="0" eb="1">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>土</t>
+    <rPh sb="0" eb="1">
+      <t>ド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3月</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>２月１９日まで</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>３月１日まで</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>３月１０日まで</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>３月１５まで</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>完全提出３月１６日</t>
+    <rPh sb="0" eb="4">
+      <t>カンゼンテイシュツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>園田</t>
+    <rPh sb="0" eb="2">
+      <t>ソノダ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>モーション</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プレイヤー必殺技(波動拳)</t>
+    <rPh sb="5" eb="8">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ハドウケン</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -602,7 +711,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -693,8 +802,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="43">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -1033,15 +1166,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="1"/>
       </left>
@@ -1054,15 +1178,6 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thin">
         <color theme="1"/>
@@ -1090,21 +1205,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1188,13 +1288,148 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1277,9 +1512,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1316,16 +1548,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1334,43 +1557,40 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="32" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1388,10 +1608,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
@@ -1453,19 +1673,19 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1486,6 +1706,108 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="41" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="45" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="44" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="45" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="46" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="47" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="48" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="44" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="45" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="44" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="45" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="44" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1822,7 +2144,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039B1606-320D-4390-8B98-CE6030BB2FAA}">
-  <dimension ref="A1:R75"/>
+  <dimension ref="A1:T72"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="3" width="25.375" bestFit="1" customWidth="1"/>
@@ -1841,53 +2163,89 @@
     <col min="18" max="18" width="7.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="I1" s="30"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="B2" s="1" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="94" t="s">
+      <c r="J1" s="89" t="s">
+        <v>78</v>
+      </c>
+      <c r="K1" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="L1" s="89" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="94" t="s">
-        <v>88</v>
-      </c>
-      <c r="L2" s="94" t="s">
-        <v>86</v>
-      </c>
-      <c r="M2" s="94" t="s">
-        <v>87</v>
+      <c r="M1" s="89" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A2" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="70">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="70">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J2" s="75" t="s">
+        <v>85</v>
+      </c>
+      <c r="K2" s="53">
+        <f>SUM(F2:F72)</f>
+        <v>50.599999999999994</v>
+      </c>
+      <c r="L2" s="53">
+        <f>SUMIF(H2:H72,"完了",F2:F72)</f>
+        <v>25</v>
+      </c>
+      <c r="M2" s="53">
+        <f>K2-L2</f>
+        <v>25.599999999999994</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A3" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>13</v>
-      </c>
+      <c r="A3" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="5"/>
       <c r="C3" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>14</v>
@@ -1895,38 +2253,38 @@
       <c r="E3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="75">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="75">
+      <c r="F3" s="70">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="70">
         <v>0.5</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J3" s="80" t="s">
-        <v>89</v>
-      </c>
-      <c r="K3" s="58">
-        <f>SUM(F3:F75)</f>
-        <v>52.599999999999994</v>
-      </c>
-      <c r="L3" s="58">
-        <f>SUMIF(H3:H75,"完了",F3:F75)</f>
-        <v>25</v>
-      </c>
-      <c r="M3" s="58">
-        <f>K3-L3</f>
-        <v>27.599999999999994</v>
+        <v>75</v>
+      </c>
+      <c r="J3" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="53">
+        <f>SUMIF(E2:E72,"プロト",F2:F72)</f>
+        <v>24</v>
+      </c>
+      <c r="L3" s="53">
+        <f>SUMIFS(F2:F72,E2:E72,"プロト",H2:H72,"完了")</f>
+        <v>24</v>
+      </c>
+      <c r="M3" s="53">
+        <f t="shared" ref="M3:M6" si="0">K3-L3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A4" s="71" t="s">
-        <v>74</v>
+      <c r="A4" s="66" t="s">
+        <v>70</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>14</v>
@@ -1934,38 +2292,38 @@
       <c r="E4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="75">
-        <v>0.5</v>
-      </c>
-      <c r="G4" s="75">
+      <c r="F4" s="70">
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="70">
         <v>0.5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J4" s="81" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" s="58">
-        <f>SUMIF(E3:E75,"プロト",F3:F75)</f>
-        <v>27.5</v>
-      </c>
-      <c r="L4" s="58">
-        <f>SUMIFS(F3:F75,E3:E75,"プロト",H3:H75,"完了")</f>
-        <v>24</v>
-      </c>
-      <c r="M4" s="58">
-        <f t="shared" ref="M4:M7" si="0">K4-L4</f>
-        <v>3.5</v>
+        <v>75</v>
+      </c>
+      <c r="J4" s="84" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="53">
+        <f>SUMIF(E2:E72,"アルファ",F2:F72)</f>
+        <v>11.100000000000001</v>
+      </c>
+      <c r="L4" s="53">
+        <f>SUMIFS(F2:F72,E2:E72,"アルファ",H2:H72,"完了")</f>
+        <v>1</v>
+      </c>
+      <c r="M4" s="53">
+        <f t="shared" si="0"/>
+        <v>10.100000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A5" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="4" t="s">
-        <v>17</v>
+      <c r="A5" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="13" t="s">
+        <v>18</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>14</v>
@@ -1973,147 +2331,140 @@
       <c r="E5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="75">
-        <v>0.5</v>
-      </c>
-      <c r="G5" s="75">
-        <v>0.5</v>
+      <c r="F5" s="70">
+        <v>1</v>
+      </c>
+      <c r="G5" s="70">
+        <v>1</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J5" s="89" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" s="58">
-        <f>SUMIF(E3:E75,"アルファ",F3:F75)</f>
-        <v>10.600000000000001</v>
-      </c>
-      <c r="L5" s="58">
-        <f>SUMIFS(F3:F75,E3:E75,"アルファ",H3:H75,"完了")</f>
+        <v>75</v>
+      </c>
+      <c r="J5" s="77" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="53">
+        <f>SUMIF(E2:E72,"ベータ",F2:F72)</f>
+        <v>13.5</v>
+      </c>
+      <c r="L5" s="53">
+        <f>SUMIFS(F2:F72,E2:E72,"ベータ",H2:H72,"完了")</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="53">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A6" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="70">
         <v>1</v>
       </c>
-      <c r="M5" s="58">
-        <f t="shared" si="0"/>
-        <v>9.6000000000000014</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A6" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="75">
-        <v>1</v>
-      </c>
-      <c r="G6" s="75">
-        <v>1</v>
-      </c>
+      <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J6" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="K6" s="58">
-        <f>SUMIF(E3:E75,"ベータ",F3:F75)</f>
-        <v>12.5</v>
-      </c>
-      <c r="L6" s="58">
-        <f>SUMIFS(F3:F75,E3:E75,"ベータ",H3:H75,"完了")</f>
+        <v>76</v>
+      </c>
+      <c r="J6" s="85" t="s">
+        <v>86</v>
+      </c>
+      <c r="K6" s="80">
+        <f>SUMIF(E2:E72,"マスタ",F2:F72)</f>
+        <v>2</v>
+      </c>
+      <c r="L6" s="80">
+        <f>SUMIFS(F2:F72,E2:E72,"ベータ",H2:H72,"完了")</f>
         <v>0</v>
       </c>
-      <c r="M6" s="58">
-        <f t="shared" si="0"/>
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A7" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="75">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J7" s="90" t="s">
-        <v>90</v>
-      </c>
-      <c r="K7" s="85">
-        <f>SUMIF(E3:E75,"マスタ",F3:F75)</f>
-        <v>2</v>
-      </c>
-      <c r="L7" s="85">
-        <f>SUMIFS(F3:F75,E3:E75,"ベータ",H3:H75,"完了")</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="58">
+      <c r="M6" s="53">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A7" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="70">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="70">
+        <v>0.25</v>
+      </c>
+      <c r="H7" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="I7" s="79"/>
+      <c r="J7" s="78"/>
+      <c r="K7" s="79"/>
+      <c r="L7" s="79"/>
+      <c r="M7" s="79"/>
+      <c r="N7" s="79"/>
+      <c r="O7" s="79"/>
+    </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A8" s="71" t="s">
-        <v>74</v>
+      <c r="A8" s="66" t="s">
+        <v>70</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="75">
-        <v>0.5</v>
-      </c>
-      <c r="G8" s="75">
+        <v>8</v>
+      </c>
+      <c r="F8" s="70">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="81">
         <v>0.25</v>
       </c>
-      <c r="H8" s="48" t="s">
-        <v>79</v>
-      </c>
-      <c r="I8" s="84"/>
-      <c r="J8" s="83"/>
-      <c r="K8" s="84"/>
-      <c r="L8" s="84"/>
-      <c r="M8" s="84"/>
-      <c r="N8" s="84"/>
-      <c r="O8" s="84"/>
+      <c r="H8" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="I8" s="90"/>
+      <c r="J8" s="92" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" s="93"/>
+      <c r="L8" s="93"/>
+      <c r="M8" s="93"/>
+      <c r="N8" s="79"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A9" s="71" t="s">
-        <v>74</v>
+      <c r="A9" s="66" t="s">
+        <v>70</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>14</v>
@@ -2121,31 +2472,49 @@
       <c r="E9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="75">
-        <v>0.5</v>
-      </c>
-      <c r="G9" s="86">
-        <v>0.25</v>
-      </c>
-      <c r="H9" s="88" t="s">
+      <c r="F9" s="70">
+        <v>0.5</v>
+      </c>
+      <c r="G9" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="H9" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="91"/>
+      <c r="J9" s="75" t="s">
+        <v>85</v>
+      </c>
+      <c r="K9" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="L9" s="75" t="s">
+        <v>82</v>
+      </c>
+      <c r="M9" s="75" t="s">
+        <v>88</v>
+      </c>
+      <c r="N9" s="79"/>
+      <c r="O9" s="99" t="s">
         <v>79</v>
       </c>
-      <c r="I9" s="95"/>
-      <c r="J9" s="97" t="s">
-        <v>91</v>
-      </c>
-      <c r="K9" s="98"/>
-      <c r="L9" s="98"/>
-      <c r="M9" s="98"/>
-      <c r="N9" s="84"/>
+      <c r="P9" s="99" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q9" s="99" t="s">
+        <v>82</v>
+      </c>
+      <c r="R9" s="99" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A10" s="71" t="s">
-        <v>74</v>
+      <c r="A10" s="66" t="s">
+        <v>70</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>14</v>
@@ -2153,49 +2522,55 @@
       <c r="E10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="75">
-        <v>0.5</v>
-      </c>
-      <c r="G10" s="86">
-        <v>0.5</v>
-      </c>
-      <c r="H10" s="88" t="s">
-        <v>79</v>
-      </c>
-      <c r="I10" s="96"/>
-      <c r="J10" s="80" t="s">
-        <v>89</v>
-      </c>
-      <c r="K10" s="80" t="s">
-        <v>88</v>
-      </c>
-      <c r="L10" s="80" t="s">
-        <v>86</v>
-      </c>
-      <c r="M10" s="80" t="s">
-        <v>92</v>
-      </c>
-      <c r="N10" s="84"/>
-      <c r="O10" s="104" t="s">
-        <v>83</v>
-      </c>
-      <c r="P10" s="104" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q10" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="R10" s="104" t="s">
-        <v>92</v>
+      <c r="F10" s="70">
+        <v>0.5</v>
+      </c>
+      <c r="G10" s="81">
+        <v>0.25</v>
+      </c>
+      <c r="H10" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="91"/>
+      <c r="J10" s="94" t="s">
+        <v>70</v>
+      </c>
+      <c r="K10" s="80">
+        <f>SUMIF(A2:A72,"大崎",F2:F72)</f>
+        <v>12.099999999999998</v>
+      </c>
+      <c r="L10" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"大崎",H2:H72,"完了")</f>
+        <v>5.5</v>
+      </c>
+      <c r="M10" s="80">
+        <f>K10 - L10</f>
+        <v>6.5999999999999979</v>
+      </c>
+      <c r="N10" s="79"/>
+      <c r="O10" s="94" t="s">
+        <v>70</v>
+      </c>
+      <c r="P10" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"大崎",E2:E72,"プロト")</f>
+        <v>5</v>
+      </c>
+      <c r="Q10" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"大崎",E2:E72,"プロト",H2:H72,"完了")</f>
+        <v>5</v>
+      </c>
+      <c r="R10" s="80">
+        <f>P10 - Q10</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A11" s="71" t="s">
-        <v>74</v>
+      <c r="A11" s="66" t="s">
+        <v>70</v>
       </c>
       <c r="B11" s="5"/>
-      <c r="C11" s="4" t="s">
-        <v>23</v>
+      <c r="C11" s="21" t="s">
+        <v>24</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>14</v>
@@ -2203,167 +2578,165 @@
       <c r="E11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="75">
-        <v>0.5</v>
-      </c>
-      <c r="G11" s="86">
-        <v>0.25</v>
-      </c>
-      <c r="H11" s="88" t="s">
-        <v>79</v>
-      </c>
-      <c r="I11" s="96"/>
-      <c r="J11" s="99" t="s">
-        <v>74</v>
-      </c>
-      <c r="K11" s="85">
-        <f>SUMIF(A3:A75,"大崎",F3:F75)</f>
-        <v>12.099999999999998</v>
-      </c>
-      <c r="L11" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"大崎",H3:H75,"完了")</f>
-        <v>5.5</v>
-      </c>
-      <c r="M11" s="85">
-        <f>K11 - L11</f>
-        <v>6.5999999999999979</v>
-      </c>
-      <c r="N11" s="84"/>
-      <c r="O11" s="99" t="s">
-        <v>74</v>
-      </c>
-      <c r="P11" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"プロト")</f>
-        <v>5</v>
-      </c>
-      <c r="Q11" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"プロト",H3:H75,"完了")</f>
-        <v>5</v>
-      </c>
-      <c r="R11" s="85">
-        <f>P11 - Q11</f>
+      <c r="F11" s="70">
+        <v>1</v>
+      </c>
+      <c r="G11" s="81">
+        <v>0.5</v>
+      </c>
+      <c r="H11" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" s="91"/>
+      <c r="J11" s="95" t="s">
+        <v>71</v>
+      </c>
+      <c r="K11" s="80">
+        <f>SUMIF(A2:A72,"上永",F2:F72)</f>
+        <v>12.5</v>
+      </c>
+      <c r="L11" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"上永",H2:H72,"完了")</f>
+        <v>8.5</v>
+      </c>
+      <c r="M11" s="80">
+        <f t="shared" ref="M11:M14" si="1">K11 - L11</f>
+        <v>4</v>
+      </c>
+      <c r="N11" s="79"/>
+      <c r="O11" s="95" t="s">
+        <v>71</v>
+      </c>
+      <c r="P11" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"上永",E2:E72,"プロト")</f>
+        <v>8</v>
+      </c>
+      <c r="Q11" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"上永",E2:E72,"プロト",H2:H72,"完了")</f>
+        <v>8</v>
+      </c>
+      <c r="R11" s="80">
+        <f t="shared" ref="R11:R14" si="2">P11 - Q11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A12" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="21" t="s">
-        <v>24</v>
+      <c r="A12" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="72"/>
+      <c r="C12" s="13" t="s">
+        <v>67</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="75">
-        <v>1</v>
-      </c>
-      <c r="G12" s="86">
-        <v>0.5</v>
-      </c>
-      <c r="H12" s="88" t="s">
-        <v>79</v>
-      </c>
-      <c r="I12" s="96"/>
-      <c r="J12" s="100" t="s">
-        <v>75</v>
-      </c>
-      <c r="K12" s="85">
-        <f>SUMIF(A3:A75,"上永",F3:F75)</f>
-        <v>17</v>
-      </c>
-      <c r="L12" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"上永",H3:H75,"完了")</f>
-        <v>8.5</v>
-      </c>
-      <c r="M12" s="85">
-        <f t="shared" ref="M12:M15" si="1">K12 - L12</f>
-        <v>8.5</v>
-      </c>
-      <c r="N12" s="84"/>
-      <c r="O12" s="100" t="s">
-        <v>75</v>
-      </c>
-      <c r="P12" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"プロト")</f>
-        <v>8</v>
-      </c>
-      <c r="Q12" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"プロト",H3:H75,"完了")</f>
-        <v>8</v>
-      </c>
-      <c r="R12" s="85">
-        <f t="shared" ref="R12:R15" si="2">P12 - Q12</f>
+        <v>9</v>
+      </c>
+      <c r="F12" s="70">
+        <v>1.5</v>
+      </c>
+      <c r="G12" s="70"/>
+      <c r="H12" s="82" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12" s="86"/>
+      <c r="J12" s="96" t="s">
+        <v>73</v>
+      </c>
+      <c r="K12" s="80">
+        <f>SUMIF(A2:A72,"川浪",F2:F72)</f>
+        <v>6.5</v>
+      </c>
+      <c r="L12" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"川浪",H2:H72,"完了")</f>
+        <v>6</v>
+      </c>
+      <c r="M12" s="80">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="N12" s="79"/>
+      <c r="O12" s="96" t="s">
+        <v>73</v>
+      </c>
+      <c r="P12" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"川浪",E2:E72,"プロト")</f>
+        <v>6</v>
+      </c>
+      <c r="Q12" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"川浪",E2:E72,"プロト",H2:H72,"完了")</f>
+        <v>6</v>
+      </c>
+      <c r="R12" s="80">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A13" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" s="77"/>
-      <c r="C13" s="13" t="s">
-        <v>71</v>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A13" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="75">
-        <v>1.5</v>
-      </c>
-      <c r="G13" s="75"/>
-      <c r="H13" s="87" t="s">
-        <v>80</v>
-      </c>
-      <c r="I13" s="91"/>
-      <c r="J13" s="101" t="s">
-        <v>77</v>
-      </c>
-      <c r="K13" s="85">
-        <f>SUMIF(A3:A75,"川浪",F3:F75)</f>
-        <v>9.5</v>
-      </c>
-      <c r="L13" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"川浪",H3:H75,"完了")</f>
-        <v>6</v>
-      </c>
-      <c r="M13" s="85">
+      <c r="F13" s="70">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I13" s="87"/>
+      <c r="J13" s="97" t="s">
+        <v>72</v>
+      </c>
+      <c r="K13" s="80">
+        <f>SUMIF(A2:A72,"佐々木",F2:F72)</f>
+        <v>10.5</v>
+      </c>
+      <c r="L13" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"佐々木",H2:H72,"完了")</f>
+        <v>4</v>
+      </c>
+      <c r="M13" s="80">
         <f t="shared" si="1"/>
-        <v>3.5</v>
-      </c>
-      <c r="N13" s="84"/>
-      <c r="O13" s="101" t="s">
-        <v>77</v>
-      </c>
-      <c r="P13" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"プロト")</f>
-        <v>8.5</v>
-      </c>
-      <c r="Q13" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"プロト",H3:H75,"完了")</f>
-        <v>6</v>
-      </c>
-      <c r="R13" s="85">
+        <v>6.5</v>
+      </c>
+      <c r="N13" s="79"/>
+      <c r="O13" s="97" t="s">
+        <v>72</v>
+      </c>
+      <c r="P13" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"佐々木",E2:E72,"プロト")</f>
+        <v>4</v>
+      </c>
+      <c r="Q13" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"佐々木",E2:E72,"プロト",H2:H72,"完了")</f>
+        <v>4</v>
+      </c>
+      <c r="R13" s="80">
         <f t="shared" si="2"/>
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A14" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>27</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A14" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="11"/>
       <c r="C14" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>14</v>
@@ -2371,53 +2744,53 @@
       <c r="E14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="75">
+      <c r="F14" s="70">
         <v>0.2</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I14" s="92"/>
-      <c r="J14" s="102" t="s">
-        <v>76</v>
-      </c>
-      <c r="K14" s="85">
-        <f>SUMIF(A3:A75,"佐々木",F3:F75)</f>
-        <v>6</v>
-      </c>
-      <c r="L14" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"佐々木",H3:H75,"完了")</f>
-        <v>4</v>
-      </c>
-      <c r="M14" s="85">
+      <c r="I14" s="79"/>
+      <c r="J14" s="98" t="s">
+        <v>74</v>
+      </c>
+      <c r="K14" s="80">
+        <f>SUMIF(A2:A72,"誰でも",F2:F72)</f>
+        <v>8</v>
+      </c>
+      <c r="L14" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"誰でも",H2:H72,"完了")</f>
+        <v>1</v>
+      </c>
+      <c r="M14" s="80">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="N14" s="84"/>
-      <c r="O14" s="102" t="s">
-        <v>76</v>
-      </c>
-      <c r="P14" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"プロト")</f>
-        <v>4</v>
-      </c>
-      <c r="Q14" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"プロト",H3:H75,"完了")</f>
-        <v>4</v>
-      </c>
-      <c r="R14" s="85">
+        <v>7</v>
+      </c>
+      <c r="N14" s="79"/>
+      <c r="O14" s="98" t="s">
+        <v>74</v>
+      </c>
+      <c r="P14" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"誰でも",E2:E72,"プロト")</f>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"誰でも",E2:E72,"プロト",H2:H72,"完了")</f>
+        <v>1</v>
+      </c>
+      <c r="R14" s="80">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A15" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="4" t="s">
-        <v>29</v>
+      <c r="A15" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="12"/>
+      <c r="C15" s="13" t="s">
+        <v>30</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>14</v>
@@ -2425,80 +2798,74 @@
       <c r="E15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="75">
+      <c r="F15" s="70">
         <v>0.2</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I15" s="84"/>
-      <c r="J15" s="103" t="s">
-        <v>78</v>
-      </c>
-      <c r="K15" s="85">
-        <f>SUMIF(A3:A75,"誰でも",F3:F75)</f>
-        <v>8</v>
-      </c>
-      <c r="L15" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"誰でも",H3:H75,"完了")</f>
-        <v>1</v>
-      </c>
-      <c r="M15" s="85">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="N15" s="84"/>
-      <c r="O15" s="103" t="s">
-        <v>78</v>
-      </c>
-      <c r="P15" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"プロト")</f>
-        <v>2</v>
-      </c>
-      <c r="Q15" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"プロト",H3:H75,"完了")</f>
-        <v>1</v>
-      </c>
-      <c r="R15" s="85">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="I15" s="79"/>
+      <c r="N15" s="79"/>
+      <c r="O15" s="79"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A16" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="13" t="s">
-        <v>30</v>
+      <c r="A16" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="75">
-        <v>0.2</v>
-      </c>
-      <c r="G16" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="F16" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="G16" s="22"/>
       <c r="H16" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I16" s="84"/>
-      <c r="N16" s="84"/>
-      <c r="O16" s="84"/>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A17" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>32</v>
+      <c r="I16" s="79"/>
+      <c r="J16" s="100" t="s">
+        <v>80</v>
+      </c>
+      <c r="K16" s="100" t="s">
+        <v>84</v>
+      </c>
+      <c r="L16" s="100" t="s">
+        <v>82</v>
+      </c>
+      <c r="M16" s="100" t="s">
+        <v>88</v>
+      </c>
+      <c r="N16" s="88"/>
+      <c r="O16" s="101" t="s">
+        <v>81</v>
+      </c>
+      <c r="P16" s="101" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q16" s="101" t="s">
+        <v>82</v>
+      </c>
+      <c r="R16" s="101" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A17" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="17"/>
+      <c r="C17" s="21" t="s">
+        <v>33</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>14</v>
@@ -2506,47 +2873,53 @@
       <c r="E17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="76">
-        <v>0.5</v>
-      </c>
-      <c r="G17" s="22"/>
+      <c r="F17" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="G17" s="26"/>
       <c r="H17" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I17" s="84"/>
-      <c r="J17" s="105" t="s">
-        <v>84</v>
-      </c>
-      <c r="K17" s="105" t="s">
-        <v>88</v>
-      </c>
-      <c r="L17" s="105" t="s">
-        <v>86</v>
-      </c>
-      <c r="M17" s="105" t="s">
-        <v>92</v>
-      </c>
-      <c r="N17" s="93"/>
-      <c r="O17" s="106" t="s">
-        <v>85</v>
-      </c>
-      <c r="P17" s="106" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q17" s="106" t="s">
-        <v>86</v>
-      </c>
-      <c r="R17" s="106" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A18" s="71" t="s">
-        <v>74</v>
+      <c r="I17" s="79"/>
+      <c r="J17" s="94" t="s">
+        <v>70</v>
+      </c>
+      <c r="K17" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"大崎",E2:E72,"アルファ")</f>
+        <v>3.6000000000000005</v>
+      </c>
+      <c r="L17" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"大崎",E2:E72,"アルファ",H2:H72,"完了")</f>
+        <v>0.5</v>
+      </c>
+      <c r="M17" s="80">
+        <f>K17 - L17</f>
+        <v>3.1000000000000005</v>
+      </c>
+      <c r="N17" s="79"/>
+      <c r="O17" s="94" t="s">
+        <v>70</v>
+      </c>
+      <c r="P17" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"大崎",E2:E72,"ベータ")</f>
+        <v>3.5</v>
+      </c>
+      <c r="Q17" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"大崎",E2:E72,"ベータ",H2:H72,"完了")</f>
+        <v>0</v>
+      </c>
+      <c r="R17" s="80">
+        <f>P17 - Q17</f>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A18" s="66" t="s">
+        <v>70</v>
       </c>
       <c r="B18" s="17"/>
       <c r="C18" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>14</v>
@@ -2554,53 +2927,53 @@
       <c r="E18" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="76">
-        <v>0.5</v>
-      </c>
-      <c r="G18" s="26"/>
+      <c r="F18" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="G18" s="24"/>
       <c r="H18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I18" s="84"/>
-      <c r="J18" s="99" t="s">
-        <v>74</v>
-      </c>
-      <c r="K18" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"アルファ")</f>
-        <v>3.6000000000000005</v>
-      </c>
-      <c r="L18" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"アルファ",H3:H75,"完了")</f>
-        <v>0.5</v>
-      </c>
-      <c r="M18" s="85">
-        <f>K18 - L18</f>
-        <v>3.1000000000000005</v>
-      </c>
-      <c r="N18" s="84"/>
-      <c r="O18" s="99" t="s">
-        <v>74</v>
-      </c>
-      <c r="P18" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"ベータ")</f>
-        <v>3.5</v>
-      </c>
-      <c r="Q18" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"大崎",E3:E75,"ベータ",H3:H75,"完了")</f>
+      <c r="I18" s="79"/>
+      <c r="J18" s="95" t="s">
+        <v>71</v>
+      </c>
+      <c r="K18" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"上永",E2:E72,"アルファ")</f>
+        <v>1.5</v>
+      </c>
+      <c r="L18" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"上永",E2:E72,"アルファ",H2:H72,"完了")</f>
+        <v>0.5</v>
+      </c>
+      <c r="M18" s="80">
+        <f t="shared" ref="M18:M21" si="3">K18 - L18</f>
+        <v>1</v>
+      </c>
+      <c r="N18" s="79"/>
+      <c r="O18" s="95" t="s">
+        <v>71</v>
+      </c>
+      <c r="P18" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"上永",E2:E72,"ベータ")</f>
+        <v>3</v>
+      </c>
+      <c r="Q18" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"上永",E2:E72,"ベータ",H2:H72,"完了")</f>
         <v>0</v>
       </c>
-      <c r="R18" s="85">
-        <f>P18 - Q18</f>
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A19" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="21" t="s">
-        <v>34</v>
+      <c r="R18" s="80">
+        <f t="shared" ref="R18:R21" si="4">P18 - Q18</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A19" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="18"/>
+      <c r="C19" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>14</v>
@@ -2608,53 +2981,53 @@
       <c r="E19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="76">
+      <c r="F19" s="71">
         <v>0.5</v>
       </c>
       <c r="G19" s="24"/>
       <c r="H19" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I19" s="84"/>
-      <c r="J19" s="100" t="s">
-        <v>75</v>
-      </c>
-      <c r="K19" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"アルファ")</f>
-        <v>4</v>
-      </c>
-      <c r="L19" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"アルファ",H3:H75,"完了")</f>
-        <v>0.5</v>
-      </c>
-      <c r="M19" s="85">
-        <f t="shared" ref="M19:M22" si="3">K19 - L19</f>
-        <v>3.5</v>
-      </c>
-      <c r="N19" s="84"/>
-      <c r="O19" s="100" t="s">
-        <v>75</v>
-      </c>
-      <c r="P19" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"ベータ")</f>
-        <v>5</v>
-      </c>
-      <c r="Q19" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"上永",E3:E75,"ベータ",H3:H75,"完了")</f>
+      <c r="J19" s="96" t="s">
+        <v>73</v>
+      </c>
+      <c r="K19" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"川浪",E2:E72,"アルファ")</f>
+        <v>0.5</v>
+      </c>
+      <c r="L19" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"川浪",E2:E72,"アルファ",H2:H72,"完了")</f>
         <v>0</v>
       </c>
-      <c r="R19" s="85">
-        <f t="shared" ref="R19:R22" si="4">P19 - Q19</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A20" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="13" t="s">
-        <v>26</v>
+      <c r="M19" s="80">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="O19" s="96" t="s">
+        <v>73</v>
+      </c>
+      <c r="P19" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"川浪",E2:E72,"ベータ")</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"川浪",E2:E72,"ベータ",H2:H72,"完了")</f>
+        <v>0</v>
+      </c>
+      <c r="R19" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A20" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>14</v>
@@ -2662,53 +3035,51 @@
       <c r="E20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="76">
-        <v>0.5</v>
-      </c>
-      <c r="G20" s="24"/>
+      <c r="F20" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="G20" s="22"/>
       <c r="H20" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J20" s="101" t="s">
-        <v>77</v>
-      </c>
-      <c r="K20" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"アルファ")</f>
-        <v>1</v>
-      </c>
-      <c r="L20" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"アルファ",H3:H75,"完了")</f>
+      <c r="J20" s="97" t="s">
+        <v>72</v>
+      </c>
+      <c r="K20" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"佐々木",E2:E72,"アルファ")</f>
+        <v>2.5</v>
+      </c>
+      <c r="L20" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"佐々木",E2:E72,"アルファ",H2:H72,"完了")</f>
         <v>0</v>
       </c>
-      <c r="M20" s="85">
+      <c r="M20" s="80">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O20" s="101" t="s">
-        <v>77</v>
-      </c>
-      <c r="P20" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"ベータ")</f>
+        <v>2.5</v>
+      </c>
+      <c r="O20" s="97" t="s">
+        <v>72</v>
+      </c>
+      <c r="P20" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"佐々木",E2:E72,"ベータ")</f>
+        <v>2</v>
+      </c>
+      <c r="Q20" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"佐々木",E2:E72,"ベータ",H2:H72,"完了")</f>
         <v>0</v>
       </c>
-      <c r="Q20" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"川浪",E3:E75,"ベータ",H3:H75,"完了")</f>
-        <v>0</v>
-      </c>
-      <c r="R20" s="85">
+      <c r="R20" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A21" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>32</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A21" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="17"/>
+      <c r="C21" s="21" t="s">
+        <v>33</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>14</v>
@@ -2716,51 +3087,51 @@
       <c r="E21" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="76">
-        <v>0.5</v>
-      </c>
-      <c r="G21" s="22"/>
+      <c r="F21" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="G21" s="26"/>
       <c r="H21" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J21" s="102" t="s">
-        <v>76</v>
-      </c>
-      <c r="K21" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"アルファ")</f>
+      <c r="J21" s="98" t="s">
+        <v>74</v>
+      </c>
+      <c r="K21" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"誰でも",E2:E72,"アルファ")</f>
+        <v>3</v>
+      </c>
+      <c r="L21" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"誰でも",E2:E72,"アルファ",H2:H72,"完了")</f>
         <v>0</v>
       </c>
-      <c r="L21" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"アルファ",H3:H75,"完了")</f>
+      <c r="M21" s="80">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="O21" s="98" t="s">
+        <v>74</v>
+      </c>
+      <c r="P21" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"誰でも",E2:E72,"ベータ")</f>
+        <v>4</v>
+      </c>
+      <c r="Q21" s="80">
+        <f>SUMIFS(F2:F72,A2:A72,"誰でも",E2:E72,"ベータ",H2:H72,"完了")</f>
         <v>0</v>
       </c>
-      <c r="M21" s="85">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="102" t="s">
-        <v>76</v>
-      </c>
-      <c r="P21" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"ベータ")</f>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"佐々木",E3:E75,"ベータ",H3:H75,"完了")</f>
-        <v>0</v>
-      </c>
-      <c r="R21" s="85">
+      <c r="R21" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A22" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="21" t="s">
-        <v>33</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>14</v>
@@ -2768,75 +3139,58 @@
       <c r="E22" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="76">
-        <v>0.5</v>
-      </c>
-      <c r="G22" s="26"/>
+      <c r="F22" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="G22" s="24"/>
       <c r="H22" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J22" s="103" t="s">
-        <v>78</v>
-      </c>
-      <c r="K22" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"アルファ")</f>
-        <v>2</v>
-      </c>
-      <c r="L22" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"アルファ",H3:H75,"完了")</f>
-        <v>0</v>
-      </c>
-      <c r="M22" s="85">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="O22" s="103" t="s">
-        <v>78</v>
-      </c>
-      <c r="P22" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"ベータ")</f>
-        <v>4</v>
-      </c>
-      <c r="Q22" s="85">
-        <f>SUMIFS(F3:F75,A3:A75,"誰でも",E3:E75,"ベータ",H3:H75,"完了")</f>
-        <v>0</v>
-      </c>
-      <c r="R22" s="85">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A23" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" s="18"/>
-      <c r="C23" s="13" t="s">
-        <v>34</v>
+    </row>
+    <row r="23" spans="1:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>38</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" s="76">
-        <v>0.5</v>
-      </c>
-      <c r="G23" s="24"/>
+        <v>8</v>
+      </c>
+      <c r="F23" s="22">
+        <v>1</v>
+      </c>
+      <c r="G23" s="16">
+        <v>1</v>
+      </c>
       <c r="H23" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A24" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>38</v>
+      <c r="J23" s="102" t="s">
+        <v>89</v>
+      </c>
+      <c r="K23" s="103"/>
+      <c r="R23" s="129" t="s">
+        <v>79</v>
+      </c>
+      <c r="S23" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="T23" s="130"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A24" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="17"/>
+      <c r="C24" s="21" t="s">
+        <v>39</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>14</v>
@@ -2844,23 +3198,51 @@
       <c r="E24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="22">
+      <c r="F24" s="26">
         <v>1</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="29">
         <v>1</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A25" s="72" t="s">
         <v>75</v>
+      </c>
+      <c r="J24" s="104" t="s">
+        <v>90</v>
+      </c>
+      <c r="K24" s="105" t="s">
+        <v>91</v>
+      </c>
+      <c r="L24" s="105" t="s">
+        <v>92</v>
+      </c>
+      <c r="M24" s="105" t="s">
+        <v>93</v>
+      </c>
+      <c r="N24" s="105" t="s">
+        <v>94</v>
+      </c>
+      <c r="O24" s="105" t="s">
+        <v>95</v>
+      </c>
+      <c r="P24" s="106" t="s">
+        <v>96</v>
+      </c>
+      <c r="R24" s="68" t="s">
+        <v>80</v>
+      </c>
+      <c r="S24" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="T24" s="68"/>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A25" s="67" t="s">
+        <v>71</v>
       </c>
       <c r="B25" s="17"/>
       <c r="C25" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>14</v>
@@ -2868,23 +3250,51 @@
       <c r="E25" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="23">
+        <v>0.5</v>
+      </c>
+      <c r="G25" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J25" s="107">
         <v>1</v>
       </c>
-      <c r="G25" s="29">
-        <v>1</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A26" s="72" t="s">
-        <v>75</v>
+      <c r="K25" s="26">
+        <v>2</v>
+      </c>
+      <c r="L25" s="26">
+        <v>3</v>
+      </c>
+      <c r="M25" s="26">
+        <v>4</v>
+      </c>
+      <c r="N25" s="108">
+        <v>5</v>
+      </c>
+      <c r="O25" s="108">
+        <v>6</v>
+      </c>
+      <c r="P25" s="109">
+        <v>7</v>
+      </c>
+      <c r="R25" s="131" t="s">
+        <v>81</v>
+      </c>
+      <c r="S25" s="131" t="s">
+        <v>100</v>
+      </c>
+      <c r="T25" s="131"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A26" s="67" t="s">
+        <v>71</v>
       </c>
       <c r="B26" s="17"/>
       <c r="C26" s="21" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>14</v>
@@ -2892,23 +3302,51 @@
       <c r="E26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="G26" s="7">
-        <v>0.5</v>
+      <c r="F26" s="26">
+        <v>1</v>
+      </c>
+      <c r="G26" s="29">
+        <v>1</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A27" s="72" t="s">
         <v>75</v>
+      </c>
+      <c r="J26" s="110">
+        <v>8</v>
+      </c>
+      <c r="K26" s="108">
+        <v>9</v>
+      </c>
+      <c r="L26" s="108">
+        <v>10</v>
+      </c>
+      <c r="M26" s="108">
+        <v>11</v>
+      </c>
+      <c r="N26" s="108">
+        <v>12</v>
+      </c>
+      <c r="O26" s="108">
+        <v>13</v>
+      </c>
+      <c r="P26" s="109">
+        <v>14</v>
+      </c>
+      <c r="R26" s="132" t="s">
+        <v>86</v>
+      </c>
+      <c r="S26" s="132" t="s">
+        <v>101</v>
+      </c>
+      <c r="T26" s="132"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A27" s="67" t="s">
+        <v>71</v>
       </c>
       <c r="B27" s="17"/>
       <c r="C27" s="21" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>14</v>
@@ -2917,70 +3355,119 @@
         <v>8</v>
       </c>
       <c r="F27" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="G27" s="29">
+        <v>0.5</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J27" s="110">
+        <v>15</v>
+      </c>
+      <c r="K27" s="108">
+        <v>16</v>
+      </c>
+      <c r="L27" s="108">
+        <v>17</v>
+      </c>
+      <c r="M27" s="108">
+        <v>18</v>
+      </c>
+      <c r="N27" s="108">
+        <v>19</v>
+      </c>
+      <c r="O27" s="111">
+        <v>20</v>
+      </c>
+      <c r="P27" s="112">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="18"/>
+      <c r="C28" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F28" s="23">
         <v>1</v>
       </c>
-      <c r="G27" s="29">
+      <c r="G28" s="29"/>
+      <c r="H28" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J28" s="113">
+        <v>22</v>
+      </c>
+      <c r="K28" s="114">
+        <v>23</v>
+      </c>
+      <c r="L28" s="114">
+        <v>24</v>
+      </c>
+      <c r="M28" s="114">
+        <v>25</v>
+      </c>
+      <c r="N28" s="114">
+        <v>26</v>
+      </c>
+      <c r="O28" s="114">
+        <v>27</v>
+      </c>
+      <c r="P28" s="115">
+        <v>28</v>
+      </c>
+      <c r="R28" s="133" t="s">
+        <v>102</v>
+      </c>
+      <c r="S28" s="133"/>
+    </row>
+    <row r="29" spans="1:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="16">
         <v>1</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A28" s="72" t="s">
+      <c r="G29" s="22">
+        <v>2</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" s="26">
-        <v>0.5</v>
-      </c>
-      <c r="G28" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A29" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="B29" s="18"/>
-      <c r="C29" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F29" s="23">
-        <v>1</v>
-      </c>
-      <c r="G29" s="29"/>
-      <c r="H29" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A30" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>24</v>
+      <c r="J29" s="102" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A30" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="17"/>
+      <c r="C30" s="21" t="s">
+        <v>44</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>14</v>
@@ -2988,23 +3475,44 @@
       <c r="E30" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="16">
-        <v>1</v>
-      </c>
-      <c r="G30" s="22">
-        <v>2</v>
+      <c r="F30" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="G30" s="26">
+        <v>0.5</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A31" s="72" t="s">
         <v>75</v>
+      </c>
+      <c r="J30" s="116" t="s">
+        <v>90</v>
+      </c>
+      <c r="K30" s="105" t="s">
+        <v>91</v>
+      </c>
+      <c r="L30" s="105" t="s">
+        <v>92</v>
+      </c>
+      <c r="M30" s="105" t="s">
+        <v>93</v>
+      </c>
+      <c r="N30" s="105" t="s">
+        <v>94</v>
+      </c>
+      <c r="O30" s="105" t="s">
+        <v>95</v>
+      </c>
+      <c r="P30" s="106" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A31" s="67" t="s">
+        <v>71</v>
       </c>
       <c r="B31" s="17"/>
       <c r="C31" s="21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>14</v>
@@ -3016,19 +3524,40 @@
         <v>0.5</v>
       </c>
       <c r="G31" s="26">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A32" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="21" t="s">
-        <v>45</v>
+      <c r="J31" s="117">
+        <v>1</v>
+      </c>
+      <c r="K31" s="118">
+        <v>2</v>
+      </c>
+      <c r="L31" s="118">
+        <v>3</v>
+      </c>
+      <c r="M31" s="118">
+        <v>4</v>
+      </c>
+      <c r="N31" s="118">
+        <v>5</v>
+      </c>
+      <c r="O31" s="118">
+        <v>6</v>
+      </c>
+      <c r="P31" s="119">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A32" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="18"/>
+      <c r="C32" s="13" t="s">
+        <v>46</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>14</v>
@@ -3036,49 +3565,89 @@
       <c r="E32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="26">
-        <v>0.5</v>
-      </c>
-      <c r="G32" s="26">
+      <c r="F32" s="19">
         <v>1</v>
       </c>
+      <c r="G32" s="24">
+        <v>1</v>
+      </c>
       <c r="H32" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A33" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="B33" s="18"/>
-      <c r="C33" s="13" t="s">
-        <v>46</v>
+      <c r="J32" s="120">
+        <v>8</v>
+      </c>
+      <c r="K32" s="118">
+        <v>9</v>
+      </c>
+      <c r="L32" s="118">
+        <v>10</v>
+      </c>
+      <c r="M32" s="121">
+        <v>11</v>
+      </c>
+      <c r="N32" s="121">
+        <v>12</v>
+      </c>
+      <c r="O32" s="121">
+        <v>13</v>
+      </c>
+      <c r="P32" s="122">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A33" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>48</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="19">
-        <v>1</v>
-      </c>
-      <c r="G33" s="24">
-        <v>1</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="F33" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="G33" s="22"/>
       <c r="H33" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A34" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="J33" s="123">
+        <v>15</v>
+      </c>
+      <c r="K33" s="124">
+        <v>16</v>
+      </c>
+      <c r="L33" s="26">
+        <v>17</v>
+      </c>
+      <c r="M33" s="26">
+        <v>18</v>
+      </c>
+      <c r="N33" s="26">
+        <v>19</v>
+      </c>
+      <c r="O33" s="26">
+        <v>20</v>
+      </c>
+      <c r="P33" s="125">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A34" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B34" s="17"/>
+      <c r="C34" s="21" t="s">
+        <v>32</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>14</v>
@@ -3086,21 +3655,42 @@
       <c r="E34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F34" s="22">
-        <v>0.5</v>
-      </c>
-      <c r="G34" s="22"/>
+      <c r="F34" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="G34" s="26"/>
       <c r="H34" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A35" s="72" t="s">
-        <v>75</v>
+      <c r="J34" s="107">
+        <v>22</v>
+      </c>
+      <c r="K34" s="26">
+        <v>23</v>
+      </c>
+      <c r="L34" s="26">
+        <v>24</v>
+      </c>
+      <c r="M34" s="26">
+        <v>25</v>
+      </c>
+      <c r="N34" s="26">
+        <v>26</v>
+      </c>
+      <c r="O34" s="26">
+        <v>27</v>
+      </c>
+      <c r="P34" s="125">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="67" t="s">
+        <v>71</v>
       </c>
       <c r="B35" s="17"/>
       <c r="C35" s="21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>14</v>
@@ -3115,14 +3705,27 @@
       <c r="H35" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A36" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="B36" s="17"/>
-      <c r="C36" s="21" t="s">
-        <v>33</v>
+      <c r="J35" s="126">
+        <v>29</v>
+      </c>
+      <c r="K35" s="127">
+        <v>30</v>
+      </c>
+      <c r="L35" s="127">
+        <v>31</v>
+      </c>
+      <c r="M35" s="127"/>
+      <c r="N35" s="127"/>
+      <c r="O35" s="127"/>
+      <c r="P35" s="128"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A36" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="18"/>
+      <c r="C36" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>14</v>
@@ -3130,45 +3733,47 @@
       <c r="E36" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F36" s="26">
-        <v>0.5</v>
-      </c>
-      <c r="G36" s="26"/>
+      <c r="F36" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="G36" s="24"/>
       <c r="H36" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A37" s="72" t="s">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A37" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G37" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="18"/>
-      <c r="C37" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F37" s="24">
-        <v>0.5</v>
-      </c>
-      <c r="G37" s="24"/>
-      <c r="H37" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A38" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>32</v>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A38" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" s="17"/>
+      <c r="C38" s="21" t="s">
+        <v>33</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>14</v>
@@ -3176,23 +3781,22 @@
       <c r="E38" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F38" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="G38" s="22">
-        <v>0.5</v>
-      </c>
+      <c r="F38" s="25">
+        <v>0.5</v>
+      </c>
+      <c r="G38" s="26"/>
       <c r="H38" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A39" s="72" t="s">
-        <v>75</v>
+        <v>57</v>
+      </c>
+      <c r="K38" s="74"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A39" s="67" t="s">
+        <v>71</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>14</v>
@@ -3207,65 +3811,65 @@
       <c r="H39" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K39" s="79"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A40" s="72" t="s">
+      <c r="K39" s="74"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A40" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" s="18"/>
+      <c r="C40" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" s="9">
+        <v>1</v>
+      </c>
+      <c r="G40" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" s="25">
-        <v>0.5</v>
-      </c>
-      <c r="G40" s="26"/>
-      <c r="H40" s="3" t="s">
+      <c r="K40" s="74"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A41" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F41" s="15">
+        <v>1</v>
+      </c>
+      <c r="G41" s="22"/>
+      <c r="H41" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K40" s="79"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A41" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" s="9">
-        <v>1</v>
-      </c>
-      <c r="G41" s="24">
-        <v>0.5</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="K41" s="79"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A42" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>52</v>
+      <c r="K41" s="74"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A42" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="B42" s="17"/>
+      <c r="C42" s="21" t="s">
+        <v>32</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>7</v>
@@ -3273,89 +3877,88 @@
       <c r="E42" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F42" s="15">
-        <v>1</v>
-      </c>
-      <c r="G42" s="22"/>
+      <c r="F42" s="25">
+        <v>0.5</v>
+      </c>
+      <c r="G42" s="26"/>
       <c r="H42" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K42" s="79"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A43" s="72" t="s">
-        <v>75</v>
+      <c r="K42" s="74"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A43" s="65" t="s">
+        <v>72</v>
       </c>
       <c r="B43" s="17"/>
       <c r="C43" s="21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F43" s="25">
         <v>0.5</v>
       </c>
-      <c r="G43" s="26"/>
+      <c r="G43" s="23"/>
       <c r="H43" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K43" s="79"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A44" s="72" t="s">
-        <v>75</v>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A44" s="65" t="s">
+        <v>72</v>
       </c>
       <c r="B44" s="17"/>
       <c r="C44" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F44" s="25">
         <v>0.5</v>
       </c>
-      <c r="G44" s="23"/>
+      <c r="G44" s="26"/>
       <c r="H44" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A45" s="72" t="s">
-        <v>75</v>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A45" s="65" t="s">
+        <v>72</v>
       </c>
       <c r="B45" s="17"/>
       <c r="C45" s="21" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F45" s="25">
         <v>0.5</v>
       </c>
-      <c r="G45" s="26"/>
+      <c r="G45" s="23"/>
       <c r="H45" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A46" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="B46" s="17"/>
-      <c r="C46" s="21" t="s">
-        <v>53</v>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A46" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="B46" s="18"/>
+      <c r="C46" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>14</v>
@@ -3366,21 +3969,23 @@
       <c r="F46" s="25">
         <v>0.5</v>
       </c>
-      <c r="G46" s="23"/>
+      <c r="G46" s="26"/>
       <c r="H46" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A47" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="B47" s="18"/>
-      <c r="C47" s="13" t="s">
-        <v>26</v>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A47" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>28</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>9</v>
@@ -3393,15 +3998,13 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A48" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C48" s="20" t="s">
-        <v>28</v>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A48" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="B48" s="18"/>
+      <c r="C48" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>7</v>
@@ -3412,42 +4015,46 @@
       <c r="F48" s="25">
         <v>0.5</v>
       </c>
-      <c r="G48" s="26"/>
+      <c r="G48" s="24"/>
       <c r="H48" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A49" s="72" t="s">
+      <c r="A49" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" s="28">
+        <v>1</v>
+      </c>
+      <c r="G49" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="H49" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B49" s="18"/>
-      <c r="C49" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" s="25">
-        <v>0.5</v>
-      </c>
-      <c r="G49" s="24"/>
-      <c r="H49" s="3" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A50" s="70" t="s">
-        <v>76</v>
-      </c>
-      <c r="B50" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50" s="27" t="s">
-        <v>56</v>
+      <c r="A50" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="B50" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" s="32" t="s">
+        <v>59</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>14</v>
@@ -3455,612 +4062,542 @@
       <c r="E50" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F50" s="28">
+      <c r="F50" s="33">
+        <v>3</v>
+      </c>
+      <c r="G50" s="34">
+        <v>3</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A51" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="B51" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F51" s="40">
         <v>1</v>
       </c>
-      <c r="G50" s="26">
-        <v>0.5</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A51" s="70" t="s">
-        <v>76</v>
-      </c>
-      <c r="B51" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="C51" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" s="34">
-        <v>3</v>
-      </c>
-      <c r="G51" s="35">
-        <v>3</v>
-      </c>
+      <c r="G51" s="30"/>
       <c r="H51" s="3" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A52" s="70" t="s">
-        <v>76</v>
-      </c>
-      <c r="B52" s="40" t="s">
-        <v>60</v>
-      </c>
+      <c r="A52" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="B52" s="42"/>
       <c r="C52" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="D52" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="E52" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D52" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="F52" s="41">
+      <c r="F52" s="40">
         <v>1</v>
       </c>
-      <c r="G52" s="31"/>
+      <c r="G52" s="30"/>
       <c r="H52" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A53" s="70" t="s">
-        <v>76</v>
-      </c>
-      <c r="B53" s="44"/>
-      <c r="C53" s="39" t="s">
-        <v>62</v>
-      </c>
-      <c r="D53" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="E53" s="42" t="s">
-        <v>63</v>
-      </c>
-      <c r="F53" s="41">
+      <c r="A53" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="B53" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="D53" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="G53" s="46">
+        <v>0.5</v>
+      </c>
+      <c r="H53" s="44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A54" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" s="47"/>
+      <c r="C54" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="D54" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E54" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" s="52">
         <v>1</v>
       </c>
-      <c r="G53" s="31"/>
-      <c r="H53" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A54" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B54" s="40" t="s">
-        <v>64</v>
-      </c>
-      <c r="C54" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="D54" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="E54" s="42" t="s">
+      <c r="G54" s="53">
+        <v>1</v>
+      </c>
+      <c r="H54" s="44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A55" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="B55" s="47"/>
+      <c r="C55" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" s="44" t="s">
         <v>8</v>
-      </c>
-      <c r="F54" s="43">
-        <v>1</v>
-      </c>
-      <c r="G54" s="31"/>
-      <c r="H54" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A55" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B55" s="45"/>
-      <c r="C55" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="D55" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E55" s="48" t="s">
-        <v>9</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
-      <c r="G55" s="23"/>
-      <c r="H55" s="48" t="s">
+      <c r="G55" s="23">
+        <v>1</v>
+      </c>
+      <c r="H55" s="44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A56" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" s="55" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="G56" s="63">
+        <v>0.5</v>
+      </c>
+      <c r="H56" s="44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A57" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="B57" s="47"/>
+      <c r="C57" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="D57" s="58" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="60" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="53">
+        <v>0.5</v>
+      </c>
+      <c r="G57" s="63">
+        <v>0.5</v>
+      </c>
+      <c r="H57" s="44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A58" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="B58" s="47"/>
+      <c r="C58" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D58" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="53">
+        <v>0.5</v>
+      </c>
+      <c r="G58" s="63">
+        <v>0.5</v>
+      </c>
+      <c r="H58" s="44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A59" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="47"/>
+      <c r="C59" s="50" t="s">
+        <v>47</v>
+      </c>
+      <c r="D59" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" s="53">
+        <v>0.5</v>
+      </c>
+      <c r="G59" s="63"/>
+      <c r="H59" s="44" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A56" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B56" s="37" t="s">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A60" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="B60" s="47"/>
+      <c r="C60" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="D60" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60" s="59" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" s="62">
+        <v>0.5</v>
+      </c>
+      <c r="G60" s="63">
+        <v>0.5</v>
+      </c>
+      <c r="H60" s="44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A61" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" s="47"/>
+      <c r="C61" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="D61" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="59" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="53">
+        <v>0.5</v>
+      </c>
+      <c r="G61" s="63">
+        <v>0.5</v>
+      </c>
+      <c r="H61" s="44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A62" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="B62" s="47"/>
+      <c r="C62" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="D62" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" s="59" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="53">
+        <v>0.5</v>
+      </c>
+      <c r="G62" s="63">
+        <v>0.5</v>
+      </c>
+      <c r="H62" s="44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A63" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="B63" s="48"/>
+      <c r="C63" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="D63" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="60" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" s="53">
+        <v>0.5</v>
+      </c>
+      <c r="G63" s="63">
+        <v>0.5</v>
+      </c>
+      <c r="H63" s="58" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A64" s="135" t="s">
+        <v>103</v>
+      </c>
+      <c r="B64" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="C64" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="D64" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="F64" s="64">
+        <v>1</v>
+      </c>
+      <c r="G64" s="134"/>
+      <c r="H64" s="58" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A65" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="B65" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="D65" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" s="60" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" s="64">
+        <v>1</v>
+      </c>
+      <c r="G65" s="64">
+        <v>1</v>
+      </c>
+      <c r="H65" s="58" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A66" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="B66" s="47"/>
+      <c r="C66" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="C56" s="53" t="s">
+      <c r="D66" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" s="64">
+        <v>1</v>
+      </c>
+      <c r="G66" s="53"/>
+      <c r="H66" s="58" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A67" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" s="47"/>
+      <c r="C67" s="50" t="s">
+        <v>47</v>
+      </c>
+      <c r="D67" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="F67" s="64">
+        <v>1</v>
+      </c>
+      <c r="G67" s="62"/>
+      <c r="H67" s="58" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A68" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="47"/>
+      <c r="C68" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="D68" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="F68" s="64">
+        <v>1</v>
+      </c>
+      <c r="G68" s="53"/>
+      <c r="H68" s="58" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A69" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="B69" s="47"/>
+      <c r="C69" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="D69" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="F69" s="64">
+        <v>1</v>
+      </c>
+      <c r="G69" s="62"/>
+      <c r="H69" s="58" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A70" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" s="47"/>
+      <c r="C70" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D70" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" s="64">
+        <v>1</v>
+      </c>
+      <c r="G70" s="53"/>
+      <c r="H70" s="58" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A71" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="B71" s="47"/>
+      <c r="C71" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="D71" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="F71" s="64">
+        <v>1</v>
+      </c>
+      <c r="G71" s="53"/>
+      <c r="H71" s="58" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A72" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="B72" s="48"/>
+      <c r="C72" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="D56" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E56" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" s="49">
-        <v>0.5</v>
-      </c>
-      <c r="G56" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="H56" s="48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A57" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B57" s="51"/>
-      <c r="C57" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="D57" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E57" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" s="57">
+      <c r="D72" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" s="26">
         <v>1</v>
       </c>
-      <c r="G57" s="58">
-        <v>1</v>
-      </c>
-      <c r="H57" s="48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A58" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B58" s="51"/>
-      <c r="C58" s="54" t="s">
-        <v>69</v>
-      </c>
-      <c r="D58" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E58" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="57">
-        <v>1</v>
-      </c>
-      <c r="G58" s="56"/>
-      <c r="H58" s="48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A59" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B59" s="51"/>
-      <c r="C59" s="54" t="s">
-        <v>23</v>
-      </c>
-      <c r="D59" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E59" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59">
-        <v>1</v>
-      </c>
-      <c r="G59" s="23">
-        <v>1</v>
-      </c>
-      <c r="H59" s="48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A60" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B60" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="C60" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="D60" s="59" t="s">
-        <v>14</v>
-      </c>
-      <c r="E60" s="60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" s="49">
-        <v>0.5</v>
-      </c>
-      <c r="G60" s="68">
-        <v>0.5</v>
-      </c>
-      <c r="H60" s="48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A61" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B61" s="51"/>
-      <c r="C61" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="D61" s="63" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" s="58">
-        <v>0.5</v>
-      </c>
-      <c r="G61" s="68">
-        <v>0.5</v>
-      </c>
-      <c r="H61" s="48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A62" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B62" s="51"/>
-      <c r="C62" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="D62" s="62" t="s">
-        <v>14</v>
-      </c>
-      <c r="E62" s="66" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" s="58">
-        <v>0.5</v>
-      </c>
-      <c r="G62" s="68">
-        <v>0.5</v>
-      </c>
-      <c r="H62" s="48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A63" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B63" s="51"/>
-      <c r="C63" s="54" t="s">
-        <v>47</v>
-      </c>
-      <c r="D63" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E63" s="64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" s="58">
-        <v>0.5</v>
-      </c>
-      <c r="G63" s="68"/>
-      <c r="H63" s="48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A64" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B64" s="51"/>
-      <c r="C64" s="54" t="s">
-        <v>32</v>
-      </c>
-      <c r="D64" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E64" s="64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" s="67">
-        <v>0.5</v>
-      </c>
-      <c r="G64" s="68">
-        <v>0.5</v>
-      </c>
-      <c r="H64" s="48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A65" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B65" s="51"/>
-      <c r="C65" s="54" t="s">
-        <v>34</v>
-      </c>
-      <c r="D65" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E65" s="64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" s="58">
-        <v>0.5</v>
-      </c>
-      <c r="G65" s="68">
-        <v>0.5</v>
-      </c>
-      <c r="H65" s="48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A66" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B66" s="51"/>
-      <c r="C66" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="D66" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F66" s="58">
-        <v>0.5</v>
-      </c>
-      <c r="G66" s="68">
-        <v>0.5</v>
-      </c>
-      <c r="H66" s="48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A67" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B67" s="52"/>
-      <c r="C67" s="55" t="s">
-        <v>37</v>
-      </c>
-      <c r="D67" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F67" s="58">
-        <v>0.5</v>
-      </c>
-      <c r="G67" s="68">
-        <v>0.5</v>
-      </c>
-      <c r="H67" s="63" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A68" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B68" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="C68" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="D68" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E68" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" s="69">
-        <v>1</v>
-      </c>
-      <c r="G68" s="69">
-        <v>1</v>
-      </c>
-      <c r="H68" s="63" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A69" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B69" s="51"/>
-      <c r="C69" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="D69" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E69" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" s="69">
-        <v>1</v>
-      </c>
-      <c r="G69" s="58"/>
-      <c r="H69" s="63" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A70" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B70" s="51"/>
-      <c r="C70" s="54" t="s">
-        <v>47</v>
-      </c>
-      <c r="D70" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="F70" s="69">
-        <v>1</v>
-      </c>
-      <c r="G70" s="67"/>
-      <c r="H70" s="63" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A71" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B71" s="51"/>
-      <c r="C71" s="54" t="s">
-        <v>35</v>
-      </c>
-      <c r="D71" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E71" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="F71" s="69">
-        <v>1</v>
-      </c>
-      <c r="G71" s="58"/>
-      <c r="H71" s="63" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A72" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B72" s="51"/>
-      <c r="C72" s="54" t="s">
-        <v>31</v>
-      </c>
-      <c r="D72" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E72" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="F72" s="69">
-        <v>1</v>
-      </c>
-      <c r="G72" s="67"/>
-      <c r="H72" s="63" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A73" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B73" s="51"/>
-      <c r="C73" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="D73" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E73" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="F73" s="69">
-        <v>1</v>
-      </c>
-      <c r="G73" s="58"/>
-      <c r="H73" s="63" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A74" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B74" s="51"/>
-      <c r="C74" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="D74" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E74" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="F74" s="69">
-        <v>1</v>
-      </c>
-      <c r="G74" s="58"/>
-      <c r="H74" s="63" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A75" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B75" s="52"/>
-      <c r="C75" s="55" t="s">
-        <v>71</v>
-      </c>
-      <c r="D75" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E75" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="F75" s="26">
-        <v>1</v>
-      </c>
-      <c r="G75" s="78"/>
-      <c r="H75" s="63" t="s">
+      <c r="G72" s="73"/>
+      <c r="H72" s="58" t="s">
         <v>57</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H75" xr:uid="{6668A6B0-AE49-40A9-BDCA-1EF7E08764AB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H72" xr:uid="{6668A6B0-AE49-40A9-BDCA-1EF7E08764AB}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E75" xr:uid="{3F25CF45-EEFF-4838-8184-2DB508A95967}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E72" xr:uid="{3F25CF45-EEFF-4838-8184-2DB508A95967}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D75" xr:uid="{D99FF9D9-52C2-47CC-BC93-4ACF23B2DA2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D72" xr:uid="{D99FF9D9-52C2-47CC-BC93-4ACF23B2DA2A}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
   </dataValidations>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hakutokawanami\Desktop\github\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD0CE35-9F3E-4220-8A57-D84D7A3D6477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0E6020-05AE-4D2C-834A-F8866784AF7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -1429,7 +1429,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1805,9 +1805,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2232,11 +2229,11 @@
       </c>
       <c r="L2" s="53">
         <f>SUMIF(H2:H72,"完了",F2:F72)</f>
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="M2" s="53">
         <f>K2-L2</f>
-        <v>25.599999999999994</v>
+        <v>23.099999999999994</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
@@ -2310,11 +2307,11 @@
       </c>
       <c r="L4" s="53">
         <f>SUMIFS(F2:F72,E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="M4" s="53">
         <f t="shared" si="0"/>
-        <v>10.100000000000001</v>
+        <v>7.6000000000000014</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
@@ -2375,9 +2372,11 @@
       <c r="F6" s="70">
         <v>1</v>
       </c>
-      <c r="G6" s="3"/>
+      <c r="G6" s="70">
+        <v>1</v>
+      </c>
       <c r="H6" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J6" s="85" t="s">
         <v>86</v>
@@ -2541,11 +2540,11 @@
       </c>
       <c r="L10" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"大崎",H2:H72,"完了")</f>
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="M10" s="80">
         <f>K10 - L10</f>
-        <v>6.5999999999999979</v>
+        <v>4.0999999999999979</v>
       </c>
       <c r="N10" s="79"/>
       <c r="O10" s="94" t="s">
@@ -2637,9 +2636,11 @@
       <c r="F12" s="70">
         <v>1.5</v>
       </c>
-      <c r="G12" s="70"/>
+      <c r="G12" s="70">
+        <v>1.5</v>
+      </c>
       <c r="H12" s="82" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I12" s="86"/>
       <c r="J12" s="96" t="s">
@@ -2890,11 +2891,11 @@
       </c>
       <c r="L17" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"大崎",E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="M17" s="80">
         <f>K17 - L17</f>
-        <v>3.1000000000000005</v>
+        <v>0.60000000000000053</v>
       </c>
       <c r="N17" s="79"/>
       <c r="O17" s="94" t="s">
@@ -3054,7 +3055,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="80">
-        <f t="shared" si="3"/>
+        <f>K20 - L20</f>
         <v>2.5</v>
       </c>
       <c r="O20" s="97" t="s">
@@ -4385,7 +4386,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A64" s="135" t="s">
+      <c r="A64" s="133" t="s">
         <v>103</v>
       </c>
       <c r="B64" s="47" t="s">

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hakutokawanami\Desktop\github\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0E6020-05AE-4D2C-834A-F8866784AF7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6517C567-3B5C-491F-9E13-34C11A8AA6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -2229,11 +2229,11 @@
       </c>
       <c r="L2" s="53">
         <f>SUMIF(H2:H72,"完了",F2:F72)</f>
-        <v>27.5</v>
+        <v>28</v>
       </c>
       <c r="M2" s="53">
         <f>K2-L2</f>
-        <v>23.099999999999994</v>
+        <v>22.599999999999994</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
@@ -2307,11 +2307,11 @@
       </c>
       <c r="L4" s="53">
         <f>SUMIFS(F2:F72,E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="M4" s="53">
         <f t="shared" si="0"/>
-        <v>7.6000000000000014</v>
+        <v>7.1000000000000014</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
@@ -2652,11 +2652,11 @@
       </c>
       <c r="L12" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"川浪",H2:H72,"完了")</f>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M12" s="80">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N12" s="79"/>
       <c r="O12" s="96" t="s">
@@ -2998,11 +2998,11 @@
       </c>
       <c r="L19" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"川浪",E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M19" s="80">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O19" s="96" t="s">
         <v>73</v>
@@ -4284,9 +4284,11 @@
       <c r="F59" s="53">
         <v>0.5</v>
       </c>
-      <c r="G59" s="63"/>
+      <c r="G59" s="63">
+        <v>0.5</v>
+      </c>
       <c r="H59" s="44" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.4">

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hakutokawanami\Desktop\github\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6517C567-3B5C-491F-9E13-34C11A8AA6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237CB94B-5A15-4703-A062-882B90CAF62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -2229,11 +2229,11 @@
       </c>
       <c r="L2" s="53">
         <f>SUMIF(H2:H72,"完了",F2:F72)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" s="53">
         <f>K2-L2</f>
-        <v>22.599999999999994</v>
+        <v>21.599999999999994</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
@@ -2307,11 +2307,11 @@
       </c>
       <c r="L4" s="53">
         <f>SUMIFS(F2:F72,E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4" s="53">
         <f t="shared" si="0"/>
-        <v>7.1000000000000014</v>
+        <v>6.1000000000000014</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
@@ -2708,11 +2708,11 @@
       </c>
       <c r="L13" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"佐々木",H2:H72,"完了")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M13" s="80">
         <f t="shared" si="1"/>
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="N13" s="79"/>
       <c r="O13" s="97" t="s">
@@ -3052,11 +3052,11 @@
       </c>
       <c r="L20" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"佐々木",E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="80">
         <f>K20 - L20</f>
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="O20" s="97" t="s">
         <v>72</v>
@@ -3994,9 +3994,11 @@
       <c r="F47" s="25">
         <v>0.5</v>
       </c>
-      <c r="G47" s="26"/>
+      <c r="G47" s="26">
+        <v>0.5</v>
+      </c>
       <c r="H47" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.4">
@@ -4016,9 +4018,11 @@
       <c r="F48" s="25">
         <v>0.5</v>
       </c>
-      <c r="G48" s="24"/>
+      <c r="G48" s="24">
+        <v>0.5</v>
+      </c>
       <c r="H48" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AyumuKaminaga\Documents\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237CB94B-5A15-4703-A062-882B90CAF62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E4B207-16D4-412C-860A-D4418657E519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -2229,11 +2229,11 @@
       </c>
       <c r="L2" s="53">
         <f>SUMIF(H2:H72,"完了",F2:F72)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="53">
         <f>K2-L2</f>
-        <v>21.599999999999994</v>
+        <v>20.599999999999994</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
@@ -2307,11 +2307,11 @@
       </c>
       <c r="L4" s="53">
         <f>SUMIFS(F2:F72,E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4" s="53">
         <f t="shared" si="0"/>
-        <v>6.1000000000000014</v>
+        <v>5.1000000000000014</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
@@ -2596,11 +2596,11 @@
       </c>
       <c r="L11" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"上永",H2:H72,"完了")</f>
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="M11" s="80">
         <f t="shared" ref="M11:M14" si="1">K11 - L11</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N11" s="79"/>
       <c r="O11" s="95" t="s">
@@ -2945,11 +2945,11 @@
       </c>
       <c r="L18" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"上永",E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M18" s="80">
         <f t="shared" ref="M18:M21" si="3">K18 - L18</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="79"/>
       <c r="O18" s="95" t="s">
@@ -3785,9 +3785,11 @@
       <c r="F38" s="25">
         <v>0.5</v>
       </c>
-      <c r="G38" s="26"/>
+      <c r="G38" s="26">
+        <v>0.5</v>
+      </c>
       <c r="H38" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="K38" s="74"/>
     </row>
@@ -3808,9 +3810,11 @@
       <c r="F39" s="25">
         <v>0.5</v>
       </c>
-      <c r="G39" s="26"/>
+      <c r="G39" s="26">
+        <v>0.5</v>
+      </c>
       <c r="H39" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="K39" s="74"/>
     </row>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0E6020-05AE-4D2C-834A-F8866784AF7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3FCB35-5FBD-4D16-8529-0CE06BD01FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -2229,11 +2229,11 @@
       </c>
       <c r="L2" s="53">
         <f>SUMIF(H2:H72,"完了",F2:F72)</f>
-        <v>27.5</v>
+        <v>28.099999999999998</v>
       </c>
       <c r="M2" s="53">
         <f>K2-L2</f>
-        <v>23.099999999999994</v>
+        <v>22.499999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
@@ -2307,11 +2307,11 @@
       </c>
       <c r="L4" s="53">
         <f>SUMIFS(F2:F72,E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>3.5</v>
+        <v>4.1000000000000005</v>
       </c>
       <c r="M4" s="53">
         <f t="shared" si="0"/>
-        <v>7.6000000000000014</v>
+        <v>7.0000000000000009</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
@@ -2540,11 +2540,11 @@
       </c>
       <c r="L10" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"大崎",H2:H72,"完了")</f>
-        <v>8</v>
+        <v>8.5999999999999979</v>
       </c>
       <c r="M10" s="80">
         <f>K10 - L10</f>
-        <v>4.0999999999999979</v>
+        <v>3.5</v>
       </c>
       <c r="N10" s="79"/>
       <c r="O10" s="94" t="s">
@@ -2694,9 +2694,11 @@
       <c r="F13" s="70">
         <v>0.2</v>
       </c>
-      <c r="G13" s="3"/>
+      <c r="G13" s="70">
+        <v>0.2</v>
+      </c>
       <c r="H13" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="I13" s="87"/>
       <c r="J13" s="97" t="s">
@@ -2748,9 +2750,11 @@
       <c r="F14" s="70">
         <v>0.2</v>
       </c>
-      <c r="G14" s="3"/>
+      <c r="G14" s="70">
+        <v>0.2</v>
+      </c>
       <c r="H14" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="I14" s="79"/>
       <c r="J14" s="98" t="s">
@@ -2802,9 +2806,11 @@
       <c r="F15" s="70">
         <v>0.2</v>
       </c>
-      <c r="G15" s="3"/>
+      <c r="G15" s="70">
+        <v>0.2</v>
+      </c>
       <c r="H15" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="I15" s="79"/>
       <c r="N15" s="79"/>
@@ -2891,11 +2897,11 @@
       </c>
       <c r="L17" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"大崎",E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>3</v>
+        <v>3.6000000000000005</v>
       </c>
       <c r="M17" s="80">
         <f>K17 - L17</f>
-        <v>0.60000000000000053</v>
+        <v>0</v>
       </c>
       <c r="N17" s="79"/>
       <c r="O17" s="94" t="s">

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AyumuKaminaga\Documents\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0E6020-05AE-4D2C-834A-F8866784AF7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E4B207-16D4-412C-860A-D4418657E519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -2229,11 +2229,11 @@
       </c>
       <c r="L2" s="53">
         <f>SUMIF(H2:H72,"完了",F2:F72)</f>
-        <v>27.5</v>
+        <v>30</v>
       </c>
       <c r="M2" s="53">
         <f>K2-L2</f>
-        <v>23.099999999999994</v>
+        <v>20.599999999999994</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
@@ -2307,11 +2307,11 @@
       </c>
       <c r="L4" s="53">
         <f>SUMIFS(F2:F72,E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="M4" s="53">
         <f t="shared" si="0"/>
-        <v>7.6000000000000014</v>
+        <v>5.1000000000000014</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
@@ -2596,11 +2596,11 @@
       </c>
       <c r="L11" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"上永",H2:H72,"完了")</f>
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="M11" s="80">
         <f t="shared" ref="M11:M14" si="1">K11 - L11</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N11" s="79"/>
       <c r="O11" s="95" t="s">
@@ -2652,11 +2652,11 @@
       </c>
       <c r="L12" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"川浪",H2:H72,"完了")</f>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M12" s="80">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N12" s="79"/>
       <c r="O12" s="96" t="s">
@@ -2708,11 +2708,11 @@
       </c>
       <c r="L13" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"佐々木",H2:H72,"完了")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M13" s="80">
         <f t="shared" si="1"/>
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="N13" s="79"/>
       <c r="O13" s="97" t="s">
@@ -2945,11 +2945,11 @@
       </c>
       <c r="L18" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"上永",E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M18" s="80">
         <f t="shared" ref="M18:M21" si="3">K18 - L18</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="79"/>
       <c r="O18" s="95" t="s">
@@ -2998,11 +2998,11 @@
       </c>
       <c r="L19" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"川浪",E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M19" s="80">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O19" s="96" t="s">
         <v>73</v>
@@ -3052,11 +3052,11 @@
       </c>
       <c r="L20" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"佐々木",E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="80">
         <f>K20 - L20</f>
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="O20" s="97" t="s">
         <v>72</v>
@@ -3785,9 +3785,11 @@
       <c r="F38" s="25">
         <v>0.5</v>
       </c>
-      <c r="G38" s="26"/>
+      <c r="G38" s="26">
+        <v>0.5</v>
+      </c>
       <c r="H38" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="K38" s="74"/>
     </row>
@@ -3808,9 +3810,11 @@
       <c r="F39" s="25">
         <v>0.5</v>
       </c>
-      <c r="G39" s="26"/>
+      <c r="G39" s="26">
+        <v>0.5</v>
+      </c>
       <c r="H39" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="K39" s="74"/>
     </row>
@@ -3994,9 +3998,11 @@
       <c r="F47" s="25">
         <v>0.5</v>
       </c>
-      <c r="G47" s="26"/>
+      <c r="G47" s="26">
+        <v>0.5</v>
+      </c>
       <c r="H47" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.4">
@@ -4016,9 +4022,11 @@
       <c r="F48" s="25">
         <v>0.5</v>
       </c>
-      <c r="G48" s="24"/>
+      <c r="G48" s="24">
+        <v>0.5</v>
+      </c>
       <c r="H48" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
@@ -4284,9 +4292,11 @@
       <c r="F59" s="53">
         <v>0.5</v>
       </c>
-      <c r="G59" s="63"/>
+      <c r="G59" s="63">
+        <v>0.5</v>
+      </c>
       <c r="H59" s="44" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.4">

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3FCB35-5FBD-4D16-8529-0CE06BD01FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1C3648-7657-481E-A69A-E75510B25100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -2229,11 +2229,11 @@
       </c>
       <c r="L2" s="53">
         <f>SUMIF(H2:H72,"完了",F2:F72)</f>
-        <v>28.099999999999998</v>
+        <v>29.099999999999998</v>
       </c>
       <c r="M2" s="53">
         <f>K2-L2</f>
-        <v>22.499999999999996</v>
+        <v>21.499999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
@@ -2307,11 +2307,11 @@
       </c>
       <c r="L4" s="53">
         <f>SUMIFS(F2:F72,E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>4.1000000000000005</v>
+        <v>5.1000000000000005</v>
       </c>
       <c r="M4" s="53">
         <f t="shared" si="0"/>
-        <v>7.0000000000000009</v>
+        <v>6.0000000000000009</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
@@ -2596,11 +2596,11 @@
       </c>
       <c r="L11" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"上永",H2:H72,"完了")</f>
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="M11" s="80">
         <f t="shared" ref="M11:M14" si="1">K11 - L11</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N11" s="79"/>
       <c r="O11" s="95" t="s">
@@ -2951,11 +2951,11 @@
       </c>
       <c r="L18" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"上永",E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M18" s="80">
         <f t="shared" ref="M18:M21" si="3">K18 - L18</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="79"/>
       <c r="O18" s="95" t="s">
@@ -3791,9 +3791,11 @@
       <c r="F38" s="25">
         <v>0.5</v>
       </c>
-      <c r="G38" s="26"/>
+      <c r="G38" s="26">
+        <v>0.5</v>
+      </c>
       <c r="H38" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="K38" s="74"/>
     </row>
@@ -3814,9 +3816,11 @@
       <c r="F39" s="25">
         <v>0.5</v>
       </c>
-      <c r="G39" s="26"/>
+      <c r="G39" s="26">
+        <v>0.5</v>
+      </c>
       <c r="H39" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="K39" s="74"/>
     </row>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1C3648-7657-481E-A69A-E75510B25100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B49E324-9EBC-4183-8C30-85EDEBBE0849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="3720" yWindow="2520" windowWidth="21600" windowHeight="11295" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2158,6 +2158,7 @@
     <col min="16" max="16" width="7.75" customWidth="1"/>
     <col min="17" max="17" width="7.5" customWidth="1"/>
     <col min="18" max="18" width="7.625" customWidth="1"/>
+    <col min="19" max="19" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.35">

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hakutokawanami\Desktop\github\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B49E324-9EBC-4183-8C30-85EDEBBE0849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D4A784-CC98-4D8E-8F43-F4A64ADF720A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="2520" windowWidth="21600" windowHeight="11295" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2230,11 +2230,11 @@
       </c>
       <c r="L2" s="53">
         <f>SUMIF(H2:H72,"完了",F2:F72)</f>
-        <v>29.099999999999998</v>
+        <v>29.599999999999998</v>
       </c>
       <c r="M2" s="53">
         <f>K2-L2</f>
-        <v>21.499999999999996</v>
+        <v>20.999999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
@@ -2308,11 +2308,11 @@
       </c>
       <c r="L4" s="53">
         <f>SUMIFS(F2:F72,E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>5.1000000000000005</v>
+        <v>5.6000000000000005</v>
       </c>
       <c r="M4" s="53">
         <f t="shared" si="0"/>
-        <v>6.0000000000000009</v>
+        <v>5.5000000000000009</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
@@ -2653,11 +2653,11 @@
       </c>
       <c r="L12" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"川浪",H2:H72,"完了")</f>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M12" s="80">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N12" s="79"/>
       <c r="O12" s="96" t="s">
@@ -3005,11 +3005,11 @@
       </c>
       <c r="L19" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"川浪",E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M19" s="80">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O19" s="96" t="s">
         <v>73</v>
@@ -4295,9 +4295,11 @@
       <c r="F59" s="53">
         <v>0.5</v>
       </c>
-      <c r="G59" s="63"/>
+      <c r="G59" s="63">
+        <v>0.5</v>
+      </c>
       <c r="H59" s="44" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.4">

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hakutokawanami\Desktop\github\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yongy\git\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D4A784-CC98-4D8E-8F43-F4A64ADF720A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B0CE6B-D533-423C-BA8D-7CF5268B7B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="G16" s="22"/>
       <c r="H16" s="3" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="I16" s="79"/>
       <c r="J16" s="100" t="s">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="G17" s="26"/>
       <c r="H17" s="3" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="I17" s="79"/>
       <c r="J17" s="94" t="s">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="G18" s="24"/>
       <c r="H18" s="3" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="I18" s="79"/>
       <c r="J18" s="95" t="s">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="G19" s="24"/>
       <c r="H19" s="3" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="J19" s="96" t="s">
         <v>73</v>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="G20" s="22"/>
       <c r="H20" s="3" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="J20" s="97" t="s">
         <v>72</v>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="G21" s="26"/>
       <c r="H21" s="3" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="J21" s="98" t="s">
         <v>74</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="G22" s="24"/>
       <c r="H22" s="3" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yongy\git\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B0CE6B-D533-423C-BA8D-7CF5268B7B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83EBADC-D1A8-4462-BFF7-3F0C165246CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -2230,11 +2230,11 @@
       </c>
       <c r="L2" s="53">
         <f>SUMIF(H2:H72,"完了",F2:F72)</f>
-        <v>29.599999999999998</v>
+        <v>32.599999999999994</v>
       </c>
       <c r="M2" s="53">
         <f>K2-L2</f>
-        <v>20.999999999999996</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
@@ -2308,11 +2308,11 @@
       </c>
       <c r="L4" s="53">
         <f>SUMIFS(F2:F72,E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>5.6000000000000005</v>
+        <v>6.6000000000000005</v>
       </c>
       <c r="M4" s="53">
         <f t="shared" si="0"/>
-        <v>5.5000000000000009</v>
+        <v>4.5000000000000009</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
@@ -2347,11 +2347,11 @@
       </c>
       <c r="L5" s="53">
         <f>SUMIFS(F2:F72,E2:E72,"ベータ",H2:H72,"完了")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" s="53">
         <f t="shared" si="0"/>
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.4">
@@ -2388,11 +2388,11 @@
       </c>
       <c r="L6" s="80">
         <f>SUMIFS(F2:F72,E2:E72,"ベータ",H2:H72,"完了")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="53">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.4">
@@ -2767,11 +2767,11 @@
       </c>
       <c r="L14" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"誰でも",H2:H72,"完了")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M14" s="80">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N14" s="79"/>
       <c r="O14" s="98" t="s">
@@ -3111,11 +3111,11 @@
       </c>
       <c r="L21" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"誰でも",E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="80">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O21" s="98" t="s">
         <v>74</v>
@@ -3126,11 +3126,11 @@
       </c>
       <c r="Q21" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"誰でも",E2:E72,"ベータ",H2:H72,"完了")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R21" s="80">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4509,9 +4509,11 @@
       <c r="F68" s="64">
         <v>1</v>
       </c>
-      <c r="G68" s="53"/>
+      <c r="G68" s="53">
+        <v>1</v>
+      </c>
       <c r="H68" s="58" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.4">
@@ -4531,9 +4533,11 @@
       <c r="F69" s="64">
         <v>1</v>
       </c>
-      <c r="G69" s="62"/>
+      <c r="G69" s="62">
+        <v>1</v>
+      </c>
       <c r="H69" s="58" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.4">
@@ -4553,9 +4557,11 @@
       <c r="F70" s="64">
         <v>1</v>
       </c>
-      <c r="G70" s="53"/>
+      <c r="G70" s="53">
+        <v>1</v>
+      </c>
       <c r="H70" s="58" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.4">

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yongy\git\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83EBADC-D1A8-4462-BFF7-3F0C165246CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AFB3CB-91CF-4082-8DC5-ADB2D71E4398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -2230,11 +2230,11 @@
       </c>
       <c r="L2" s="53">
         <f>SUMIF(H2:H72,"完了",F2:F72)</f>
-        <v>32.599999999999994</v>
+        <v>34.599999999999994</v>
       </c>
       <c r="M2" s="53">
         <f>K2-L2</f>
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
@@ -2347,11 +2347,11 @@
       </c>
       <c r="L5" s="53">
         <f>SUMIFS(F2:F72,E2:E72,"ベータ",H2:H72,"完了")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M5" s="53">
         <f t="shared" si="0"/>
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.4">
@@ -2388,11 +2388,11 @@
       </c>
       <c r="L6" s="80">
         <f>SUMIFS(F2:F72,E2:E72,"ベータ",H2:H72,"完了")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M6" s="53">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.4">
@@ -2541,11 +2541,11 @@
       </c>
       <c r="L10" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"大崎",H2:H72,"完了")</f>
-        <v>8.5999999999999979</v>
+        <v>10.599999999999998</v>
       </c>
       <c r="M10" s="80">
         <f>K10 - L10</f>
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="N10" s="79"/>
       <c r="O10" s="94" t="s">
@@ -2914,11 +2914,11 @@
       </c>
       <c r="Q17" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"大崎",E2:E72,"ベータ",H2:H72,"完了")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R17" s="80">
         <f>P17 - Q17</f>
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.35">
@@ -2992,9 +2992,11 @@
       <c r="F19" s="71">
         <v>0.5</v>
       </c>
-      <c r="G19" s="24"/>
+      <c r="G19" s="24">
+        <v>0.2</v>
+      </c>
       <c r="H19" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J19" s="96" t="s">
         <v>73</v>
@@ -3046,9 +3048,11 @@
       <c r="F20" s="71">
         <v>0.5</v>
       </c>
-      <c r="G20" s="22"/>
+      <c r="G20" s="22">
+        <v>0.2</v>
+      </c>
       <c r="H20" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J20" s="97" t="s">
         <v>72</v>
@@ -3098,9 +3102,11 @@
       <c r="F21" s="71">
         <v>0.5</v>
       </c>
-      <c r="G21" s="26"/>
+      <c r="G21" s="26">
+        <v>0.2</v>
+      </c>
       <c r="H21" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J21" s="98" t="s">
         <v>74</v>
@@ -3150,9 +3156,11 @@
       <c r="F22" s="71">
         <v>0.5</v>
       </c>
-      <c r="G22" s="24"/>
+      <c r="G22" s="24">
+        <v>0.2</v>
+      </c>
       <c r="H22" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yongy\git\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OsakiTowa\Desktop\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AFB3CB-91CF-4082-8DC5-ADB2D71E4398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892C050B-4047-407F-92A1-223723045BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="3060" yWindow="-14820" windowWidth="25140" windowHeight="13320" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2230,11 +2230,11 @@
       </c>
       <c r="L2" s="53">
         <f>SUMIF(H2:H72,"完了",F2:F72)</f>
-        <v>34.599999999999994</v>
+        <v>35.599999999999994</v>
       </c>
       <c r="M2" s="53">
         <f>K2-L2</f>
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
@@ -2308,11 +2308,11 @@
       </c>
       <c r="L4" s="53">
         <f>SUMIFS(F2:F72,E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>6.6000000000000005</v>
+        <v>7.6000000000000005</v>
       </c>
       <c r="M4" s="53">
         <f t="shared" si="0"/>
-        <v>4.5000000000000009</v>
+        <v>3.5000000000000009</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
@@ -2767,11 +2767,11 @@
       </c>
       <c r="L14" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"誰でも",H2:H72,"完了")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M14" s="80">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N14" s="79"/>
       <c r="O14" s="98" t="s">
@@ -3117,11 +3117,11 @@
       </c>
       <c r="L21" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"誰でも",E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M21" s="80">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O21" s="98" t="s">
         <v>74</v>
@@ -4611,9 +4611,11 @@
       <c r="F72" s="26">
         <v>1</v>
       </c>
-      <c r="G72" s="73"/>
+      <c r="G72" s="73">
+        <v>1</v>
+      </c>
       <c r="H72" s="58" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OsakiTowa\Desktop\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yongy\git\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892C050B-4047-407F-92A1-223723045BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AFB3CB-91CF-4082-8DC5-ADB2D71E4398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="-14820" windowWidth="25140" windowHeight="13320" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2230,11 +2230,11 @@
       </c>
       <c r="L2" s="53">
         <f>SUMIF(H2:H72,"完了",F2:F72)</f>
-        <v>35.599999999999994</v>
+        <v>34.599999999999994</v>
       </c>
       <c r="M2" s="53">
         <f>K2-L2</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
@@ -2308,11 +2308,11 @@
       </c>
       <c r="L4" s="53">
         <f>SUMIFS(F2:F72,E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>7.6000000000000005</v>
+        <v>6.6000000000000005</v>
       </c>
       <c r="M4" s="53">
         <f t="shared" si="0"/>
-        <v>3.5000000000000009</v>
+        <v>4.5000000000000009</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
@@ -2767,11 +2767,11 @@
       </c>
       <c r="L14" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"誰でも",H2:H72,"完了")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M14" s="80">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N14" s="79"/>
       <c r="O14" s="98" t="s">
@@ -3117,11 +3117,11 @@
       </c>
       <c r="L21" s="80">
         <f>SUMIFS(F2:F72,A2:A72,"誰でも",E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M21" s="80">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O21" s="98" t="s">
         <v>74</v>
@@ -4611,11 +4611,9 @@
       <c r="F72" s="26">
         <v>1</v>
       </c>
-      <c r="G72" s="73">
-        <v>1</v>
-      </c>
+      <c r="G72" s="73"/>
       <c r="H72" s="58" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yongy\git\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AFB3CB-91CF-4082-8DC5-ADB2D71E4398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD6EAE79-CCC1-4D93-939D-66DE9B059411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="106">
   <si>
     <t>概要</t>
     <rPh sb="0" eb="2">
@@ -1809,7 +1809,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2141,7 +2141,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039B1606-320D-4390-8B98-CE6030BB2FAA}">
-  <dimension ref="A1:T72"/>
+  <dimension ref="A1:T71"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="3" width="25.375" bestFit="1" customWidth="1"/>
@@ -2225,16 +2225,16 @@
         <v>85</v>
       </c>
       <c r="K2" s="53">
-        <f>SUM(F2:F72)</f>
-        <v>50.599999999999994</v>
+        <f>SUM(F2:F71)</f>
+        <v>50.099999999999994</v>
       </c>
       <c r="L2" s="53">
-        <f>SUMIF(H2:H72,"完了",F2:F72)</f>
-        <v>34.599999999999994</v>
+        <f>SUMIF(H2:H71,"完了",F2:F71)</f>
+        <v>40.099999999999994</v>
       </c>
       <c r="M2" s="53">
         <f>K2-L2</f>
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
@@ -2264,11 +2264,11 @@
         <v>10</v>
       </c>
       <c r="K3" s="53">
-        <f>SUMIF(E2:E72,"プロト",F2:F72)</f>
+        <f>SUMIF(E2:E71,"プロト",F2:F71)</f>
         <v>24</v>
       </c>
       <c r="L3" s="53">
-        <f>SUMIFS(F2:F72,E2:E72,"プロト",H2:H72,"完了")</f>
+        <f>SUMIFS(F2:F71,E2:E71,"プロト",H2:H71,"完了")</f>
         <v>24</v>
       </c>
       <c r="M3" s="53">
@@ -2303,16 +2303,16 @@
         <v>11</v>
       </c>
       <c r="K4" s="53">
-        <f>SUMIF(E2:E72,"アルファ",F2:F72)</f>
-        <v>11.100000000000001</v>
+        <f>SUMIF(E2:E71,"アルファ",F2:F71)</f>
+        <v>10.600000000000001</v>
       </c>
       <c r="L4" s="53">
-        <f>SUMIFS(F2:F72,E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>6.6000000000000005</v>
+        <f>SUMIFS(F2:F71,E2:E71,"アルファ",H2:H71,"完了")</f>
+        <v>10.100000000000001</v>
       </c>
       <c r="M4" s="53">
         <f t="shared" si="0"/>
-        <v>4.5000000000000009</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
@@ -2342,16 +2342,16 @@
         <v>12</v>
       </c>
       <c r="K5" s="53">
-        <f>SUMIF(E2:E72,"ベータ",F2:F72)</f>
+        <f>SUMIF(E2:E71,"ベータ",F2:F71)</f>
         <v>13.5</v>
       </c>
       <c r="L5" s="53">
-        <f>SUMIFS(F2:F72,E2:E72,"ベータ",H2:H72,"完了")</f>
-        <v>4</v>
+        <f>SUMIFS(F2:F71,E2:E71,"ベータ",H2:H71,"完了")</f>
+        <v>6</v>
       </c>
       <c r="M5" s="53">
         <f t="shared" si="0"/>
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.4">
@@ -2383,16 +2383,16 @@
         <v>86</v>
       </c>
       <c r="K6" s="80">
-        <f>SUMIF(E2:E72,"マスタ",F2:F72)</f>
+        <f>SUMIF(E2:E71,"マスタ",F2:F71)</f>
         <v>2</v>
       </c>
       <c r="L6" s="80">
-        <f>SUMIFS(F2:F72,E2:E72,"ベータ",H2:H72,"完了")</f>
-        <v>4</v>
+        <f>SUMIFS(F2:F71,E2:E71,"ベータ",H2:H71,"完了")</f>
+        <v>6</v>
       </c>
       <c r="M6" s="53">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.4">
@@ -2536,11 +2536,11 @@
         <v>70</v>
       </c>
       <c r="K10" s="80">
-        <f>SUMIF(A2:A72,"大崎",F2:F72)</f>
+        <f>SUMIF(A2:A71,"大崎",F2:F71)</f>
         <v>12.099999999999998</v>
       </c>
       <c r="L10" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"大崎",H2:H72,"完了")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"大崎",H2:H71,"完了")</f>
         <v>10.599999999999998</v>
       </c>
       <c r="M10" s="80">
@@ -2552,11 +2552,11 @@
         <v>70</v>
       </c>
       <c r="P10" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"大崎",E2:E72,"プロト")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"大崎",E2:E71,"プロト")</f>
         <v>5</v>
       </c>
       <c r="Q10" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"大崎",E2:E72,"プロト",H2:H72,"完了")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"大崎",E2:E71,"プロト",H2:H71,"完了")</f>
         <v>5</v>
       </c>
       <c r="R10" s="80">
@@ -2592,11 +2592,11 @@
         <v>71</v>
       </c>
       <c r="K11" s="80">
-        <f>SUMIF(A2:A72,"上永",F2:F72)</f>
+        <f>SUMIF(A2:A71,"上永",F2:F71)</f>
         <v>12.5</v>
       </c>
       <c r="L11" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"上永",H2:H72,"完了")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"上永",H2:H71,"完了")</f>
         <v>9.5</v>
       </c>
       <c r="M11" s="80">
@@ -2608,11 +2608,11 @@
         <v>71</v>
       </c>
       <c r="P11" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"上永",E2:E72,"プロト")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"上永",E2:E71,"プロト")</f>
         <v>8</v>
       </c>
       <c r="Q11" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"上永",E2:E72,"プロト",H2:H72,"完了")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"上永",E2:E71,"プロト",H2:H71,"完了")</f>
         <v>8</v>
       </c>
       <c r="R11" s="80">
@@ -2648,11 +2648,11 @@
         <v>73</v>
       </c>
       <c r="K12" s="80">
-        <f>SUMIF(A2:A72,"川浪",F2:F72)</f>
+        <f>SUMIF(A2:A71,"川浪",F2:F71)</f>
         <v>6.5</v>
       </c>
       <c r="L12" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"川浪",H2:H72,"完了")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"川浪",H2:H71,"完了")</f>
         <v>6.5</v>
       </c>
       <c r="M12" s="80">
@@ -2664,11 +2664,11 @@
         <v>73</v>
       </c>
       <c r="P12" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"川浪",E2:E72,"プロト")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"川浪",E2:E71,"プロト")</f>
         <v>6</v>
       </c>
       <c r="Q12" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"川浪",E2:E72,"プロト",H2:H72,"完了")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"川浪",E2:E71,"プロト",H2:H71,"完了")</f>
         <v>6</v>
       </c>
       <c r="R12" s="80">
@@ -2706,27 +2706,27 @@
         <v>72</v>
       </c>
       <c r="K13" s="80">
-        <f>SUMIF(A2:A72,"佐々木",F2:F72)</f>
-        <v>10.5</v>
+        <f>SUMIF(A2:A71,"佐々木",F2:F71)</f>
+        <v>10</v>
       </c>
       <c r="L13" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"佐々木",H2:H72,"完了")</f>
-        <v>4</v>
+        <f>SUMIFS(F2:F71,A2:A71,"佐々木",H2:H71,"完了")</f>
+        <v>6.5</v>
       </c>
       <c r="M13" s="80">
         <f t="shared" si="1"/>
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="N13" s="79"/>
       <c r="O13" s="97" t="s">
         <v>72</v>
       </c>
       <c r="P13" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"佐々木",E2:E72,"プロト")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"佐々木",E2:E71,"プロト")</f>
         <v>4</v>
       </c>
       <c r="Q13" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"佐々木",E2:E72,"プロト",H2:H72,"完了")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"佐々木",E2:E71,"プロト",H2:H71,"完了")</f>
         <v>4</v>
       </c>
       <c r="R13" s="80">
@@ -2762,27 +2762,27 @@
         <v>74</v>
       </c>
       <c r="K14" s="80">
-        <f>SUMIF(A2:A72,"誰でも",F2:F72)</f>
+        <f>SUMIF(A2:A71,"誰でも",F2:F71)</f>
         <v>8</v>
       </c>
       <c r="L14" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"誰でも",H2:H72,"完了")</f>
-        <v>4</v>
+        <f>SUMIFS(F2:F71,A2:A71,"誰でも",H2:H71,"完了")</f>
+        <v>7</v>
       </c>
       <c r="M14" s="80">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N14" s="79"/>
       <c r="O14" s="98" t="s">
         <v>74</v>
       </c>
       <c r="P14" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"誰でも",E2:E72,"プロト")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"誰でも",E2:E71,"プロト")</f>
         <v>1</v>
       </c>
       <c r="Q14" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"誰でも",E2:E72,"プロト",H2:H72,"完了")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"誰でも",E2:E71,"プロト",H2:H71,"完了")</f>
         <v>1</v>
       </c>
       <c r="R14" s="80">
@@ -2893,11 +2893,11 @@
         <v>70</v>
       </c>
       <c r="K17" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"大崎",E2:E72,"アルファ")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"大崎",E2:E71,"アルファ")</f>
         <v>3.6000000000000005</v>
       </c>
       <c r="L17" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"大崎",E2:E72,"アルファ",H2:H72,"完了")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"大崎",E2:E71,"アルファ",H2:H71,"完了")</f>
         <v>3.6000000000000005</v>
       </c>
       <c r="M17" s="80">
@@ -2909,11 +2909,11 @@
         <v>70</v>
       </c>
       <c r="P17" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"大崎",E2:E72,"ベータ")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"大崎",E2:E71,"ベータ")</f>
         <v>3.5</v>
       </c>
       <c r="Q17" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"大崎",E2:E72,"ベータ",H2:H72,"完了")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"大崎",E2:E71,"ベータ",H2:H71,"完了")</f>
         <v>2</v>
       </c>
       <c r="R17" s="80">
@@ -2947,11 +2947,11 @@
         <v>71</v>
       </c>
       <c r="K18" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"上永",E2:E72,"アルファ")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"上永",E2:E71,"アルファ")</f>
         <v>1.5</v>
       </c>
       <c r="L18" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"上永",E2:E72,"アルファ",H2:H72,"完了")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"上永",E2:E71,"アルファ",H2:H71,"完了")</f>
         <v>1.5</v>
       </c>
       <c r="M18" s="80">
@@ -2963,11 +2963,11 @@
         <v>71</v>
       </c>
       <c r="P18" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"上永",E2:E72,"ベータ")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"上永",E2:E71,"ベータ")</f>
         <v>3</v>
       </c>
       <c r="Q18" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"上永",E2:E72,"ベータ",H2:H72,"完了")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"上永",E2:E71,"ベータ",H2:H71,"完了")</f>
         <v>0</v>
       </c>
       <c r="R18" s="80">
@@ -3002,11 +3002,11 @@
         <v>73</v>
       </c>
       <c r="K19" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"川浪",E2:E72,"アルファ")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"川浪",E2:E71,"アルファ")</f>
         <v>0.5</v>
       </c>
       <c r="L19" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"川浪",E2:E72,"アルファ",H2:H72,"完了")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"川浪",E2:E71,"アルファ",H2:H71,"完了")</f>
         <v>0.5</v>
       </c>
       <c r="M19" s="80">
@@ -3017,11 +3017,11 @@
         <v>73</v>
       </c>
       <c r="P19" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"川浪",E2:E72,"ベータ")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"川浪",E2:E71,"ベータ")</f>
         <v>0</v>
       </c>
       <c r="Q19" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"川浪",E2:E72,"ベータ",H2:H72,"完了")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"川浪",E2:E71,"ベータ",H2:H71,"完了")</f>
         <v>0</v>
       </c>
       <c r="R19" s="80">
@@ -3058,31 +3058,31 @@
         <v>72</v>
       </c>
       <c r="K20" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"佐々木",E2:E72,"アルファ")</f>
-        <v>2.5</v>
+        <f>SUMIFS(F2:F71,A2:A71,"佐々木",E2:E71,"アルファ")</f>
+        <v>2</v>
       </c>
       <c r="L20" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"佐々木",E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>0</v>
+        <f>SUMIFS(F2:F71,A2:A71,"佐々木",E2:E71,"アルファ",H2:H71,"完了")</f>
+        <v>1.5</v>
       </c>
       <c r="M20" s="80">
         <f>K20 - L20</f>
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="O20" s="97" t="s">
         <v>72</v>
       </c>
       <c r="P20" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"佐々木",E2:E72,"ベータ")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"佐々木",E2:E71,"ベータ")</f>
         <v>2</v>
       </c>
       <c r="Q20" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"佐々木",E2:E72,"ベータ",H2:H72,"完了")</f>
-        <v>0</v>
+        <f>SUMIFS(F2:F71,A2:A71,"佐々木",E2:E71,"ベータ",H2:H71,"完了")</f>
+        <v>1</v>
       </c>
       <c r="R20" s="80">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.4">
@@ -3112,31 +3112,31 @@
         <v>74</v>
       </c>
       <c r="K21" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"誰でも",E2:E72,"アルファ")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"誰でも",E2:E71,"アルファ")</f>
         <v>3</v>
       </c>
       <c r="L21" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"誰でも",E2:E72,"アルファ",H2:H72,"完了")</f>
-        <v>1</v>
+        <f>SUMIFS(F2:F71,A2:A71,"誰でも",E2:E71,"アルファ",H2:H71,"完了")</f>
+        <v>3</v>
       </c>
       <c r="M21" s="80">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O21" s="98" t="s">
         <v>74</v>
       </c>
       <c r="P21" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"誰でも",E2:E72,"ベータ")</f>
+        <f>SUMIFS(F2:F71,A2:A71,"誰でも",E2:E71,"ベータ")</f>
         <v>4</v>
       </c>
       <c r="Q21" s="80">
-        <f>SUMIFS(F2:F72,A2:A72,"誰でも",E2:E72,"ベータ",H2:H72,"完了")</f>
-        <v>2</v>
+        <f>SUMIFS(F2:F71,A2:A71,"誰でも",E2:E71,"ベータ",H2:H71,"完了")</f>
+        <v>3</v>
       </c>
       <c r="R21" s="80">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3877,9 +3877,11 @@
       <c r="F41" s="15">
         <v>1</v>
       </c>
-      <c r="G41" s="22"/>
+      <c r="G41" s="22">
+        <v>0.5</v>
+      </c>
       <c r="H41" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="K41" s="74"/>
     </row>
@@ -3923,9 +3925,11 @@
       <c r="F43" s="25">
         <v>0.5</v>
       </c>
-      <c r="G43" s="23"/>
+      <c r="G43" s="23">
+        <v>0.5</v>
+      </c>
       <c r="H43" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.4">
@@ -3954,9 +3958,9 @@
       <c r="A45" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="B45" s="17"/>
-      <c r="C45" s="21" t="s">
-        <v>53</v>
+      <c r="B45" s="18"/>
+      <c r="C45" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>14</v>
@@ -3967,21 +3971,23 @@
       <c r="F45" s="25">
         <v>0.5</v>
       </c>
-      <c r="G45" s="23"/>
+      <c r="G45" s="26"/>
       <c r="H45" s="3" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A46" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="B46" s="18"/>
-      <c r="C46" s="13" t="s">
-        <v>26</v>
+      <c r="B46" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>28</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>9</v>
@@ -3989,20 +3995,20 @@
       <c r="F46" s="25">
         <v>0.5</v>
       </c>
-      <c r="G46" s="26"/>
+      <c r="G46" s="26">
+        <v>0.5</v>
+      </c>
       <c r="H46" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A47" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="B47" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C47" s="20" t="s">
-        <v>28</v>
+      <c r="B47" s="18"/>
+      <c r="C47" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>7</v>
@@ -4013,42 +4019,48 @@
       <c r="F47" s="25">
         <v>0.5</v>
       </c>
-      <c r="G47" s="26"/>
+      <c r="G47" s="24">
+        <v>0.5</v>
+      </c>
       <c r="H47" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A48" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="B48" s="18"/>
-      <c r="C48" s="13" t="s">
-        <v>29</v>
+      <c r="B48" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" s="27" t="s">
+        <v>56</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" s="25">
-        <v>0.5</v>
-      </c>
-      <c r="G48" s="24"/>
+        <v>8</v>
+      </c>
+      <c r="F48" s="28">
+        <v>1</v>
+      </c>
+      <c r="G48" s="26">
+        <v>0.5</v>
+      </c>
       <c r="H48" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A49" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="B49" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C49" s="27" t="s">
-        <v>56</v>
+      <c r="B49" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="32" t="s">
+        <v>59</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>14</v>
@@ -4056,11 +4068,11 @@
       <c r="E49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="28">
-        <v>1</v>
-      </c>
-      <c r="G49" s="26">
-        <v>0.5</v>
+      <c r="F49" s="33">
+        <v>3</v>
+      </c>
+      <c r="G49" s="34">
+        <v>3</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>75</v>
@@ -4070,42 +4082,38 @@
       <c r="A50" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="B50" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="C50" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="D50" s="3" t="s">
+      <c r="B50" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D50" s="35" t="s">
         <v>14</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" s="33">
-        <v>3</v>
-      </c>
-      <c r="G50" s="34">
-        <v>3</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="F50" s="40">
+        <v>1</v>
+      </c>
+      <c r="G50" s="30"/>
       <c r="H50" s="3" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A51" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="B51" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="C51" s="37" t="s">
-        <v>61</v>
+      <c r="B51" s="42"/>
+      <c r="C51" s="38" t="s">
+        <v>62</v>
       </c>
       <c r="D51" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" s="41" t="s">
         <v>63</v>
       </c>
       <c r="F51" s="40">
@@ -4117,36 +4125,38 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A52" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="B52" s="42"/>
-      <c r="C52" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="D52" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="E52" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="F52" s="40">
-        <v>1</v>
-      </c>
-      <c r="G52" s="30"/>
-      <c r="H52" s="3" t="s">
-        <v>57</v>
+      <c r="A52" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="B52" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C52" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="D52" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="G52" s="46">
+        <v>0.5</v>
+      </c>
+      <c r="H52" s="44" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A53" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="B53" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C53" s="49" t="s">
-        <v>64</v>
+      <c r="B53" s="47"/>
+      <c r="C53" s="50" t="s">
+        <v>65</v>
       </c>
       <c r="D53" s="43" t="s">
         <v>14</v>
@@ -4154,11 +4164,11 @@
       <c r="E53" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="F53" s="45">
-        <v>0.5</v>
-      </c>
-      <c r="G53" s="46">
-        <v>0.5</v>
+      <c r="F53" s="52">
+        <v>1</v>
+      </c>
+      <c r="G53" s="53">
+        <v>1</v>
       </c>
       <c r="H53" s="44" t="s">
         <v>75</v>
@@ -4170,7 +4180,7 @@
       </c>
       <c r="B54" s="47"/>
       <c r="C54" s="50" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="D54" s="43" t="s">
         <v>14</v>
@@ -4178,10 +4188,10 @@
       <c r="E54" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="52">
-        <v>1</v>
-      </c>
-      <c r="G54" s="53">
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54" s="23">
         <v>1</v>
       </c>
       <c r="H54" s="44" t="s">
@@ -4192,21 +4202,23 @@
       <c r="A55" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="B55" s="47"/>
-      <c r="C55" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D55" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="E55" s="44" t="s">
+      <c r="B55" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="C55" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D55" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
-      <c r="G55" s="23">
-        <v>1</v>
+      <c r="F55" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="G55" s="63">
+        <v>0.5</v>
       </c>
       <c r="H55" s="44" t="s">
         <v>75</v>
@@ -4216,19 +4228,17 @@
       <c r="A56" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="B56" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="C56" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="D56" s="54" t="s">
-        <v>14</v>
-      </c>
-      <c r="E56" s="55" t="s">
+      <c r="B56" s="47"/>
+      <c r="C56" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="D56" s="58" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="F56" s="45">
+      <c r="F56" s="53">
         <v>0.5</v>
       </c>
       <c r="G56" s="63">
@@ -4244,12 +4254,12 @@
       </c>
       <c r="B57" s="47"/>
       <c r="C57" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="D57" s="58" t="s">
-        <v>14</v>
-      </c>
-      <c r="E57" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="D57" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="61" t="s">
         <v>8</v>
       </c>
       <c r="F57" s="53">
@@ -4268,13 +4278,13 @@
       </c>
       <c r="B58" s="47"/>
       <c r="C58" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="D58" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="E58" s="61" t="s">
-        <v>8</v>
+        <v>47</v>
+      </c>
+      <c r="D58" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="59" t="s">
+        <v>9</v>
       </c>
       <c r="F58" s="53">
         <v>0.5</v>
@@ -4292,15 +4302,15 @@
       </c>
       <c r="B59" s="47"/>
       <c r="C59" s="50" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D59" s="43" t="s">
         <v>14</v>
       </c>
       <c r="E59" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" s="53">
+        <v>8</v>
+      </c>
+      <c r="F59" s="62">
         <v>0.5</v>
       </c>
       <c r="G59" s="63">
@@ -4316,7 +4326,7 @@
       </c>
       <c r="B60" s="47"/>
       <c r="C60" s="50" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D60" s="43" t="s">
         <v>14</v>
@@ -4324,7 +4334,7 @@
       <c r="E60" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="F60" s="62">
+      <c r="F60" s="53">
         <v>0.5</v>
       </c>
       <c r="G60" s="63">
@@ -4340,7 +4350,7 @@
       </c>
       <c r="B61" s="47"/>
       <c r="C61" s="50" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="D61" s="43" t="s">
         <v>14</v>
@@ -4362,14 +4372,14 @@
       <c r="A62" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="B62" s="47"/>
-      <c r="C62" s="50" t="s">
-        <v>68</v>
-      </c>
-      <c r="D62" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="E62" s="59" t="s">
+      <c r="B62" s="48"/>
+      <c r="C62" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="D62" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" s="60" t="s">
         <v>8</v>
       </c>
       <c r="F62" s="53">
@@ -4378,78 +4388,78 @@
       <c r="G62" s="63">
         <v>0.5</v>
       </c>
-      <c r="H62" s="44" t="s">
+      <c r="H62" s="58" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A63" s="68" t="s">
-        <v>73</v>
-      </c>
-      <c r="B63" s="48"/>
-      <c r="C63" s="51" t="s">
-        <v>37</v>
+      <c r="A63" s="133" t="s">
+        <v>103</v>
+      </c>
+      <c r="B63" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="C63" s="50" t="s">
+        <v>105</v>
       </c>
       <c r="D63" s="56" t="s">
         <v>14</v>
       </c>
       <c r="E63" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="F63" s="64">
+        <v>1</v>
+      </c>
+      <c r="G63" s="134"/>
+      <c r="H63" s="58" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A64" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="B64" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="C64" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="D64" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="F63" s="53">
-        <v>0.5</v>
-      </c>
-      <c r="G63" s="63">
-        <v>0.5</v>
-      </c>
-      <c r="H63" s="58" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A64" s="133" t="s">
-        <v>103</v>
-      </c>
-      <c r="B64" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="C64" s="50" t="s">
-        <v>105</v>
-      </c>
-      <c r="D64" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="E64" s="60" t="s">
-        <v>36</v>
-      </c>
       <c r="F64" s="64">
         <v>1</v>
       </c>
-      <c r="G64" s="134"/>
+      <c r="G64" s="64">
+        <v>1</v>
+      </c>
       <c r="H64" s="58" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A65" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="B65" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="C65" s="49" t="s">
-        <v>26</v>
+      <c r="B65" s="47"/>
+      <c r="C65" s="50" t="s">
+        <v>53</v>
       </c>
       <c r="D65" s="56" t="s">
         <v>14</v>
       </c>
       <c r="E65" s="60" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F65" s="64">
         <v>1</v>
       </c>
-      <c r="G65" s="64">
+      <c r="G65" s="53">
         <v>1</v>
       </c>
       <c r="H65" s="58" t="s">
@@ -4462,18 +4472,18 @@
       </c>
       <c r="B66" s="47"/>
       <c r="C66" s="50" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D66" s="56" t="s">
         <v>14</v>
       </c>
       <c r="E66" s="60" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F66" s="64">
         <v>1</v>
       </c>
-      <c r="G66" s="53"/>
+      <c r="G66" s="62"/>
       <c r="H66" s="58" t="s">
         <v>76</v>
       </c>
@@ -4484,7 +4494,7 @@
       </c>
       <c r="B67" s="47"/>
       <c r="C67" s="50" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D67" s="56" t="s">
         <v>14</v>
@@ -4495,9 +4505,11 @@
       <c r="F67" s="64">
         <v>1</v>
       </c>
-      <c r="G67" s="62"/>
+      <c r="G67" s="53">
+        <v>1</v>
+      </c>
       <c r="H67" s="58" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.4">
@@ -4506,7 +4518,7 @@
       </c>
       <c r="B68" s="47"/>
       <c r="C68" s="50" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D68" s="56" t="s">
         <v>14</v>
@@ -4517,7 +4529,7 @@
       <c r="F68" s="64">
         <v>1</v>
       </c>
-      <c r="G68" s="53">
+      <c r="G68" s="62">
         <v>1</v>
       </c>
       <c r="H68" s="58" t="s">
@@ -4530,18 +4542,18 @@
       </c>
       <c r="B69" s="47"/>
       <c r="C69" s="50" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D69" s="56" t="s">
         <v>14</v>
       </c>
       <c r="E69" s="60" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F69" s="64">
         <v>1</v>
       </c>
-      <c r="G69" s="62">
+      <c r="G69" s="53">
         <v>1</v>
       </c>
       <c r="H69" s="58" t="s">
@@ -4554,13 +4566,13 @@
       </c>
       <c r="B70" s="47"/>
       <c r="C70" s="50" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="D70" s="56" t="s">
         <v>14</v>
       </c>
       <c r="E70" s="60" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F70" s="64">
         <v>1</v>
@@ -4576,56 +4588,36 @@
       <c r="A71" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="B71" s="47"/>
-      <c r="C71" s="50" t="s">
-        <v>52</v>
+      <c r="B71" s="48"/>
+      <c r="C71" s="51" t="s">
+        <v>67</v>
       </c>
       <c r="D71" s="56" t="s">
         <v>14</v>
       </c>
       <c r="E71" s="60" t="s">
-        <v>36</v>
-      </c>
-      <c r="F71" s="64">
-        <v>1</v>
-      </c>
-      <c r="G71" s="53"/>
+        <v>9</v>
+      </c>
+      <c r="F71" s="26">
+        <v>1</v>
+      </c>
+      <c r="G71" s="73">
+        <v>1</v>
+      </c>
       <c r="H71" s="58" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A72" s="69" t="s">
-        <v>74</v>
-      </c>
-      <c r="B72" s="48"/>
-      <c r="C72" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="D72" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="E72" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" s="26">
-        <v>1</v>
-      </c>
-      <c r="G72" s="73"/>
-      <c r="H72" s="58" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H72" xr:uid="{6668A6B0-AE49-40A9-BDCA-1EF7E08764AB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H71" xr:uid="{6668A6B0-AE49-40A9-BDCA-1EF7E08764AB}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E72" xr:uid="{3F25CF45-EEFF-4838-8184-2DB508A95967}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E71" xr:uid="{3F25CF45-EEFF-4838-8184-2DB508A95967}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D72" xr:uid="{D99FF9D9-52C2-47CC-BC93-4ACF23B2DA2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D71" xr:uid="{D99FF9D9-52C2-47CC-BC93-4ACF23B2DA2A}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
   </dataValidations>

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kawanamihakuto\Desktop\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD6EAE79-CCC1-4D93-939D-66DE9B059411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8E9663-13D4-4B1C-AEAC-019B284CF20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -1809,7 +1809,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2387,12 +2387,12 @@
         <v>2</v>
       </c>
       <c r="L6" s="80">
-        <f>SUMIFS(F2:F71,E2:E71,"ベータ",H2:H71,"完了")</f>
-        <v>6</v>
+        <f>SUMIFS(F2:F71,E2:E71,"マスタ",H2:H71,"完了")</f>
+        <v>0</v>
       </c>
       <c r="M6" s="53">
         <f t="shared" si="0"/>
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.4">

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kawanamihakuto\Desktop\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OsakiTowa\Desktop\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8E9663-13D4-4B1C-AEAC-019B284CF20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63025CE8-9061-418B-95F8-4958342457EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="3060" yWindow="-14820" windowWidth="25140" windowHeight="13320" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2230,11 +2230,11 @@
       </c>
       <c r="L2" s="53">
         <f>SUMIF(H2:H71,"完了",F2:F71)</f>
-        <v>40.099999999999994</v>
+        <v>40.599999999999994</v>
       </c>
       <c r="M2" s="53">
         <f>K2-L2</f>
-        <v>10</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
@@ -2347,11 +2347,11 @@
       </c>
       <c r="L5" s="53">
         <f>SUMIFS(F2:F71,E2:E71,"ベータ",H2:H71,"完了")</f>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M5" s="53">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.4">
@@ -2541,11 +2541,11 @@
       </c>
       <c r="L10" s="80">
         <f>SUMIFS(F2:F71,A2:A71,"大崎",H2:H71,"完了")</f>
-        <v>10.599999999999998</v>
+        <v>11.099999999999998</v>
       </c>
       <c r="M10" s="80">
         <f>K10 - L10</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N10" s="79"/>
       <c r="O10" s="94" t="s">
@@ -2884,9 +2884,11 @@
       <c r="F17" s="71">
         <v>0.5</v>
       </c>
-      <c r="G17" s="26"/>
+      <c r="G17" s="26">
+        <v>0.5</v>
+      </c>
       <c r="H17" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I17" s="79"/>
       <c r="J17" s="94" t="s">
@@ -2914,11 +2916,11 @@
       </c>
       <c r="Q17" s="80">
         <f>SUMIFS(F2:F71,A2:A71,"大崎",E2:E71,"ベータ",H2:H71,"完了")</f>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="R17" s="80">
         <f>P17 - Q17</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.35">

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OsakiTowa\Desktop\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63025CE8-9061-418B-95F8-4958342457EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBC51AA-E1AF-44EA-96BE-2FE605AEA4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="-14820" windowWidth="25140" windowHeight="13320" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2230,11 +2230,11 @@
       </c>
       <c r="L2" s="53">
         <f>SUMIF(H2:H71,"完了",F2:F71)</f>
-        <v>40.599999999999994</v>
+        <v>44.599999999999994</v>
       </c>
       <c r="M2" s="53">
         <f>K2-L2</f>
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
@@ -2347,11 +2347,11 @@
       </c>
       <c r="L5" s="53">
         <f>SUMIFS(F2:F71,E2:E71,"ベータ",H2:H71,"完了")</f>
-        <v>6.5</v>
+        <v>10.5</v>
       </c>
       <c r="M5" s="53">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.4">
@@ -2597,11 +2597,11 @@
       </c>
       <c r="L11" s="80">
         <f>SUMIFS(F2:F71,A2:A71,"上永",H2:H71,"完了")</f>
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="M11" s="80">
         <f t="shared" ref="M11:M14" si="1">K11 - L11</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N11" s="79"/>
       <c r="O11" s="95" t="s">
@@ -2767,11 +2767,11 @@
       </c>
       <c r="L14" s="80">
         <f>SUMIFS(F2:F71,A2:A71,"誰でも",H2:H71,"完了")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M14" s="80">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" s="79"/>
       <c r="O14" s="98" t="s">
@@ -2970,11 +2970,11 @@
       </c>
       <c r="Q18" s="80">
         <f>SUMIFS(F2:F71,A2:A71,"上永",E2:E71,"ベータ",H2:H71,"完了")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R18" s="80">
         <f t="shared" ref="R18:R21" si="4">P18 - Q18</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.35">
@@ -3134,11 +3134,11 @@
       </c>
       <c r="Q21" s="80">
         <f>SUMIFS(F2:F71,A2:A71,"誰でも",E2:E71,"ベータ",H2:H71,"完了")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R21" s="80">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3420,9 +3420,11 @@
       <c r="F28" s="23">
         <v>1</v>
       </c>
-      <c r="G28" s="29"/>
+      <c r="G28" s="29">
+        <v>0.5</v>
+      </c>
       <c r="H28" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="J28" s="113">
         <v>22</v>
@@ -3633,9 +3635,11 @@
       <c r="F33" s="22">
         <v>0.5</v>
       </c>
-      <c r="G33" s="22"/>
+      <c r="G33" s="22">
+        <v>0.5</v>
+      </c>
       <c r="H33" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="J33" s="123">
         <v>15</v>
@@ -3676,9 +3680,11 @@
       <c r="F34" s="26">
         <v>0.5</v>
       </c>
-      <c r="G34" s="26"/>
+      <c r="G34" s="26">
+        <v>1</v>
+      </c>
       <c r="H34" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="J34" s="107">
         <v>22</v>
@@ -3719,9 +3725,11 @@
       <c r="F35" s="26">
         <v>0.5</v>
       </c>
-      <c r="G35" s="26"/>
+      <c r="G35" s="26">
+        <v>1</v>
+      </c>
       <c r="H35" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="J35" s="126">
         <v>29</v>
@@ -3754,9 +3762,11 @@
       <c r="F36" s="24">
         <v>0.5</v>
       </c>
-      <c r="G36" s="24"/>
+      <c r="G36" s="26">
+        <v>1</v>
+      </c>
       <c r="H36" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.4">
@@ -4485,9 +4495,11 @@
       <c r="F66" s="64">
         <v>1</v>
       </c>
-      <c r="G66" s="62"/>
+      <c r="G66" s="62">
+        <v>1</v>
+      </c>
       <c r="H66" s="58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.4">

--- a/コスト表（改）.xlsx
+++ b/コスト表（改）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Fall3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OsakiTowa\Desktop\Fall3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBC51AA-E1AF-44EA-96BE-2FE605AEA4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59DCFB3-3432-4630-AC3F-5445BC87E956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="3060" yWindow="-14820" windowWidth="25140" windowHeight="13320" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2230,11 +2230,11 @@
       </c>
       <c r="L2" s="53">
         <f>SUMIF(H2:H71,"完了",F2:F71)</f>
-        <v>44.599999999999994</v>
+        <v>46.599999999999994</v>
       </c>
       <c r="M2" s="53">
         <f>K2-L2</f>
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
@@ -2347,11 +2347,11 @@
       </c>
       <c r="L5" s="53">
         <f>SUMIFS(F2:F71,E2:E71,"ベータ",H2:H71,"完了")</f>
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="M5" s="53">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.4">
@@ -2541,11 +2541,11 @@
       </c>
       <c r="L10" s="80">
         <f>SUMIFS(F2:F71,A2:A71,"大崎",H2:H71,"完了")</f>
-        <v>11.099999999999998</v>
+        <v>12.099999999999998</v>
       </c>
       <c r="M10" s="80">
         <f>K10 - L10</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" s="79"/>
       <c r="O10" s="94" t="s">
@@ -2836,9 +2836,11 @@
       <c r="F16" s="71">
         <v>0.5</v>
       </c>
-      <c r="G16" s="22"/>
+      <c r="G16" s="22">
+        <v>0.5</v>
+      </c>
       <c r="H16" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I16" s="79"/>
       <c r="J16" s="100" t="s">
@@ -2916,11 +2918,11 @@
       </c>
       <c r="Q17" s="80">
         <f>SUMIFS(F2:F71,A2:A71,"大崎",E2:E71,"ベータ",H2:H71,"完了")</f>
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="R17" s="80">
         <f>P17 - Q17</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.35">
@@ -2940,9 +2942,11 @@
       <c r="F18" s="71">
         <v>0.5</v>
       </c>
-      <c r="G18" s="24"/>
+      <c r="G18" s="24">
+        <v>0.5</v>
+      </c>
       <c r="H18" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I18" s="79"/>
       <c r="J18" s="95" t="s">
@@ -4423,9 +4427,11 @@
       <c r="F63" s="64">
         <v>1</v>
       </c>
-      <c r="G63" s="134"/>
+      <c r="G63" s="134">
+        <v>3</v>
+      </c>
       <c r="H63" s="58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.4">
